--- a/Data/CombatInputPanel.xlsx
+++ b/Data/CombatInputPanel.xlsx
@@ -1,12 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\CombatCalculatorTest\Data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21B9DB26-E924-41B0-AB2D-9DFB20F6268B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="CombatInputPanel" sheetId="1" r:id="rId4"/>
+    <sheet name="CombatInputPanel" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="0"/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="cz4Y9RvWg6YKSpJqLCKmKNCfw14TqYuz+1jw1+BbLgo="/>
@@ -16,47 +25,95 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author/>
   </authors>
   <commentList>
-    <comment authorId="0" ref="E1">
+    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
-        <t xml:space="preserve">從0開始
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>從0開始
 ======</t>
+        </r>
       </text>
     </comment>
-    <comment authorId="0" ref="F1">
+    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
       <text>
-        <t xml:space="preserve">角色搭配的夥伴是否符合角色職業
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>角色搭配的夥伴是否符合角色職業
 有的話才會應用額外的能力加成
 ======</t>
+        </r>
       </text>
     </comment>
-    <comment authorId="0" ref="G1">
+    <comment ref="G1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
       <text>
-        <t xml:space="preserve">從1開始
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>從1開始
 ======</t>
+        </r>
       </text>
     </comment>
-    <comment authorId="0" ref="H1">
+    <comment ref="H1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
       <text>
-        <t xml:space="preserve">最多裝6個
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>最多裝6個
 0~5
 ======</t>
+        </r>
       </text>
     </comment>
-    <comment authorId="0" ref="I1">
+    <comment ref="I1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
       <text>
-        <t xml:space="preserve">0~5
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>0~5
 ======</t>
+        </r>
       </text>
     </comment>
-    <comment authorId="0" ref="L1">
+    <comment ref="L1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000006000000}">
       <text>
-        <t xml:space="preserve">最多裝3個
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>最多裝3個
 ======</t>
+        </r>
       </text>
     </comment>
   </commentList>
@@ -156,31 +213,40 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="5">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Arial"/>
+      <family val="3"/>
+      <charset val="136"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -189,7 +255,7 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -211,7 +277,13 @@
     </fill>
   </fills>
   <borders count="2">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left style="thin">
         <color rgb="FFBFBFBF"/>
@@ -225,51 +297,45 @@
       <bottom style="thin">
         <color rgb="FFBFBFBF"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="13">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
-    <xf borderId="1" fillId="3" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
-    <xf borderId="1" fillId="4" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
-    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="一般" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -459,34 +525,36 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
-    <pageSetUpPr/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
+  <dimension ref="A1:AC1010"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col customWidth="1" min="1" max="3" width="9.63"/>
-    <col customWidth="1" min="4" max="4" width="11.5"/>
-    <col customWidth="1" min="5" max="5" width="20.63"/>
-    <col customWidth="1" min="6" max="6" width="22.88"/>
-    <col customWidth="1" min="7" max="7" width="12.75"/>
-    <col customWidth="1" min="8" max="8" width="22.38"/>
-    <col customWidth="1" min="9" max="9" width="20.25"/>
-    <col customWidth="1" min="10" max="10" width="27.25"/>
-    <col customWidth="1" min="11" max="11" width="28.63"/>
-    <col customWidth="1" min="12" max="12" width="20.75"/>
-    <col customWidth="1" min="13" max="13" width="9.63"/>
-    <col customWidth="1" min="14" max="14" width="10.0"/>
-    <col customWidth="1" min="15" max="16" width="11.5"/>
-    <col customWidth="1" min="17" max="29" width="9.63"/>
+    <col min="1" max="3" width="9.5703125" customWidth="1"/>
+    <col min="4" max="4" width="11.42578125" customWidth="1"/>
+    <col min="5" max="5" width="20.5703125" customWidth="1"/>
+    <col min="6" max="6" width="22.85546875" customWidth="1"/>
+    <col min="7" max="7" width="12.7109375" customWidth="1"/>
+    <col min="8" max="8" width="22.42578125" customWidth="1"/>
+    <col min="9" max="9" width="20.28515625" customWidth="1"/>
+    <col min="10" max="10" width="27.28515625" customWidth="1"/>
+    <col min="11" max="11" width="28.5703125" customWidth="1"/>
+    <col min="12" max="12" width="20.7109375" customWidth="1"/>
+    <col min="13" max="13" width="9.5703125" customWidth="1"/>
+    <col min="14" max="14" width="10" customWidth="1"/>
+    <col min="15" max="16" width="11.42578125" customWidth="1"/>
+    <col min="17" max="29" width="9.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" customHeight="1">
+    <row r="1" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -551,39 +619,39 @@
       <c r="AB1" s="4"/>
       <c r="AC1" s="4"/>
     </row>
-    <row r="2" ht="15.75" customHeight="1">
+    <row r="2" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
         <v>17</v>
       </c>
       <c r="B2" s="5">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="C2" s="6" t="s">
         <v>18</v>
       </c>
       <c r="D2" s="5">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="E2" s="5">
-        <v>0.0</v>
+        <v>4</v>
       </c>
       <c r="F2" s="6" t="b">
         <v>0</v>
       </c>
       <c r="G2" s="5">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="H2" s="7" t="s">
         <v>19</v>
       </c>
       <c r="I2" s="5">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="J2" s="7" t="s">
         <v>20</v>
       </c>
       <c r="K2" s="8">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="L2" s="9" t="s">
         <v>21</v>
@@ -606,7 +674,7 @@
       <c r="AB2" s="4"/>
       <c r="AC2" s="4"/>
     </row>
-    <row r="3" ht="15.75" customHeight="1">
+    <row r="3" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="5"/>
       <c r="B3" s="5"/>
       <c r="C3" s="6"/>
@@ -620,7 +688,7 @@
         <v>20</v>
       </c>
       <c r="K3" s="8">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="L3" s="10" t="s">
         <v>22</v>
@@ -643,7 +711,7 @@
       <c r="AB3" s="4"/>
       <c r="AC3" s="4"/>
     </row>
-    <row r="4" ht="15.75" customHeight="1">
+    <row r="4" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="5"/>
       <c r="B4" s="5"/>
       <c r="C4" s="6"/>
@@ -657,7 +725,7 @@
         <v>20</v>
       </c>
       <c r="K4" s="8">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="L4" s="10" t="s">
         <v>22</v>
@@ -680,7 +748,7 @@
       <c r="AB4" s="4"/>
       <c r="AC4" s="4"/>
     </row>
-    <row r="5" ht="15.75" customHeight="1">
+    <row r="5" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="5"/>
       <c r="B5" s="5"/>
       <c r="C5" s="6"/>
@@ -692,13 +760,13 @@
         <v>23</v>
       </c>
       <c r="I5" s="8">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="J5" s="7" t="s">
         <v>20</v>
       </c>
       <c r="K5" s="8">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="L5" s="11"/>
       <c r="M5" s="5"/>
@@ -719,7 +787,7 @@
       <c r="AB5" s="4"/>
       <c r="AC5" s="4"/>
     </row>
-    <row r="6" ht="15.75" customHeight="1">
+    <row r="6" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="5"/>
       <c r="B6" s="5"/>
       <c r="C6" s="6"/>
@@ -733,7 +801,7 @@
         <v>24</v>
       </c>
       <c r="K6" s="8">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="L6" s="11"/>
       <c r="M6" s="5"/>
@@ -754,7 +822,7 @@
       <c r="AB6" s="4"/>
       <c r="AC6" s="4"/>
     </row>
-    <row r="7" ht="15.75" customHeight="1">
+    <row r="7" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="5"/>
       <c r="B7" s="5"/>
       <c r="C7" s="6"/>
@@ -768,7 +836,7 @@
         <v>25</v>
       </c>
       <c r="K7" s="8">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="L7" s="11"/>
       <c r="M7" s="5"/>
@@ -789,7 +857,7 @@
       <c r="AB7" s="4"/>
       <c r="AC7" s="4"/>
     </row>
-    <row r="8" ht="15.75" customHeight="1">
+    <row r="8" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="5"/>
       <c r="B8" s="5"/>
       <c r="C8" s="6"/>
@@ -803,7 +871,7 @@
         <v>25</v>
       </c>
       <c r="K8" s="8">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="L8" s="11"/>
       <c r="M8" s="5"/>
@@ -824,7 +892,7 @@
       <c r="AB8" s="4"/>
       <c r="AC8" s="4"/>
     </row>
-    <row r="9" ht="15.75" customHeight="1">
+    <row r="9" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="5"/>
       <c r="B9" s="5"/>
       <c r="C9" s="6"/>
@@ -836,13 +904,13 @@
         <v>22</v>
       </c>
       <c r="I9" s="10">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="J9" s="10" t="s">
         <v>22</v>
       </c>
       <c r="K9" s="10">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L9" s="11"/>
       <c r="M9" s="5"/>
@@ -863,7 +931,7 @@
       <c r="AB9" s="4"/>
       <c r="AC9" s="4"/>
     </row>
-    <row r="10" ht="15.75" customHeight="1">
+    <row r="10" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="5"/>
       <c r="B10" s="5"/>
       <c r="C10" s="6"/>
@@ -875,13 +943,13 @@
         <v>22</v>
       </c>
       <c r="I10" s="10">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="J10" s="10" t="s">
         <v>22</v>
       </c>
       <c r="K10" s="10">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L10" s="6"/>
       <c r="M10" s="5"/>
@@ -902,7 +970,7 @@
       <c r="AB10" s="4"/>
       <c r="AC10" s="4"/>
     </row>
-    <row r="11" ht="15.75" customHeight="1">
+    <row r="11" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="5"/>
       <c r="B11" s="5"/>
       <c r="C11" s="6"/>
@@ -914,13 +982,13 @@
         <v>22</v>
       </c>
       <c r="I11" s="10">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="J11" s="10" t="s">
         <v>22</v>
       </c>
       <c r="K11" s="10">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L11" s="6"/>
       <c r="M11" s="5"/>
@@ -941,7 +1009,7 @@
       <c r="AB11" s="4"/>
       <c r="AC11" s="4"/>
     </row>
-    <row r="12" ht="15.75" customHeight="1">
+    <row r="12" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="5"/>
       <c r="B12" s="5"/>
       <c r="C12" s="6"/>
@@ -953,13 +1021,13 @@
         <v>22</v>
       </c>
       <c r="I12" s="10">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="J12" s="10" t="s">
         <v>22</v>
       </c>
       <c r="K12" s="10">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L12" s="6"/>
       <c r="M12" s="5"/>
@@ -980,7 +1048,7 @@
       <c r="AB12" s="4"/>
       <c r="AC12" s="4"/>
     </row>
-    <row r="13" ht="15.75" customHeight="1">
+    <row r="13" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="5" t="s">
         <v>26</v>
       </c>
@@ -991,28 +1059,28 @@
         <v>27</v>
       </c>
       <c r="D13" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="E13" s="5">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F13" s="6" t="b">
         <v>0</v>
       </c>
       <c r="G13" s="5">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="H13" s="10" t="s">
         <v>22</v>
       </c>
       <c r="I13" s="5">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="J13" s="10" t="s">
         <v>22</v>
       </c>
       <c r="K13" s="5">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L13" s="10" t="s">
         <v>22</v>
@@ -1035,39 +1103,39 @@
       <c r="AB13" s="4"/>
       <c r="AC13" s="4"/>
     </row>
-    <row r="14" ht="15.75" customHeight="1">
+    <row r="14" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="5" t="s">
         <v>28</v>
       </c>
       <c r="B14" s="5">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>18</v>
       </c>
       <c r="D14" s="5">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="E14" s="5">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="F14" s="6" t="b">
         <v>1</v>
       </c>
       <c r="G14" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="H14" s="10" t="s">
         <v>22</v>
       </c>
       <c r="I14" s="5">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="J14" s="10" t="s">
         <v>22</v>
       </c>
       <c r="K14" s="5">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L14" s="10" t="s">
         <v>22</v>
@@ -1090,7 +1158,7 @@
       <c r="AB14" s="4"/>
       <c r="AC14" s="4"/>
     </row>
-    <row r="15" ht="15.75" customHeight="1">
+    <row r="15" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="4"/>
       <c r="B15" s="4"/>
       <c r="C15" s="4"/>
@@ -1121,7 +1189,7 @@
       <c r="AB15" s="4"/>
       <c r="AC15" s="4"/>
     </row>
-    <row r="16" ht="15.75" customHeight="1">
+    <row r="16" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="4"/>
       <c r="B16" s="4"/>
       <c r="C16" s="4"/>
@@ -1152,7 +1220,7 @@
       <c r="AB16" s="4"/>
       <c r="AC16" s="4"/>
     </row>
-    <row r="17" ht="15.75" customHeight="1">
+    <row r="17" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="4"/>
       <c r="B17" s="4"/>
       <c r="C17" s="4"/>
@@ -1183,7 +1251,7 @@
       <c r="AB17" s="4"/>
       <c r="AC17" s="4"/>
     </row>
-    <row r="18" ht="15.75" customHeight="1">
+    <row r="18" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="4"/>
       <c r="B18" s="4"/>
       <c r="C18" s="4"/>
@@ -1214,7 +1282,7 @@
       <c r="AB18" s="4"/>
       <c r="AC18" s="4"/>
     </row>
-    <row r="19" ht="15.75" customHeight="1">
+    <row r="19" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="4"/>
       <c r="B19" s="4"/>
       <c r="C19" s="4"/>
@@ -1245,7 +1313,7 @@
       <c r="AB19" s="4"/>
       <c r="AC19" s="4"/>
     </row>
-    <row r="20" ht="15.75" customHeight="1">
+    <row r="20" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="4"/>
       <c r="B20" s="4"/>
       <c r="C20" s="4"/>
@@ -1276,7 +1344,7 @@
       <c r="AB20" s="4"/>
       <c r="AC20" s="4"/>
     </row>
-    <row r="21" ht="15.75" customHeight="1">
+    <row r="21" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="4"/>
       <c r="B21" s="4"/>
       <c r="C21" s="4"/>
@@ -1307,7 +1375,7 @@
       <c r="AB21" s="4"/>
       <c r="AC21" s="4"/>
     </row>
-    <row r="22" ht="15.75" customHeight="1">
+    <row r="22" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="4"/>
       <c r="B22" s="4"/>
       <c r="C22" s="4"/>
@@ -1338,7 +1406,7 @@
       <c r="AB22" s="4"/>
       <c r="AC22" s="4"/>
     </row>
-    <row r="23" ht="15.75" customHeight="1">
+    <row r="23" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="4"/>
       <c r="B23" s="4"/>
       <c r="C23" s="4"/>
@@ -1369,7 +1437,7 @@
       <c r="AB23" s="4"/>
       <c r="AC23" s="4"/>
     </row>
-    <row r="24" ht="15.75" customHeight="1">
+    <row r="24" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="4"/>
       <c r="B24" s="4"/>
       <c r="C24" s="4"/>
@@ -1400,7 +1468,7 @@
       <c r="AB24" s="4"/>
       <c r="AC24" s="4"/>
     </row>
-    <row r="25" ht="15.75" customHeight="1">
+    <row r="25" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="4"/>
       <c r="B25" s="4"/>
       <c r="C25" s="4"/>
@@ -1431,7 +1499,7 @@
       <c r="AB25" s="4"/>
       <c r="AC25" s="4"/>
     </row>
-    <row r="26" ht="15.75" customHeight="1">
+    <row r="26" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="4"/>
       <c r="B26" s="4"/>
       <c r="C26" s="4"/>
@@ -1462,7 +1530,7 @@
       <c r="AB26" s="4"/>
       <c r="AC26" s="4"/>
     </row>
-    <row r="27" ht="15.75" customHeight="1">
+    <row r="27" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="4"/>
       <c r="B27" s="4"/>
       <c r="C27" s="4"/>
@@ -1493,7 +1561,7 @@
       <c r="AB27" s="4"/>
       <c r="AC27" s="4"/>
     </row>
-    <row r="28" ht="15.75" customHeight="1">
+    <row r="28" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="4"/>
       <c r="B28" s="4"/>
       <c r="C28" s="4"/>
@@ -1524,7 +1592,7 @@
       <c r="AB28" s="4"/>
       <c r="AC28" s="4"/>
     </row>
-    <row r="29" ht="15.75" customHeight="1">
+    <row r="29" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="4"/>
       <c r="B29" s="4"/>
       <c r="C29" s="4"/>
@@ -1555,7 +1623,7 @@
       <c r="AB29" s="4"/>
       <c r="AC29" s="4"/>
     </row>
-    <row r="30" ht="15.75" customHeight="1">
+    <row r="30" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="4"/>
       <c r="B30" s="4"/>
       <c r="C30" s="4"/>
@@ -1586,7 +1654,7 @@
       <c r="AB30" s="4"/>
       <c r="AC30" s="4"/>
     </row>
-    <row r="31" ht="15.75" customHeight="1">
+    <row r="31" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="4"/>
       <c r="B31" s="4"/>
       <c r="C31" s="4"/>
@@ -1617,7 +1685,7 @@
       <c r="AB31" s="4"/>
       <c r="AC31" s="4"/>
     </row>
-    <row r="32" ht="15.75" customHeight="1">
+    <row r="32" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="4"/>
       <c r="B32" s="4"/>
       <c r="C32" s="4"/>
@@ -1648,7 +1716,7 @@
       <c r="AB32" s="4"/>
       <c r="AC32" s="4"/>
     </row>
-    <row r="33" ht="15.75" customHeight="1">
+    <row r="33" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="4"/>
       <c r="B33" s="4"/>
       <c r="C33" s="4"/>
@@ -1679,7 +1747,7 @@
       <c r="AB33" s="4"/>
       <c r="AC33" s="4"/>
     </row>
-    <row r="34" ht="15.75" customHeight="1">
+    <row r="34" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="4"/>
       <c r="B34" s="4"/>
       <c r="C34" s="4"/>
@@ -1710,7 +1778,7 @@
       <c r="AB34" s="4"/>
       <c r="AC34" s="4"/>
     </row>
-    <row r="35" ht="15.75" customHeight="1">
+    <row r="35" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="4"/>
       <c r="B35" s="4"/>
       <c r="C35" s="4"/>
@@ -1741,7 +1809,7 @@
       <c r="AB35" s="4"/>
       <c r="AC35" s="4"/>
     </row>
-    <row r="36" ht="15.75" customHeight="1">
+    <row r="36" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="4"/>
       <c r="B36" s="4"/>
       <c r="C36" s="4"/>
@@ -1772,7 +1840,7 @@
       <c r="AB36" s="4"/>
       <c r="AC36" s="4"/>
     </row>
-    <row r="37" ht="15.75" customHeight="1">
+    <row r="37" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="4"/>
       <c r="B37" s="4"/>
       <c r="C37" s="4"/>
@@ -1803,7 +1871,7 @@
       <c r="AB37" s="4"/>
       <c r="AC37" s="4"/>
     </row>
-    <row r="38" ht="15.75" customHeight="1">
+    <row r="38" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="4"/>
       <c r="B38" s="4"/>
       <c r="C38" s="4"/>
@@ -1834,7 +1902,7 @@
       <c r="AB38" s="4"/>
       <c r="AC38" s="4"/>
     </row>
-    <row r="39" ht="15.75" customHeight="1">
+    <row r="39" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="4"/>
       <c r="B39" s="4"/>
       <c r="C39" s="4"/>
@@ -1865,7 +1933,7 @@
       <c r="AB39" s="4"/>
       <c r="AC39" s="4"/>
     </row>
-    <row r="40" ht="15.75" customHeight="1">
+    <row r="40" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="4"/>
       <c r="B40" s="4"/>
       <c r="C40" s="4"/>
@@ -1896,7 +1964,7 @@
       <c r="AB40" s="4"/>
       <c r="AC40" s="4"/>
     </row>
-    <row r="41" ht="15.75" customHeight="1">
+    <row r="41" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="4"/>
       <c r="B41" s="4"/>
       <c r="C41" s="4"/>
@@ -1927,7 +1995,7 @@
       <c r="AB41" s="4"/>
       <c r="AC41" s="4"/>
     </row>
-    <row r="42" ht="15.75" customHeight="1">
+    <row r="42" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="4"/>
       <c r="B42" s="4"/>
       <c r="C42" s="4"/>
@@ -1958,7 +2026,7 @@
       <c r="AB42" s="4"/>
       <c r="AC42" s="4"/>
     </row>
-    <row r="43" ht="15.75" customHeight="1">
+    <row r="43" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="4"/>
       <c r="B43" s="4"/>
       <c r="C43" s="4"/>
@@ -1989,7 +2057,7 @@
       <c r="AB43" s="4"/>
       <c r="AC43" s="4"/>
     </row>
-    <row r="44" ht="15.75" customHeight="1">
+    <row r="44" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="4"/>
       <c r="B44" s="4"/>
       <c r="C44" s="4"/>
@@ -2020,7 +2088,7 @@
       <c r="AB44" s="4"/>
       <c r="AC44" s="4"/>
     </row>
-    <row r="45" ht="15.75" customHeight="1">
+    <row r="45" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="4"/>
       <c r="B45" s="4"/>
       <c r="C45" s="4"/>
@@ -2051,7 +2119,7 @@
       <c r="AB45" s="4"/>
       <c r="AC45" s="4"/>
     </row>
-    <row r="46" ht="15.75" customHeight="1">
+    <row r="46" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="4"/>
       <c r="B46" s="4"/>
       <c r="C46" s="4"/>
@@ -2082,7 +2150,7 @@
       <c r="AB46" s="4"/>
       <c r="AC46" s="4"/>
     </row>
-    <row r="47" ht="15.75" customHeight="1">
+    <row r="47" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="4"/>
       <c r="B47" s="4"/>
       <c r="C47" s="4"/>
@@ -2113,7 +2181,7 @@
       <c r="AB47" s="4"/>
       <c r="AC47" s="4"/>
     </row>
-    <row r="48" ht="15.75" customHeight="1">
+    <row r="48" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="4"/>
       <c r="B48" s="4"/>
       <c r="C48" s="4"/>
@@ -2144,7 +2212,7 @@
       <c r="AB48" s="4"/>
       <c r="AC48" s="4"/>
     </row>
-    <row r="49" ht="15.75" customHeight="1">
+    <row r="49" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="4"/>
       <c r="B49" s="4"/>
       <c r="C49" s="4"/>
@@ -2175,7 +2243,7 @@
       <c r="AB49" s="4"/>
       <c r="AC49" s="4"/>
     </row>
-    <row r="50" ht="15.75" customHeight="1">
+    <row r="50" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="4"/>
       <c r="B50" s="4"/>
       <c r="C50" s="4"/>
@@ -2206,7 +2274,7 @@
       <c r="AB50" s="4"/>
       <c r="AC50" s="4"/>
     </row>
-    <row r="51" ht="15.75" customHeight="1">
+    <row r="51" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="4"/>
       <c r="B51" s="4"/>
       <c r="C51" s="4"/>
@@ -2237,7 +2305,7 @@
       <c r="AB51" s="4"/>
       <c r="AC51" s="4"/>
     </row>
-    <row r="52" ht="15.75" customHeight="1">
+    <row r="52" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="4"/>
       <c r="B52" s="4"/>
       <c r="C52" s="4"/>
@@ -2268,7 +2336,7 @@
       <c r="AB52" s="4"/>
       <c r="AC52" s="4"/>
     </row>
-    <row r="53" ht="15.75" customHeight="1">
+    <row r="53" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="4"/>
       <c r="B53" s="4"/>
       <c r="C53" s="4"/>
@@ -2299,7 +2367,7 @@
       <c r="AB53" s="4"/>
       <c r="AC53" s="4"/>
     </row>
-    <row r="54" ht="15.75" customHeight="1">
+    <row r="54" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="4"/>
       <c r="B54" s="4"/>
       <c r="C54" s="4"/>
@@ -2330,7 +2398,7 @@
       <c r="AB54" s="4"/>
       <c r="AC54" s="4"/>
     </row>
-    <row r="55" ht="15.75" customHeight="1">
+    <row r="55" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="4"/>
       <c r="B55" s="4"/>
       <c r="C55" s="4"/>
@@ -2361,7 +2429,7 @@
       <c r="AB55" s="4"/>
       <c r="AC55" s="4"/>
     </row>
-    <row r="56" ht="15.75" customHeight="1">
+    <row r="56" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="4"/>
       <c r="B56" s="4"/>
       <c r="C56" s="4"/>
@@ -2392,7 +2460,7 @@
       <c r="AB56" s="4"/>
       <c r="AC56" s="4"/>
     </row>
-    <row r="57" ht="15.75" customHeight="1">
+    <row r="57" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="4"/>
       <c r="B57" s="4"/>
       <c r="C57" s="4"/>
@@ -2423,7 +2491,7 @@
       <c r="AB57" s="4"/>
       <c r="AC57" s="4"/>
     </row>
-    <row r="58" ht="15.75" customHeight="1">
+    <row r="58" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="4"/>
       <c r="B58" s="4"/>
       <c r="C58" s="4"/>
@@ -2454,7 +2522,7 @@
       <c r="AB58" s="4"/>
       <c r="AC58" s="4"/>
     </row>
-    <row r="59" ht="15.75" customHeight="1">
+    <row r="59" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="4"/>
       <c r="B59" s="4"/>
       <c r="C59" s="4"/>
@@ -2485,7 +2553,7 @@
       <c r="AB59" s="4"/>
       <c r="AC59" s="4"/>
     </row>
-    <row r="60" ht="15.75" customHeight="1">
+    <row r="60" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="4"/>
       <c r="B60" s="4"/>
       <c r="C60" s="4"/>
@@ -2516,7 +2584,7 @@
       <c r="AB60" s="4"/>
       <c r="AC60" s="4"/>
     </row>
-    <row r="61" ht="15.75" customHeight="1">
+    <row r="61" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="4"/>
       <c r="B61" s="4"/>
       <c r="C61" s="4"/>
@@ -2547,7 +2615,7 @@
       <c r="AB61" s="4"/>
       <c r="AC61" s="4"/>
     </row>
-    <row r="62" ht="15.75" customHeight="1">
+    <row r="62" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="4"/>
       <c r="B62" s="4"/>
       <c r="C62" s="4"/>
@@ -2578,7 +2646,7 @@
       <c r="AB62" s="4"/>
       <c r="AC62" s="4"/>
     </row>
-    <row r="63" ht="15.75" customHeight="1">
+    <row r="63" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="4"/>
       <c r="B63" s="4"/>
       <c r="C63" s="4"/>
@@ -2609,7 +2677,7 @@
       <c r="AB63" s="4"/>
       <c r="AC63" s="4"/>
     </row>
-    <row r="64" ht="15.75" customHeight="1">
+    <row r="64" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="4"/>
       <c r="B64" s="4"/>
       <c r="C64" s="4"/>
@@ -2640,7 +2708,7 @@
       <c r="AB64" s="4"/>
       <c r="AC64" s="4"/>
     </row>
-    <row r="65" ht="15.75" customHeight="1">
+    <row r="65" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="4"/>
       <c r="B65" s="4"/>
       <c r="C65" s="4"/>
@@ -2671,7 +2739,7 @@
       <c r="AB65" s="4"/>
       <c r="AC65" s="4"/>
     </row>
-    <row r="66" ht="15.75" customHeight="1">
+    <row r="66" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="4"/>
       <c r="B66" s="4"/>
       <c r="C66" s="4"/>
@@ -2702,7 +2770,7 @@
       <c r="AB66" s="4"/>
       <c r="AC66" s="4"/>
     </row>
-    <row r="67" ht="15.75" customHeight="1">
+    <row r="67" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="4"/>
       <c r="B67" s="4"/>
       <c r="C67" s="4"/>
@@ -2733,7 +2801,7 @@
       <c r="AB67" s="4"/>
       <c r="AC67" s="4"/>
     </row>
-    <row r="68" ht="15.75" customHeight="1">
+    <row r="68" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="4"/>
       <c r="B68" s="4"/>
       <c r="C68" s="4"/>
@@ -2764,7 +2832,7 @@
       <c r="AB68" s="4"/>
       <c r="AC68" s="4"/>
     </row>
-    <row r="69" ht="15.75" customHeight="1">
+    <row r="69" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="4"/>
       <c r="B69" s="4"/>
       <c r="C69" s="4"/>
@@ -2795,7 +2863,7 @@
       <c r="AB69" s="4"/>
       <c r="AC69" s="4"/>
     </row>
-    <row r="70" ht="15.75" customHeight="1">
+    <row r="70" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="4"/>
       <c r="B70" s="4"/>
       <c r="C70" s="4"/>
@@ -2826,7 +2894,7 @@
       <c r="AB70" s="4"/>
       <c r="AC70" s="4"/>
     </row>
-    <row r="71" ht="15.75" customHeight="1">
+    <row r="71" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="4"/>
       <c r="B71" s="4"/>
       <c r="C71" s="4"/>
@@ -2857,7 +2925,7 @@
       <c r="AB71" s="4"/>
       <c r="AC71" s="4"/>
     </row>
-    <row r="72" ht="15.75" customHeight="1">
+    <row r="72" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="4"/>
       <c r="B72" s="4"/>
       <c r="C72" s="4"/>
@@ -2888,7 +2956,7 @@
       <c r="AB72" s="4"/>
       <c r="AC72" s="4"/>
     </row>
-    <row r="73" ht="15.75" customHeight="1">
+    <row r="73" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="4"/>
       <c r="B73" s="4"/>
       <c r="C73" s="4"/>
@@ -2919,7 +2987,7 @@
       <c r="AB73" s="4"/>
       <c r="AC73" s="4"/>
     </row>
-    <row r="74" ht="15.75" customHeight="1">
+    <row r="74" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="4"/>
       <c r="B74" s="4"/>
       <c r="C74" s="4"/>
@@ -2950,7 +3018,7 @@
       <c r="AB74" s="4"/>
       <c r="AC74" s="4"/>
     </row>
-    <row r="75" ht="15.75" customHeight="1">
+    <row r="75" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="4"/>
       <c r="B75" s="4"/>
       <c r="C75" s="4"/>
@@ -2981,7 +3049,7 @@
       <c r="AB75" s="4"/>
       <c r="AC75" s="4"/>
     </row>
-    <row r="76" ht="15.75" customHeight="1">
+    <row r="76" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="4"/>
       <c r="B76" s="4"/>
       <c r="C76" s="4"/>
@@ -3012,7 +3080,7 @@
       <c r="AB76" s="4"/>
       <c r="AC76" s="4"/>
     </row>
-    <row r="77" ht="15.75" customHeight="1">
+    <row r="77" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="4"/>
       <c r="B77" s="4"/>
       <c r="C77" s="4"/>
@@ -3043,7 +3111,7 @@
       <c r="AB77" s="4"/>
       <c r="AC77" s="4"/>
     </row>
-    <row r="78" ht="15.75" customHeight="1">
+    <row r="78" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" s="4"/>
       <c r="B78" s="4"/>
       <c r="C78" s="4"/>
@@ -3074,7 +3142,7 @@
       <c r="AB78" s="4"/>
       <c r="AC78" s="4"/>
     </row>
-    <row r="79" ht="15.75" customHeight="1">
+    <row r="79" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" s="4"/>
       <c r="B79" s="4"/>
       <c r="C79" s="4"/>
@@ -3105,7 +3173,7 @@
       <c r="AB79" s="4"/>
       <c r="AC79" s="4"/>
     </row>
-    <row r="80" ht="15.75" customHeight="1">
+    <row r="80" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="4"/>
       <c r="B80" s="4"/>
       <c r="C80" s="4"/>
@@ -3136,7 +3204,7 @@
       <c r="AB80" s="4"/>
       <c r="AC80" s="4"/>
     </row>
-    <row r="81" ht="15.75" customHeight="1">
+    <row r="81" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="4"/>
       <c r="B81" s="4"/>
       <c r="C81" s="4"/>
@@ -3167,7 +3235,7 @@
       <c r="AB81" s="4"/>
       <c r="AC81" s="4"/>
     </row>
-    <row r="82" ht="15.75" customHeight="1">
+    <row r="82" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="4"/>
       <c r="B82" s="4"/>
       <c r="C82" s="4"/>
@@ -3198,7 +3266,7 @@
       <c r="AB82" s="4"/>
       <c r="AC82" s="4"/>
     </row>
-    <row r="83" ht="15.75" customHeight="1">
+    <row r="83" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="4"/>
       <c r="B83" s="4"/>
       <c r="C83" s="4"/>
@@ -3229,7 +3297,7 @@
       <c r="AB83" s="4"/>
       <c r="AC83" s="4"/>
     </row>
-    <row r="84" ht="15.75" customHeight="1">
+    <row r="84" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="4"/>
       <c r="B84" s="4"/>
       <c r="C84" s="4"/>
@@ -3260,7 +3328,7 @@
       <c r="AB84" s="4"/>
       <c r="AC84" s="4"/>
     </row>
-    <row r="85" ht="15.75" customHeight="1">
+    <row r="85" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="4"/>
       <c r="B85" s="4"/>
       <c r="C85" s="4"/>
@@ -3291,7 +3359,7 @@
       <c r="AB85" s="4"/>
       <c r="AC85" s="4"/>
     </row>
-    <row r="86" ht="15.75" customHeight="1">
+    <row r="86" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="4"/>
       <c r="B86" s="4"/>
       <c r="C86" s="4"/>
@@ -3322,7 +3390,7 @@
       <c r="AB86" s="4"/>
       <c r="AC86" s="4"/>
     </row>
-    <row r="87" ht="15.75" customHeight="1">
+    <row r="87" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="4"/>
       <c r="B87" s="4"/>
       <c r="C87" s="4"/>
@@ -3353,7 +3421,7 @@
       <c r="AB87" s="4"/>
       <c r="AC87" s="4"/>
     </row>
-    <row r="88" ht="15.75" customHeight="1">
+    <row r="88" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="4"/>
       <c r="B88" s="4"/>
       <c r="C88" s="4"/>
@@ -3384,7 +3452,7 @@
       <c r="AB88" s="4"/>
       <c r="AC88" s="4"/>
     </row>
-    <row r="89" ht="15.75" customHeight="1">
+    <row r="89" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="4"/>
       <c r="B89" s="4"/>
       <c r="C89" s="4"/>
@@ -3415,7 +3483,7 @@
       <c r="AB89" s="4"/>
       <c r="AC89" s="4"/>
     </row>
-    <row r="90" ht="15.75" customHeight="1">
+    <row r="90" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" s="4"/>
       <c r="B90" s="4"/>
       <c r="C90" s="4"/>
@@ -3446,7 +3514,7 @@
       <c r="AB90" s="4"/>
       <c r="AC90" s="4"/>
     </row>
-    <row r="91" ht="15.75" customHeight="1">
+    <row r="91" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="4"/>
       <c r="B91" s="4"/>
       <c r="C91" s="4"/>
@@ -3477,7 +3545,7 @@
       <c r="AB91" s="4"/>
       <c r="AC91" s="4"/>
     </row>
-    <row r="92" ht="15.75" customHeight="1">
+    <row r="92" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="4"/>
       <c r="B92" s="4"/>
       <c r="C92" s="4"/>
@@ -3508,7 +3576,7 @@
       <c r="AB92" s="4"/>
       <c r="AC92" s="4"/>
     </row>
-    <row r="93" ht="15.75" customHeight="1">
+    <row r="93" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="4"/>
       <c r="B93" s="4"/>
       <c r="C93" s="4"/>
@@ -3539,7 +3607,7 @@
       <c r="AB93" s="4"/>
       <c r="AC93" s="4"/>
     </row>
-    <row r="94" ht="15.75" customHeight="1">
+    <row r="94" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="4"/>
       <c r="B94" s="4"/>
       <c r="C94" s="4"/>
@@ -3570,7 +3638,7 @@
       <c r="AB94" s="4"/>
       <c r="AC94" s="4"/>
     </row>
-    <row r="95" ht="15.75" customHeight="1">
+    <row r="95" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="4"/>
       <c r="B95" s="4"/>
       <c r="C95" s="4"/>
@@ -3601,7 +3669,7 @@
       <c r="AB95" s="4"/>
       <c r="AC95" s="4"/>
     </row>
-    <row r="96" ht="15.75" customHeight="1">
+    <row r="96" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96" s="4"/>
       <c r="B96" s="4"/>
       <c r="C96" s="4"/>
@@ -3632,7 +3700,7 @@
       <c r="AB96" s="4"/>
       <c r="AC96" s="4"/>
     </row>
-    <row r="97" ht="15.75" customHeight="1">
+    <row r="97" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="4"/>
       <c r="B97" s="4"/>
       <c r="C97" s="4"/>
@@ -3663,7 +3731,7 @@
       <c r="AB97" s="4"/>
       <c r="AC97" s="4"/>
     </row>
-    <row r="98" ht="15.75" customHeight="1">
+    <row r="98" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="4"/>
       <c r="B98" s="4"/>
       <c r="C98" s="4"/>
@@ -3694,7 +3762,7 @@
       <c r="AB98" s="4"/>
       <c r="AC98" s="4"/>
     </row>
-    <row r="99" ht="15.75" customHeight="1">
+    <row r="99" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" s="4"/>
       <c r="B99" s="4"/>
       <c r="C99" s="4"/>
@@ -3725,7 +3793,7 @@
       <c r="AB99" s="4"/>
       <c r="AC99" s="4"/>
     </row>
-    <row r="100" ht="15.75" customHeight="1">
+    <row r="100" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" s="4"/>
       <c r="B100" s="4"/>
       <c r="C100" s="4"/>
@@ -3756,7 +3824,7 @@
       <c r="AB100" s="4"/>
       <c r="AC100" s="4"/>
     </row>
-    <row r="101" ht="15.75" customHeight="1">
+    <row r="101" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="4"/>
       <c r="B101" s="4"/>
       <c r="C101" s="4"/>
@@ -3787,7 +3855,7 @@
       <c r="AB101" s="4"/>
       <c r="AC101" s="4"/>
     </row>
-    <row r="102" ht="15.75" customHeight="1">
+    <row r="102" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" s="4"/>
       <c r="B102" s="4"/>
       <c r="C102" s="4"/>
@@ -3818,7 +3886,7 @@
       <c r="AB102" s="4"/>
       <c r="AC102" s="4"/>
     </row>
-    <row r="103" ht="15.75" customHeight="1">
+    <row r="103" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103" s="4"/>
       <c r="B103" s="4"/>
       <c r="C103" s="4"/>
@@ -3849,7 +3917,7 @@
       <c r="AB103" s="4"/>
       <c r="AC103" s="4"/>
     </row>
-    <row r="104" ht="15.75" customHeight="1">
+    <row r="104" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" s="4"/>
       <c r="B104" s="4"/>
       <c r="C104" s="4"/>
@@ -3880,7 +3948,7 @@
       <c r="AB104" s="4"/>
       <c r="AC104" s="4"/>
     </row>
-    <row r="105" ht="15.75" customHeight="1">
+    <row r="105" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A105" s="4"/>
       <c r="B105" s="4"/>
       <c r="C105" s="4"/>
@@ -3911,7 +3979,7 @@
       <c r="AB105" s="4"/>
       <c r="AC105" s="4"/>
     </row>
-    <row r="106" ht="15.75" customHeight="1">
+    <row r="106" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A106" s="4"/>
       <c r="B106" s="4"/>
       <c r="C106" s="4"/>
@@ -3942,7 +4010,7 @@
       <c r="AB106" s="4"/>
       <c r="AC106" s="4"/>
     </row>
-    <row r="107" ht="15.75" customHeight="1">
+    <row r="107" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A107" s="4"/>
       <c r="B107" s="4"/>
       <c r="C107" s="4"/>
@@ -3973,7 +4041,7 @@
       <c r="AB107" s="4"/>
       <c r="AC107" s="4"/>
     </row>
-    <row r="108" ht="15.75" customHeight="1">
+    <row r="108" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" s="4"/>
       <c r="B108" s="4"/>
       <c r="C108" s="4"/>
@@ -4004,7 +4072,7 @@
       <c r="AB108" s="4"/>
       <c r="AC108" s="4"/>
     </row>
-    <row r="109" ht="15.75" customHeight="1">
+    <row r="109" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" s="4"/>
       <c r="B109" s="4"/>
       <c r="C109" s="4"/>
@@ -4035,7 +4103,7 @@
       <c r="AB109" s="4"/>
       <c r="AC109" s="4"/>
     </row>
-    <row r="110" ht="15.75" customHeight="1">
+    <row r="110" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" s="4"/>
       <c r="B110" s="4"/>
       <c r="C110" s="4"/>
@@ -4066,7 +4134,7 @@
       <c r="AB110" s="4"/>
       <c r="AC110" s="4"/>
     </row>
-    <row r="111" ht="15.75" customHeight="1">
+    <row r="111" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" s="4"/>
       <c r="B111" s="4"/>
       <c r="C111" s="4"/>
@@ -4097,7 +4165,7 @@
       <c r="AB111" s="4"/>
       <c r="AC111" s="4"/>
     </row>
-    <row r="112" ht="15.75" customHeight="1">
+    <row r="112" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A112" s="4"/>
       <c r="B112" s="4"/>
       <c r="C112" s="4"/>
@@ -4128,7 +4196,7 @@
       <c r="AB112" s="4"/>
       <c r="AC112" s="4"/>
     </row>
-    <row r="113" ht="15.75" customHeight="1">
+    <row r="113" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A113" s="4"/>
       <c r="B113" s="4"/>
       <c r="C113" s="4"/>
@@ -4159,7 +4227,7 @@
       <c r="AB113" s="4"/>
       <c r="AC113" s="4"/>
     </row>
-    <row r="114" ht="15.75" customHeight="1">
+    <row r="114" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A114" s="4"/>
       <c r="B114" s="4"/>
       <c r="C114" s="4"/>
@@ -4190,7 +4258,7 @@
       <c r="AB114" s="4"/>
       <c r="AC114" s="4"/>
     </row>
-    <row r="115" ht="15.75" customHeight="1">
+    <row r="115" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A115" s="4"/>
       <c r="B115" s="4"/>
       <c r="C115" s="4"/>
@@ -4221,7 +4289,7 @@
       <c r="AB115" s="4"/>
       <c r="AC115" s="4"/>
     </row>
-    <row r="116" ht="15.75" customHeight="1">
+    <row r="116" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A116" s="4"/>
       <c r="B116" s="4"/>
       <c r="C116" s="4"/>
@@ -4252,7 +4320,7 @@
       <c r="AB116" s="4"/>
       <c r="AC116" s="4"/>
     </row>
-    <row r="117" ht="15.75" customHeight="1">
+    <row r="117" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A117" s="4"/>
       <c r="B117" s="4"/>
       <c r="C117" s="4"/>
@@ -4283,7 +4351,7 @@
       <c r="AB117" s="4"/>
       <c r="AC117" s="4"/>
     </row>
-    <row r="118" ht="15.75" customHeight="1">
+    <row r="118" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A118" s="4"/>
       <c r="B118" s="4"/>
       <c r="C118" s="4"/>
@@ -4314,7 +4382,7 @@
       <c r="AB118" s="4"/>
       <c r="AC118" s="4"/>
     </row>
-    <row r="119" ht="15.75" customHeight="1">
+    <row r="119" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A119" s="4"/>
       <c r="B119" s="4"/>
       <c r="C119" s="4"/>
@@ -4345,7 +4413,7 @@
       <c r="AB119" s="4"/>
       <c r="AC119" s="4"/>
     </row>
-    <row r="120" ht="15.75" customHeight="1">
+    <row r="120" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A120" s="4"/>
       <c r="B120" s="4"/>
       <c r="C120" s="4"/>
@@ -4376,7 +4444,7 @@
       <c r="AB120" s="4"/>
       <c r="AC120" s="4"/>
     </row>
-    <row r="121" ht="15.75" customHeight="1">
+    <row r="121" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A121" s="4"/>
       <c r="B121" s="4"/>
       <c r="C121" s="4"/>
@@ -4407,7 +4475,7 @@
       <c r="AB121" s="4"/>
       <c r="AC121" s="4"/>
     </row>
-    <row r="122" ht="15.75" customHeight="1">
+    <row r="122" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A122" s="4"/>
       <c r="B122" s="4"/>
       <c r="C122" s="4"/>
@@ -4438,7 +4506,7 @@
       <c r="AB122" s="4"/>
       <c r="AC122" s="4"/>
     </row>
-    <row r="123" ht="15.75" customHeight="1">
+    <row r="123" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A123" s="4"/>
       <c r="B123" s="4"/>
       <c r="C123" s="4"/>
@@ -4469,7 +4537,7 @@
       <c r="AB123" s="4"/>
       <c r="AC123" s="4"/>
     </row>
-    <row r="124" ht="15.75" customHeight="1">
+    <row r="124" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A124" s="4"/>
       <c r="B124" s="4"/>
       <c r="C124" s="4"/>
@@ -4500,7 +4568,7 @@
       <c r="AB124" s="4"/>
       <c r="AC124" s="4"/>
     </row>
-    <row r="125" ht="15.75" customHeight="1">
+    <row r="125" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A125" s="4"/>
       <c r="B125" s="4"/>
       <c r="C125" s="4"/>
@@ -4531,7 +4599,7 @@
       <c r="AB125" s="4"/>
       <c r="AC125" s="4"/>
     </row>
-    <row r="126" ht="15.75" customHeight="1">
+    <row r="126" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A126" s="4"/>
       <c r="B126" s="4"/>
       <c r="C126" s="4"/>
@@ -4562,7 +4630,7 @@
       <c r="AB126" s="4"/>
       <c r="AC126" s="4"/>
     </row>
-    <row r="127" ht="15.75" customHeight="1">
+    <row r="127" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A127" s="4"/>
       <c r="B127" s="4"/>
       <c r="C127" s="4"/>
@@ -4593,7 +4661,7 @@
       <c r="AB127" s="4"/>
       <c r="AC127" s="4"/>
     </row>
-    <row r="128" ht="15.75" customHeight="1">
+    <row r="128" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A128" s="4"/>
       <c r="B128" s="4"/>
       <c r="C128" s="4"/>
@@ -4624,7 +4692,7 @@
       <c r="AB128" s="4"/>
       <c r="AC128" s="4"/>
     </row>
-    <row r="129" ht="15.75" customHeight="1">
+    <row r="129" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A129" s="4"/>
       <c r="B129" s="4"/>
       <c r="C129" s="4"/>
@@ -4655,7 +4723,7 @@
       <c r="AB129" s="4"/>
       <c r="AC129" s="4"/>
     </row>
-    <row r="130" ht="15.75" customHeight="1">
+    <row r="130" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A130" s="4"/>
       <c r="B130" s="4"/>
       <c r="C130" s="4"/>
@@ -4686,7 +4754,7 @@
       <c r="AB130" s="4"/>
       <c r="AC130" s="4"/>
     </row>
-    <row r="131" ht="15.75" customHeight="1">
+    <row r="131" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A131" s="4"/>
       <c r="B131" s="4"/>
       <c r="C131" s="4"/>
@@ -4717,7 +4785,7 @@
       <c r="AB131" s="4"/>
       <c r="AC131" s="4"/>
     </row>
-    <row r="132" ht="15.75" customHeight="1">
+    <row r="132" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A132" s="4"/>
       <c r="B132" s="4"/>
       <c r="C132" s="4"/>
@@ -4748,7 +4816,7 @@
       <c r="AB132" s="4"/>
       <c r="AC132" s="4"/>
     </row>
-    <row r="133" ht="15.75" customHeight="1">
+    <row r="133" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A133" s="4"/>
       <c r="B133" s="4"/>
       <c r="C133" s="4"/>
@@ -4779,7 +4847,7 @@
       <c r="AB133" s="4"/>
       <c r="AC133" s="4"/>
     </row>
-    <row r="134" ht="15.75" customHeight="1">
+    <row r="134" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A134" s="4"/>
       <c r="B134" s="4"/>
       <c r="C134" s="4"/>
@@ -4810,7 +4878,7 @@
       <c r="AB134" s="4"/>
       <c r="AC134" s="4"/>
     </row>
-    <row r="135" ht="15.75" customHeight="1">
+    <row r="135" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A135" s="4"/>
       <c r="B135" s="4"/>
       <c r="C135" s="4"/>
@@ -4841,7 +4909,7 @@
       <c r="AB135" s="4"/>
       <c r="AC135" s="4"/>
     </row>
-    <row r="136" ht="15.75" customHeight="1">
+    <row r="136" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A136" s="4"/>
       <c r="B136" s="4"/>
       <c r="C136" s="4"/>
@@ -4872,7 +4940,7 @@
       <c r="AB136" s="4"/>
       <c r="AC136" s="4"/>
     </row>
-    <row r="137" ht="15.75" customHeight="1">
+    <row r="137" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A137" s="4"/>
       <c r="B137" s="4"/>
       <c r="C137" s="4"/>
@@ -4903,7 +4971,7 @@
       <c r="AB137" s="4"/>
       <c r="AC137" s="4"/>
     </row>
-    <row r="138" ht="15.75" customHeight="1">
+    <row r="138" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A138" s="4"/>
       <c r="B138" s="4"/>
       <c r="C138" s="4"/>
@@ -4934,7 +5002,7 @@
       <c r="AB138" s="4"/>
       <c r="AC138" s="4"/>
     </row>
-    <row r="139" ht="15.75" customHeight="1">
+    <row r="139" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A139" s="4"/>
       <c r="B139" s="4"/>
       <c r="C139" s="4"/>
@@ -4965,7 +5033,7 @@
       <c r="AB139" s="4"/>
       <c r="AC139" s="4"/>
     </row>
-    <row r="140" ht="15.75" customHeight="1">
+    <row r="140" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A140" s="4"/>
       <c r="B140" s="4"/>
       <c r="C140" s="4"/>
@@ -4996,7 +5064,7 @@
       <c r="AB140" s="4"/>
       <c r="AC140" s="4"/>
     </row>
-    <row r="141" ht="15.75" customHeight="1">
+    <row r="141" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A141" s="4"/>
       <c r="B141" s="4"/>
       <c r="C141" s="4"/>
@@ -5027,7 +5095,7 @@
       <c r="AB141" s="4"/>
       <c r="AC141" s="4"/>
     </row>
-    <row r="142" ht="15.75" customHeight="1">
+    <row r="142" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A142" s="4"/>
       <c r="B142" s="4"/>
       <c r="C142" s="4"/>
@@ -5058,7 +5126,7 @@
       <c r="AB142" s="4"/>
       <c r="AC142" s="4"/>
     </row>
-    <row r="143" ht="15.75" customHeight="1">
+    <row r="143" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A143" s="4"/>
       <c r="B143" s="4"/>
       <c r="C143" s="4"/>
@@ -5089,7 +5157,7 @@
       <c r="AB143" s="4"/>
       <c r="AC143" s="4"/>
     </row>
-    <row r="144" ht="15.75" customHeight="1">
+    <row r="144" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A144" s="4"/>
       <c r="B144" s="4"/>
       <c r="C144" s="4"/>
@@ -5120,7 +5188,7 @@
       <c r="AB144" s="4"/>
       <c r="AC144" s="4"/>
     </row>
-    <row r="145" ht="15.75" customHeight="1">
+    <row r="145" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A145" s="4"/>
       <c r="B145" s="4"/>
       <c r="C145" s="4"/>
@@ -5151,7 +5219,7 @@
       <c r="AB145" s="4"/>
       <c r="AC145" s="4"/>
     </row>
-    <row r="146" ht="15.75" customHeight="1">
+    <row r="146" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A146" s="4"/>
       <c r="B146" s="4"/>
       <c r="C146" s="4"/>
@@ -5182,7 +5250,7 @@
       <c r="AB146" s="4"/>
       <c r="AC146" s="4"/>
     </row>
-    <row r="147" ht="15.75" customHeight="1">
+    <row r="147" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A147" s="4"/>
       <c r="B147" s="4"/>
       <c r="C147" s="4"/>
@@ -5213,7 +5281,7 @@
       <c r="AB147" s="4"/>
       <c r="AC147" s="4"/>
     </row>
-    <row r="148" ht="15.75" customHeight="1">
+    <row r="148" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A148" s="4"/>
       <c r="B148" s="4"/>
       <c r="C148" s="4"/>
@@ -5244,7 +5312,7 @@
       <c r="AB148" s="4"/>
       <c r="AC148" s="4"/>
     </row>
-    <row r="149" ht="15.75" customHeight="1">
+    <row r="149" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A149" s="4"/>
       <c r="B149" s="4"/>
       <c r="C149" s="4"/>
@@ -5275,7 +5343,7 @@
       <c r="AB149" s="4"/>
       <c r="AC149" s="4"/>
     </row>
-    <row r="150" ht="15.75" customHeight="1">
+    <row r="150" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A150" s="4"/>
       <c r="B150" s="4"/>
       <c r="C150" s="4"/>
@@ -5306,7 +5374,7 @@
       <c r="AB150" s="4"/>
       <c r="AC150" s="4"/>
     </row>
-    <row r="151" ht="15.75" customHeight="1">
+    <row r="151" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A151" s="4"/>
       <c r="B151" s="4"/>
       <c r="C151" s="4"/>
@@ -5337,7 +5405,7 @@
       <c r="AB151" s="4"/>
       <c r="AC151" s="4"/>
     </row>
-    <row r="152" ht="15.75" customHeight="1">
+    <row r="152" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A152" s="4"/>
       <c r="B152" s="4"/>
       <c r="C152" s="4"/>
@@ -5368,7 +5436,7 @@
       <c r="AB152" s="4"/>
       <c r="AC152" s="4"/>
     </row>
-    <row r="153" ht="15.75" customHeight="1">
+    <row r="153" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A153" s="4"/>
       <c r="B153" s="4"/>
       <c r="C153" s="4"/>
@@ -5399,7 +5467,7 @@
       <c r="AB153" s="4"/>
       <c r="AC153" s="4"/>
     </row>
-    <row r="154" ht="15.75" customHeight="1">
+    <row r="154" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A154" s="4"/>
       <c r="B154" s="4"/>
       <c r="C154" s="4"/>
@@ -5430,7 +5498,7 @@
       <c r="AB154" s="4"/>
       <c r="AC154" s="4"/>
     </row>
-    <row r="155" ht="15.75" customHeight="1">
+    <row r="155" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A155" s="4"/>
       <c r="B155" s="4"/>
       <c r="C155" s="4"/>
@@ -5461,7 +5529,7 @@
       <c r="AB155" s="4"/>
       <c r="AC155" s="4"/>
     </row>
-    <row r="156" ht="15.75" customHeight="1">
+    <row r="156" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A156" s="4"/>
       <c r="B156" s="4"/>
       <c r="C156" s="4"/>
@@ -5492,7 +5560,7 @@
       <c r="AB156" s="4"/>
       <c r="AC156" s="4"/>
     </row>
-    <row r="157" ht="15.75" customHeight="1">
+    <row r="157" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A157" s="4"/>
       <c r="B157" s="4"/>
       <c r="C157" s="4"/>
@@ -5523,7 +5591,7 @@
       <c r="AB157" s="4"/>
       <c r="AC157" s="4"/>
     </row>
-    <row r="158" ht="15.75" customHeight="1">
+    <row r="158" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A158" s="4"/>
       <c r="B158" s="4"/>
       <c r="C158" s="4"/>
@@ -5554,7 +5622,7 @@
       <c r="AB158" s="4"/>
       <c r="AC158" s="4"/>
     </row>
-    <row r="159" ht="15.75" customHeight="1">
+    <row r="159" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A159" s="4"/>
       <c r="B159" s="4"/>
       <c r="C159" s="4"/>
@@ -5585,7 +5653,7 @@
       <c r="AB159" s="4"/>
       <c r="AC159" s="4"/>
     </row>
-    <row r="160" ht="15.75" customHeight="1">
+    <row r="160" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A160" s="4"/>
       <c r="B160" s="4"/>
       <c r="C160" s="4"/>
@@ -5616,7 +5684,7 @@
       <c r="AB160" s="4"/>
       <c r="AC160" s="4"/>
     </row>
-    <row r="161" ht="15.75" customHeight="1">
+    <row r="161" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A161" s="4"/>
       <c r="B161" s="4"/>
       <c r="C161" s="4"/>
@@ -5647,7 +5715,7 @@
       <c r="AB161" s="4"/>
       <c r="AC161" s="4"/>
     </row>
-    <row r="162" ht="15.75" customHeight="1">
+    <row r="162" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A162" s="4"/>
       <c r="B162" s="4"/>
       <c r="C162" s="4"/>
@@ -5678,7 +5746,7 @@
       <c r="AB162" s="4"/>
       <c r="AC162" s="4"/>
     </row>
-    <row r="163" ht="15.75" customHeight="1">
+    <row r="163" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A163" s="4"/>
       <c r="B163" s="4"/>
       <c r="C163" s="4"/>
@@ -5709,7 +5777,7 @@
       <c r="AB163" s="4"/>
       <c r="AC163" s="4"/>
     </row>
-    <row r="164" ht="15.75" customHeight="1">
+    <row r="164" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A164" s="4"/>
       <c r="B164" s="4"/>
       <c r="C164" s="4"/>
@@ -5740,7 +5808,7 @@
       <c r="AB164" s="4"/>
       <c r="AC164" s="4"/>
     </row>
-    <row r="165" ht="15.75" customHeight="1">
+    <row r="165" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A165" s="4"/>
       <c r="B165" s="4"/>
       <c r="C165" s="4"/>
@@ -5771,7 +5839,7 @@
       <c r="AB165" s="4"/>
       <c r="AC165" s="4"/>
     </row>
-    <row r="166" ht="15.75" customHeight="1">
+    <row r="166" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A166" s="4"/>
       <c r="B166" s="4"/>
       <c r="C166" s="4"/>
@@ -5802,7 +5870,7 @@
       <c r="AB166" s="4"/>
       <c r="AC166" s="4"/>
     </row>
-    <row r="167" ht="15.75" customHeight="1">
+    <row r="167" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A167" s="4"/>
       <c r="B167" s="4"/>
       <c r="C167" s="4"/>
@@ -5833,7 +5901,7 @@
       <c r="AB167" s="4"/>
       <c r="AC167" s="4"/>
     </row>
-    <row r="168" ht="15.75" customHeight="1">
+    <row r="168" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A168" s="4"/>
       <c r="B168" s="4"/>
       <c r="C168" s="4"/>
@@ -5864,7 +5932,7 @@
       <c r="AB168" s="4"/>
       <c r="AC168" s="4"/>
     </row>
-    <row r="169" ht="15.75" customHeight="1">
+    <row r="169" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A169" s="4"/>
       <c r="B169" s="4"/>
       <c r="C169" s="4"/>
@@ -5895,7 +5963,7 @@
       <c r="AB169" s="4"/>
       <c r="AC169" s="4"/>
     </row>
-    <row r="170" ht="15.75" customHeight="1">
+    <row r="170" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A170" s="4"/>
       <c r="B170" s="4"/>
       <c r="C170" s="4"/>
@@ -5926,7 +5994,7 @@
       <c r="AB170" s="4"/>
       <c r="AC170" s="4"/>
     </row>
-    <row r="171" ht="15.75" customHeight="1">
+    <row r="171" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A171" s="4"/>
       <c r="B171" s="4"/>
       <c r="C171" s="4"/>
@@ -5957,7 +6025,7 @@
       <c r="AB171" s="4"/>
       <c r="AC171" s="4"/>
     </row>
-    <row r="172" ht="15.75" customHeight="1">
+    <row r="172" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A172" s="4"/>
       <c r="B172" s="4"/>
       <c r="C172" s="4"/>
@@ -5988,7 +6056,7 @@
       <c r="AB172" s="4"/>
       <c r="AC172" s="4"/>
     </row>
-    <row r="173" ht="15.75" customHeight="1">
+    <row r="173" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A173" s="4"/>
       <c r="B173" s="4"/>
       <c r="C173" s="4"/>
@@ -6019,7 +6087,7 @@
       <c r="AB173" s="4"/>
       <c r="AC173" s="4"/>
     </row>
-    <row r="174" ht="15.75" customHeight="1">
+    <row r="174" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A174" s="4"/>
       <c r="B174" s="4"/>
       <c r="C174" s="4"/>
@@ -6050,7 +6118,7 @@
       <c r="AB174" s="4"/>
       <c r="AC174" s="4"/>
     </row>
-    <row r="175" ht="15.75" customHeight="1">
+    <row r="175" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A175" s="4"/>
       <c r="B175" s="4"/>
       <c r="C175" s="4"/>
@@ -6081,7 +6149,7 @@
       <c r="AB175" s="4"/>
       <c r="AC175" s="4"/>
     </row>
-    <row r="176" ht="15.75" customHeight="1">
+    <row r="176" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A176" s="4"/>
       <c r="B176" s="4"/>
       <c r="C176" s="4"/>
@@ -6112,7 +6180,7 @@
       <c r="AB176" s="4"/>
       <c r="AC176" s="4"/>
     </row>
-    <row r="177" ht="15.75" customHeight="1">
+    <row r="177" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A177" s="4"/>
       <c r="B177" s="4"/>
       <c r="C177" s="4"/>
@@ -6143,7 +6211,7 @@
       <c r="AB177" s="4"/>
       <c r="AC177" s="4"/>
     </row>
-    <row r="178" ht="15.75" customHeight="1">
+    <row r="178" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A178" s="4"/>
       <c r="B178" s="4"/>
       <c r="C178" s="4"/>
@@ -6174,7 +6242,7 @@
       <c r="AB178" s="4"/>
       <c r="AC178" s="4"/>
     </row>
-    <row r="179" ht="15.75" customHeight="1">
+    <row r="179" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A179" s="4"/>
       <c r="B179" s="4"/>
       <c r="C179" s="4"/>
@@ -6205,7 +6273,7 @@
       <c r="AB179" s="4"/>
       <c r="AC179" s="4"/>
     </row>
-    <row r="180" ht="15.75" customHeight="1">
+    <row r="180" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A180" s="4"/>
       <c r="B180" s="4"/>
       <c r="C180" s="4"/>
@@ -6236,7 +6304,7 @@
       <c r="AB180" s="4"/>
       <c r="AC180" s="4"/>
     </row>
-    <row r="181" ht="15.75" customHeight="1">
+    <row r="181" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A181" s="4"/>
       <c r="B181" s="4"/>
       <c r="C181" s="4"/>
@@ -6267,7 +6335,7 @@
       <c r="AB181" s="4"/>
       <c r="AC181" s="4"/>
     </row>
-    <row r="182" ht="15.75" customHeight="1">
+    <row r="182" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A182" s="4"/>
       <c r="B182" s="4"/>
       <c r="C182" s="4"/>
@@ -6298,7 +6366,7 @@
       <c r="AB182" s="4"/>
       <c r="AC182" s="4"/>
     </row>
-    <row r="183" ht="15.75" customHeight="1">
+    <row r="183" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A183" s="4"/>
       <c r="B183" s="4"/>
       <c r="C183" s="4"/>
@@ -6329,7 +6397,7 @@
       <c r="AB183" s="4"/>
       <c r="AC183" s="4"/>
     </row>
-    <row r="184" ht="15.75" customHeight="1">
+    <row r="184" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A184" s="4"/>
       <c r="B184" s="4"/>
       <c r="C184" s="4"/>
@@ -6360,7 +6428,7 @@
       <c r="AB184" s="4"/>
       <c r="AC184" s="4"/>
     </row>
-    <row r="185" ht="15.75" customHeight="1">
+    <row r="185" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A185" s="4"/>
       <c r="B185" s="4"/>
       <c r="C185" s="4"/>
@@ -6391,7 +6459,7 @@
       <c r="AB185" s="4"/>
       <c r="AC185" s="4"/>
     </row>
-    <row r="186" ht="15.75" customHeight="1">
+    <row r="186" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A186" s="4"/>
       <c r="B186" s="4"/>
       <c r="C186" s="4"/>
@@ -6422,7 +6490,7 @@
       <c r="AB186" s="4"/>
       <c r="AC186" s="4"/>
     </row>
-    <row r="187" ht="15.75" customHeight="1">
+    <row r="187" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A187" s="4"/>
       <c r="B187" s="4"/>
       <c r="C187" s="4"/>
@@ -6453,7 +6521,7 @@
       <c r="AB187" s="4"/>
       <c r="AC187" s="4"/>
     </row>
-    <row r="188" ht="15.75" customHeight="1">
+    <row r="188" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A188" s="4"/>
       <c r="B188" s="4"/>
       <c r="C188" s="4"/>
@@ -6484,7 +6552,7 @@
       <c r="AB188" s="4"/>
       <c r="AC188" s="4"/>
     </row>
-    <row r="189" ht="15.75" customHeight="1">
+    <row r="189" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A189" s="4"/>
       <c r="B189" s="4"/>
       <c r="C189" s="4"/>
@@ -6515,7 +6583,7 @@
       <c r="AB189" s="4"/>
       <c r="AC189" s="4"/>
     </row>
-    <row r="190" ht="15.75" customHeight="1">
+    <row r="190" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A190" s="4"/>
       <c r="B190" s="4"/>
       <c r="C190" s="4"/>
@@ -6546,7 +6614,7 @@
       <c r="AB190" s="4"/>
       <c r="AC190" s="4"/>
     </row>
-    <row r="191" ht="15.75" customHeight="1">
+    <row r="191" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A191" s="4"/>
       <c r="B191" s="4"/>
       <c r="C191" s="4"/>
@@ -6577,7 +6645,7 @@
       <c r="AB191" s="4"/>
       <c r="AC191" s="4"/>
     </row>
-    <row r="192" ht="15.75" customHeight="1">
+    <row r="192" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A192" s="4"/>
       <c r="B192" s="4"/>
       <c r="C192" s="4"/>
@@ -6608,7 +6676,7 @@
       <c r="AB192" s="4"/>
       <c r="AC192" s="4"/>
     </row>
-    <row r="193" ht="15.75" customHeight="1">
+    <row r="193" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A193" s="4"/>
       <c r="B193" s="4"/>
       <c r="C193" s="4"/>
@@ -6639,7 +6707,7 @@
       <c r="AB193" s="4"/>
       <c r="AC193" s="4"/>
     </row>
-    <row r="194" ht="15.75" customHeight="1">
+    <row r="194" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A194" s="4"/>
       <c r="B194" s="4"/>
       <c r="C194" s="4"/>
@@ -6670,7 +6738,7 @@
       <c r="AB194" s="4"/>
       <c r="AC194" s="4"/>
     </row>
-    <row r="195" ht="15.75" customHeight="1">
+    <row r="195" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A195" s="4"/>
       <c r="B195" s="4"/>
       <c r="C195" s="4"/>
@@ -6701,7 +6769,7 @@
       <c r="AB195" s="4"/>
       <c r="AC195" s="4"/>
     </row>
-    <row r="196" ht="15.75" customHeight="1">
+    <row r="196" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A196" s="4"/>
       <c r="B196" s="4"/>
       <c r="C196" s="4"/>
@@ -6732,7 +6800,7 @@
       <c r="AB196" s="4"/>
       <c r="AC196" s="4"/>
     </row>
-    <row r="197" ht="15.75" customHeight="1">
+    <row r="197" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A197" s="4"/>
       <c r="B197" s="4"/>
       <c r="C197" s="4"/>
@@ -6763,7 +6831,7 @@
       <c r="AB197" s="4"/>
       <c r="AC197" s="4"/>
     </row>
-    <row r="198" ht="15.75" customHeight="1">
+    <row r="198" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A198" s="4"/>
       <c r="B198" s="4"/>
       <c r="C198" s="4"/>
@@ -6794,7 +6862,7 @@
       <c r="AB198" s="4"/>
       <c r="AC198" s="4"/>
     </row>
-    <row r="199" ht="15.75" customHeight="1">
+    <row r="199" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A199" s="4"/>
       <c r="B199" s="4"/>
       <c r="C199" s="4"/>
@@ -6825,7 +6893,7 @@
       <c r="AB199" s="4"/>
       <c r="AC199" s="4"/>
     </row>
-    <row r="200" ht="15.75" customHeight="1">
+    <row r="200" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A200" s="4"/>
       <c r="B200" s="4"/>
       <c r="C200" s="4"/>
@@ -6856,7 +6924,7 @@
       <c r="AB200" s="4"/>
       <c r="AC200" s="4"/>
     </row>
-    <row r="201" ht="15.75" customHeight="1">
+    <row r="201" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A201" s="4"/>
       <c r="B201" s="4"/>
       <c r="C201" s="4"/>
@@ -6887,7 +6955,7 @@
       <c r="AB201" s="4"/>
       <c r="AC201" s="4"/>
     </row>
-    <row r="202" ht="15.75" customHeight="1">
+    <row r="202" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A202" s="4"/>
       <c r="B202" s="4"/>
       <c r="C202" s="4"/>
@@ -6918,7 +6986,7 @@
       <c r="AB202" s="4"/>
       <c r="AC202" s="4"/>
     </row>
-    <row r="203" ht="15.75" customHeight="1">
+    <row r="203" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A203" s="4"/>
       <c r="B203" s="4"/>
       <c r="C203" s="4"/>
@@ -6949,7 +7017,7 @@
       <c r="AB203" s="4"/>
       <c r="AC203" s="4"/>
     </row>
-    <row r="204" ht="15.75" customHeight="1">
+    <row r="204" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A204" s="4"/>
       <c r="B204" s="4"/>
       <c r="C204" s="4"/>
@@ -6980,7 +7048,7 @@
       <c r="AB204" s="4"/>
       <c r="AC204" s="4"/>
     </row>
-    <row r="205" ht="15.75" customHeight="1">
+    <row r="205" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A205" s="4"/>
       <c r="B205" s="4"/>
       <c r="C205" s="4"/>
@@ -7011,7 +7079,7 @@
       <c r="AB205" s="4"/>
       <c r="AC205" s="4"/>
     </row>
-    <row r="206" ht="15.75" customHeight="1">
+    <row r="206" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A206" s="4"/>
       <c r="B206" s="4"/>
       <c r="C206" s="4"/>
@@ -7042,7 +7110,7 @@
       <c r="AB206" s="4"/>
       <c r="AC206" s="4"/>
     </row>
-    <row r="207" ht="15.75" customHeight="1">
+    <row r="207" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A207" s="4"/>
       <c r="B207" s="4"/>
       <c r="C207" s="4"/>
@@ -7073,7 +7141,7 @@
       <c r="AB207" s="4"/>
       <c r="AC207" s="4"/>
     </row>
-    <row r="208" ht="15.75" customHeight="1">
+    <row r="208" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A208" s="4"/>
       <c r="B208" s="4"/>
       <c r="C208" s="4"/>
@@ -7104,7 +7172,7 @@
       <c r="AB208" s="4"/>
       <c r="AC208" s="4"/>
     </row>
-    <row r="209" ht="15.75" customHeight="1">
+    <row r="209" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A209" s="4"/>
       <c r="B209" s="4"/>
       <c r="C209" s="4"/>
@@ -7135,7 +7203,7 @@
       <c r="AB209" s="4"/>
       <c r="AC209" s="4"/>
     </row>
-    <row r="210" ht="15.75" customHeight="1">
+    <row r="210" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A210" s="4"/>
       <c r="B210" s="4"/>
       <c r="C210" s="4"/>
@@ -7166,7 +7234,7 @@
       <c r="AB210" s="4"/>
       <c r="AC210" s="4"/>
     </row>
-    <row r="211" ht="15.75" customHeight="1">
+    <row r="211" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A211" s="4"/>
       <c r="B211" s="4"/>
       <c r="C211" s="4"/>
@@ -7197,7 +7265,7 @@
       <c r="AB211" s="4"/>
       <c r="AC211" s="4"/>
     </row>
-    <row r="212" ht="15.75" customHeight="1">
+    <row r="212" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A212" s="4"/>
       <c r="B212" s="4"/>
       <c r="C212" s="4"/>
@@ -7228,7 +7296,7 @@
       <c r="AB212" s="4"/>
       <c r="AC212" s="4"/>
     </row>
-    <row r="213" ht="15.75" customHeight="1">
+    <row r="213" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A213" s="4"/>
       <c r="B213" s="4"/>
       <c r="C213" s="4"/>
@@ -7259,7 +7327,7 @@
       <c r="AB213" s="4"/>
       <c r="AC213" s="4"/>
     </row>
-    <row r="214" ht="15.75" customHeight="1">
+    <row r="214" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A214" s="4"/>
       <c r="B214" s="4"/>
       <c r="C214" s="4"/>
@@ -7290,7 +7358,7 @@
       <c r="AB214" s="4"/>
       <c r="AC214" s="4"/>
     </row>
-    <row r="215" ht="15.75" customHeight="1">
+    <row r="215" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A215" s="4"/>
       <c r="B215" s="4"/>
       <c r="C215" s="4"/>
@@ -7321,7 +7389,7 @@
       <c r="AB215" s="4"/>
       <c r="AC215" s="4"/>
     </row>
-    <row r="216" ht="15.75" customHeight="1">
+    <row r="216" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A216" s="4"/>
       <c r="B216" s="4"/>
       <c r="C216" s="4"/>
@@ -7352,7 +7420,7 @@
       <c r="AB216" s="4"/>
       <c r="AC216" s="4"/>
     </row>
-    <row r="217" ht="15.75" customHeight="1">
+    <row r="217" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A217" s="4"/>
       <c r="B217" s="4"/>
       <c r="C217" s="4"/>
@@ -7383,7 +7451,7 @@
       <c r="AB217" s="4"/>
       <c r="AC217" s="4"/>
     </row>
-    <row r="218" ht="15.75" customHeight="1">
+    <row r="218" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A218" s="4"/>
       <c r="B218" s="4"/>
       <c r="C218" s="4"/>
@@ -7414,7 +7482,7 @@
       <c r="AB218" s="4"/>
       <c r="AC218" s="4"/>
     </row>
-    <row r="219" ht="15.75" customHeight="1">
+    <row r="219" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A219" s="4"/>
       <c r="B219" s="4"/>
       <c r="C219" s="4"/>
@@ -7445,7 +7513,7 @@
       <c r="AB219" s="4"/>
       <c r="AC219" s="4"/>
     </row>
-    <row r="220" ht="15.75" customHeight="1">
+    <row r="220" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A220" s="4"/>
       <c r="B220" s="4"/>
       <c r="C220" s="4"/>
@@ -7476,7 +7544,7 @@
       <c r="AB220" s="4"/>
       <c r="AC220" s="4"/>
     </row>
-    <row r="221" ht="15.75" customHeight="1">
+    <row r="221" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A221" s="4"/>
       <c r="B221" s="4"/>
       <c r="C221" s="4"/>
@@ -7507,7 +7575,7 @@
       <c r="AB221" s="4"/>
       <c r="AC221" s="4"/>
     </row>
-    <row r="222" ht="15.75" customHeight="1">
+    <row r="222" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A222" s="4"/>
       <c r="B222" s="4"/>
       <c r="C222" s="4"/>
@@ -7538,7 +7606,7 @@
       <c r="AB222" s="4"/>
       <c r="AC222" s="4"/>
     </row>
-    <row r="223" ht="15.75" customHeight="1">
+    <row r="223" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A223" s="4"/>
       <c r="B223" s="4"/>
       <c r="C223" s="4"/>
@@ -7569,7 +7637,7 @@
       <c r="AB223" s="4"/>
       <c r="AC223" s="4"/>
     </row>
-    <row r="224" ht="15.75" customHeight="1">
+    <row r="224" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A224" s="4"/>
       <c r="B224" s="4"/>
       <c r="C224" s="4"/>
@@ -7600,7 +7668,7 @@
       <c r="AB224" s="4"/>
       <c r="AC224" s="4"/>
     </row>
-    <row r="225" ht="15.75" customHeight="1">
+    <row r="225" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A225" s="4"/>
       <c r="B225" s="4"/>
       <c r="C225" s="4"/>
@@ -7631,7 +7699,7 @@
       <c r="AB225" s="4"/>
       <c r="AC225" s="4"/>
     </row>
-    <row r="226" ht="15.75" customHeight="1">
+    <row r="226" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A226" s="4"/>
       <c r="B226" s="4"/>
       <c r="C226" s="4"/>
@@ -7662,7 +7730,7 @@
       <c r="AB226" s="4"/>
       <c r="AC226" s="4"/>
     </row>
-    <row r="227" ht="15.75" customHeight="1">
+    <row r="227" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A227" s="4"/>
       <c r="B227" s="4"/>
       <c r="C227" s="4"/>
@@ -7693,7 +7761,7 @@
       <c r="AB227" s="4"/>
       <c r="AC227" s="4"/>
     </row>
-    <row r="228" ht="15.75" customHeight="1">
+    <row r="228" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A228" s="4"/>
       <c r="B228" s="4"/>
       <c r="C228" s="4"/>
@@ -7724,7 +7792,7 @@
       <c r="AB228" s="4"/>
       <c r="AC228" s="4"/>
     </row>
-    <row r="229" ht="15.75" customHeight="1">
+    <row r="229" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A229" s="4"/>
       <c r="B229" s="4"/>
       <c r="C229" s="4"/>
@@ -7755,7 +7823,7 @@
       <c r="AB229" s="4"/>
       <c r="AC229" s="4"/>
     </row>
-    <row r="230" ht="15.75" customHeight="1">
+    <row r="230" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A230" s="4"/>
       <c r="B230" s="4"/>
       <c r="C230" s="4"/>
@@ -7786,7 +7854,7 @@
       <c r="AB230" s="4"/>
       <c r="AC230" s="4"/>
     </row>
-    <row r="231" ht="15.75" customHeight="1">
+    <row r="231" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A231" s="4"/>
       <c r="B231" s="4"/>
       <c r="C231" s="4"/>
@@ -7817,7 +7885,7 @@
       <c r="AB231" s="4"/>
       <c r="AC231" s="4"/>
     </row>
-    <row r="232" ht="15.75" customHeight="1">
+    <row r="232" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A232" s="4"/>
       <c r="B232" s="4"/>
       <c r="C232" s="4"/>
@@ -7848,7 +7916,7 @@
       <c r="AB232" s="4"/>
       <c r="AC232" s="4"/>
     </row>
-    <row r="233" ht="15.75" customHeight="1">
+    <row r="233" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A233" s="4"/>
       <c r="B233" s="4"/>
       <c r="C233" s="4"/>
@@ -7879,7 +7947,7 @@
       <c r="AB233" s="4"/>
       <c r="AC233" s="4"/>
     </row>
-    <row r="234" ht="15.75" customHeight="1">
+    <row r="234" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A234" s="4"/>
       <c r="B234" s="4"/>
       <c r="C234" s="4"/>
@@ -7910,7 +7978,7 @@
       <c r="AB234" s="4"/>
       <c r="AC234" s="4"/>
     </row>
-    <row r="235" ht="15.75" customHeight="1">
+    <row r="235" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A235" s="4"/>
       <c r="B235" s="4"/>
       <c r="C235" s="4"/>
@@ -7941,7 +8009,7 @@
       <c r="AB235" s="4"/>
       <c r="AC235" s="4"/>
     </row>
-    <row r="236" ht="15.75" customHeight="1">
+    <row r="236" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A236" s="4"/>
       <c r="B236" s="4"/>
       <c r="C236" s="4"/>
@@ -7972,7 +8040,7 @@
       <c r="AB236" s="4"/>
       <c r="AC236" s="4"/>
     </row>
-    <row r="237" ht="15.75" customHeight="1">
+    <row r="237" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A237" s="4"/>
       <c r="B237" s="4"/>
       <c r="C237" s="4"/>
@@ -8003,7 +8071,7 @@
       <c r="AB237" s="4"/>
       <c r="AC237" s="4"/>
     </row>
-    <row r="238" ht="15.75" customHeight="1">
+    <row r="238" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A238" s="4"/>
       <c r="B238" s="4"/>
       <c r="C238" s="4"/>
@@ -8034,7 +8102,7 @@
       <c r="AB238" s="4"/>
       <c r="AC238" s="4"/>
     </row>
-    <row r="239" ht="15.75" customHeight="1">
+    <row r="239" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A239" s="4"/>
       <c r="B239" s="4"/>
       <c r="C239" s="4"/>
@@ -8065,7 +8133,7 @@
       <c r="AB239" s="4"/>
       <c r="AC239" s="4"/>
     </row>
-    <row r="240" ht="15.75" customHeight="1">
+    <row r="240" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A240" s="4"/>
       <c r="B240" s="4"/>
       <c r="C240" s="4"/>
@@ -8096,7 +8164,7 @@
       <c r="AB240" s="4"/>
       <c r="AC240" s="4"/>
     </row>
-    <row r="241" ht="15.75" customHeight="1">
+    <row r="241" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A241" s="4"/>
       <c r="B241" s="4"/>
       <c r="C241" s="4"/>
@@ -8127,7 +8195,7 @@
       <c r="AB241" s="4"/>
       <c r="AC241" s="4"/>
     </row>
-    <row r="242" ht="15.75" customHeight="1">
+    <row r="242" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A242" s="4"/>
       <c r="B242" s="4"/>
       <c r="C242" s="4"/>
@@ -8158,7 +8226,7 @@
       <c r="AB242" s="4"/>
       <c r="AC242" s="4"/>
     </row>
-    <row r="243" ht="15.75" customHeight="1">
+    <row r="243" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A243" s="4"/>
       <c r="B243" s="4"/>
       <c r="C243" s="4"/>
@@ -8189,7 +8257,7 @@
       <c r="AB243" s="4"/>
       <c r="AC243" s="4"/>
     </row>
-    <row r="244" ht="15.75" customHeight="1">
+    <row r="244" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A244" s="4"/>
       <c r="B244" s="4"/>
       <c r="C244" s="4"/>
@@ -8220,7 +8288,7 @@
       <c r="AB244" s="4"/>
       <c r="AC244" s="4"/>
     </row>
-    <row r="245" ht="15.75" customHeight="1">
+    <row r="245" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A245" s="4"/>
       <c r="B245" s="4"/>
       <c r="C245" s="4"/>
@@ -8251,7 +8319,7 @@
       <c r="AB245" s="4"/>
       <c r="AC245" s="4"/>
     </row>
-    <row r="246" ht="15.75" customHeight="1">
+    <row r="246" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A246" s="4"/>
       <c r="B246" s="4"/>
       <c r="C246" s="4"/>
@@ -8282,7 +8350,7 @@
       <c r="AB246" s="4"/>
       <c r="AC246" s="4"/>
     </row>
-    <row r="247" ht="15.75" customHeight="1">
+    <row r="247" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A247" s="4"/>
       <c r="B247" s="4"/>
       <c r="C247" s="4"/>
@@ -8313,7 +8381,7 @@
       <c r="AB247" s="4"/>
       <c r="AC247" s="4"/>
     </row>
-    <row r="248" ht="15.75" customHeight="1">
+    <row r="248" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A248" s="4"/>
       <c r="B248" s="4"/>
       <c r="C248" s="4"/>
@@ -8344,7 +8412,7 @@
       <c r="AB248" s="4"/>
       <c r="AC248" s="4"/>
     </row>
-    <row r="249" ht="15.75" customHeight="1">
+    <row r="249" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A249" s="4"/>
       <c r="B249" s="4"/>
       <c r="C249" s="4"/>
@@ -8375,7 +8443,7 @@
       <c r="AB249" s="4"/>
       <c r="AC249" s="4"/>
     </row>
-    <row r="250" ht="15.75" customHeight="1">
+    <row r="250" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A250" s="4"/>
       <c r="B250" s="4"/>
       <c r="C250" s="4"/>
@@ -8406,7 +8474,7 @@
       <c r="AB250" s="4"/>
       <c r="AC250" s="4"/>
     </row>
-    <row r="251" ht="15.75" customHeight="1">
+    <row r="251" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A251" s="4"/>
       <c r="B251" s="4"/>
       <c r="C251" s="4"/>
@@ -8437,7 +8505,7 @@
       <c r="AB251" s="4"/>
       <c r="AC251" s="4"/>
     </row>
-    <row r="252" ht="15.75" customHeight="1">
+    <row r="252" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A252" s="4"/>
       <c r="B252" s="4"/>
       <c r="C252" s="4"/>
@@ -8468,7 +8536,7 @@
       <c r="AB252" s="4"/>
       <c r="AC252" s="4"/>
     </row>
-    <row r="253" ht="15.75" customHeight="1">
+    <row r="253" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A253" s="4"/>
       <c r="B253" s="4"/>
       <c r="C253" s="4"/>
@@ -8499,7 +8567,7 @@
       <c r="AB253" s="4"/>
       <c r="AC253" s="4"/>
     </row>
-    <row r="254" ht="15.75" customHeight="1">
+    <row r="254" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A254" s="4"/>
       <c r="B254" s="4"/>
       <c r="C254" s="4"/>
@@ -8530,7 +8598,7 @@
       <c r="AB254" s="4"/>
       <c r="AC254" s="4"/>
     </row>
-    <row r="255" ht="15.75" customHeight="1">
+    <row r="255" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A255" s="4"/>
       <c r="B255" s="4"/>
       <c r="C255" s="4"/>
@@ -8561,7 +8629,7 @@
       <c r="AB255" s="4"/>
       <c r="AC255" s="4"/>
     </row>
-    <row r="256" ht="15.75" customHeight="1">
+    <row r="256" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A256" s="4"/>
       <c r="B256" s="4"/>
       <c r="C256" s="4"/>
@@ -8592,7 +8660,7 @@
       <c r="AB256" s="4"/>
       <c r="AC256" s="4"/>
     </row>
-    <row r="257" ht="15.75" customHeight="1">
+    <row r="257" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A257" s="4"/>
       <c r="B257" s="4"/>
       <c r="C257" s="4"/>
@@ -8623,7 +8691,7 @@
       <c r="AB257" s="4"/>
       <c r="AC257" s="4"/>
     </row>
-    <row r="258" ht="15.75" customHeight="1">
+    <row r="258" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A258" s="4"/>
       <c r="B258" s="4"/>
       <c r="C258" s="4"/>
@@ -8654,7 +8722,7 @@
       <c r="AB258" s="4"/>
       <c r="AC258" s="4"/>
     </row>
-    <row r="259" ht="15.75" customHeight="1">
+    <row r="259" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A259" s="4"/>
       <c r="B259" s="4"/>
       <c r="C259" s="4"/>
@@ -8685,7 +8753,7 @@
       <c r="AB259" s="4"/>
       <c r="AC259" s="4"/>
     </row>
-    <row r="260" ht="15.75" customHeight="1">
+    <row r="260" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A260" s="4"/>
       <c r="B260" s="4"/>
       <c r="C260" s="4"/>
@@ -8716,7 +8784,7 @@
       <c r="AB260" s="4"/>
       <c r="AC260" s="4"/>
     </row>
-    <row r="261" ht="15.75" customHeight="1">
+    <row r="261" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A261" s="4"/>
       <c r="B261" s="4"/>
       <c r="C261" s="4"/>
@@ -8747,7 +8815,7 @@
       <c r="AB261" s="4"/>
       <c r="AC261" s="4"/>
     </row>
-    <row r="262" ht="15.75" customHeight="1">
+    <row r="262" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A262" s="4"/>
       <c r="B262" s="4"/>
       <c r="C262" s="4"/>
@@ -8778,7 +8846,7 @@
       <c r="AB262" s="4"/>
       <c r="AC262" s="4"/>
     </row>
-    <row r="263" ht="15.75" customHeight="1">
+    <row r="263" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A263" s="4"/>
       <c r="B263" s="4"/>
       <c r="C263" s="4"/>
@@ -8809,7 +8877,7 @@
       <c r="AB263" s="4"/>
       <c r="AC263" s="4"/>
     </row>
-    <row r="264" ht="15.75" customHeight="1">
+    <row r="264" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A264" s="4"/>
       <c r="B264" s="4"/>
       <c r="C264" s="4"/>
@@ -8840,7 +8908,7 @@
       <c r="AB264" s="4"/>
       <c r="AC264" s="4"/>
     </row>
-    <row r="265" ht="15.75" customHeight="1">
+    <row r="265" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A265" s="4"/>
       <c r="B265" s="4"/>
       <c r="C265" s="4"/>
@@ -8871,7 +8939,7 @@
       <c r="AB265" s="4"/>
       <c r="AC265" s="4"/>
     </row>
-    <row r="266" ht="15.75" customHeight="1">
+    <row r="266" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A266" s="4"/>
       <c r="B266" s="4"/>
       <c r="C266" s="4"/>
@@ -8902,7 +8970,7 @@
       <c r="AB266" s="4"/>
       <c r="AC266" s="4"/>
     </row>
-    <row r="267" ht="15.75" customHeight="1">
+    <row r="267" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A267" s="4"/>
       <c r="B267" s="4"/>
       <c r="C267" s="4"/>
@@ -8933,7 +9001,7 @@
       <c r="AB267" s="4"/>
       <c r="AC267" s="4"/>
     </row>
-    <row r="268" ht="15.75" customHeight="1">
+    <row r="268" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A268" s="4"/>
       <c r="B268" s="4"/>
       <c r="C268" s="4"/>
@@ -8964,7 +9032,7 @@
       <c r="AB268" s="4"/>
       <c r="AC268" s="4"/>
     </row>
-    <row r="269" ht="15.75" customHeight="1">
+    <row r="269" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A269" s="4"/>
       <c r="B269" s="4"/>
       <c r="C269" s="4"/>
@@ -8995,7 +9063,7 @@
       <c r="AB269" s="4"/>
       <c r="AC269" s="4"/>
     </row>
-    <row r="270" ht="15.75" customHeight="1">
+    <row r="270" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A270" s="4"/>
       <c r="B270" s="4"/>
       <c r="C270" s="4"/>
@@ -9026,7 +9094,7 @@
       <c r="AB270" s="4"/>
       <c r="AC270" s="4"/>
     </row>
-    <row r="271" ht="15.75" customHeight="1">
+    <row r="271" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A271" s="4"/>
       <c r="B271" s="4"/>
       <c r="C271" s="4"/>
@@ -9057,7 +9125,7 @@
       <c r="AB271" s="4"/>
       <c r="AC271" s="4"/>
     </row>
-    <row r="272" ht="15.75" customHeight="1">
+    <row r="272" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A272" s="4"/>
       <c r="B272" s="4"/>
       <c r="C272" s="4"/>
@@ -9088,7 +9156,7 @@
       <c r="AB272" s="4"/>
       <c r="AC272" s="4"/>
     </row>
-    <row r="273" ht="15.75" customHeight="1">
+    <row r="273" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A273" s="4"/>
       <c r="B273" s="4"/>
       <c r="C273" s="4"/>
@@ -9119,7 +9187,7 @@
       <c r="AB273" s="4"/>
       <c r="AC273" s="4"/>
     </row>
-    <row r="274" ht="15.75" customHeight="1">
+    <row r="274" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A274" s="4"/>
       <c r="B274" s="4"/>
       <c r="C274" s="4"/>
@@ -9150,7 +9218,7 @@
       <c r="AB274" s="4"/>
       <c r="AC274" s="4"/>
     </row>
-    <row r="275" ht="15.75" customHeight="1">
+    <row r="275" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A275" s="4"/>
       <c r="B275" s="4"/>
       <c r="C275" s="4"/>
@@ -9181,7 +9249,7 @@
       <c r="AB275" s="4"/>
       <c r="AC275" s="4"/>
     </row>
-    <row r="276" ht="15.75" customHeight="1">
+    <row r="276" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A276" s="4"/>
       <c r="B276" s="4"/>
       <c r="C276" s="4"/>
@@ -9212,7 +9280,7 @@
       <c r="AB276" s="4"/>
       <c r="AC276" s="4"/>
     </row>
-    <row r="277" ht="15.75" customHeight="1">
+    <row r="277" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A277" s="4"/>
       <c r="B277" s="4"/>
       <c r="C277" s="4"/>
@@ -9243,7 +9311,7 @@
       <c r="AB277" s="4"/>
       <c r="AC277" s="4"/>
     </row>
-    <row r="278" ht="15.75" customHeight="1">
+    <row r="278" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A278" s="4"/>
       <c r="B278" s="4"/>
       <c r="C278" s="4"/>
@@ -9274,7 +9342,7 @@
       <c r="AB278" s="4"/>
       <c r="AC278" s="4"/>
     </row>
-    <row r="279" ht="15.75" customHeight="1">
+    <row r="279" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A279" s="4"/>
       <c r="B279" s="4"/>
       <c r="C279" s="4"/>
@@ -9305,7 +9373,7 @@
       <c r="AB279" s="4"/>
       <c r="AC279" s="4"/>
     </row>
-    <row r="280" ht="15.75" customHeight="1">
+    <row r="280" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A280" s="4"/>
       <c r="B280" s="4"/>
       <c r="C280" s="4"/>
@@ -9336,7 +9404,7 @@
       <c r="AB280" s="4"/>
       <c r="AC280" s="4"/>
     </row>
-    <row r="281" ht="15.75" customHeight="1">
+    <row r="281" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A281" s="4"/>
       <c r="B281" s="4"/>
       <c r="C281" s="4"/>
@@ -9367,7 +9435,7 @@
       <c r="AB281" s="4"/>
       <c r="AC281" s="4"/>
     </row>
-    <row r="282" ht="15.75" customHeight="1">
+    <row r="282" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A282" s="4"/>
       <c r="B282" s="4"/>
       <c r="C282" s="4"/>
@@ -9398,7 +9466,7 @@
       <c r="AB282" s="4"/>
       <c r="AC282" s="4"/>
     </row>
-    <row r="283" ht="15.75" customHeight="1">
+    <row r="283" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A283" s="4"/>
       <c r="B283" s="4"/>
       <c r="C283" s="4"/>
@@ -9429,7 +9497,7 @@
       <c r="AB283" s="4"/>
       <c r="AC283" s="4"/>
     </row>
-    <row r="284" ht="15.75" customHeight="1">
+    <row r="284" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A284" s="4"/>
       <c r="B284" s="4"/>
       <c r="C284" s="4"/>
@@ -9460,7 +9528,7 @@
       <c r="AB284" s="4"/>
       <c r="AC284" s="4"/>
     </row>
-    <row r="285" ht="15.75" customHeight="1">
+    <row r="285" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A285" s="4"/>
       <c r="B285" s="4"/>
       <c r="C285" s="4"/>
@@ -9491,7 +9559,7 @@
       <c r="AB285" s="4"/>
       <c r="AC285" s="4"/>
     </row>
-    <row r="286" ht="15.75" customHeight="1">
+    <row r="286" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A286" s="4"/>
       <c r="B286" s="4"/>
       <c r="C286" s="4"/>
@@ -9522,7 +9590,7 @@
       <c r="AB286" s="4"/>
       <c r="AC286" s="4"/>
     </row>
-    <row r="287" ht="15.75" customHeight="1">
+    <row r="287" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A287" s="4"/>
       <c r="B287" s="4"/>
       <c r="C287" s="4"/>
@@ -9553,7 +9621,7 @@
       <c r="AB287" s="4"/>
       <c r="AC287" s="4"/>
     </row>
-    <row r="288" ht="15.75" customHeight="1">
+    <row r="288" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A288" s="4"/>
       <c r="B288" s="4"/>
       <c r="C288" s="4"/>
@@ -9584,7 +9652,7 @@
       <c r="AB288" s="4"/>
       <c r="AC288" s="4"/>
     </row>
-    <row r="289" ht="15.75" customHeight="1">
+    <row r="289" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A289" s="4"/>
       <c r="B289" s="4"/>
       <c r="C289" s="4"/>
@@ -9615,7 +9683,7 @@
       <c r="AB289" s="4"/>
       <c r="AC289" s="4"/>
     </row>
-    <row r="290" ht="15.75" customHeight="1">
+    <row r="290" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A290" s="4"/>
       <c r="B290" s="4"/>
       <c r="C290" s="4"/>
@@ -9646,7 +9714,7 @@
       <c r="AB290" s="4"/>
       <c r="AC290" s="4"/>
     </row>
-    <row r="291" ht="15.75" customHeight="1">
+    <row r="291" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A291" s="4"/>
       <c r="B291" s="4"/>
       <c r="C291" s="4"/>
@@ -9677,7 +9745,7 @@
       <c r="AB291" s="4"/>
       <c r="AC291" s="4"/>
     </row>
-    <row r="292" ht="15.75" customHeight="1">
+    <row r="292" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A292" s="4"/>
       <c r="B292" s="4"/>
       <c r="C292" s="4"/>
@@ -9708,7 +9776,7 @@
       <c r="AB292" s="4"/>
       <c r="AC292" s="4"/>
     </row>
-    <row r="293" ht="15.75" customHeight="1">
+    <row r="293" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A293" s="4"/>
       <c r="B293" s="4"/>
       <c r="C293" s="4"/>
@@ -9739,7 +9807,7 @@
       <c r="AB293" s="4"/>
       <c r="AC293" s="4"/>
     </row>
-    <row r="294" ht="15.75" customHeight="1">
+    <row r="294" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A294" s="4"/>
       <c r="B294" s="4"/>
       <c r="C294" s="4"/>
@@ -9770,7 +9838,7 @@
       <c r="AB294" s="4"/>
       <c r="AC294" s="4"/>
     </row>
-    <row r="295" ht="15.75" customHeight="1">
+    <row r="295" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A295" s="4"/>
       <c r="B295" s="4"/>
       <c r="C295" s="4"/>
@@ -9801,7 +9869,7 @@
       <c r="AB295" s="4"/>
       <c r="AC295" s="4"/>
     </row>
-    <row r="296" ht="15.75" customHeight="1">
+    <row r="296" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A296" s="4"/>
       <c r="B296" s="4"/>
       <c r="C296" s="4"/>
@@ -9832,7 +9900,7 @@
       <c r="AB296" s="4"/>
       <c r="AC296" s="4"/>
     </row>
-    <row r="297" ht="15.75" customHeight="1">
+    <row r="297" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A297" s="4"/>
       <c r="B297" s="4"/>
       <c r="C297" s="4"/>
@@ -9863,7 +9931,7 @@
       <c r="AB297" s="4"/>
       <c r="AC297" s="4"/>
     </row>
-    <row r="298" ht="15.75" customHeight="1">
+    <row r="298" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A298" s="4"/>
       <c r="B298" s="4"/>
       <c r="C298" s="4"/>
@@ -9894,7 +9962,7 @@
       <c r="AB298" s="4"/>
       <c r="AC298" s="4"/>
     </row>
-    <row r="299" ht="15.75" customHeight="1">
+    <row r="299" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A299" s="4"/>
       <c r="B299" s="4"/>
       <c r="C299" s="4"/>
@@ -9925,7 +9993,7 @@
       <c r="AB299" s="4"/>
       <c r="AC299" s="4"/>
     </row>
-    <row r="300" ht="15.75" customHeight="1">
+    <row r="300" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A300" s="4"/>
       <c r="B300" s="4"/>
       <c r="C300" s="4"/>
@@ -9956,7 +10024,7 @@
       <c r="AB300" s="4"/>
       <c r="AC300" s="4"/>
     </row>
-    <row r="301" ht="15.75" customHeight="1">
+    <row r="301" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A301" s="4"/>
       <c r="B301" s="4"/>
       <c r="C301" s="4"/>
@@ -9987,7 +10055,7 @@
       <c r="AB301" s="4"/>
       <c r="AC301" s="4"/>
     </row>
-    <row r="302" ht="15.75" customHeight="1">
+    <row r="302" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A302" s="4"/>
       <c r="B302" s="4"/>
       <c r="C302" s="4"/>
@@ -10018,7 +10086,7 @@
       <c r="AB302" s="4"/>
       <c r="AC302" s="4"/>
     </row>
-    <row r="303" ht="15.75" customHeight="1">
+    <row r="303" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A303" s="4"/>
       <c r="B303" s="4"/>
       <c r="C303" s="4"/>
@@ -10049,7 +10117,7 @@
       <c r="AB303" s="4"/>
       <c r="AC303" s="4"/>
     </row>
-    <row r="304" ht="15.75" customHeight="1">
+    <row r="304" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A304" s="4"/>
       <c r="B304" s="4"/>
       <c r="C304" s="4"/>
@@ -10080,7 +10148,7 @@
       <c r="AB304" s="4"/>
       <c r="AC304" s="4"/>
     </row>
-    <row r="305" ht="15.75" customHeight="1">
+    <row r="305" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A305" s="4"/>
       <c r="B305" s="4"/>
       <c r="C305" s="4"/>
@@ -10111,7 +10179,7 @@
       <c r="AB305" s="4"/>
       <c r="AC305" s="4"/>
     </row>
-    <row r="306" ht="15.75" customHeight="1">
+    <row r="306" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A306" s="4"/>
       <c r="B306" s="4"/>
       <c r="C306" s="4"/>
@@ -10142,7 +10210,7 @@
       <c r="AB306" s="4"/>
       <c r="AC306" s="4"/>
     </row>
-    <row r="307" ht="15.75" customHeight="1">
+    <row r="307" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A307" s="4"/>
       <c r="B307" s="4"/>
       <c r="C307" s="4"/>
@@ -10173,7 +10241,7 @@
       <c r="AB307" s="4"/>
       <c r="AC307" s="4"/>
     </row>
-    <row r="308" ht="15.75" customHeight="1">
+    <row r="308" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A308" s="4"/>
       <c r="B308" s="4"/>
       <c r="C308" s="4"/>
@@ -10204,7 +10272,7 @@
       <c r="AB308" s="4"/>
       <c r="AC308" s="4"/>
     </row>
-    <row r="309" ht="15.75" customHeight="1">
+    <row r="309" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A309" s="4"/>
       <c r="B309" s="4"/>
       <c r="C309" s="4"/>
@@ -10235,7 +10303,7 @@
       <c r="AB309" s="4"/>
       <c r="AC309" s="4"/>
     </row>
-    <row r="310" ht="15.75" customHeight="1">
+    <row r="310" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A310" s="4"/>
       <c r="B310" s="4"/>
       <c r="C310" s="4"/>
@@ -10266,7 +10334,7 @@
       <c r="AB310" s="4"/>
       <c r="AC310" s="4"/>
     </row>
-    <row r="311" ht="15.75" customHeight="1">
+    <row r="311" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A311" s="4"/>
       <c r="B311" s="4"/>
       <c r="C311" s="4"/>
@@ -10297,7 +10365,7 @@
       <c r="AB311" s="4"/>
       <c r="AC311" s="4"/>
     </row>
-    <row r="312" ht="15.75" customHeight="1">
+    <row r="312" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A312" s="4"/>
       <c r="B312" s="4"/>
       <c r="C312" s="4"/>
@@ -10328,7 +10396,7 @@
       <c r="AB312" s="4"/>
       <c r="AC312" s="4"/>
     </row>
-    <row r="313" ht="15.75" customHeight="1">
+    <row r="313" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A313" s="4"/>
       <c r="B313" s="4"/>
       <c r="C313" s="4"/>
@@ -10359,7 +10427,7 @@
       <c r="AB313" s="4"/>
       <c r="AC313" s="4"/>
     </row>
-    <row r="314" ht="15.75" customHeight="1">
+    <row r="314" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A314" s="4"/>
       <c r="B314" s="4"/>
       <c r="C314" s="4"/>
@@ -10390,7 +10458,7 @@
       <c r="AB314" s="4"/>
       <c r="AC314" s="4"/>
     </row>
-    <row r="315" ht="15.75" customHeight="1">
+    <row r="315" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A315" s="4"/>
       <c r="B315" s="4"/>
       <c r="C315" s="4"/>
@@ -10421,7 +10489,7 @@
       <c r="AB315" s="4"/>
       <c r="AC315" s="4"/>
     </row>
-    <row r="316" ht="15.75" customHeight="1">
+    <row r="316" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A316" s="4"/>
       <c r="B316" s="4"/>
       <c r="C316" s="4"/>
@@ -10452,7 +10520,7 @@
       <c r="AB316" s="4"/>
       <c r="AC316" s="4"/>
     </row>
-    <row r="317" ht="15.75" customHeight="1">
+    <row r="317" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A317" s="4"/>
       <c r="B317" s="4"/>
       <c r="C317" s="4"/>
@@ -10483,7 +10551,7 @@
       <c r="AB317" s="4"/>
       <c r="AC317" s="4"/>
     </row>
-    <row r="318" ht="15.75" customHeight="1">
+    <row r="318" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A318" s="4"/>
       <c r="B318" s="4"/>
       <c r="C318" s="4"/>
@@ -10514,7 +10582,7 @@
       <c r="AB318" s="4"/>
       <c r="AC318" s="4"/>
     </row>
-    <row r="319" ht="15.75" customHeight="1">
+    <row r="319" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A319" s="4"/>
       <c r="B319" s="4"/>
       <c r="C319" s="4"/>
@@ -10545,7 +10613,7 @@
       <c r="AB319" s="4"/>
       <c r="AC319" s="4"/>
     </row>
-    <row r="320" ht="15.75" customHeight="1">
+    <row r="320" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A320" s="4"/>
       <c r="B320" s="4"/>
       <c r="C320" s="4"/>
@@ -10576,7 +10644,7 @@
       <c r="AB320" s="4"/>
       <c r="AC320" s="4"/>
     </row>
-    <row r="321" ht="15.75" customHeight="1">
+    <row r="321" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A321" s="4"/>
       <c r="B321" s="4"/>
       <c r="C321" s="4"/>
@@ -10607,7 +10675,7 @@
       <c r="AB321" s="4"/>
       <c r="AC321" s="4"/>
     </row>
-    <row r="322" ht="15.75" customHeight="1">
+    <row r="322" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A322" s="4"/>
       <c r="B322" s="4"/>
       <c r="C322" s="4"/>
@@ -10638,7 +10706,7 @@
       <c r="AB322" s="4"/>
       <c r="AC322" s="4"/>
     </row>
-    <row r="323" ht="15.75" customHeight="1">
+    <row r="323" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A323" s="4"/>
       <c r="B323" s="4"/>
       <c r="C323" s="4"/>
@@ -10669,7 +10737,7 @@
       <c r="AB323" s="4"/>
       <c r="AC323" s="4"/>
     </row>
-    <row r="324" ht="15.75" customHeight="1">
+    <row r="324" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A324" s="4"/>
       <c r="B324" s="4"/>
       <c r="C324" s="4"/>
@@ -10700,7 +10768,7 @@
       <c r="AB324" s="4"/>
       <c r="AC324" s="4"/>
     </row>
-    <row r="325" ht="15.75" customHeight="1">
+    <row r="325" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A325" s="4"/>
       <c r="B325" s="4"/>
       <c r="C325" s="4"/>
@@ -10731,7 +10799,7 @@
       <c r="AB325" s="4"/>
       <c r="AC325" s="4"/>
     </row>
-    <row r="326" ht="15.75" customHeight="1">
+    <row r="326" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A326" s="4"/>
       <c r="B326" s="4"/>
       <c r="C326" s="4"/>
@@ -10762,7 +10830,7 @@
       <c r="AB326" s="4"/>
       <c r="AC326" s="4"/>
     </row>
-    <row r="327" ht="15.75" customHeight="1">
+    <row r="327" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A327" s="4"/>
       <c r="B327" s="4"/>
       <c r="C327" s="4"/>
@@ -10793,7 +10861,7 @@
       <c r="AB327" s="4"/>
       <c r="AC327" s="4"/>
     </row>
-    <row r="328" ht="15.75" customHeight="1">
+    <row r="328" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A328" s="4"/>
       <c r="B328" s="4"/>
       <c r="C328" s="4"/>
@@ -10824,7 +10892,7 @@
       <c r="AB328" s="4"/>
       <c r="AC328" s="4"/>
     </row>
-    <row r="329" ht="15.75" customHeight="1">
+    <row r="329" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A329" s="4"/>
       <c r="B329" s="4"/>
       <c r="C329" s="4"/>
@@ -10855,7 +10923,7 @@
       <c r="AB329" s="4"/>
       <c r="AC329" s="4"/>
     </row>
-    <row r="330" ht="15.75" customHeight="1">
+    <row r="330" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A330" s="4"/>
       <c r="B330" s="4"/>
       <c r="C330" s="4"/>
@@ -10886,7 +10954,7 @@
       <c r="AB330" s="4"/>
       <c r="AC330" s="4"/>
     </row>
-    <row r="331" ht="15.75" customHeight="1">
+    <row r="331" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A331" s="4"/>
       <c r="B331" s="4"/>
       <c r="C331" s="4"/>
@@ -10917,7 +10985,7 @@
       <c r="AB331" s="4"/>
       <c r="AC331" s="4"/>
     </row>
-    <row r="332" ht="15.75" customHeight="1">
+    <row r="332" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A332" s="4"/>
       <c r="B332" s="4"/>
       <c r="C332" s="4"/>
@@ -10948,7 +11016,7 @@
       <c r="AB332" s="4"/>
       <c r="AC332" s="4"/>
     </row>
-    <row r="333" ht="15.75" customHeight="1">
+    <row r="333" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A333" s="4"/>
       <c r="B333" s="4"/>
       <c r="C333" s="4"/>
@@ -10979,7 +11047,7 @@
       <c r="AB333" s="4"/>
       <c r="AC333" s="4"/>
     </row>
-    <row r="334" ht="15.75" customHeight="1">
+    <row r="334" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A334" s="4"/>
       <c r="B334" s="4"/>
       <c r="C334" s="4"/>
@@ -11010,7 +11078,7 @@
       <c r="AB334" s="4"/>
       <c r="AC334" s="4"/>
     </row>
-    <row r="335" ht="15.75" customHeight="1">
+    <row r="335" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A335" s="4"/>
       <c r="B335" s="4"/>
       <c r="C335" s="4"/>
@@ -11041,7 +11109,7 @@
       <c r="AB335" s="4"/>
       <c r="AC335" s="4"/>
     </row>
-    <row r="336" ht="15.75" customHeight="1">
+    <row r="336" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A336" s="4"/>
       <c r="B336" s="4"/>
       <c r="C336" s="4"/>
@@ -11072,7 +11140,7 @@
       <c r="AB336" s="4"/>
       <c r="AC336" s="4"/>
     </row>
-    <row r="337" ht="15.75" customHeight="1">
+    <row r="337" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A337" s="4"/>
       <c r="B337" s="4"/>
       <c r="C337" s="4"/>
@@ -11103,7 +11171,7 @@
       <c r="AB337" s="4"/>
       <c r="AC337" s="4"/>
     </row>
-    <row r="338" ht="15.75" customHeight="1">
+    <row r="338" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A338" s="4"/>
       <c r="B338" s="4"/>
       <c r="C338" s="4"/>
@@ -11134,7 +11202,7 @@
       <c r="AB338" s="4"/>
       <c r="AC338" s="4"/>
     </row>
-    <row r="339" ht="15.75" customHeight="1">
+    <row r="339" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A339" s="4"/>
       <c r="B339" s="4"/>
       <c r="C339" s="4"/>
@@ -11165,7 +11233,7 @@
       <c r="AB339" s="4"/>
       <c r="AC339" s="4"/>
     </row>
-    <row r="340" ht="15.75" customHeight="1">
+    <row r="340" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A340" s="4"/>
       <c r="B340" s="4"/>
       <c r="C340" s="4"/>
@@ -11196,7 +11264,7 @@
       <c r="AB340" s="4"/>
       <c r="AC340" s="4"/>
     </row>
-    <row r="341" ht="15.75" customHeight="1">
+    <row r="341" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A341" s="4"/>
       <c r="B341" s="4"/>
       <c r="C341" s="4"/>
@@ -11227,7 +11295,7 @@
       <c r="AB341" s="4"/>
       <c r="AC341" s="4"/>
     </row>
-    <row r="342" ht="15.75" customHeight="1">
+    <row r="342" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A342" s="4"/>
       <c r="B342" s="4"/>
       <c r="C342" s="4"/>
@@ -11258,7 +11326,7 @@
       <c r="AB342" s="4"/>
       <c r="AC342" s="4"/>
     </row>
-    <row r="343" ht="15.75" customHeight="1">
+    <row r="343" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A343" s="4"/>
       <c r="B343" s="4"/>
       <c r="C343" s="4"/>
@@ -11289,7 +11357,7 @@
       <c r="AB343" s="4"/>
       <c r="AC343" s="4"/>
     </row>
-    <row r="344" ht="15.75" customHeight="1">
+    <row r="344" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A344" s="4"/>
       <c r="B344" s="4"/>
       <c r="C344" s="4"/>
@@ -11320,7 +11388,7 @@
       <c r="AB344" s="4"/>
       <c r="AC344" s="4"/>
     </row>
-    <row r="345" ht="15.75" customHeight="1">
+    <row r="345" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A345" s="4"/>
       <c r="B345" s="4"/>
       <c r="C345" s="4"/>
@@ -11351,7 +11419,7 @@
       <c r="AB345" s="4"/>
       <c r="AC345" s="4"/>
     </row>
-    <row r="346" ht="15.75" customHeight="1">
+    <row r="346" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A346" s="4"/>
       <c r="B346" s="4"/>
       <c r="C346" s="4"/>
@@ -11382,7 +11450,7 @@
       <c r="AB346" s="4"/>
       <c r="AC346" s="4"/>
     </row>
-    <row r="347" ht="15.75" customHeight="1">
+    <row r="347" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A347" s="4"/>
       <c r="B347" s="4"/>
       <c r="C347" s="4"/>
@@ -11413,7 +11481,7 @@
       <c r="AB347" s="4"/>
       <c r="AC347" s="4"/>
     </row>
-    <row r="348" ht="15.75" customHeight="1">
+    <row r="348" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A348" s="4"/>
       <c r="B348" s="4"/>
       <c r="C348" s="4"/>
@@ -11444,7 +11512,7 @@
       <c r="AB348" s="4"/>
       <c r="AC348" s="4"/>
     </row>
-    <row r="349" ht="15.75" customHeight="1">
+    <row r="349" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A349" s="4"/>
       <c r="B349" s="4"/>
       <c r="C349" s="4"/>
@@ -11475,7 +11543,7 @@
       <c r="AB349" s="4"/>
       <c r="AC349" s="4"/>
     </row>
-    <row r="350" ht="15.75" customHeight="1">
+    <row r="350" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A350" s="4"/>
       <c r="B350" s="4"/>
       <c r="C350" s="4"/>
@@ -11506,7 +11574,7 @@
       <c r="AB350" s="4"/>
       <c r="AC350" s="4"/>
     </row>
-    <row r="351" ht="15.75" customHeight="1">
+    <row r="351" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A351" s="4"/>
       <c r="B351" s="4"/>
       <c r="C351" s="4"/>
@@ -11537,7 +11605,7 @@
       <c r="AB351" s="4"/>
       <c r="AC351" s="4"/>
     </row>
-    <row r="352" ht="15.75" customHeight="1">
+    <row r="352" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A352" s="4"/>
       <c r="B352" s="4"/>
       <c r="C352" s="4"/>
@@ -11568,7 +11636,7 @@
       <c r="AB352" s="4"/>
       <c r="AC352" s="4"/>
     </row>
-    <row r="353" ht="15.75" customHeight="1">
+    <row r="353" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A353" s="4"/>
       <c r="B353" s="4"/>
       <c r="C353" s="4"/>
@@ -11599,7 +11667,7 @@
       <c r="AB353" s="4"/>
       <c r="AC353" s="4"/>
     </row>
-    <row r="354" ht="15.75" customHeight="1">
+    <row r="354" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A354" s="4"/>
       <c r="B354" s="4"/>
       <c r="C354" s="4"/>
@@ -11630,7 +11698,7 @@
       <c r="AB354" s="4"/>
       <c r="AC354" s="4"/>
     </row>
-    <row r="355" ht="15.75" customHeight="1">
+    <row r="355" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A355" s="4"/>
       <c r="B355" s="4"/>
       <c r="C355" s="4"/>
@@ -11661,7 +11729,7 @@
       <c r="AB355" s="4"/>
       <c r="AC355" s="4"/>
     </row>
-    <row r="356" ht="15.75" customHeight="1">
+    <row r="356" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A356" s="4"/>
       <c r="B356" s="4"/>
       <c r="C356" s="4"/>
@@ -11692,7 +11760,7 @@
       <c r="AB356" s="4"/>
       <c r="AC356" s="4"/>
     </row>
-    <row r="357" ht="15.75" customHeight="1">
+    <row r="357" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A357" s="4"/>
       <c r="B357" s="4"/>
       <c r="C357" s="4"/>
@@ -11723,7 +11791,7 @@
       <c r="AB357" s="4"/>
       <c r="AC357" s="4"/>
     </row>
-    <row r="358" ht="15.75" customHeight="1">
+    <row r="358" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A358" s="4"/>
       <c r="B358" s="4"/>
       <c r="C358" s="4"/>
@@ -11754,7 +11822,7 @@
       <c r="AB358" s="4"/>
       <c r="AC358" s="4"/>
     </row>
-    <row r="359" ht="15.75" customHeight="1">
+    <row r="359" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A359" s="4"/>
       <c r="B359" s="4"/>
       <c r="C359" s="4"/>
@@ -11785,7 +11853,7 @@
       <c r="AB359" s="4"/>
       <c r="AC359" s="4"/>
     </row>
-    <row r="360" ht="15.75" customHeight="1">
+    <row r="360" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A360" s="4"/>
       <c r="B360" s="4"/>
       <c r="C360" s="4"/>
@@ -11816,7 +11884,7 @@
       <c r="AB360" s="4"/>
       <c r="AC360" s="4"/>
     </row>
-    <row r="361" ht="15.75" customHeight="1">
+    <row r="361" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A361" s="4"/>
       <c r="B361" s="4"/>
       <c r="C361" s="4"/>
@@ -11847,7 +11915,7 @@
       <c r="AB361" s="4"/>
       <c r="AC361" s="4"/>
     </row>
-    <row r="362" ht="15.75" customHeight="1">
+    <row r="362" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A362" s="4"/>
       <c r="B362" s="4"/>
       <c r="C362" s="4"/>
@@ -11878,7 +11946,7 @@
       <c r="AB362" s="4"/>
       <c r="AC362" s="4"/>
     </row>
-    <row r="363" ht="15.75" customHeight="1">
+    <row r="363" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A363" s="4"/>
       <c r="B363" s="4"/>
       <c r="C363" s="4"/>
@@ -11909,7 +11977,7 @@
       <c r="AB363" s="4"/>
       <c r="AC363" s="4"/>
     </row>
-    <row r="364" ht="15.75" customHeight="1">
+    <row r="364" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A364" s="4"/>
       <c r="B364" s="4"/>
       <c r="C364" s="4"/>
@@ -11940,7 +12008,7 @@
       <c r="AB364" s="4"/>
       <c r="AC364" s="4"/>
     </row>
-    <row r="365" ht="15.75" customHeight="1">
+    <row r="365" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A365" s="4"/>
       <c r="B365" s="4"/>
       <c r="C365" s="4"/>
@@ -11971,7 +12039,7 @@
       <c r="AB365" s="4"/>
       <c r="AC365" s="4"/>
     </row>
-    <row r="366" ht="15.75" customHeight="1">
+    <row r="366" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A366" s="4"/>
       <c r="B366" s="4"/>
       <c r="C366" s="4"/>
@@ -12002,7 +12070,7 @@
       <c r="AB366" s="4"/>
       <c r="AC366" s="4"/>
     </row>
-    <row r="367" ht="15.75" customHeight="1">
+    <row r="367" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A367" s="4"/>
       <c r="B367" s="4"/>
       <c r="C367" s="4"/>
@@ -12033,7 +12101,7 @@
       <c r="AB367" s="4"/>
       <c r="AC367" s="4"/>
     </row>
-    <row r="368" ht="15.75" customHeight="1">
+    <row r="368" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A368" s="4"/>
       <c r="B368" s="4"/>
       <c r="C368" s="4"/>
@@ -12064,7 +12132,7 @@
       <c r="AB368" s="4"/>
       <c r="AC368" s="4"/>
     </row>
-    <row r="369" ht="15.75" customHeight="1">
+    <row r="369" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A369" s="4"/>
       <c r="B369" s="4"/>
       <c r="C369" s="4"/>
@@ -12095,7 +12163,7 @@
       <c r="AB369" s="4"/>
       <c r="AC369" s="4"/>
     </row>
-    <row r="370" ht="15.75" customHeight="1">
+    <row r="370" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A370" s="4"/>
       <c r="B370" s="4"/>
       <c r="C370" s="4"/>
@@ -12126,7 +12194,7 @@
       <c r="AB370" s="4"/>
       <c r="AC370" s="4"/>
     </row>
-    <row r="371" ht="15.75" customHeight="1">
+    <row r="371" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A371" s="4"/>
       <c r="B371" s="4"/>
       <c r="C371" s="4"/>
@@ -12157,7 +12225,7 @@
       <c r="AB371" s="4"/>
       <c r="AC371" s="4"/>
     </row>
-    <row r="372" ht="15.75" customHeight="1">
+    <row r="372" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A372" s="4"/>
       <c r="B372" s="4"/>
       <c r="C372" s="4"/>
@@ -12188,7 +12256,7 @@
       <c r="AB372" s="4"/>
       <c r="AC372" s="4"/>
     </row>
-    <row r="373" ht="15.75" customHeight="1">
+    <row r="373" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A373" s="4"/>
       <c r="B373" s="4"/>
       <c r="C373" s="4"/>
@@ -12219,7 +12287,7 @@
       <c r="AB373" s="4"/>
       <c r="AC373" s="4"/>
     </row>
-    <row r="374" ht="15.75" customHeight="1">
+    <row r="374" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A374" s="4"/>
       <c r="B374" s="4"/>
       <c r="C374" s="4"/>
@@ -12250,7 +12318,7 @@
       <c r="AB374" s="4"/>
       <c r="AC374" s="4"/>
     </row>
-    <row r="375" ht="15.75" customHeight="1">
+    <row r="375" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A375" s="4"/>
       <c r="B375" s="4"/>
       <c r="C375" s="4"/>
@@ -12281,7 +12349,7 @@
       <c r="AB375" s="4"/>
       <c r="AC375" s="4"/>
     </row>
-    <row r="376" ht="15.75" customHeight="1">
+    <row r="376" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A376" s="4"/>
       <c r="B376" s="4"/>
       <c r="C376" s="4"/>
@@ -12312,7 +12380,7 @@
       <c r="AB376" s="4"/>
       <c r="AC376" s="4"/>
     </row>
-    <row r="377" ht="15.75" customHeight="1">
+    <row r="377" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A377" s="4"/>
       <c r="B377" s="4"/>
       <c r="C377" s="4"/>
@@ -12343,7 +12411,7 @@
       <c r="AB377" s="4"/>
       <c r="AC377" s="4"/>
     </row>
-    <row r="378" ht="15.75" customHeight="1">
+    <row r="378" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A378" s="4"/>
       <c r="B378" s="4"/>
       <c r="C378" s="4"/>
@@ -12374,7 +12442,7 @@
       <c r="AB378" s="4"/>
       <c r="AC378" s="4"/>
     </row>
-    <row r="379" ht="15.75" customHeight="1">
+    <row r="379" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A379" s="4"/>
       <c r="B379" s="4"/>
       <c r="C379" s="4"/>
@@ -12405,7 +12473,7 @@
       <c r="AB379" s="4"/>
       <c r="AC379" s="4"/>
     </row>
-    <row r="380" ht="15.75" customHeight="1">
+    <row r="380" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A380" s="4"/>
       <c r="B380" s="4"/>
       <c r="C380" s="4"/>
@@ -12436,7 +12504,7 @@
       <c r="AB380" s="4"/>
       <c r="AC380" s="4"/>
     </row>
-    <row r="381" ht="15.75" customHeight="1">
+    <row r="381" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A381" s="4"/>
       <c r="B381" s="4"/>
       <c r="C381" s="4"/>
@@ -12467,7 +12535,7 @@
       <c r="AB381" s="4"/>
       <c r="AC381" s="4"/>
     </row>
-    <row r="382" ht="15.75" customHeight="1">
+    <row r="382" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A382" s="4"/>
       <c r="B382" s="4"/>
       <c r="C382" s="4"/>
@@ -12498,7 +12566,7 @@
       <c r="AB382" s="4"/>
       <c r="AC382" s="4"/>
     </row>
-    <row r="383" ht="15.75" customHeight="1">
+    <row r="383" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A383" s="4"/>
       <c r="B383" s="4"/>
       <c r="C383" s="4"/>
@@ -12529,7 +12597,7 @@
       <c r="AB383" s="4"/>
       <c r="AC383" s="4"/>
     </row>
-    <row r="384" ht="15.75" customHeight="1">
+    <row r="384" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A384" s="4"/>
       <c r="B384" s="4"/>
       <c r="C384" s="4"/>
@@ -12560,7 +12628,7 @@
       <c r="AB384" s="4"/>
       <c r="AC384" s="4"/>
     </row>
-    <row r="385" ht="15.75" customHeight="1">
+    <row r="385" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A385" s="4"/>
       <c r="B385" s="4"/>
       <c r="C385" s="4"/>
@@ -12591,7 +12659,7 @@
       <c r="AB385" s="4"/>
       <c r="AC385" s="4"/>
     </row>
-    <row r="386" ht="15.75" customHeight="1">
+    <row r="386" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A386" s="4"/>
       <c r="B386" s="4"/>
       <c r="C386" s="4"/>
@@ -12622,7 +12690,7 @@
       <c r="AB386" s="4"/>
       <c r="AC386" s="4"/>
     </row>
-    <row r="387" ht="15.75" customHeight="1">
+    <row r="387" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A387" s="4"/>
       <c r="B387" s="4"/>
       <c r="C387" s="4"/>
@@ -12653,7 +12721,7 @@
       <c r="AB387" s="4"/>
       <c r="AC387" s="4"/>
     </row>
-    <row r="388" ht="15.75" customHeight="1">
+    <row r="388" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A388" s="4"/>
       <c r="B388" s="4"/>
       <c r="C388" s="4"/>
@@ -12684,7 +12752,7 @@
       <c r="AB388" s="4"/>
       <c r="AC388" s="4"/>
     </row>
-    <row r="389" ht="15.75" customHeight="1">
+    <row r="389" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A389" s="4"/>
       <c r="B389" s="4"/>
       <c r="C389" s="4"/>
@@ -12715,7 +12783,7 @@
       <c r="AB389" s="4"/>
       <c r="AC389" s="4"/>
     </row>
-    <row r="390" ht="15.75" customHeight="1">
+    <row r="390" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A390" s="4"/>
       <c r="B390" s="4"/>
       <c r="C390" s="4"/>
@@ -12746,7 +12814,7 @@
       <c r="AB390" s="4"/>
       <c r="AC390" s="4"/>
     </row>
-    <row r="391" ht="15.75" customHeight="1">
+    <row r="391" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A391" s="4"/>
       <c r="B391" s="4"/>
       <c r="C391" s="4"/>
@@ -12777,7 +12845,7 @@
       <c r="AB391" s="4"/>
       <c r="AC391" s="4"/>
     </row>
-    <row r="392" ht="15.75" customHeight="1">
+    <row r="392" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A392" s="4"/>
       <c r="B392" s="4"/>
       <c r="C392" s="4"/>
@@ -12808,7 +12876,7 @@
       <c r="AB392" s="4"/>
       <c r="AC392" s="4"/>
     </row>
-    <row r="393" ht="15.75" customHeight="1">
+    <row r="393" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A393" s="4"/>
       <c r="B393" s="4"/>
       <c r="C393" s="4"/>
@@ -12839,7 +12907,7 @@
       <c r="AB393" s="4"/>
       <c r="AC393" s="4"/>
     </row>
-    <row r="394" ht="15.75" customHeight="1">
+    <row r="394" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A394" s="4"/>
       <c r="B394" s="4"/>
       <c r="C394" s="4"/>
@@ -12870,7 +12938,7 @@
       <c r="AB394" s="4"/>
       <c r="AC394" s="4"/>
     </row>
-    <row r="395" ht="15.75" customHeight="1">
+    <row r="395" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A395" s="4"/>
       <c r="B395" s="4"/>
       <c r="C395" s="4"/>
@@ -12901,7 +12969,7 @@
       <c r="AB395" s="4"/>
       <c r="AC395" s="4"/>
     </row>
-    <row r="396" ht="15.75" customHeight="1">
+    <row r="396" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A396" s="4"/>
       <c r="B396" s="4"/>
       <c r="C396" s="4"/>
@@ -12932,7 +13000,7 @@
       <c r="AB396" s="4"/>
       <c r="AC396" s="4"/>
     </row>
-    <row r="397" ht="15.75" customHeight="1">
+    <row r="397" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A397" s="4"/>
       <c r="B397" s="4"/>
       <c r="C397" s="4"/>
@@ -12963,7 +13031,7 @@
       <c r="AB397" s="4"/>
       <c r="AC397" s="4"/>
     </row>
-    <row r="398" ht="15.75" customHeight="1">
+    <row r="398" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A398" s="4"/>
       <c r="B398" s="4"/>
       <c r="C398" s="4"/>
@@ -12994,7 +13062,7 @@
       <c r="AB398" s="4"/>
       <c r="AC398" s="4"/>
     </row>
-    <row r="399" ht="15.75" customHeight="1">
+    <row r="399" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A399" s="4"/>
       <c r="B399" s="4"/>
       <c r="C399" s="4"/>
@@ -13025,7 +13093,7 @@
       <c r="AB399" s="4"/>
       <c r="AC399" s="4"/>
     </row>
-    <row r="400" ht="15.75" customHeight="1">
+    <row r="400" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A400" s="4"/>
       <c r="B400" s="4"/>
       <c r="C400" s="4"/>
@@ -13056,7 +13124,7 @@
       <c r="AB400" s="4"/>
       <c r="AC400" s="4"/>
     </row>
-    <row r="401" ht="15.75" customHeight="1">
+    <row r="401" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A401" s="4"/>
       <c r="B401" s="4"/>
       <c r="C401" s="4"/>
@@ -13087,7 +13155,7 @@
       <c r="AB401" s="4"/>
       <c r="AC401" s="4"/>
     </row>
-    <row r="402" ht="15.75" customHeight="1">
+    <row r="402" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A402" s="4"/>
       <c r="B402" s="4"/>
       <c r="C402" s="4"/>
@@ -13118,7 +13186,7 @@
       <c r="AB402" s="4"/>
       <c r="AC402" s="4"/>
     </row>
-    <row r="403" ht="15.75" customHeight="1">
+    <row r="403" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A403" s="4"/>
       <c r="B403" s="4"/>
       <c r="C403" s="4"/>
@@ -13149,7 +13217,7 @@
       <c r="AB403" s="4"/>
       <c r="AC403" s="4"/>
     </row>
-    <row r="404" ht="15.75" customHeight="1">
+    <row r="404" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A404" s="4"/>
       <c r="B404" s="4"/>
       <c r="C404" s="4"/>
@@ -13180,7 +13248,7 @@
       <c r="AB404" s="4"/>
       <c r="AC404" s="4"/>
     </row>
-    <row r="405" ht="15.75" customHeight="1">
+    <row r="405" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A405" s="4"/>
       <c r="B405" s="4"/>
       <c r="C405" s="4"/>
@@ -13211,7 +13279,7 @@
       <c r="AB405" s="4"/>
       <c r="AC405" s="4"/>
     </row>
-    <row r="406" ht="15.75" customHeight="1">
+    <row r="406" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A406" s="4"/>
       <c r="B406" s="4"/>
       <c r="C406" s="4"/>
@@ -13242,7 +13310,7 @@
       <c r="AB406" s="4"/>
       <c r="AC406" s="4"/>
     </row>
-    <row r="407" ht="15.75" customHeight="1">
+    <row r="407" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A407" s="4"/>
       <c r="B407" s="4"/>
       <c r="C407" s="4"/>
@@ -13273,7 +13341,7 @@
       <c r="AB407" s="4"/>
       <c r="AC407" s="4"/>
     </row>
-    <row r="408" ht="15.75" customHeight="1">
+    <row r="408" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A408" s="4"/>
       <c r="B408" s="4"/>
       <c r="C408" s="4"/>
@@ -13304,7 +13372,7 @@
       <c r="AB408" s="4"/>
       <c r="AC408" s="4"/>
     </row>
-    <row r="409" ht="15.75" customHeight="1">
+    <row r="409" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A409" s="4"/>
       <c r="B409" s="4"/>
       <c r="C409" s="4"/>
@@ -13335,7 +13403,7 @@
       <c r="AB409" s="4"/>
       <c r="AC409" s="4"/>
     </row>
-    <row r="410" ht="15.75" customHeight="1">
+    <row r="410" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A410" s="4"/>
       <c r="B410" s="4"/>
       <c r="C410" s="4"/>
@@ -13366,7 +13434,7 @@
       <c r="AB410" s="4"/>
       <c r="AC410" s="4"/>
     </row>
-    <row r="411" ht="15.75" customHeight="1">
+    <row r="411" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A411" s="4"/>
       <c r="B411" s="4"/>
       <c r="C411" s="4"/>
@@ -13397,7 +13465,7 @@
       <c r="AB411" s="4"/>
       <c r="AC411" s="4"/>
     </row>
-    <row r="412" ht="15.75" customHeight="1">
+    <row r="412" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A412" s="4"/>
       <c r="B412" s="4"/>
       <c r="C412" s="4"/>
@@ -13428,7 +13496,7 @@
       <c r="AB412" s="4"/>
       <c r="AC412" s="4"/>
     </row>
-    <row r="413" ht="15.75" customHeight="1">
+    <row r="413" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A413" s="4"/>
       <c r="B413" s="4"/>
       <c r="C413" s="4"/>
@@ -13459,7 +13527,7 @@
       <c r="AB413" s="4"/>
       <c r="AC413" s="4"/>
     </row>
-    <row r="414" ht="15.75" customHeight="1">
+    <row r="414" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A414" s="4"/>
       <c r="B414" s="4"/>
       <c r="C414" s="4"/>
@@ -13490,7 +13558,7 @@
       <c r="AB414" s="4"/>
       <c r="AC414" s="4"/>
     </row>
-    <row r="415" ht="15.75" customHeight="1">
+    <row r="415" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A415" s="4"/>
       <c r="B415" s="4"/>
       <c r="C415" s="4"/>
@@ -13521,7 +13589,7 @@
       <c r="AB415" s="4"/>
       <c r="AC415" s="4"/>
     </row>
-    <row r="416" ht="15.75" customHeight="1">
+    <row r="416" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A416" s="4"/>
       <c r="B416" s="4"/>
       <c r="C416" s="4"/>
@@ -13552,7 +13620,7 @@
       <c r="AB416" s="4"/>
       <c r="AC416" s="4"/>
     </row>
-    <row r="417" ht="15.75" customHeight="1">
+    <row r="417" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A417" s="4"/>
       <c r="B417" s="4"/>
       <c r="C417" s="4"/>
@@ -13583,7 +13651,7 @@
       <c r="AB417" s="4"/>
       <c r="AC417" s="4"/>
     </row>
-    <row r="418" ht="15.75" customHeight="1">
+    <row r="418" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A418" s="4"/>
       <c r="B418" s="4"/>
       <c r="C418" s="4"/>
@@ -13614,7 +13682,7 @@
       <c r="AB418" s="4"/>
       <c r="AC418" s="4"/>
     </row>
-    <row r="419" ht="15.75" customHeight="1">
+    <row r="419" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A419" s="4"/>
       <c r="B419" s="4"/>
       <c r="C419" s="4"/>
@@ -13645,7 +13713,7 @@
       <c r="AB419" s="4"/>
       <c r="AC419" s="4"/>
     </row>
-    <row r="420" ht="15.75" customHeight="1">
+    <row r="420" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A420" s="4"/>
       <c r="B420" s="4"/>
       <c r="C420" s="4"/>
@@ -13676,7 +13744,7 @@
       <c r="AB420" s="4"/>
       <c r="AC420" s="4"/>
     </row>
-    <row r="421" ht="15.75" customHeight="1">
+    <row r="421" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A421" s="4"/>
       <c r="B421" s="4"/>
       <c r="C421" s="4"/>
@@ -13707,7 +13775,7 @@
       <c r="AB421" s="4"/>
       <c r="AC421" s="4"/>
     </row>
-    <row r="422" ht="15.75" customHeight="1">
+    <row r="422" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A422" s="4"/>
       <c r="B422" s="4"/>
       <c r="C422" s="4"/>
@@ -13738,7 +13806,7 @@
       <c r="AB422" s="4"/>
       <c r="AC422" s="4"/>
     </row>
-    <row r="423" ht="15.75" customHeight="1">
+    <row r="423" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A423" s="4"/>
       <c r="B423" s="4"/>
       <c r="C423" s="4"/>
@@ -13769,7 +13837,7 @@
       <c r="AB423" s="4"/>
       <c r="AC423" s="4"/>
     </row>
-    <row r="424" ht="15.75" customHeight="1">
+    <row r="424" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A424" s="4"/>
       <c r="B424" s="4"/>
       <c r="C424" s="4"/>
@@ -13800,7 +13868,7 @@
       <c r="AB424" s="4"/>
       <c r="AC424" s="4"/>
     </row>
-    <row r="425" ht="15.75" customHeight="1">
+    <row r="425" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A425" s="4"/>
       <c r="B425" s="4"/>
       <c r="C425" s="4"/>
@@ -13831,7 +13899,7 @@
       <c r="AB425" s="4"/>
       <c r="AC425" s="4"/>
     </row>
-    <row r="426" ht="15.75" customHeight="1">
+    <row r="426" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A426" s="4"/>
       <c r="B426" s="4"/>
       <c r="C426" s="4"/>
@@ -13862,7 +13930,7 @@
       <c r="AB426" s="4"/>
       <c r="AC426" s="4"/>
     </row>
-    <row r="427" ht="15.75" customHeight="1">
+    <row r="427" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A427" s="4"/>
       <c r="B427" s="4"/>
       <c r="C427" s="4"/>
@@ -13893,7 +13961,7 @@
       <c r="AB427" s="4"/>
       <c r="AC427" s="4"/>
     </row>
-    <row r="428" ht="15.75" customHeight="1">
+    <row r="428" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A428" s="4"/>
       <c r="B428" s="4"/>
       <c r="C428" s="4"/>
@@ -13924,7 +13992,7 @@
       <c r="AB428" s="4"/>
       <c r="AC428" s="4"/>
     </row>
-    <row r="429" ht="15.75" customHeight="1">
+    <row r="429" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A429" s="4"/>
       <c r="B429" s="4"/>
       <c r="C429" s="4"/>
@@ -13955,7 +14023,7 @@
       <c r="AB429" s="4"/>
       <c r="AC429" s="4"/>
     </row>
-    <row r="430" ht="15.75" customHeight="1">
+    <row r="430" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A430" s="4"/>
       <c r="B430" s="4"/>
       <c r="C430" s="4"/>
@@ -13986,7 +14054,7 @@
       <c r="AB430" s="4"/>
       <c r="AC430" s="4"/>
     </row>
-    <row r="431" ht="15.75" customHeight="1">
+    <row r="431" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A431" s="4"/>
       <c r="B431" s="4"/>
       <c r="C431" s="4"/>
@@ -14017,7 +14085,7 @@
       <c r="AB431" s="4"/>
       <c r="AC431" s="4"/>
     </row>
-    <row r="432" ht="15.75" customHeight="1">
+    <row r="432" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A432" s="4"/>
       <c r="B432" s="4"/>
       <c r="C432" s="4"/>
@@ -14048,7 +14116,7 @@
       <c r="AB432" s="4"/>
       <c r="AC432" s="4"/>
     </row>
-    <row r="433" ht="15.75" customHeight="1">
+    <row r="433" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A433" s="4"/>
       <c r="B433" s="4"/>
       <c r="C433" s="4"/>
@@ -14079,7 +14147,7 @@
       <c r="AB433" s="4"/>
       <c r="AC433" s="4"/>
     </row>
-    <row r="434" ht="15.75" customHeight="1">
+    <row r="434" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A434" s="4"/>
       <c r="B434" s="4"/>
       <c r="C434" s="4"/>
@@ -14110,7 +14178,7 @@
       <c r="AB434" s="4"/>
       <c r="AC434" s="4"/>
     </row>
-    <row r="435" ht="15.75" customHeight="1">
+    <row r="435" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A435" s="4"/>
       <c r="B435" s="4"/>
       <c r="C435" s="4"/>
@@ -14141,7 +14209,7 @@
       <c r="AB435" s="4"/>
       <c r="AC435" s="4"/>
     </row>
-    <row r="436" ht="15.75" customHeight="1">
+    <row r="436" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A436" s="4"/>
       <c r="B436" s="4"/>
       <c r="C436" s="4"/>
@@ -14172,7 +14240,7 @@
       <c r="AB436" s="4"/>
       <c r="AC436" s="4"/>
     </row>
-    <row r="437" ht="15.75" customHeight="1">
+    <row r="437" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A437" s="4"/>
       <c r="B437" s="4"/>
       <c r="C437" s="4"/>
@@ -14203,7 +14271,7 @@
       <c r="AB437" s="4"/>
       <c r="AC437" s="4"/>
     </row>
-    <row r="438" ht="15.75" customHeight="1">
+    <row r="438" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A438" s="4"/>
       <c r="B438" s="4"/>
       <c r="C438" s="4"/>
@@ -14234,7 +14302,7 @@
       <c r="AB438" s="4"/>
       <c r="AC438" s="4"/>
     </row>
-    <row r="439" ht="15.75" customHeight="1">
+    <row r="439" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A439" s="4"/>
       <c r="B439" s="4"/>
       <c r="C439" s="4"/>
@@ -14265,7 +14333,7 @@
       <c r="AB439" s="4"/>
       <c r="AC439" s="4"/>
     </row>
-    <row r="440" ht="15.75" customHeight="1">
+    <row r="440" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A440" s="4"/>
       <c r="B440" s="4"/>
       <c r="C440" s="4"/>
@@ -14296,7 +14364,7 @@
       <c r="AB440" s="4"/>
       <c r="AC440" s="4"/>
     </row>
-    <row r="441" ht="15.75" customHeight="1">
+    <row r="441" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A441" s="4"/>
       <c r="B441" s="4"/>
       <c r="C441" s="4"/>
@@ -14327,7 +14395,7 @@
       <c r="AB441" s="4"/>
       <c r="AC441" s="4"/>
     </row>
-    <row r="442" ht="15.75" customHeight="1">
+    <row r="442" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A442" s="4"/>
       <c r="B442" s="4"/>
       <c r="C442" s="4"/>
@@ -14358,7 +14426,7 @@
       <c r="AB442" s="4"/>
       <c r="AC442" s="4"/>
     </row>
-    <row r="443" ht="15.75" customHeight="1">
+    <row r="443" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A443" s="4"/>
       <c r="B443" s="4"/>
       <c r="C443" s="4"/>
@@ -14389,7 +14457,7 @@
       <c r="AB443" s="4"/>
       <c r="AC443" s="4"/>
     </row>
-    <row r="444" ht="15.75" customHeight="1">
+    <row r="444" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A444" s="4"/>
       <c r="B444" s="4"/>
       <c r="C444" s="4"/>
@@ -14420,7 +14488,7 @@
       <c r="AB444" s="4"/>
       <c r="AC444" s="4"/>
     </row>
-    <row r="445" ht="15.75" customHeight="1">
+    <row r="445" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A445" s="4"/>
       <c r="B445" s="4"/>
       <c r="C445" s="4"/>
@@ -14451,7 +14519,7 @@
       <c r="AB445" s="4"/>
       <c r="AC445" s="4"/>
     </row>
-    <row r="446" ht="15.75" customHeight="1">
+    <row r="446" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A446" s="4"/>
       <c r="B446" s="4"/>
       <c r="C446" s="4"/>
@@ -14482,7 +14550,7 @@
       <c r="AB446" s="4"/>
       <c r="AC446" s="4"/>
     </row>
-    <row r="447" ht="15.75" customHeight="1">
+    <row r="447" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A447" s="4"/>
       <c r="B447" s="4"/>
       <c r="C447" s="4"/>
@@ -14513,7 +14581,7 @@
       <c r="AB447" s="4"/>
       <c r="AC447" s="4"/>
     </row>
-    <row r="448" ht="15.75" customHeight="1">
+    <row r="448" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A448" s="4"/>
       <c r="B448" s="4"/>
       <c r="C448" s="4"/>
@@ -14544,7 +14612,7 @@
       <c r="AB448" s="4"/>
       <c r="AC448" s="4"/>
     </row>
-    <row r="449" ht="15.75" customHeight="1">
+    <row r="449" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A449" s="4"/>
       <c r="B449" s="4"/>
       <c r="C449" s="4"/>
@@ -14575,7 +14643,7 @@
       <c r="AB449" s="4"/>
       <c r="AC449" s="4"/>
     </row>
-    <row r="450" ht="15.75" customHeight="1">
+    <row r="450" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A450" s="4"/>
       <c r="B450" s="4"/>
       <c r="C450" s="4"/>
@@ -14606,7 +14674,7 @@
       <c r="AB450" s="4"/>
       <c r="AC450" s="4"/>
     </row>
-    <row r="451" ht="15.75" customHeight="1">
+    <row r="451" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A451" s="4"/>
       <c r="B451" s="4"/>
       <c r="C451" s="4"/>
@@ -14637,7 +14705,7 @@
       <c r="AB451" s="4"/>
       <c r="AC451" s="4"/>
     </row>
-    <row r="452" ht="15.75" customHeight="1">
+    <row r="452" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A452" s="4"/>
       <c r="B452" s="4"/>
       <c r="C452" s="4"/>
@@ -14668,7 +14736,7 @@
       <c r="AB452" s="4"/>
       <c r="AC452" s="4"/>
     </row>
-    <row r="453" ht="15.75" customHeight="1">
+    <row r="453" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A453" s="4"/>
       <c r="B453" s="4"/>
       <c r="C453" s="4"/>
@@ -14699,7 +14767,7 @@
       <c r="AB453" s="4"/>
       <c r="AC453" s="4"/>
     </row>
-    <row r="454" ht="15.75" customHeight="1">
+    <row r="454" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A454" s="4"/>
       <c r="B454" s="4"/>
       <c r="C454" s="4"/>
@@ -14730,7 +14798,7 @@
       <c r="AB454" s="4"/>
       <c r="AC454" s="4"/>
     </row>
-    <row r="455" ht="15.75" customHeight="1">
+    <row r="455" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A455" s="4"/>
       <c r="B455" s="4"/>
       <c r="C455" s="4"/>
@@ -14761,7 +14829,7 @@
       <c r="AB455" s="4"/>
       <c r="AC455" s="4"/>
     </row>
-    <row r="456" ht="15.75" customHeight="1">
+    <row r="456" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A456" s="4"/>
       <c r="B456" s="4"/>
       <c r="C456" s="4"/>
@@ -14792,7 +14860,7 @@
       <c r="AB456" s="4"/>
       <c r="AC456" s="4"/>
     </row>
-    <row r="457" ht="15.75" customHeight="1">
+    <row r="457" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A457" s="4"/>
       <c r="B457" s="4"/>
       <c r="C457" s="4"/>
@@ -14823,7 +14891,7 @@
       <c r="AB457" s="4"/>
       <c r="AC457" s="4"/>
     </row>
-    <row r="458" ht="15.75" customHeight="1">
+    <row r="458" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A458" s="4"/>
       <c r="B458" s="4"/>
       <c r="C458" s="4"/>
@@ -14854,7 +14922,7 @@
       <c r="AB458" s="4"/>
       <c r="AC458" s="4"/>
     </row>
-    <row r="459" ht="15.75" customHeight="1">
+    <row r="459" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A459" s="4"/>
       <c r="B459" s="4"/>
       <c r="C459" s="4"/>
@@ -14885,7 +14953,7 @@
       <c r="AB459" s="4"/>
       <c r="AC459" s="4"/>
     </row>
-    <row r="460" ht="15.75" customHeight="1">
+    <row r="460" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A460" s="4"/>
       <c r="B460" s="4"/>
       <c r="C460" s="4"/>
@@ -14916,7 +14984,7 @@
       <c r="AB460" s="4"/>
       <c r="AC460" s="4"/>
     </row>
-    <row r="461" ht="15.75" customHeight="1">
+    <row r="461" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A461" s="4"/>
       <c r="B461" s="4"/>
       <c r="C461" s="4"/>
@@ -14947,7 +15015,7 @@
       <c r="AB461" s="4"/>
       <c r="AC461" s="4"/>
     </row>
-    <row r="462" ht="15.75" customHeight="1">
+    <row r="462" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A462" s="4"/>
       <c r="B462" s="4"/>
       <c r="C462" s="4"/>
@@ -14978,7 +15046,7 @@
       <c r="AB462" s="4"/>
       <c r="AC462" s="4"/>
     </row>
-    <row r="463" ht="15.75" customHeight="1">
+    <row r="463" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A463" s="4"/>
       <c r="B463" s="4"/>
       <c r="C463" s="4"/>
@@ -15009,7 +15077,7 @@
       <c r="AB463" s="4"/>
       <c r="AC463" s="4"/>
     </row>
-    <row r="464" ht="15.75" customHeight="1">
+    <row r="464" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A464" s="4"/>
       <c r="B464" s="4"/>
       <c r="C464" s="4"/>
@@ -15040,7 +15108,7 @@
       <c r="AB464" s="4"/>
       <c r="AC464" s="4"/>
     </row>
-    <row r="465" ht="15.75" customHeight="1">
+    <row r="465" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A465" s="4"/>
       <c r="B465" s="4"/>
       <c r="C465" s="4"/>
@@ -15071,7 +15139,7 @@
       <c r="AB465" s="4"/>
       <c r="AC465" s="4"/>
     </row>
-    <row r="466" ht="15.75" customHeight="1">
+    <row r="466" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A466" s="4"/>
       <c r="B466" s="4"/>
       <c r="C466" s="4"/>
@@ -15102,7 +15170,7 @@
       <c r="AB466" s="4"/>
       <c r="AC466" s="4"/>
     </row>
-    <row r="467" ht="15.75" customHeight="1">
+    <row r="467" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A467" s="4"/>
       <c r="B467" s="4"/>
       <c r="C467" s="4"/>
@@ -15133,7 +15201,7 @@
       <c r="AB467" s="4"/>
       <c r="AC467" s="4"/>
     </row>
-    <row r="468" ht="15.75" customHeight="1">
+    <row r="468" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A468" s="4"/>
       <c r="B468" s="4"/>
       <c r="C468" s="4"/>
@@ -15164,7 +15232,7 @@
       <c r="AB468" s="4"/>
       <c r="AC468" s="4"/>
     </row>
-    <row r="469" ht="15.75" customHeight="1">
+    <row r="469" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A469" s="4"/>
       <c r="B469" s="4"/>
       <c r="C469" s="4"/>
@@ -15195,7 +15263,7 @@
       <c r="AB469" s="4"/>
       <c r="AC469" s="4"/>
     </row>
-    <row r="470" ht="15.75" customHeight="1">
+    <row r="470" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A470" s="4"/>
       <c r="B470" s="4"/>
       <c r="C470" s="4"/>
@@ -15226,7 +15294,7 @@
       <c r="AB470" s="4"/>
       <c r="AC470" s="4"/>
     </row>
-    <row r="471" ht="15.75" customHeight="1">
+    <row r="471" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A471" s="4"/>
       <c r="B471" s="4"/>
       <c r="C471" s="4"/>
@@ -15257,7 +15325,7 @@
       <c r="AB471" s="4"/>
       <c r="AC471" s="4"/>
     </row>
-    <row r="472" ht="15.75" customHeight="1">
+    <row r="472" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A472" s="4"/>
       <c r="B472" s="4"/>
       <c r="C472" s="4"/>
@@ -15288,7 +15356,7 @@
       <c r="AB472" s="4"/>
       <c r="AC472" s="4"/>
     </row>
-    <row r="473" ht="15.75" customHeight="1">
+    <row r="473" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A473" s="4"/>
       <c r="B473" s="4"/>
       <c r="C473" s="4"/>
@@ -15319,7 +15387,7 @@
       <c r="AB473" s="4"/>
       <c r="AC473" s="4"/>
     </row>
-    <row r="474" ht="15.75" customHeight="1">
+    <row r="474" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A474" s="4"/>
       <c r="B474" s="4"/>
       <c r="C474" s="4"/>
@@ -15350,7 +15418,7 @@
       <c r="AB474" s="4"/>
       <c r="AC474" s="4"/>
     </row>
-    <row r="475" ht="15.75" customHeight="1">
+    <row r="475" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A475" s="4"/>
       <c r="B475" s="4"/>
       <c r="C475" s="4"/>
@@ -15381,7 +15449,7 @@
       <c r="AB475" s="4"/>
       <c r="AC475" s="4"/>
     </row>
-    <row r="476" ht="15.75" customHeight="1">
+    <row r="476" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A476" s="4"/>
       <c r="B476" s="4"/>
       <c r="C476" s="4"/>
@@ -15412,7 +15480,7 @@
       <c r="AB476" s="4"/>
       <c r="AC476" s="4"/>
     </row>
-    <row r="477" ht="15.75" customHeight="1">
+    <row r="477" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A477" s="4"/>
       <c r="B477" s="4"/>
       <c r="C477" s="4"/>
@@ -15443,7 +15511,7 @@
       <c r="AB477" s="4"/>
       <c r="AC477" s="4"/>
     </row>
-    <row r="478" ht="15.75" customHeight="1">
+    <row r="478" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A478" s="4"/>
       <c r="B478" s="4"/>
       <c r="C478" s="4"/>
@@ -15474,7 +15542,7 @@
       <c r="AB478" s="4"/>
       <c r="AC478" s="4"/>
     </row>
-    <row r="479" ht="15.75" customHeight="1">
+    <row r="479" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A479" s="4"/>
       <c r="B479" s="4"/>
       <c r="C479" s="4"/>
@@ -15505,7 +15573,7 @@
       <c r="AB479" s="4"/>
       <c r="AC479" s="4"/>
     </row>
-    <row r="480" ht="15.75" customHeight="1">
+    <row r="480" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A480" s="4"/>
       <c r="B480" s="4"/>
       <c r="C480" s="4"/>
@@ -15536,7 +15604,7 @@
       <c r="AB480" s="4"/>
       <c r="AC480" s="4"/>
     </row>
-    <row r="481" ht="15.75" customHeight="1">
+    <row r="481" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A481" s="4"/>
       <c r="B481" s="4"/>
       <c r="C481" s="4"/>
@@ -15567,7 +15635,7 @@
       <c r="AB481" s="4"/>
       <c r="AC481" s="4"/>
     </row>
-    <row r="482" ht="15.75" customHeight="1">
+    <row r="482" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A482" s="4"/>
       <c r="B482" s="4"/>
       <c r="C482" s="4"/>
@@ -15598,7 +15666,7 @@
       <c r="AB482" s="4"/>
       <c r="AC482" s="4"/>
     </row>
-    <row r="483" ht="15.75" customHeight="1">
+    <row r="483" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A483" s="4"/>
       <c r="B483" s="4"/>
       <c r="C483" s="4"/>
@@ -15629,7 +15697,7 @@
       <c r="AB483" s="4"/>
       <c r="AC483" s="4"/>
     </row>
-    <row r="484" ht="15.75" customHeight="1">
+    <row r="484" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A484" s="4"/>
       <c r="B484" s="4"/>
       <c r="C484" s="4"/>
@@ -15660,7 +15728,7 @@
       <c r="AB484" s="4"/>
       <c r="AC484" s="4"/>
     </row>
-    <row r="485" ht="15.75" customHeight="1">
+    <row r="485" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A485" s="4"/>
       <c r="B485" s="4"/>
       <c r="C485" s="4"/>
@@ -15691,7 +15759,7 @@
       <c r="AB485" s="4"/>
       <c r="AC485" s="4"/>
     </row>
-    <row r="486" ht="15.75" customHeight="1">
+    <row r="486" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A486" s="4"/>
       <c r="B486" s="4"/>
       <c r="C486" s="4"/>
@@ -15722,7 +15790,7 @@
       <c r="AB486" s="4"/>
       <c r="AC486" s="4"/>
     </row>
-    <row r="487" ht="15.75" customHeight="1">
+    <row r="487" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A487" s="4"/>
       <c r="B487" s="4"/>
       <c r="C487" s="4"/>
@@ -15753,7 +15821,7 @@
       <c r="AB487" s="4"/>
       <c r="AC487" s="4"/>
     </row>
-    <row r="488" ht="15.75" customHeight="1">
+    <row r="488" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A488" s="4"/>
       <c r="B488" s="4"/>
       <c r="C488" s="4"/>
@@ -15784,7 +15852,7 @@
       <c r="AB488" s="4"/>
       <c r="AC488" s="4"/>
     </row>
-    <row r="489" ht="15.75" customHeight="1">
+    <row r="489" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A489" s="4"/>
       <c r="B489" s="4"/>
       <c r="C489" s="4"/>
@@ -15815,7 +15883,7 @@
       <c r="AB489" s="4"/>
       <c r="AC489" s="4"/>
     </row>
-    <row r="490" ht="15.75" customHeight="1">
+    <row r="490" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A490" s="4"/>
       <c r="B490" s="4"/>
       <c r="C490" s="4"/>
@@ -15846,7 +15914,7 @@
       <c r="AB490" s="4"/>
       <c r="AC490" s="4"/>
     </row>
-    <row r="491" ht="15.75" customHeight="1">
+    <row r="491" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A491" s="4"/>
       <c r="B491" s="4"/>
       <c r="C491" s="4"/>
@@ -15877,7 +15945,7 @@
       <c r="AB491" s="4"/>
       <c r="AC491" s="4"/>
     </row>
-    <row r="492" ht="15.75" customHeight="1">
+    <row r="492" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A492" s="4"/>
       <c r="B492" s="4"/>
       <c r="C492" s="4"/>
@@ -15908,7 +15976,7 @@
       <c r="AB492" s="4"/>
       <c r="AC492" s="4"/>
     </row>
-    <row r="493" ht="15.75" customHeight="1">
+    <row r="493" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A493" s="4"/>
       <c r="B493" s="4"/>
       <c r="C493" s="4"/>
@@ -15939,7 +16007,7 @@
       <c r="AB493" s="4"/>
       <c r="AC493" s="4"/>
     </row>
-    <row r="494" ht="15.75" customHeight="1">
+    <row r="494" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A494" s="4"/>
       <c r="B494" s="4"/>
       <c r="C494" s="4"/>
@@ -15970,7 +16038,7 @@
       <c r="AB494" s="4"/>
       <c r="AC494" s="4"/>
     </row>
-    <row r="495" ht="15.75" customHeight="1">
+    <row r="495" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A495" s="4"/>
       <c r="B495" s="4"/>
       <c r="C495" s="4"/>
@@ -16001,7 +16069,7 @@
       <c r="AB495" s="4"/>
       <c r="AC495" s="4"/>
     </row>
-    <row r="496" ht="15.75" customHeight="1">
+    <row r="496" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A496" s="4"/>
       <c r="B496" s="4"/>
       <c r="C496" s="4"/>
@@ -16032,7 +16100,7 @@
       <c r="AB496" s="4"/>
       <c r="AC496" s="4"/>
     </row>
-    <row r="497" ht="15.75" customHeight="1">
+    <row r="497" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A497" s="4"/>
       <c r="B497" s="4"/>
       <c r="C497" s="4"/>
@@ -16063,7 +16131,7 @@
       <c r="AB497" s="4"/>
       <c r="AC497" s="4"/>
     </row>
-    <row r="498" ht="15.75" customHeight="1">
+    <row r="498" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A498" s="4"/>
       <c r="B498" s="4"/>
       <c r="C498" s="4"/>
@@ -16094,7 +16162,7 @@
       <c r="AB498" s="4"/>
       <c r="AC498" s="4"/>
     </row>
-    <row r="499" ht="15.75" customHeight="1">
+    <row r="499" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A499" s="4"/>
       <c r="B499" s="4"/>
       <c r="C499" s="4"/>
@@ -16125,7 +16193,7 @@
       <c r="AB499" s="4"/>
       <c r="AC499" s="4"/>
     </row>
-    <row r="500" ht="15.75" customHeight="1">
+    <row r="500" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A500" s="4"/>
       <c r="B500" s="4"/>
       <c r="C500" s="4"/>
@@ -16156,7 +16224,7 @@
       <c r="AB500" s="4"/>
       <c r="AC500" s="4"/>
     </row>
-    <row r="501" ht="15.75" customHeight="1">
+    <row r="501" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A501" s="4"/>
       <c r="B501" s="4"/>
       <c r="C501" s="4"/>
@@ -16187,7 +16255,7 @@
       <c r="AB501" s="4"/>
       <c r="AC501" s="4"/>
     </row>
-    <row r="502" ht="15.75" customHeight="1">
+    <row r="502" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A502" s="4"/>
       <c r="B502" s="4"/>
       <c r="C502" s="4"/>
@@ -16218,7 +16286,7 @@
       <c r="AB502" s="4"/>
       <c r="AC502" s="4"/>
     </row>
-    <row r="503" ht="15.75" customHeight="1">
+    <row r="503" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A503" s="4"/>
       <c r="B503" s="4"/>
       <c r="C503" s="4"/>
@@ -16249,7 +16317,7 @@
       <c r="AB503" s="4"/>
       <c r="AC503" s="4"/>
     </row>
-    <row r="504" ht="15.75" customHeight="1">
+    <row r="504" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A504" s="4"/>
       <c r="B504" s="4"/>
       <c r="C504" s="4"/>
@@ -16280,7 +16348,7 @@
       <c r="AB504" s="4"/>
       <c r="AC504" s="4"/>
     </row>
-    <row r="505" ht="15.75" customHeight="1">
+    <row r="505" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A505" s="4"/>
       <c r="B505" s="4"/>
       <c r="C505" s="4"/>
@@ -16311,7 +16379,7 @@
       <c r="AB505" s="4"/>
       <c r="AC505" s="4"/>
     </row>
-    <row r="506" ht="15.75" customHeight="1">
+    <row r="506" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A506" s="4"/>
       <c r="B506" s="4"/>
       <c r="C506" s="4"/>
@@ -16342,7 +16410,7 @@
       <c r="AB506" s="4"/>
       <c r="AC506" s="4"/>
     </row>
-    <row r="507" ht="15.75" customHeight="1">
+    <row r="507" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A507" s="4"/>
       <c r="B507" s="4"/>
       <c r="C507" s="4"/>
@@ -16373,7 +16441,7 @@
       <c r="AB507" s="4"/>
       <c r="AC507" s="4"/>
     </row>
-    <row r="508" ht="15.75" customHeight="1">
+    <row r="508" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A508" s="4"/>
       <c r="B508" s="4"/>
       <c r="C508" s="4"/>
@@ -16404,7 +16472,7 @@
       <c r="AB508" s="4"/>
       <c r="AC508" s="4"/>
     </row>
-    <row r="509" ht="15.75" customHeight="1">
+    <row r="509" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A509" s="4"/>
       <c r="B509" s="4"/>
       <c r="C509" s="4"/>
@@ -16435,7 +16503,7 @@
       <c r="AB509" s="4"/>
       <c r="AC509" s="4"/>
     </row>
-    <row r="510" ht="15.75" customHeight="1">
+    <row r="510" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A510" s="4"/>
       <c r="B510" s="4"/>
       <c r="C510" s="4"/>
@@ -16466,7 +16534,7 @@
       <c r="AB510" s="4"/>
       <c r="AC510" s="4"/>
     </row>
-    <row r="511" ht="15.75" customHeight="1">
+    <row r="511" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A511" s="4"/>
       <c r="B511" s="4"/>
       <c r="C511" s="4"/>
@@ -16497,7 +16565,7 @@
       <c r="AB511" s="4"/>
       <c r="AC511" s="4"/>
     </row>
-    <row r="512" ht="15.75" customHeight="1">
+    <row r="512" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A512" s="4"/>
       <c r="B512" s="4"/>
       <c r="C512" s="4"/>
@@ -16528,7 +16596,7 @@
       <c r="AB512" s="4"/>
       <c r="AC512" s="4"/>
     </row>
-    <row r="513" ht="15.75" customHeight="1">
+    <row r="513" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A513" s="4"/>
       <c r="B513" s="4"/>
       <c r="C513" s="4"/>
@@ -16559,7 +16627,7 @@
       <c r="AB513" s="4"/>
       <c r="AC513" s="4"/>
     </row>
-    <row r="514" ht="15.75" customHeight="1">
+    <row r="514" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A514" s="4"/>
       <c r="B514" s="4"/>
       <c r="C514" s="4"/>
@@ -16590,7 +16658,7 @@
       <c r="AB514" s="4"/>
       <c r="AC514" s="4"/>
     </row>
-    <row r="515" ht="15.75" customHeight="1">
+    <row r="515" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A515" s="4"/>
       <c r="B515" s="4"/>
       <c r="C515" s="4"/>
@@ -16621,7 +16689,7 @@
       <c r="AB515" s="4"/>
       <c r="AC515" s="4"/>
     </row>
-    <row r="516" ht="15.75" customHeight="1">
+    <row r="516" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A516" s="4"/>
       <c r="B516" s="4"/>
       <c r="C516" s="4"/>
@@ -16652,7 +16720,7 @@
       <c r="AB516" s="4"/>
       <c r="AC516" s="4"/>
     </row>
-    <row r="517" ht="15.75" customHeight="1">
+    <row r="517" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A517" s="4"/>
       <c r="B517" s="4"/>
       <c r="C517" s="4"/>
@@ -16683,7 +16751,7 @@
       <c r="AB517" s="4"/>
       <c r="AC517" s="4"/>
     </row>
-    <row r="518" ht="15.75" customHeight="1">
+    <row r="518" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A518" s="4"/>
       <c r="B518" s="4"/>
       <c r="C518" s="4"/>
@@ -16714,7 +16782,7 @@
       <c r="AB518" s="4"/>
       <c r="AC518" s="4"/>
     </row>
-    <row r="519" ht="15.75" customHeight="1">
+    <row r="519" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A519" s="4"/>
       <c r="B519" s="4"/>
       <c r="C519" s="4"/>
@@ -16745,7 +16813,7 @@
       <c r="AB519" s="4"/>
       <c r="AC519" s="4"/>
     </row>
-    <row r="520" ht="15.75" customHeight="1">
+    <row r="520" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A520" s="4"/>
       <c r="B520" s="4"/>
       <c r="C520" s="4"/>
@@ -16776,7 +16844,7 @@
       <c r="AB520" s="4"/>
       <c r="AC520" s="4"/>
     </row>
-    <row r="521" ht="15.75" customHeight="1">
+    <row r="521" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A521" s="4"/>
       <c r="B521" s="4"/>
       <c r="C521" s="4"/>
@@ -16807,7 +16875,7 @@
       <c r="AB521" s="4"/>
       <c r="AC521" s="4"/>
     </row>
-    <row r="522" ht="15.75" customHeight="1">
+    <row r="522" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A522" s="4"/>
       <c r="B522" s="4"/>
       <c r="C522" s="4"/>
@@ -16838,7 +16906,7 @@
       <c r="AB522" s="4"/>
       <c r="AC522" s="4"/>
     </row>
-    <row r="523" ht="15.75" customHeight="1">
+    <row r="523" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A523" s="4"/>
       <c r="B523" s="4"/>
       <c r="C523" s="4"/>
@@ -16869,7 +16937,7 @@
       <c r="AB523" s="4"/>
       <c r="AC523" s="4"/>
     </row>
-    <row r="524" ht="15.75" customHeight="1">
+    <row r="524" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A524" s="4"/>
       <c r="B524" s="4"/>
       <c r="C524" s="4"/>
@@ -16900,7 +16968,7 @@
       <c r="AB524" s="4"/>
       <c r="AC524" s="4"/>
     </row>
-    <row r="525" ht="15.75" customHeight="1">
+    <row r="525" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A525" s="4"/>
       <c r="B525" s="4"/>
       <c r="C525" s="4"/>
@@ -16931,7 +16999,7 @@
       <c r="AB525" s="4"/>
       <c r="AC525" s="4"/>
     </row>
-    <row r="526" ht="15.75" customHeight="1">
+    <row r="526" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A526" s="4"/>
       <c r="B526" s="4"/>
       <c r="C526" s="4"/>
@@ -16962,7 +17030,7 @@
       <c r="AB526" s="4"/>
       <c r="AC526" s="4"/>
     </row>
-    <row r="527" ht="15.75" customHeight="1">
+    <row r="527" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A527" s="4"/>
       <c r="B527" s="4"/>
       <c r="C527" s="4"/>
@@ -16993,7 +17061,7 @@
       <c r="AB527" s="4"/>
       <c r="AC527" s="4"/>
     </row>
-    <row r="528" ht="15.75" customHeight="1">
+    <row r="528" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A528" s="4"/>
       <c r="B528" s="4"/>
       <c r="C528" s="4"/>
@@ -17024,7 +17092,7 @@
       <c r="AB528" s="4"/>
       <c r="AC528" s="4"/>
     </row>
-    <row r="529" ht="15.75" customHeight="1">
+    <row r="529" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A529" s="4"/>
       <c r="B529" s="4"/>
       <c r="C529" s="4"/>
@@ -17055,7 +17123,7 @@
       <c r="AB529" s="4"/>
       <c r="AC529" s="4"/>
     </row>
-    <row r="530" ht="15.75" customHeight="1">
+    <row r="530" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A530" s="4"/>
       <c r="B530" s="4"/>
       <c r="C530" s="4"/>
@@ -17086,7 +17154,7 @@
       <c r="AB530" s="4"/>
       <c r="AC530" s="4"/>
     </row>
-    <row r="531" ht="15.75" customHeight="1">
+    <row r="531" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A531" s="4"/>
       <c r="B531" s="4"/>
       <c r="C531" s="4"/>
@@ -17117,7 +17185,7 @@
       <c r="AB531" s="4"/>
       <c r="AC531" s="4"/>
     </row>
-    <row r="532" ht="15.75" customHeight="1">
+    <row r="532" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A532" s="4"/>
       <c r="B532" s="4"/>
       <c r="C532" s="4"/>
@@ -17148,7 +17216,7 @@
       <c r="AB532" s="4"/>
       <c r="AC532" s="4"/>
     </row>
-    <row r="533" ht="15.75" customHeight="1">
+    <row r="533" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A533" s="4"/>
       <c r="B533" s="4"/>
       <c r="C533" s="4"/>
@@ -17179,7 +17247,7 @@
       <c r="AB533" s="4"/>
       <c r="AC533" s="4"/>
     </row>
-    <row r="534" ht="15.75" customHeight="1">
+    <row r="534" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A534" s="4"/>
       <c r="B534" s="4"/>
       <c r="C534" s="4"/>
@@ -17210,7 +17278,7 @@
       <c r="AB534" s="4"/>
       <c r="AC534" s="4"/>
     </row>
-    <row r="535" ht="15.75" customHeight="1">
+    <row r="535" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A535" s="4"/>
       <c r="B535" s="4"/>
       <c r="C535" s="4"/>
@@ -17241,7 +17309,7 @@
       <c r="AB535" s="4"/>
       <c r="AC535" s="4"/>
     </row>
-    <row r="536" ht="15.75" customHeight="1">
+    <row r="536" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A536" s="4"/>
       <c r="B536" s="4"/>
       <c r="C536" s="4"/>
@@ -17272,7 +17340,7 @@
       <c r="AB536" s="4"/>
       <c r="AC536" s="4"/>
     </row>
-    <row r="537" ht="15.75" customHeight="1">
+    <row r="537" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A537" s="4"/>
       <c r="B537" s="4"/>
       <c r="C537" s="4"/>
@@ -17303,7 +17371,7 @@
       <c r="AB537" s="4"/>
       <c r="AC537" s="4"/>
     </row>
-    <row r="538" ht="15.75" customHeight="1">
+    <row r="538" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A538" s="4"/>
       <c r="B538" s="4"/>
       <c r="C538" s="4"/>
@@ -17334,7 +17402,7 @@
       <c r="AB538" s="4"/>
       <c r="AC538" s="4"/>
     </row>
-    <row r="539" ht="15.75" customHeight="1">
+    <row r="539" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A539" s="4"/>
       <c r="B539" s="4"/>
       <c r="C539" s="4"/>
@@ -17365,7 +17433,7 @@
       <c r="AB539" s="4"/>
       <c r="AC539" s="4"/>
     </row>
-    <row r="540" ht="15.75" customHeight="1">
+    <row r="540" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A540" s="4"/>
       <c r="B540" s="4"/>
       <c r="C540" s="4"/>
@@ -17396,7 +17464,7 @@
       <c r="AB540" s="4"/>
       <c r="AC540" s="4"/>
     </row>
-    <row r="541" ht="15.75" customHeight="1">
+    <row r="541" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A541" s="4"/>
       <c r="B541" s="4"/>
       <c r="C541" s="4"/>
@@ -17427,7 +17495,7 @@
       <c r="AB541" s="4"/>
       <c r="AC541" s="4"/>
     </row>
-    <row r="542" ht="15.75" customHeight="1">
+    <row r="542" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A542" s="4"/>
       <c r="B542" s="4"/>
       <c r="C542" s="4"/>
@@ -17458,7 +17526,7 @@
       <c r="AB542" s="4"/>
       <c r="AC542" s="4"/>
     </row>
-    <row r="543" ht="15.75" customHeight="1">
+    <row r="543" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A543" s="4"/>
       <c r="B543" s="4"/>
       <c r="C543" s="4"/>
@@ -17489,7 +17557,7 @@
       <c r="AB543" s="4"/>
       <c r="AC543" s="4"/>
     </row>
-    <row r="544" ht="15.75" customHeight="1">
+    <row r="544" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A544" s="4"/>
       <c r="B544" s="4"/>
       <c r="C544" s="4"/>
@@ -17520,7 +17588,7 @@
       <c r="AB544" s="4"/>
       <c r="AC544" s="4"/>
     </row>
-    <row r="545" ht="15.75" customHeight="1">
+    <row r="545" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A545" s="4"/>
       <c r="B545" s="4"/>
       <c r="C545" s="4"/>
@@ -17551,7 +17619,7 @@
       <c r="AB545" s="4"/>
       <c r="AC545" s="4"/>
     </row>
-    <row r="546" ht="15.75" customHeight="1">
+    <row r="546" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A546" s="4"/>
       <c r="B546" s="4"/>
       <c r="C546" s="4"/>
@@ -17582,7 +17650,7 @@
       <c r="AB546" s="4"/>
       <c r="AC546" s="4"/>
     </row>
-    <row r="547" ht="15.75" customHeight="1">
+    <row r="547" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A547" s="4"/>
       <c r="B547" s="4"/>
       <c r="C547" s="4"/>
@@ -17613,7 +17681,7 @@
       <c r="AB547" s="4"/>
       <c r="AC547" s="4"/>
     </row>
-    <row r="548" ht="15.75" customHeight="1">
+    <row r="548" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A548" s="4"/>
       <c r="B548" s="4"/>
       <c r="C548" s="4"/>
@@ -17644,7 +17712,7 @@
       <c r="AB548" s="4"/>
       <c r="AC548" s="4"/>
     </row>
-    <row r="549" ht="15.75" customHeight="1">
+    <row r="549" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A549" s="4"/>
       <c r="B549" s="4"/>
       <c r="C549" s="4"/>
@@ -17675,7 +17743,7 @@
       <c r="AB549" s="4"/>
       <c r="AC549" s="4"/>
     </row>
-    <row r="550" ht="15.75" customHeight="1">
+    <row r="550" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A550" s="4"/>
       <c r="B550" s="4"/>
       <c r="C550" s="4"/>
@@ -17706,7 +17774,7 @@
       <c r="AB550" s="4"/>
       <c r="AC550" s="4"/>
     </row>
-    <row r="551" ht="15.75" customHeight="1">
+    <row r="551" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A551" s="4"/>
       <c r="B551" s="4"/>
       <c r="C551" s="4"/>
@@ -17737,7 +17805,7 @@
       <c r="AB551" s="4"/>
       <c r="AC551" s="4"/>
     </row>
-    <row r="552" ht="15.75" customHeight="1">
+    <row r="552" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A552" s="4"/>
       <c r="B552" s="4"/>
       <c r="C552" s="4"/>
@@ -17768,7 +17836,7 @@
       <c r="AB552" s="4"/>
       <c r="AC552" s="4"/>
     </row>
-    <row r="553" ht="15.75" customHeight="1">
+    <row r="553" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A553" s="4"/>
       <c r="B553" s="4"/>
       <c r="C553" s="4"/>
@@ -17799,7 +17867,7 @@
       <c r="AB553" s="4"/>
       <c r="AC553" s="4"/>
     </row>
-    <row r="554" ht="15.75" customHeight="1">
+    <row r="554" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A554" s="4"/>
       <c r="B554" s="4"/>
       <c r="C554" s="4"/>
@@ -17830,7 +17898,7 @@
       <c r="AB554" s="4"/>
       <c r="AC554" s="4"/>
     </row>
-    <row r="555" ht="15.75" customHeight="1">
+    <row r="555" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A555" s="4"/>
       <c r="B555" s="4"/>
       <c r="C555" s="4"/>
@@ -17861,7 +17929,7 @@
       <c r="AB555" s="4"/>
       <c r="AC555" s="4"/>
     </row>
-    <row r="556" ht="15.75" customHeight="1">
+    <row r="556" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A556" s="4"/>
       <c r="B556" s="4"/>
       <c r="C556" s="4"/>
@@ -17892,7 +17960,7 @@
       <c r="AB556" s="4"/>
       <c r="AC556" s="4"/>
     </row>
-    <row r="557" ht="15.75" customHeight="1">
+    <row r="557" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A557" s="4"/>
       <c r="B557" s="4"/>
       <c r="C557" s="4"/>
@@ -17923,7 +17991,7 @@
       <c r="AB557" s="4"/>
       <c r="AC557" s="4"/>
     </row>
-    <row r="558" ht="15.75" customHeight="1">
+    <row r="558" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A558" s="4"/>
       <c r="B558" s="4"/>
       <c r="C558" s="4"/>
@@ -17954,7 +18022,7 @@
       <c r="AB558" s="4"/>
       <c r="AC558" s="4"/>
     </row>
-    <row r="559" ht="15.75" customHeight="1">
+    <row r="559" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A559" s="4"/>
       <c r="B559" s="4"/>
       <c r="C559" s="4"/>
@@ -17985,7 +18053,7 @@
       <c r="AB559" s="4"/>
       <c r="AC559" s="4"/>
     </row>
-    <row r="560" ht="15.75" customHeight="1">
+    <row r="560" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A560" s="4"/>
       <c r="B560" s="4"/>
       <c r="C560" s="4"/>
@@ -18016,7 +18084,7 @@
       <c r="AB560" s="4"/>
       <c r="AC560" s="4"/>
     </row>
-    <row r="561" ht="15.75" customHeight="1">
+    <row r="561" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A561" s="4"/>
       <c r="B561" s="4"/>
       <c r="C561" s="4"/>
@@ -18047,7 +18115,7 @@
       <c r="AB561" s="4"/>
       <c r="AC561" s="4"/>
     </row>
-    <row r="562" ht="15.75" customHeight="1">
+    <row r="562" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A562" s="4"/>
       <c r="B562" s="4"/>
       <c r="C562" s="4"/>
@@ -18078,7 +18146,7 @@
       <c r="AB562" s="4"/>
       <c r="AC562" s="4"/>
     </row>
-    <row r="563" ht="15.75" customHeight="1">
+    <row r="563" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A563" s="4"/>
       <c r="B563" s="4"/>
       <c r="C563" s="4"/>
@@ -18109,7 +18177,7 @@
       <c r="AB563" s="4"/>
       <c r="AC563" s="4"/>
     </row>
-    <row r="564" ht="15.75" customHeight="1">
+    <row r="564" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A564" s="4"/>
       <c r="B564" s="4"/>
       <c r="C564" s="4"/>
@@ -18140,7 +18208,7 @@
       <c r="AB564" s="4"/>
       <c r="AC564" s="4"/>
     </row>
-    <row r="565" ht="15.75" customHeight="1">
+    <row r="565" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A565" s="4"/>
       <c r="B565" s="4"/>
       <c r="C565" s="4"/>
@@ -18171,7 +18239,7 @@
       <c r="AB565" s="4"/>
       <c r="AC565" s="4"/>
     </row>
-    <row r="566" ht="15.75" customHeight="1">
+    <row r="566" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A566" s="4"/>
       <c r="B566" s="4"/>
       <c r="C566" s="4"/>
@@ -18202,7 +18270,7 @@
       <c r="AB566" s="4"/>
       <c r="AC566" s="4"/>
     </row>
-    <row r="567" ht="15.75" customHeight="1">
+    <row r="567" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A567" s="4"/>
       <c r="B567" s="4"/>
       <c r="C567" s="4"/>
@@ -18233,7 +18301,7 @@
       <c r="AB567" s="4"/>
       <c r="AC567" s="4"/>
     </row>
-    <row r="568" ht="15.75" customHeight="1">
+    <row r="568" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A568" s="4"/>
       <c r="B568" s="4"/>
       <c r="C568" s="4"/>
@@ -18264,7 +18332,7 @@
       <c r="AB568" s="4"/>
       <c r="AC568" s="4"/>
     </row>
-    <row r="569" ht="15.75" customHeight="1">
+    <row r="569" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A569" s="4"/>
       <c r="B569" s="4"/>
       <c r="C569" s="4"/>
@@ -18295,7 +18363,7 @@
       <c r="AB569" s="4"/>
       <c r="AC569" s="4"/>
     </row>
-    <row r="570" ht="15.75" customHeight="1">
+    <row r="570" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A570" s="4"/>
       <c r="B570" s="4"/>
       <c r="C570" s="4"/>
@@ -18326,7 +18394,7 @@
       <c r="AB570" s="4"/>
       <c r="AC570" s="4"/>
     </row>
-    <row r="571" ht="15.75" customHeight="1">
+    <row r="571" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A571" s="4"/>
       <c r="B571" s="4"/>
       <c r="C571" s="4"/>
@@ -18357,7 +18425,7 @@
       <c r="AB571" s="4"/>
       <c r="AC571" s="4"/>
     </row>
-    <row r="572" ht="15.75" customHeight="1">
+    <row r="572" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A572" s="4"/>
       <c r="B572" s="4"/>
       <c r="C572" s="4"/>
@@ -18388,7 +18456,7 @@
       <c r="AB572" s="4"/>
       <c r="AC572" s="4"/>
     </row>
-    <row r="573" ht="15.75" customHeight="1">
+    <row r="573" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A573" s="4"/>
       <c r="B573" s="4"/>
       <c r="C573" s="4"/>
@@ -18419,7 +18487,7 @@
       <c r="AB573" s="4"/>
       <c r="AC573" s="4"/>
     </row>
-    <row r="574" ht="15.75" customHeight="1">
+    <row r="574" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A574" s="4"/>
       <c r="B574" s="4"/>
       <c r="C574" s="4"/>
@@ -18450,7 +18518,7 @@
       <c r="AB574" s="4"/>
       <c r="AC574" s="4"/>
     </row>
-    <row r="575" ht="15.75" customHeight="1">
+    <row r="575" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A575" s="4"/>
       <c r="B575" s="4"/>
       <c r="C575" s="4"/>
@@ -18481,7 +18549,7 @@
       <c r="AB575" s="4"/>
       <c r="AC575" s="4"/>
     </row>
-    <row r="576" ht="15.75" customHeight="1">
+    <row r="576" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A576" s="4"/>
       <c r="B576" s="4"/>
       <c r="C576" s="4"/>
@@ -18512,7 +18580,7 @@
       <c r="AB576" s="4"/>
       <c r="AC576" s="4"/>
     </row>
-    <row r="577" ht="15.75" customHeight="1">
+    <row r="577" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A577" s="4"/>
       <c r="B577" s="4"/>
       <c r="C577" s="4"/>
@@ -18543,7 +18611,7 @@
       <c r="AB577" s="4"/>
       <c r="AC577" s="4"/>
     </row>
-    <row r="578" ht="15.75" customHeight="1">
+    <row r="578" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A578" s="4"/>
       <c r="B578" s="4"/>
       <c r="C578" s="4"/>
@@ -18574,7 +18642,7 @@
       <c r="AB578" s="4"/>
       <c r="AC578" s="4"/>
     </row>
-    <row r="579" ht="15.75" customHeight="1">
+    <row r="579" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A579" s="4"/>
       <c r="B579" s="4"/>
       <c r="C579" s="4"/>
@@ -18605,7 +18673,7 @@
       <c r="AB579" s="4"/>
       <c r="AC579" s="4"/>
     </row>
-    <row r="580" ht="15.75" customHeight="1">
+    <row r="580" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A580" s="4"/>
       <c r="B580" s="4"/>
       <c r="C580" s="4"/>
@@ -18636,7 +18704,7 @@
       <c r="AB580" s="4"/>
       <c r="AC580" s="4"/>
     </row>
-    <row r="581" ht="15.75" customHeight="1">
+    <row r="581" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A581" s="4"/>
       <c r="B581" s="4"/>
       <c r="C581" s="4"/>
@@ -18667,7 +18735,7 @@
       <c r="AB581" s="4"/>
       <c r="AC581" s="4"/>
     </row>
-    <row r="582" ht="15.75" customHeight="1">
+    <row r="582" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A582" s="4"/>
       <c r="B582" s="4"/>
       <c r="C582" s="4"/>
@@ -18698,7 +18766,7 @@
       <c r="AB582" s="4"/>
       <c r="AC582" s="4"/>
     </row>
-    <row r="583" ht="15.75" customHeight="1">
+    <row r="583" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A583" s="4"/>
       <c r="B583" s="4"/>
       <c r="C583" s="4"/>
@@ -18729,7 +18797,7 @@
       <c r="AB583" s="4"/>
       <c r="AC583" s="4"/>
     </row>
-    <row r="584" ht="15.75" customHeight="1">
+    <row r="584" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A584" s="4"/>
       <c r="B584" s="4"/>
       <c r="C584" s="4"/>
@@ -18760,7 +18828,7 @@
       <c r="AB584" s="4"/>
       <c r="AC584" s="4"/>
     </row>
-    <row r="585" ht="15.75" customHeight="1">
+    <row r="585" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A585" s="4"/>
       <c r="B585" s="4"/>
       <c r="C585" s="4"/>
@@ -18791,7 +18859,7 @@
       <c r="AB585" s="4"/>
       <c r="AC585" s="4"/>
     </row>
-    <row r="586" ht="15.75" customHeight="1">
+    <row r="586" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A586" s="4"/>
       <c r="B586" s="4"/>
       <c r="C586" s="4"/>
@@ -18822,7 +18890,7 @@
       <c r="AB586" s="4"/>
       <c r="AC586" s="4"/>
     </row>
-    <row r="587" ht="15.75" customHeight="1">
+    <row r="587" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A587" s="4"/>
       <c r="B587" s="4"/>
       <c r="C587" s="4"/>
@@ -18853,7 +18921,7 @@
       <c r="AB587" s="4"/>
       <c r="AC587" s="4"/>
     </row>
-    <row r="588" ht="15.75" customHeight="1">
+    <row r="588" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A588" s="4"/>
       <c r="B588" s="4"/>
       <c r="C588" s="4"/>
@@ -18884,7 +18952,7 @@
       <c r="AB588" s="4"/>
       <c r="AC588" s="4"/>
     </row>
-    <row r="589" ht="15.75" customHeight="1">
+    <row r="589" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A589" s="4"/>
       <c r="B589" s="4"/>
       <c r="C589" s="4"/>
@@ -18915,7 +18983,7 @@
       <c r="AB589" s="4"/>
       <c r="AC589" s="4"/>
     </row>
-    <row r="590" ht="15.75" customHeight="1">
+    <row r="590" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A590" s="4"/>
       <c r="B590" s="4"/>
       <c r="C590" s="4"/>
@@ -18946,7 +19014,7 @@
       <c r="AB590" s="4"/>
       <c r="AC590" s="4"/>
     </row>
-    <row r="591" ht="15.75" customHeight="1">
+    <row r="591" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A591" s="4"/>
       <c r="B591" s="4"/>
       <c r="C591" s="4"/>
@@ -18977,7 +19045,7 @@
       <c r="AB591" s="4"/>
       <c r="AC591" s="4"/>
     </row>
-    <row r="592" ht="15.75" customHeight="1">
+    <row r="592" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A592" s="4"/>
       <c r="B592" s="4"/>
       <c r="C592" s="4"/>
@@ -19008,7 +19076,7 @@
       <c r="AB592" s="4"/>
       <c r="AC592" s="4"/>
     </row>
-    <row r="593" ht="15.75" customHeight="1">
+    <row r="593" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A593" s="4"/>
       <c r="B593" s="4"/>
       <c r="C593" s="4"/>
@@ -19039,7 +19107,7 @@
       <c r="AB593" s="4"/>
       <c r="AC593" s="4"/>
     </row>
-    <row r="594" ht="15.75" customHeight="1">
+    <row r="594" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A594" s="4"/>
       <c r="B594" s="4"/>
       <c r="C594" s="4"/>
@@ -19070,7 +19138,7 @@
       <c r="AB594" s="4"/>
       <c r="AC594" s="4"/>
     </row>
-    <row r="595" ht="15.75" customHeight="1">
+    <row r="595" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A595" s="4"/>
       <c r="B595" s="4"/>
       <c r="C595" s="4"/>
@@ -19101,7 +19169,7 @@
       <c r="AB595" s="4"/>
       <c r="AC595" s="4"/>
     </row>
-    <row r="596" ht="15.75" customHeight="1">
+    <row r="596" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A596" s="4"/>
       <c r="B596" s="4"/>
       <c r="C596" s="4"/>
@@ -19132,7 +19200,7 @@
       <c r="AB596" s="4"/>
       <c r="AC596" s="4"/>
     </row>
-    <row r="597" ht="15.75" customHeight="1">
+    <row r="597" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A597" s="4"/>
       <c r="B597" s="4"/>
       <c r="C597" s="4"/>
@@ -19163,7 +19231,7 @@
       <c r="AB597" s="4"/>
       <c r="AC597" s="4"/>
     </row>
-    <row r="598" ht="15.75" customHeight="1">
+    <row r="598" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A598" s="4"/>
       <c r="B598" s="4"/>
       <c r="C598" s="4"/>
@@ -19194,7 +19262,7 @@
       <c r="AB598" s="4"/>
       <c r="AC598" s="4"/>
     </row>
-    <row r="599" ht="15.75" customHeight="1">
+    <row r="599" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A599" s="4"/>
       <c r="B599" s="4"/>
       <c r="C599" s="4"/>
@@ -19225,7 +19293,7 @@
       <c r="AB599" s="4"/>
       <c r="AC599" s="4"/>
     </row>
-    <row r="600" ht="15.75" customHeight="1">
+    <row r="600" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A600" s="4"/>
       <c r="B600" s="4"/>
       <c r="C600" s="4"/>
@@ -19256,7 +19324,7 @@
       <c r="AB600" s="4"/>
       <c r="AC600" s="4"/>
     </row>
-    <row r="601" ht="15.75" customHeight="1">
+    <row r="601" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A601" s="4"/>
       <c r="B601" s="4"/>
       <c r="C601" s="4"/>
@@ -19287,7 +19355,7 @@
       <c r="AB601" s="4"/>
       <c r="AC601" s="4"/>
     </row>
-    <row r="602" ht="15.75" customHeight="1">
+    <row r="602" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A602" s="4"/>
       <c r="B602" s="4"/>
       <c r="C602" s="4"/>
@@ -19318,7 +19386,7 @@
       <c r="AB602" s="4"/>
       <c r="AC602" s="4"/>
     </row>
-    <row r="603" ht="15.75" customHeight="1">
+    <row r="603" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A603" s="4"/>
       <c r="B603" s="4"/>
       <c r="C603" s="4"/>
@@ -19349,7 +19417,7 @@
       <c r="AB603" s="4"/>
       <c r="AC603" s="4"/>
     </row>
-    <row r="604" ht="15.75" customHeight="1">
+    <row r="604" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A604" s="4"/>
       <c r="B604" s="4"/>
       <c r="C604" s="4"/>
@@ -19380,7 +19448,7 @@
       <c r="AB604" s="4"/>
       <c r="AC604" s="4"/>
     </row>
-    <row r="605" ht="15.75" customHeight="1">
+    <row r="605" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A605" s="4"/>
       <c r="B605" s="4"/>
       <c r="C605" s="4"/>
@@ -19411,7 +19479,7 @@
       <c r="AB605" s="4"/>
       <c r="AC605" s="4"/>
     </row>
-    <row r="606" ht="15.75" customHeight="1">
+    <row r="606" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A606" s="4"/>
       <c r="B606" s="4"/>
       <c r="C606" s="4"/>
@@ -19442,7 +19510,7 @@
       <c r="AB606" s="4"/>
       <c r="AC606" s="4"/>
     </row>
-    <row r="607" ht="15.75" customHeight="1">
+    <row r="607" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A607" s="4"/>
       <c r="B607" s="4"/>
       <c r="C607" s="4"/>
@@ -19473,7 +19541,7 @@
       <c r="AB607" s="4"/>
       <c r="AC607" s="4"/>
     </row>
-    <row r="608" ht="15.75" customHeight="1">
+    <row r="608" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A608" s="4"/>
       <c r="B608" s="4"/>
       <c r="C608" s="4"/>
@@ -19504,7 +19572,7 @@
       <c r="AB608" s="4"/>
       <c r="AC608" s="4"/>
     </row>
-    <row r="609" ht="15.75" customHeight="1">
+    <row r="609" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A609" s="4"/>
       <c r="B609" s="4"/>
       <c r="C609" s="4"/>
@@ -19535,7 +19603,7 @@
       <c r="AB609" s="4"/>
       <c r="AC609" s="4"/>
     </row>
-    <row r="610" ht="15.75" customHeight="1">
+    <row r="610" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A610" s="4"/>
       <c r="B610" s="4"/>
       <c r="C610" s="4"/>
@@ -19566,7 +19634,7 @@
       <c r="AB610" s="4"/>
       <c r="AC610" s="4"/>
     </row>
-    <row r="611" ht="15.75" customHeight="1">
+    <row r="611" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A611" s="4"/>
       <c r="B611" s="4"/>
       <c r="C611" s="4"/>
@@ -19597,7 +19665,7 @@
       <c r="AB611" s="4"/>
       <c r="AC611" s="4"/>
     </row>
-    <row r="612" ht="15.75" customHeight="1">
+    <row r="612" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A612" s="4"/>
       <c r="B612" s="4"/>
       <c r="C612" s="4"/>
@@ -19628,7 +19696,7 @@
       <c r="AB612" s="4"/>
       <c r="AC612" s="4"/>
     </row>
-    <row r="613" ht="15.75" customHeight="1">
+    <row r="613" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A613" s="4"/>
       <c r="B613" s="4"/>
       <c r="C613" s="4"/>
@@ -19659,7 +19727,7 @@
       <c r="AB613" s="4"/>
       <c r="AC613" s="4"/>
     </row>
-    <row r="614" ht="15.75" customHeight="1">
+    <row r="614" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A614" s="4"/>
       <c r="B614" s="4"/>
       <c r="C614" s="4"/>
@@ -19690,7 +19758,7 @@
       <c r="AB614" s="4"/>
       <c r="AC614" s="4"/>
     </row>
-    <row r="615" ht="15.75" customHeight="1">
+    <row r="615" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A615" s="4"/>
       <c r="B615" s="4"/>
       <c r="C615" s="4"/>
@@ -19721,7 +19789,7 @@
       <c r="AB615" s="4"/>
       <c r="AC615" s="4"/>
     </row>
-    <row r="616" ht="15.75" customHeight="1">
+    <row r="616" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A616" s="4"/>
       <c r="B616" s="4"/>
       <c r="C616" s="4"/>
@@ -19752,7 +19820,7 @@
       <c r="AB616" s="4"/>
       <c r="AC616" s="4"/>
     </row>
-    <row r="617" ht="15.75" customHeight="1">
+    <row r="617" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A617" s="4"/>
       <c r="B617" s="4"/>
       <c r="C617" s="4"/>
@@ -19783,7 +19851,7 @@
       <c r="AB617" s="4"/>
       <c r="AC617" s="4"/>
     </row>
-    <row r="618" ht="15.75" customHeight="1">
+    <row r="618" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A618" s="4"/>
       <c r="B618" s="4"/>
       <c r="C618" s="4"/>
@@ -19814,7 +19882,7 @@
       <c r="AB618" s="4"/>
       <c r="AC618" s="4"/>
     </row>
-    <row r="619" ht="15.75" customHeight="1">
+    <row r="619" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A619" s="4"/>
       <c r="B619" s="4"/>
       <c r="C619" s="4"/>
@@ -19845,7 +19913,7 @@
       <c r="AB619" s="4"/>
       <c r="AC619" s="4"/>
     </row>
-    <row r="620" ht="15.75" customHeight="1">
+    <row r="620" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A620" s="4"/>
       <c r="B620" s="4"/>
       <c r="C620" s="4"/>
@@ -19876,7 +19944,7 @@
       <c r="AB620" s="4"/>
       <c r="AC620" s="4"/>
     </row>
-    <row r="621" ht="15.75" customHeight="1">
+    <row r="621" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A621" s="4"/>
       <c r="B621" s="4"/>
       <c r="C621" s="4"/>
@@ -19907,7 +19975,7 @@
       <c r="AB621" s="4"/>
       <c r="AC621" s="4"/>
     </row>
-    <row r="622" ht="15.75" customHeight="1">
+    <row r="622" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A622" s="4"/>
       <c r="B622" s="4"/>
       <c r="C622" s="4"/>
@@ -19938,7 +20006,7 @@
       <c r="AB622" s="4"/>
       <c r="AC622" s="4"/>
     </row>
-    <row r="623" ht="15.75" customHeight="1">
+    <row r="623" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A623" s="4"/>
       <c r="B623" s="4"/>
       <c r="C623" s="4"/>
@@ -19969,7 +20037,7 @@
       <c r="AB623" s="4"/>
       <c r="AC623" s="4"/>
     </row>
-    <row r="624" ht="15.75" customHeight="1">
+    <row r="624" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A624" s="4"/>
       <c r="B624" s="4"/>
       <c r="C624" s="4"/>
@@ -20000,7 +20068,7 @@
       <c r="AB624" s="4"/>
       <c r="AC624" s="4"/>
     </row>
-    <row r="625" ht="15.75" customHeight="1">
+    <row r="625" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A625" s="4"/>
       <c r="B625" s="4"/>
       <c r="C625" s="4"/>
@@ -20031,7 +20099,7 @@
       <c r="AB625" s="4"/>
       <c r="AC625" s="4"/>
     </row>
-    <row r="626" ht="15.75" customHeight="1">
+    <row r="626" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A626" s="4"/>
       <c r="B626" s="4"/>
       <c r="C626" s="4"/>
@@ -20062,7 +20130,7 @@
       <c r="AB626" s="4"/>
       <c r="AC626" s="4"/>
     </row>
-    <row r="627" ht="15.75" customHeight="1">
+    <row r="627" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A627" s="4"/>
       <c r="B627" s="4"/>
       <c r="C627" s="4"/>
@@ -20093,7 +20161,7 @@
       <c r="AB627" s="4"/>
       <c r="AC627" s="4"/>
     </row>
-    <row r="628" ht="15.75" customHeight="1">
+    <row r="628" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A628" s="4"/>
       <c r="B628" s="4"/>
       <c r="C628" s="4"/>
@@ -20124,7 +20192,7 @@
       <c r="AB628" s="4"/>
       <c r="AC628" s="4"/>
     </row>
-    <row r="629" ht="15.75" customHeight="1">
+    <row r="629" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A629" s="4"/>
       <c r="B629" s="4"/>
       <c r="C629" s="4"/>
@@ -20155,7 +20223,7 @@
       <c r="AB629" s="4"/>
       <c r="AC629" s="4"/>
     </row>
-    <row r="630" ht="15.75" customHeight="1">
+    <row r="630" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A630" s="4"/>
       <c r="B630" s="4"/>
       <c r="C630" s="4"/>
@@ -20186,7 +20254,7 @@
       <c r="AB630" s="4"/>
       <c r="AC630" s="4"/>
     </row>
-    <row r="631" ht="15.75" customHeight="1">
+    <row r="631" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A631" s="4"/>
       <c r="B631" s="4"/>
       <c r="C631" s="4"/>
@@ -20217,7 +20285,7 @@
       <c r="AB631" s="4"/>
       <c r="AC631" s="4"/>
     </row>
-    <row r="632" ht="15.75" customHeight="1">
+    <row r="632" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A632" s="4"/>
       <c r="B632" s="4"/>
       <c r="C632" s="4"/>
@@ -20248,7 +20316,7 @@
       <c r="AB632" s="4"/>
       <c r="AC632" s="4"/>
     </row>
-    <row r="633" ht="15.75" customHeight="1">
+    <row r="633" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A633" s="4"/>
       <c r="B633" s="4"/>
       <c r="C633" s="4"/>
@@ -20279,7 +20347,7 @@
       <c r="AB633" s="4"/>
       <c r="AC633" s="4"/>
     </row>
-    <row r="634" ht="15.75" customHeight="1">
+    <row r="634" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A634" s="4"/>
       <c r="B634" s="4"/>
       <c r="C634" s="4"/>
@@ -20310,7 +20378,7 @@
       <c r="AB634" s="4"/>
       <c r="AC634" s="4"/>
     </row>
-    <row r="635" ht="15.75" customHeight="1">
+    <row r="635" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A635" s="4"/>
       <c r="B635" s="4"/>
       <c r="C635" s="4"/>
@@ -20341,7 +20409,7 @@
       <c r="AB635" s="4"/>
       <c r="AC635" s="4"/>
     </row>
-    <row r="636" ht="15.75" customHeight="1">
+    <row r="636" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A636" s="4"/>
       <c r="B636" s="4"/>
       <c r="C636" s="4"/>
@@ -20372,7 +20440,7 @@
       <c r="AB636" s="4"/>
       <c r="AC636" s="4"/>
     </row>
-    <row r="637" ht="15.75" customHeight="1">
+    <row r="637" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A637" s="4"/>
       <c r="B637" s="4"/>
       <c r="C637" s="4"/>
@@ -20403,7 +20471,7 @@
       <c r="AB637" s="4"/>
       <c r="AC637" s="4"/>
     </row>
-    <row r="638" ht="15.75" customHeight="1">
+    <row r="638" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A638" s="4"/>
       <c r="B638" s="4"/>
       <c r="C638" s="4"/>
@@ -20434,7 +20502,7 @@
       <c r="AB638" s="4"/>
       <c r="AC638" s="4"/>
     </row>
-    <row r="639" ht="15.75" customHeight="1">
+    <row r="639" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A639" s="4"/>
       <c r="B639" s="4"/>
       <c r="C639" s="4"/>
@@ -20465,7 +20533,7 @@
       <c r="AB639" s="4"/>
       <c r="AC639" s="4"/>
     </row>
-    <row r="640" ht="15.75" customHeight="1">
+    <row r="640" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A640" s="4"/>
       <c r="B640" s="4"/>
       <c r="C640" s="4"/>
@@ -20496,7 +20564,7 @@
       <c r="AB640" s="4"/>
       <c r="AC640" s="4"/>
     </row>
-    <row r="641" ht="15.75" customHeight="1">
+    <row r="641" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A641" s="4"/>
       <c r="B641" s="4"/>
       <c r="C641" s="4"/>
@@ -20527,7 +20595,7 @@
       <c r="AB641" s="4"/>
       <c r="AC641" s="4"/>
     </row>
-    <row r="642" ht="15.75" customHeight="1">
+    <row r="642" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A642" s="4"/>
       <c r="B642" s="4"/>
       <c r="C642" s="4"/>
@@ -20558,7 +20626,7 @@
       <c r="AB642" s="4"/>
       <c r="AC642" s="4"/>
     </row>
-    <row r="643" ht="15.75" customHeight="1">
+    <row r="643" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A643" s="4"/>
       <c r="B643" s="4"/>
       <c r="C643" s="4"/>
@@ -20589,7 +20657,7 @@
       <c r="AB643" s="4"/>
       <c r="AC643" s="4"/>
     </row>
-    <row r="644" ht="15.75" customHeight="1">
+    <row r="644" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A644" s="4"/>
       <c r="B644" s="4"/>
       <c r="C644" s="4"/>
@@ -20620,7 +20688,7 @@
       <c r="AB644" s="4"/>
       <c r="AC644" s="4"/>
     </row>
-    <row r="645" ht="15.75" customHeight="1">
+    <row r="645" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A645" s="4"/>
       <c r="B645" s="4"/>
       <c r="C645" s="4"/>
@@ -20651,7 +20719,7 @@
       <c r="AB645" s="4"/>
       <c r="AC645" s="4"/>
     </row>
-    <row r="646" ht="15.75" customHeight="1">
+    <row r="646" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A646" s="4"/>
       <c r="B646" s="4"/>
       <c r="C646" s="4"/>
@@ -20682,7 +20750,7 @@
       <c r="AB646" s="4"/>
       <c r="AC646" s="4"/>
     </row>
-    <row r="647" ht="15.75" customHeight="1">
+    <row r="647" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A647" s="4"/>
       <c r="B647" s="4"/>
       <c r="C647" s="4"/>
@@ -20713,7 +20781,7 @@
       <c r="AB647" s="4"/>
       <c r="AC647" s="4"/>
     </row>
-    <row r="648" ht="15.75" customHeight="1">
+    <row r="648" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A648" s="4"/>
       <c r="B648" s="4"/>
       <c r="C648" s="4"/>
@@ -20744,7 +20812,7 @@
       <c r="AB648" s="4"/>
       <c r="AC648" s="4"/>
     </row>
-    <row r="649" ht="15.75" customHeight="1">
+    <row r="649" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A649" s="4"/>
       <c r="B649" s="4"/>
       <c r="C649" s="4"/>
@@ -20775,7 +20843,7 @@
       <c r="AB649" s="4"/>
       <c r="AC649" s="4"/>
     </row>
-    <row r="650" ht="15.75" customHeight="1">
+    <row r="650" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A650" s="4"/>
       <c r="B650" s="4"/>
       <c r="C650" s="4"/>
@@ -20806,7 +20874,7 @@
       <c r="AB650" s="4"/>
       <c r="AC650" s="4"/>
     </row>
-    <row r="651" ht="15.75" customHeight="1">
+    <row r="651" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A651" s="4"/>
       <c r="B651" s="4"/>
       <c r="C651" s="4"/>
@@ -20837,7 +20905,7 @@
       <c r="AB651" s="4"/>
       <c r="AC651" s="4"/>
     </row>
-    <row r="652" ht="15.75" customHeight="1">
+    <row r="652" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A652" s="4"/>
       <c r="B652" s="4"/>
       <c r="C652" s="4"/>
@@ -20868,7 +20936,7 @@
       <c r="AB652" s="4"/>
       <c r="AC652" s="4"/>
     </row>
-    <row r="653" ht="15.75" customHeight="1">
+    <row r="653" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A653" s="4"/>
       <c r="B653" s="4"/>
       <c r="C653" s="4"/>
@@ -20899,7 +20967,7 @@
       <c r="AB653" s="4"/>
       <c r="AC653" s="4"/>
     </row>
-    <row r="654" ht="15.75" customHeight="1">
+    <row r="654" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A654" s="4"/>
       <c r="B654" s="4"/>
       <c r="C654" s="4"/>
@@ -20930,7 +20998,7 @@
       <c r="AB654" s="4"/>
       <c r="AC654" s="4"/>
     </row>
-    <row r="655" ht="15.75" customHeight="1">
+    <row r="655" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A655" s="4"/>
       <c r="B655" s="4"/>
       <c r="C655" s="4"/>
@@ -20961,7 +21029,7 @@
       <c r="AB655" s="4"/>
       <c r="AC655" s="4"/>
     </row>
-    <row r="656" ht="15.75" customHeight="1">
+    <row r="656" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A656" s="4"/>
       <c r="B656" s="4"/>
       <c r="C656" s="4"/>
@@ -20992,7 +21060,7 @@
       <c r="AB656" s="4"/>
       <c r="AC656" s="4"/>
     </row>
-    <row r="657" ht="15.75" customHeight="1">
+    <row r="657" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A657" s="4"/>
       <c r="B657" s="4"/>
       <c r="C657" s="4"/>
@@ -21023,7 +21091,7 @@
       <c r="AB657" s="4"/>
       <c r="AC657" s="4"/>
     </row>
-    <row r="658" ht="15.75" customHeight="1">
+    <row r="658" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A658" s="4"/>
       <c r="B658" s="4"/>
       <c r="C658" s="4"/>
@@ -21054,7 +21122,7 @@
       <c r="AB658" s="4"/>
       <c r="AC658" s="4"/>
     </row>
-    <row r="659" ht="15.75" customHeight="1">
+    <row r="659" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A659" s="4"/>
       <c r="B659" s="4"/>
       <c r="C659" s="4"/>
@@ -21085,7 +21153,7 @@
       <c r="AB659" s="4"/>
       <c r="AC659" s="4"/>
     </row>
-    <row r="660" ht="15.75" customHeight="1">
+    <row r="660" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A660" s="4"/>
       <c r="B660" s="4"/>
       <c r="C660" s="4"/>
@@ -21116,7 +21184,7 @@
       <c r="AB660" s="4"/>
       <c r="AC660" s="4"/>
     </row>
-    <row r="661" ht="15.75" customHeight="1">
+    <row r="661" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A661" s="4"/>
       <c r="B661" s="4"/>
       <c r="C661" s="4"/>
@@ -21147,7 +21215,7 @@
       <c r="AB661" s="4"/>
       <c r="AC661" s="4"/>
     </row>
-    <row r="662" ht="15.75" customHeight="1">
+    <row r="662" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A662" s="4"/>
       <c r="B662" s="4"/>
       <c r="C662" s="4"/>
@@ -21178,7 +21246,7 @@
       <c r="AB662" s="4"/>
       <c r="AC662" s="4"/>
     </row>
-    <row r="663" ht="15.75" customHeight="1">
+    <row r="663" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A663" s="4"/>
       <c r="B663" s="4"/>
       <c r="C663" s="4"/>
@@ -21209,7 +21277,7 @@
       <c r="AB663" s="4"/>
       <c r="AC663" s="4"/>
     </row>
-    <row r="664" ht="15.75" customHeight="1">
+    <row r="664" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A664" s="4"/>
       <c r="B664" s="4"/>
       <c r="C664" s="4"/>
@@ -21240,7 +21308,7 @@
       <c r="AB664" s="4"/>
       <c r="AC664" s="4"/>
     </row>
-    <row r="665" ht="15.75" customHeight="1">
+    <row r="665" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A665" s="4"/>
       <c r="B665" s="4"/>
       <c r="C665" s="4"/>
@@ -21271,7 +21339,7 @@
       <c r="AB665" s="4"/>
       <c r="AC665" s="4"/>
     </row>
-    <row r="666" ht="15.75" customHeight="1">
+    <row r="666" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A666" s="4"/>
       <c r="B666" s="4"/>
       <c r="C666" s="4"/>
@@ -21302,7 +21370,7 @@
       <c r="AB666" s="4"/>
       <c r="AC666" s="4"/>
     </row>
-    <row r="667" ht="15.75" customHeight="1">
+    <row r="667" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A667" s="4"/>
       <c r="B667" s="4"/>
       <c r="C667" s="4"/>
@@ -21333,7 +21401,7 @@
       <c r="AB667" s="4"/>
       <c r="AC667" s="4"/>
     </row>
-    <row r="668" ht="15.75" customHeight="1">
+    <row r="668" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A668" s="4"/>
       <c r="B668" s="4"/>
       <c r="C668" s="4"/>
@@ -21364,7 +21432,7 @@
       <c r="AB668" s="4"/>
       <c r="AC668" s="4"/>
     </row>
-    <row r="669" ht="15.75" customHeight="1">
+    <row r="669" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A669" s="4"/>
       <c r="B669" s="4"/>
       <c r="C669" s="4"/>
@@ -21395,7 +21463,7 @@
       <c r="AB669" s="4"/>
       <c r="AC669" s="4"/>
     </row>
-    <row r="670" ht="15.75" customHeight="1">
+    <row r="670" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A670" s="4"/>
       <c r="B670" s="4"/>
       <c r="C670" s="4"/>
@@ -21426,7 +21494,7 @@
       <c r="AB670" s="4"/>
       <c r="AC670" s="4"/>
     </row>
-    <row r="671" ht="15.75" customHeight="1">
+    <row r="671" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A671" s="4"/>
       <c r="B671" s="4"/>
       <c r="C671" s="4"/>
@@ -21457,7 +21525,7 @@
       <c r="AB671" s="4"/>
       <c r="AC671" s="4"/>
     </row>
-    <row r="672" ht="15.75" customHeight="1">
+    <row r="672" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A672" s="4"/>
       <c r="B672" s="4"/>
       <c r="C672" s="4"/>
@@ -21488,7 +21556,7 @@
       <c r="AB672" s="4"/>
       <c r="AC672" s="4"/>
     </row>
-    <row r="673" ht="15.75" customHeight="1">
+    <row r="673" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A673" s="4"/>
       <c r="B673" s="4"/>
       <c r="C673" s="4"/>
@@ -21519,7 +21587,7 @@
       <c r="AB673" s="4"/>
       <c r="AC673" s="4"/>
     </row>
-    <row r="674" ht="15.75" customHeight="1">
+    <row r="674" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A674" s="4"/>
       <c r="B674" s="4"/>
       <c r="C674" s="4"/>
@@ -21550,7 +21618,7 @@
       <c r="AB674" s="4"/>
       <c r="AC674" s="4"/>
     </row>
-    <row r="675" ht="15.75" customHeight="1">
+    <row r="675" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A675" s="4"/>
       <c r="B675" s="4"/>
       <c r="C675" s="4"/>
@@ -21581,7 +21649,7 @@
       <c r="AB675" s="4"/>
       <c r="AC675" s="4"/>
     </row>
-    <row r="676" ht="15.75" customHeight="1">
+    <row r="676" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A676" s="4"/>
       <c r="B676" s="4"/>
       <c r="C676" s="4"/>
@@ -21612,7 +21680,7 @@
       <c r="AB676" s="4"/>
       <c r="AC676" s="4"/>
     </row>
-    <row r="677" ht="15.75" customHeight="1">
+    <row r="677" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A677" s="4"/>
       <c r="B677" s="4"/>
       <c r="C677" s="4"/>
@@ -21643,7 +21711,7 @@
       <c r="AB677" s="4"/>
       <c r="AC677" s="4"/>
     </row>
-    <row r="678" ht="15.75" customHeight="1">
+    <row r="678" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A678" s="4"/>
       <c r="B678" s="4"/>
       <c r="C678" s="4"/>
@@ -21674,7 +21742,7 @@
       <c r="AB678" s="4"/>
       <c r="AC678" s="4"/>
     </row>
-    <row r="679" ht="15.75" customHeight="1">
+    <row r="679" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A679" s="4"/>
       <c r="B679" s="4"/>
       <c r="C679" s="4"/>
@@ -21705,7 +21773,7 @@
       <c r="AB679" s="4"/>
       <c r="AC679" s="4"/>
     </row>
-    <row r="680" ht="15.75" customHeight="1">
+    <row r="680" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A680" s="4"/>
       <c r="B680" s="4"/>
       <c r="C680" s="4"/>
@@ -21736,7 +21804,7 @@
       <c r="AB680" s="4"/>
       <c r="AC680" s="4"/>
     </row>
-    <row r="681" ht="15.75" customHeight="1">
+    <row r="681" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A681" s="4"/>
       <c r="B681" s="4"/>
       <c r="C681" s="4"/>
@@ -21767,7 +21835,7 @@
       <c r="AB681" s="4"/>
       <c r="AC681" s="4"/>
     </row>
-    <row r="682" ht="15.75" customHeight="1">
+    <row r="682" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A682" s="4"/>
       <c r="B682" s="4"/>
       <c r="C682" s="4"/>
@@ -21798,7 +21866,7 @@
       <c r="AB682" s="4"/>
       <c r="AC682" s="4"/>
     </row>
-    <row r="683" ht="15.75" customHeight="1">
+    <row r="683" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A683" s="4"/>
       <c r="B683" s="4"/>
       <c r="C683" s="4"/>
@@ -21829,7 +21897,7 @@
       <c r="AB683" s="4"/>
       <c r="AC683" s="4"/>
     </row>
-    <row r="684" ht="15.75" customHeight="1">
+    <row r="684" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A684" s="4"/>
       <c r="B684" s="4"/>
       <c r="C684" s="4"/>
@@ -21860,7 +21928,7 @@
       <c r="AB684" s="4"/>
       <c r="AC684" s="4"/>
     </row>
-    <row r="685" ht="15.75" customHeight="1">
+    <row r="685" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A685" s="4"/>
       <c r="B685" s="4"/>
       <c r="C685" s="4"/>
@@ -21891,7 +21959,7 @@
       <c r="AB685" s="4"/>
       <c r="AC685" s="4"/>
     </row>
-    <row r="686" ht="15.75" customHeight="1">
+    <row r="686" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A686" s="4"/>
       <c r="B686" s="4"/>
       <c r="C686" s="4"/>
@@ -21922,7 +21990,7 @@
       <c r="AB686" s="4"/>
       <c r="AC686" s="4"/>
     </row>
-    <row r="687" ht="15.75" customHeight="1">
+    <row r="687" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A687" s="4"/>
       <c r="B687" s="4"/>
       <c r="C687" s="4"/>
@@ -21953,7 +22021,7 @@
       <c r="AB687" s="4"/>
       <c r="AC687" s="4"/>
     </row>
-    <row r="688" ht="15.75" customHeight="1">
+    <row r="688" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A688" s="4"/>
       <c r="B688" s="4"/>
       <c r="C688" s="4"/>
@@ -21984,7 +22052,7 @@
       <c r="AB688" s="4"/>
       <c r="AC688" s="4"/>
     </row>
-    <row r="689" ht="15.75" customHeight="1">
+    <row r="689" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A689" s="4"/>
       <c r="B689" s="4"/>
       <c r="C689" s="4"/>
@@ -22015,7 +22083,7 @@
       <c r="AB689" s="4"/>
       <c r="AC689" s="4"/>
     </row>
-    <row r="690" ht="15.75" customHeight="1">
+    <row r="690" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A690" s="4"/>
       <c r="B690" s="4"/>
       <c r="C690" s="4"/>
@@ -22046,7 +22114,7 @@
       <c r="AB690" s="4"/>
       <c r="AC690" s="4"/>
     </row>
-    <row r="691" ht="15.75" customHeight="1">
+    <row r="691" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A691" s="4"/>
       <c r="B691" s="4"/>
       <c r="C691" s="4"/>
@@ -22077,7 +22145,7 @@
       <c r="AB691" s="4"/>
       <c r="AC691" s="4"/>
     </row>
-    <row r="692" ht="15.75" customHeight="1">
+    <row r="692" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A692" s="4"/>
       <c r="B692" s="4"/>
       <c r="C692" s="4"/>
@@ -22108,7 +22176,7 @@
       <c r="AB692" s="4"/>
       <c r="AC692" s="4"/>
     </row>
-    <row r="693" ht="15.75" customHeight="1">
+    <row r="693" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A693" s="4"/>
       <c r="B693" s="4"/>
       <c r="C693" s="4"/>
@@ -22139,7 +22207,7 @@
       <c r="AB693" s="4"/>
       <c r="AC693" s="4"/>
     </row>
-    <row r="694" ht="15.75" customHeight="1">
+    <row r="694" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A694" s="4"/>
       <c r="B694" s="4"/>
       <c r="C694" s="4"/>
@@ -22170,7 +22238,7 @@
       <c r="AB694" s="4"/>
       <c r="AC694" s="4"/>
     </row>
-    <row r="695" ht="15.75" customHeight="1">
+    <row r="695" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A695" s="4"/>
       <c r="B695" s="4"/>
       <c r="C695" s="4"/>
@@ -22201,7 +22269,7 @@
       <c r="AB695" s="4"/>
       <c r="AC695" s="4"/>
     </row>
-    <row r="696" ht="15.75" customHeight="1">
+    <row r="696" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A696" s="4"/>
       <c r="B696" s="4"/>
       <c r="C696" s="4"/>
@@ -22232,7 +22300,7 @@
       <c r="AB696" s="4"/>
       <c r="AC696" s="4"/>
     </row>
-    <row r="697" ht="15.75" customHeight="1">
+    <row r="697" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A697" s="4"/>
       <c r="B697" s="4"/>
       <c r="C697" s="4"/>
@@ -22263,7 +22331,7 @@
       <c r="AB697" s="4"/>
       <c r="AC697" s="4"/>
     </row>
-    <row r="698" ht="15.75" customHeight="1">
+    <row r="698" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A698" s="4"/>
       <c r="B698" s="4"/>
       <c r="C698" s="4"/>
@@ -22294,7 +22362,7 @@
       <c r="AB698" s="4"/>
       <c r="AC698" s="4"/>
     </row>
-    <row r="699" ht="15.75" customHeight="1">
+    <row r="699" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A699" s="4"/>
       <c r="B699" s="4"/>
       <c r="C699" s="4"/>
@@ -22325,7 +22393,7 @@
       <c r="AB699" s="4"/>
       <c r="AC699" s="4"/>
     </row>
-    <row r="700" ht="15.75" customHeight="1">
+    <row r="700" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A700" s="4"/>
       <c r="B700" s="4"/>
       <c r="C700" s="4"/>
@@ -22356,7 +22424,7 @@
       <c r="AB700" s="4"/>
       <c r="AC700" s="4"/>
     </row>
-    <row r="701" ht="15.75" customHeight="1">
+    <row r="701" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A701" s="4"/>
       <c r="B701" s="4"/>
       <c r="C701" s="4"/>
@@ -22387,7 +22455,7 @@
       <c r="AB701" s="4"/>
       <c r="AC701" s="4"/>
     </row>
-    <row r="702" ht="15.75" customHeight="1">
+    <row r="702" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A702" s="4"/>
       <c r="B702" s="4"/>
       <c r="C702" s="4"/>
@@ -22418,7 +22486,7 @@
       <c r="AB702" s="4"/>
       <c r="AC702" s="4"/>
     </row>
-    <row r="703" ht="15.75" customHeight="1">
+    <row r="703" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A703" s="4"/>
       <c r="B703" s="4"/>
       <c r="C703" s="4"/>
@@ -22449,7 +22517,7 @@
       <c r="AB703" s="4"/>
       <c r="AC703" s="4"/>
     </row>
-    <row r="704" ht="15.75" customHeight="1">
+    <row r="704" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A704" s="4"/>
       <c r="B704" s="4"/>
       <c r="C704" s="4"/>
@@ -22480,7 +22548,7 @@
       <c r="AB704" s="4"/>
       <c r="AC704" s="4"/>
     </row>
-    <row r="705" ht="15.75" customHeight="1">
+    <row r="705" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A705" s="4"/>
       <c r="B705" s="4"/>
       <c r="C705" s="4"/>
@@ -22511,7 +22579,7 @@
       <c r="AB705" s="4"/>
       <c r="AC705" s="4"/>
     </row>
-    <row r="706" ht="15.75" customHeight="1">
+    <row r="706" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A706" s="4"/>
       <c r="B706" s="4"/>
       <c r="C706" s="4"/>
@@ -22542,7 +22610,7 @@
       <c r="AB706" s="4"/>
       <c r="AC706" s="4"/>
     </row>
-    <row r="707" ht="15.75" customHeight="1">
+    <row r="707" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A707" s="4"/>
       <c r="B707" s="4"/>
       <c r="C707" s="4"/>
@@ -22573,7 +22641,7 @@
       <c r="AB707" s="4"/>
       <c r="AC707" s="4"/>
     </row>
-    <row r="708" ht="15.75" customHeight="1">
+    <row r="708" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A708" s="4"/>
       <c r="B708" s="4"/>
       <c r="C708" s="4"/>
@@ -22604,7 +22672,7 @@
       <c r="AB708" s="4"/>
       <c r="AC708" s="4"/>
     </row>
-    <row r="709" ht="15.75" customHeight="1">
+    <row r="709" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A709" s="4"/>
       <c r="B709" s="4"/>
       <c r="C709" s="4"/>
@@ -22635,7 +22703,7 @@
       <c r="AB709" s="4"/>
       <c r="AC709" s="4"/>
     </row>
-    <row r="710" ht="15.75" customHeight="1">
+    <row r="710" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A710" s="4"/>
       <c r="B710" s="4"/>
       <c r="C710" s="4"/>
@@ -22666,7 +22734,7 @@
       <c r="AB710" s="4"/>
       <c r="AC710" s="4"/>
     </row>
-    <row r="711" ht="15.75" customHeight="1">
+    <row r="711" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A711" s="4"/>
       <c r="B711" s="4"/>
       <c r="C711" s="4"/>
@@ -22697,7 +22765,7 @@
       <c r="AB711" s="4"/>
       <c r="AC711" s="4"/>
     </row>
-    <row r="712" ht="15.75" customHeight="1">
+    <row r="712" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A712" s="4"/>
       <c r="B712" s="4"/>
       <c r="C712" s="4"/>
@@ -22728,7 +22796,7 @@
       <c r="AB712" s="4"/>
       <c r="AC712" s="4"/>
     </row>
-    <row r="713" ht="15.75" customHeight="1">
+    <row r="713" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A713" s="4"/>
       <c r="B713" s="4"/>
       <c r="C713" s="4"/>
@@ -22759,7 +22827,7 @@
       <c r="AB713" s="4"/>
       <c r="AC713" s="4"/>
     </row>
-    <row r="714" ht="15.75" customHeight="1">
+    <row r="714" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A714" s="4"/>
       <c r="B714" s="4"/>
       <c r="C714" s="4"/>
@@ -22790,7 +22858,7 @@
       <c r="AB714" s="4"/>
       <c r="AC714" s="4"/>
     </row>
-    <row r="715" ht="15.75" customHeight="1">
+    <row r="715" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A715" s="4"/>
       <c r="B715" s="4"/>
       <c r="C715" s="4"/>
@@ -22821,7 +22889,7 @@
       <c r="AB715" s="4"/>
       <c r="AC715" s="4"/>
     </row>
-    <row r="716" ht="15.75" customHeight="1">
+    <row r="716" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A716" s="4"/>
       <c r="B716" s="4"/>
       <c r="C716" s="4"/>
@@ -22852,7 +22920,7 @@
       <c r="AB716" s="4"/>
       <c r="AC716" s="4"/>
     </row>
-    <row r="717" ht="15.75" customHeight="1">
+    <row r="717" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A717" s="4"/>
       <c r="B717" s="4"/>
       <c r="C717" s="4"/>
@@ -22883,7 +22951,7 @@
       <c r="AB717" s="4"/>
       <c r="AC717" s="4"/>
     </row>
-    <row r="718" ht="15.75" customHeight="1">
+    <row r="718" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A718" s="4"/>
       <c r="B718" s="4"/>
       <c r="C718" s="4"/>
@@ -22914,7 +22982,7 @@
       <c r="AB718" s="4"/>
       <c r="AC718" s="4"/>
     </row>
-    <row r="719" ht="15.75" customHeight="1">
+    <row r="719" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A719" s="4"/>
       <c r="B719" s="4"/>
       <c r="C719" s="4"/>
@@ -22945,7 +23013,7 @@
       <c r="AB719" s="4"/>
       <c r="AC719" s="4"/>
     </row>
-    <row r="720" ht="15.75" customHeight="1">
+    <row r="720" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A720" s="4"/>
       <c r="B720" s="4"/>
       <c r="C720" s="4"/>
@@ -22976,7 +23044,7 @@
       <c r="AB720" s="4"/>
       <c r="AC720" s="4"/>
     </row>
-    <row r="721" ht="15.75" customHeight="1">
+    <row r="721" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A721" s="4"/>
       <c r="B721" s="4"/>
       <c r="C721" s="4"/>
@@ -23007,7 +23075,7 @@
       <c r="AB721" s="4"/>
       <c r="AC721" s="4"/>
     </row>
-    <row r="722" ht="15.75" customHeight="1">
+    <row r="722" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A722" s="4"/>
       <c r="B722" s="4"/>
       <c r="C722" s="4"/>
@@ -23038,7 +23106,7 @@
       <c r="AB722" s="4"/>
       <c r="AC722" s="4"/>
     </row>
-    <row r="723" ht="15.75" customHeight="1">
+    <row r="723" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A723" s="4"/>
       <c r="B723" s="4"/>
       <c r="C723" s="4"/>
@@ -23069,7 +23137,7 @@
       <c r="AB723" s="4"/>
       <c r="AC723" s="4"/>
     </row>
-    <row r="724" ht="15.75" customHeight="1">
+    <row r="724" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A724" s="4"/>
       <c r="B724" s="4"/>
       <c r="C724" s="4"/>
@@ -23100,7 +23168,7 @@
       <c r="AB724" s="4"/>
       <c r="AC724" s="4"/>
     </row>
-    <row r="725" ht="15.75" customHeight="1">
+    <row r="725" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A725" s="4"/>
       <c r="B725" s="4"/>
       <c r="C725" s="4"/>
@@ -23131,7 +23199,7 @@
       <c r="AB725" s="4"/>
       <c r="AC725" s="4"/>
     </row>
-    <row r="726" ht="15.75" customHeight="1">
+    <row r="726" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A726" s="4"/>
       <c r="B726" s="4"/>
       <c r="C726" s="4"/>
@@ -23162,7 +23230,7 @@
       <c r="AB726" s="4"/>
       <c r="AC726" s="4"/>
     </row>
-    <row r="727" ht="15.75" customHeight="1">
+    <row r="727" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A727" s="4"/>
       <c r="B727" s="4"/>
       <c r="C727" s="4"/>
@@ -23193,7 +23261,7 @@
       <c r="AB727" s="4"/>
       <c r="AC727" s="4"/>
     </row>
-    <row r="728" ht="15.75" customHeight="1">
+    <row r="728" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A728" s="4"/>
       <c r="B728" s="4"/>
       <c r="C728" s="4"/>
@@ -23224,7 +23292,7 @@
       <c r="AB728" s="4"/>
       <c r="AC728" s="4"/>
     </row>
-    <row r="729" ht="15.75" customHeight="1">
+    <row r="729" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A729" s="4"/>
       <c r="B729" s="4"/>
       <c r="C729" s="4"/>
@@ -23255,7 +23323,7 @@
       <c r="AB729" s="4"/>
       <c r="AC729" s="4"/>
     </row>
-    <row r="730" ht="15.75" customHeight="1">
+    <row r="730" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A730" s="4"/>
       <c r="B730" s="4"/>
       <c r="C730" s="4"/>
@@ -23286,7 +23354,7 @@
       <c r="AB730" s="4"/>
       <c r="AC730" s="4"/>
     </row>
-    <row r="731" ht="15.75" customHeight="1">
+    <row r="731" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A731" s="4"/>
       <c r="B731" s="4"/>
       <c r="C731" s="4"/>
@@ -23317,7 +23385,7 @@
       <c r="AB731" s="4"/>
       <c r="AC731" s="4"/>
     </row>
-    <row r="732" ht="15.75" customHeight="1">
+    <row r="732" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A732" s="4"/>
       <c r="B732" s="4"/>
       <c r="C732" s="4"/>
@@ -23348,7 +23416,7 @@
       <c r="AB732" s="4"/>
       <c r="AC732" s="4"/>
     </row>
-    <row r="733" ht="15.75" customHeight="1">
+    <row r="733" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A733" s="4"/>
       <c r="B733" s="4"/>
       <c r="C733" s="4"/>
@@ -23379,7 +23447,7 @@
       <c r="AB733" s="4"/>
       <c r="AC733" s="4"/>
     </row>
-    <row r="734" ht="15.75" customHeight="1">
+    <row r="734" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A734" s="4"/>
       <c r="B734" s="4"/>
       <c r="C734" s="4"/>
@@ -23410,7 +23478,7 @@
       <c r="AB734" s="4"/>
       <c r="AC734" s="4"/>
     </row>
-    <row r="735" ht="15.75" customHeight="1">
+    <row r="735" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A735" s="4"/>
       <c r="B735" s="4"/>
       <c r="C735" s="4"/>
@@ -23441,7 +23509,7 @@
       <c r="AB735" s="4"/>
       <c r="AC735" s="4"/>
     </row>
-    <row r="736" ht="15.75" customHeight="1">
+    <row r="736" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A736" s="4"/>
       <c r="B736" s="4"/>
       <c r="C736" s="4"/>
@@ -23472,7 +23540,7 @@
       <c r="AB736" s="4"/>
       <c r="AC736" s="4"/>
     </row>
-    <row r="737" ht="15.75" customHeight="1">
+    <row r="737" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A737" s="4"/>
       <c r="B737" s="4"/>
       <c r="C737" s="4"/>
@@ -23503,7 +23571,7 @@
       <c r="AB737" s="4"/>
       <c r="AC737" s="4"/>
     </row>
-    <row r="738" ht="15.75" customHeight="1">
+    <row r="738" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A738" s="4"/>
       <c r="B738" s="4"/>
       <c r="C738" s="4"/>
@@ -23534,7 +23602,7 @@
       <c r="AB738" s="4"/>
       <c r="AC738" s="4"/>
     </row>
-    <row r="739" ht="15.75" customHeight="1">
+    <row r="739" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A739" s="4"/>
       <c r="B739" s="4"/>
       <c r="C739" s="4"/>
@@ -23565,7 +23633,7 @@
       <c r="AB739" s="4"/>
       <c r="AC739" s="4"/>
     </row>
-    <row r="740" ht="15.75" customHeight="1">
+    <row r="740" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A740" s="4"/>
       <c r="B740" s="4"/>
       <c r="C740" s="4"/>
@@ -23596,7 +23664,7 @@
       <c r="AB740" s="4"/>
       <c r="AC740" s="4"/>
     </row>
-    <row r="741" ht="15.75" customHeight="1">
+    <row r="741" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A741" s="4"/>
       <c r="B741" s="4"/>
       <c r="C741" s="4"/>
@@ -23627,7 +23695,7 @@
       <c r="AB741" s="4"/>
       <c r="AC741" s="4"/>
     </row>
-    <row r="742" ht="15.75" customHeight="1">
+    <row r="742" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A742" s="4"/>
       <c r="B742" s="4"/>
       <c r="C742" s="4"/>
@@ -23658,7 +23726,7 @@
       <c r="AB742" s="4"/>
       <c r="AC742" s="4"/>
     </row>
-    <row r="743" ht="15.75" customHeight="1">
+    <row r="743" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A743" s="4"/>
       <c r="B743" s="4"/>
       <c r="C743" s="4"/>
@@ -23689,7 +23757,7 @@
       <c r="AB743" s="4"/>
       <c r="AC743" s="4"/>
     </row>
-    <row r="744" ht="15.75" customHeight="1">
+    <row r="744" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A744" s="4"/>
       <c r="B744" s="4"/>
       <c r="C744" s="4"/>
@@ -23720,7 +23788,7 @@
       <c r="AB744" s="4"/>
       <c r="AC744" s="4"/>
     </row>
-    <row r="745" ht="15.75" customHeight="1">
+    <row r="745" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A745" s="4"/>
       <c r="B745" s="4"/>
       <c r="C745" s="4"/>
@@ -23751,7 +23819,7 @@
       <c r="AB745" s="4"/>
       <c r="AC745" s="4"/>
     </row>
-    <row r="746" ht="15.75" customHeight="1">
+    <row r="746" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A746" s="4"/>
       <c r="B746" s="4"/>
       <c r="C746" s="4"/>
@@ -23782,7 +23850,7 @@
       <c r="AB746" s="4"/>
       <c r="AC746" s="4"/>
     </row>
-    <row r="747" ht="15.75" customHeight="1">
+    <row r="747" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A747" s="4"/>
       <c r="B747" s="4"/>
       <c r="C747" s="4"/>
@@ -23813,7 +23881,7 @@
       <c r="AB747" s="4"/>
       <c r="AC747" s="4"/>
     </row>
-    <row r="748" ht="15.75" customHeight="1">
+    <row r="748" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A748" s="4"/>
       <c r="B748" s="4"/>
       <c r="C748" s="4"/>
@@ -23844,7 +23912,7 @@
       <c r="AB748" s="4"/>
       <c r="AC748" s="4"/>
     </row>
-    <row r="749" ht="15.75" customHeight="1">
+    <row r="749" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A749" s="4"/>
       <c r="B749" s="4"/>
       <c r="C749" s="4"/>
@@ -23875,7 +23943,7 @@
       <c r="AB749" s="4"/>
       <c r="AC749" s="4"/>
     </row>
-    <row r="750" ht="15.75" customHeight="1">
+    <row r="750" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A750" s="4"/>
       <c r="B750" s="4"/>
       <c r="C750" s="4"/>
@@ -23906,7 +23974,7 @@
       <c r="AB750" s="4"/>
       <c r="AC750" s="4"/>
     </row>
-    <row r="751" ht="15.75" customHeight="1">
+    <row r="751" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A751" s="4"/>
       <c r="B751" s="4"/>
       <c r="C751" s="4"/>
@@ -23937,7 +24005,7 @@
       <c r="AB751" s="4"/>
       <c r="AC751" s="4"/>
     </row>
-    <row r="752" ht="15.75" customHeight="1">
+    <row r="752" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A752" s="4"/>
       <c r="B752" s="4"/>
       <c r="C752" s="4"/>
@@ -23968,7 +24036,7 @@
       <c r="AB752" s="4"/>
       <c r="AC752" s="4"/>
     </row>
-    <row r="753" ht="15.75" customHeight="1">
+    <row r="753" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A753" s="4"/>
       <c r="B753" s="4"/>
       <c r="C753" s="4"/>
@@ -23999,7 +24067,7 @@
       <c r="AB753" s="4"/>
       <c r="AC753" s="4"/>
     </row>
-    <row r="754" ht="15.75" customHeight="1">
+    <row r="754" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A754" s="4"/>
       <c r="B754" s="4"/>
       <c r="C754" s="4"/>
@@ -24030,7 +24098,7 @@
       <c r="AB754" s="4"/>
       <c r="AC754" s="4"/>
     </row>
-    <row r="755" ht="15.75" customHeight="1">
+    <row r="755" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A755" s="4"/>
       <c r="B755" s="4"/>
       <c r="C755" s="4"/>
@@ -24061,7 +24129,7 @@
       <c r="AB755" s="4"/>
       <c r="AC755" s="4"/>
     </row>
-    <row r="756" ht="15.75" customHeight="1">
+    <row r="756" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A756" s="4"/>
       <c r="B756" s="4"/>
       <c r="C756" s="4"/>
@@ -24092,7 +24160,7 @@
       <c r="AB756" s="4"/>
       <c r="AC756" s="4"/>
     </row>
-    <row r="757" ht="15.75" customHeight="1">
+    <row r="757" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A757" s="4"/>
       <c r="B757" s="4"/>
       <c r="C757" s="4"/>
@@ -24123,7 +24191,7 @@
       <c r="AB757" s="4"/>
       <c r="AC757" s="4"/>
     </row>
-    <row r="758" ht="15.75" customHeight="1">
+    <row r="758" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A758" s="4"/>
       <c r="B758" s="4"/>
       <c r="C758" s="4"/>
@@ -24154,7 +24222,7 @@
       <c r="AB758" s="4"/>
       <c r="AC758" s="4"/>
     </row>
-    <row r="759" ht="15.75" customHeight="1">
+    <row r="759" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A759" s="4"/>
       <c r="B759" s="4"/>
       <c r="C759" s="4"/>
@@ -24185,7 +24253,7 @@
       <c r="AB759" s="4"/>
       <c r="AC759" s="4"/>
     </row>
-    <row r="760" ht="15.75" customHeight="1">
+    <row r="760" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A760" s="4"/>
       <c r="B760" s="4"/>
       <c r="C760" s="4"/>
@@ -24216,7 +24284,7 @@
       <c r="AB760" s="4"/>
       <c r="AC760" s="4"/>
     </row>
-    <row r="761" ht="15.75" customHeight="1">
+    <row r="761" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A761" s="4"/>
       <c r="B761" s="4"/>
       <c r="C761" s="4"/>
@@ -24247,7 +24315,7 @@
       <c r="AB761" s="4"/>
       <c r="AC761" s="4"/>
     </row>
-    <row r="762" ht="15.75" customHeight="1">
+    <row r="762" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A762" s="4"/>
       <c r="B762" s="4"/>
       <c r="C762" s="4"/>
@@ -24278,7 +24346,7 @@
       <c r="AB762" s="4"/>
       <c r="AC762" s="4"/>
     </row>
-    <row r="763" ht="15.75" customHeight="1">
+    <row r="763" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A763" s="4"/>
       <c r="B763" s="4"/>
       <c r="C763" s="4"/>
@@ -24309,7 +24377,7 @@
       <c r="AB763" s="4"/>
       <c r="AC763" s="4"/>
     </row>
-    <row r="764" ht="15.75" customHeight="1">
+    <row r="764" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A764" s="4"/>
       <c r="B764" s="4"/>
       <c r="C764" s="4"/>
@@ -24340,7 +24408,7 @@
       <c r="AB764" s="4"/>
       <c r="AC764" s="4"/>
     </row>
-    <row r="765" ht="15.75" customHeight="1">
+    <row r="765" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A765" s="4"/>
       <c r="B765" s="4"/>
       <c r="C765" s="4"/>
@@ -24371,7 +24439,7 @@
       <c r="AB765" s="4"/>
       <c r="AC765" s="4"/>
     </row>
-    <row r="766" ht="15.75" customHeight="1">
+    <row r="766" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A766" s="4"/>
       <c r="B766" s="4"/>
       <c r="C766" s="4"/>
@@ -24402,7 +24470,7 @@
       <c r="AB766" s="4"/>
       <c r="AC766" s="4"/>
     </row>
-    <row r="767" ht="15.75" customHeight="1">
+    <row r="767" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A767" s="4"/>
       <c r="B767" s="4"/>
       <c r="C767" s="4"/>
@@ -24433,7 +24501,7 @@
       <c r="AB767" s="4"/>
       <c r="AC767" s="4"/>
     </row>
-    <row r="768" ht="15.75" customHeight="1">
+    <row r="768" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A768" s="4"/>
       <c r="B768" s="4"/>
       <c r="C768" s="4"/>
@@ -24464,7 +24532,7 @@
       <c r="AB768" s="4"/>
       <c r="AC768" s="4"/>
     </row>
-    <row r="769" ht="15.75" customHeight="1">
+    <row r="769" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A769" s="4"/>
       <c r="B769" s="4"/>
       <c r="C769" s="4"/>
@@ -24495,7 +24563,7 @@
       <c r="AB769" s="4"/>
       <c r="AC769" s="4"/>
     </row>
-    <row r="770" ht="15.75" customHeight="1">
+    <row r="770" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A770" s="4"/>
       <c r="B770" s="4"/>
       <c r="C770" s="4"/>
@@ -24526,7 +24594,7 @@
       <c r="AB770" s="4"/>
       <c r="AC770" s="4"/>
     </row>
-    <row r="771" ht="15.75" customHeight="1">
+    <row r="771" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A771" s="4"/>
       <c r="B771" s="4"/>
       <c r="C771" s="4"/>
@@ -24557,7 +24625,7 @@
       <c r="AB771" s="4"/>
       <c r="AC771" s="4"/>
     </row>
-    <row r="772" ht="15.75" customHeight="1">
+    <row r="772" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A772" s="4"/>
       <c r="B772" s="4"/>
       <c r="C772" s="4"/>
@@ -24588,7 +24656,7 @@
       <c r="AB772" s="4"/>
       <c r="AC772" s="4"/>
     </row>
-    <row r="773" ht="15.75" customHeight="1">
+    <row r="773" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A773" s="4"/>
       <c r="B773" s="4"/>
       <c r="C773" s="4"/>
@@ -24619,7 +24687,7 @@
       <c r="AB773" s="4"/>
       <c r="AC773" s="4"/>
     </row>
-    <row r="774" ht="15.75" customHeight="1">
+    <row r="774" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A774" s="4"/>
       <c r="B774" s="4"/>
       <c r="C774" s="4"/>
@@ -24650,7 +24718,7 @@
       <c r="AB774" s="4"/>
       <c r="AC774" s="4"/>
     </row>
-    <row r="775" ht="15.75" customHeight="1">
+    <row r="775" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A775" s="4"/>
       <c r="B775" s="4"/>
       <c r="C775" s="4"/>
@@ -24681,7 +24749,7 @@
       <c r="AB775" s="4"/>
       <c r="AC775" s="4"/>
     </row>
-    <row r="776" ht="15.75" customHeight="1">
+    <row r="776" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A776" s="4"/>
       <c r="B776" s="4"/>
       <c r="C776" s="4"/>
@@ -24712,7 +24780,7 @@
       <c r="AB776" s="4"/>
       <c r="AC776" s="4"/>
     </row>
-    <row r="777" ht="15.75" customHeight="1">
+    <row r="777" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A777" s="4"/>
       <c r="B777" s="4"/>
       <c r="C777" s="4"/>
@@ -24743,7 +24811,7 @@
       <c r="AB777" s="4"/>
       <c r="AC777" s="4"/>
     </row>
-    <row r="778" ht="15.75" customHeight="1">
+    <row r="778" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A778" s="4"/>
       <c r="B778" s="4"/>
       <c r="C778" s="4"/>
@@ -24774,7 +24842,7 @@
       <c r="AB778" s="4"/>
       <c r="AC778" s="4"/>
     </row>
-    <row r="779" ht="15.75" customHeight="1">
+    <row r="779" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A779" s="4"/>
       <c r="B779" s="4"/>
       <c r="C779" s="4"/>
@@ -24805,7 +24873,7 @@
       <c r="AB779" s="4"/>
       <c r="AC779" s="4"/>
     </row>
-    <row r="780" ht="15.75" customHeight="1">
+    <row r="780" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A780" s="4"/>
       <c r="B780" s="4"/>
       <c r="C780" s="4"/>
@@ -24836,7 +24904,7 @@
       <c r="AB780" s="4"/>
       <c r="AC780" s="4"/>
     </row>
-    <row r="781" ht="15.75" customHeight="1">
+    <row r="781" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A781" s="4"/>
       <c r="B781" s="4"/>
       <c r="C781" s="4"/>
@@ -24867,7 +24935,7 @@
       <c r="AB781" s="4"/>
       <c r="AC781" s="4"/>
     </row>
-    <row r="782" ht="15.75" customHeight="1">
+    <row r="782" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A782" s="4"/>
       <c r="B782" s="4"/>
       <c r="C782" s="4"/>
@@ -24898,7 +24966,7 @@
       <c r="AB782" s="4"/>
       <c r="AC782" s="4"/>
     </row>
-    <row r="783" ht="15.75" customHeight="1">
+    <row r="783" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A783" s="4"/>
       <c r="B783" s="4"/>
       <c r="C783" s="4"/>
@@ -24929,7 +24997,7 @@
       <c r="AB783" s="4"/>
       <c r="AC783" s="4"/>
     </row>
-    <row r="784" ht="15.75" customHeight="1">
+    <row r="784" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A784" s="4"/>
       <c r="B784" s="4"/>
       <c r="C784" s="4"/>
@@ -24960,7 +25028,7 @@
       <c r="AB784" s="4"/>
       <c r="AC784" s="4"/>
     </row>
-    <row r="785" ht="15.75" customHeight="1">
+    <row r="785" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A785" s="4"/>
       <c r="B785" s="4"/>
       <c r="C785" s="4"/>
@@ -24991,7 +25059,7 @@
       <c r="AB785" s="4"/>
       <c r="AC785" s="4"/>
     </row>
-    <row r="786" ht="15.75" customHeight="1">
+    <row r="786" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A786" s="4"/>
       <c r="B786" s="4"/>
       <c r="C786" s="4"/>
@@ -25022,7 +25090,7 @@
       <c r="AB786" s="4"/>
       <c r="AC786" s="4"/>
     </row>
-    <row r="787" ht="15.75" customHeight="1">
+    <row r="787" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A787" s="4"/>
       <c r="B787" s="4"/>
       <c r="C787" s="4"/>
@@ -25053,7 +25121,7 @@
       <c r="AB787" s="4"/>
       <c r="AC787" s="4"/>
     </row>
-    <row r="788" ht="15.75" customHeight="1">
+    <row r="788" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A788" s="4"/>
       <c r="B788" s="4"/>
       <c r="C788" s="4"/>
@@ -25084,7 +25152,7 @@
       <c r="AB788" s="4"/>
       <c r="AC788" s="4"/>
     </row>
-    <row r="789" ht="15.75" customHeight="1">
+    <row r="789" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A789" s="4"/>
       <c r="B789" s="4"/>
       <c r="C789" s="4"/>
@@ -25115,7 +25183,7 @@
       <c r="AB789" s="4"/>
       <c r="AC789" s="4"/>
     </row>
-    <row r="790" ht="15.75" customHeight="1">
+    <row r="790" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A790" s="4"/>
       <c r="B790" s="4"/>
       <c r="C790" s="4"/>
@@ -25146,7 +25214,7 @@
       <c r="AB790" s="4"/>
       <c r="AC790" s="4"/>
     </row>
-    <row r="791" ht="15.75" customHeight="1">
+    <row r="791" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A791" s="4"/>
       <c r="B791" s="4"/>
       <c r="C791" s="4"/>
@@ -25177,7 +25245,7 @@
       <c r="AB791" s="4"/>
       <c r="AC791" s="4"/>
     </row>
-    <row r="792" ht="15.75" customHeight="1">
+    <row r="792" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A792" s="4"/>
       <c r="B792" s="4"/>
       <c r="C792" s="4"/>
@@ -25208,7 +25276,7 @@
       <c r="AB792" s="4"/>
       <c r="AC792" s="4"/>
     </row>
-    <row r="793" ht="15.75" customHeight="1">
+    <row r="793" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A793" s="4"/>
       <c r="B793" s="4"/>
       <c r="C793" s="4"/>
@@ -25239,7 +25307,7 @@
       <c r="AB793" s="4"/>
       <c r="AC793" s="4"/>
     </row>
-    <row r="794" ht="15.75" customHeight="1">
+    <row r="794" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A794" s="4"/>
       <c r="B794" s="4"/>
       <c r="C794" s="4"/>
@@ -25270,7 +25338,7 @@
       <c r="AB794" s="4"/>
       <c r="AC794" s="4"/>
     </row>
-    <row r="795" ht="15.75" customHeight="1">
+    <row r="795" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A795" s="4"/>
       <c r="B795" s="4"/>
       <c r="C795" s="4"/>
@@ -25301,7 +25369,7 @@
       <c r="AB795" s="4"/>
       <c r="AC795" s="4"/>
     </row>
-    <row r="796" ht="15.75" customHeight="1">
+    <row r="796" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A796" s="4"/>
       <c r="B796" s="4"/>
       <c r="C796" s="4"/>
@@ -25332,7 +25400,7 @@
       <c r="AB796" s="4"/>
       <c r="AC796" s="4"/>
     </row>
-    <row r="797" ht="15.75" customHeight="1">
+    <row r="797" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A797" s="4"/>
       <c r="B797" s="4"/>
       <c r="C797" s="4"/>
@@ -25363,7 +25431,7 @@
       <c r="AB797" s="4"/>
       <c r="AC797" s="4"/>
     </row>
-    <row r="798" ht="15.75" customHeight="1">
+    <row r="798" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A798" s="4"/>
       <c r="B798" s="4"/>
       <c r="C798" s="4"/>
@@ -25394,7 +25462,7 @@
       <c r="AB798" s="4"/>
       <c r="AC798" s="4"/>
     </row>
-    <row r="799" ht="15.75" customHeight="1">
+    <row r="799" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A799" s="4"/>
       <c r="B799" s="4"/>
       <c r="C799" s="4"/>
@@ -25425,7 +25493,7 @@
       <c r="AB799" s="4"/>
       <c r="AC799" s="4"/>
     </row>
-    <row r="800" ht="15.75" customHeight="1">
+    <row r="800" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A800" s="4"/>
       <c r="B800" s="4"/>
       <c r="C800" s="4"/>
@@ -25456,7 +25524,7 @@
       <c r="AB800" s="4"/>
       <c r="AC800" s="4"/>
     </row>
-    <row r="801" ht="15.75" customHeight="1">
+    <row r="801" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A801" s="4"/>
       <c r="B801" s="4"/>
       <c r="C801" s="4"/>
@@ -25487,7 +25555,7 @@
       <c r="AB801" s="4"/>
       <c r="AC801" s="4"/>
     </row>
-    <row r="802" ht="15.75" customHeight="1">
+    <row r="802" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A802" s="4"/>
       <c r="B802" s="4"/>
       <c r="C802" s="4"/>
@@ -25518,7 +25586,7 @@
       <c r="AB802" s="4"/>
       <c r="AC802" s="4"/>
     </row>
-    <row r="803" ht="15.75" customHeight="1">
+    <row r="803" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A803" s="4"/>
       <c r="B803" s="4"/>
       <c r="C803" s="4"/>
@@ -25549,7 +25617,7 @@
       <c r="AB803" s="4"/>
       <c r="AC803" s="4"/>
     </row>
-    <row r="804" ht="15.75" customHeight="1">
+    <row r="804" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A804" s="4"/>
       <c r="B804" s="4"/>
       <c r="C804" s="4"/>
@@ -25580,7 +25648,7 @@
       <c r="AB804" s="4"/>
       <c r="AC804" s="4"/>
     </row>
-    <row r="805" ht="15.75" customHeight="1">
+    <row r="805" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A805" s="4"/>
       <c r="B805" s="4"/>
       <c r="C805" s="4"/>
@@ -25611,7 +25679,7 @@
       <c r="AB805" s="4"/>
       <c r="AC805" s="4"/>
     </row>
-    <row r="806" ht="15.75" customHeight="1">
+    <row r="806" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A806" s="4"/>
       <c r="B806" s="4"/>
       <c r="C806" s="4"/>
@@ -25642,7 +25710,7 @@
       <c r="AB806" s="4"/>
       <c r="AC806" s="4"/>
     </row>
-    <row r="807" ht="15.75" customHeight="1">
+    <row r="807" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A807" s="4"/>
       <c r="B807" s="4"/>
       <c r="C807" s="4"/>
@@ -25673,7 +25741,7 @@
       <c r="AB807" s="4"/>
       <c r="AC807" s="4"/>
     </row>
-    <row r="808" ht="15.75" customHeight="1">
+    <row r="808" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A808" s="4"/>
       <c r="B808" s="4"/>
       <c r="C808" s="4"/>
@@ -25704,7 +25772,7 @@
       <c r="AB808" s="4"/>
       <c r="AC808" s="4"/>
     </row>
-    <row r="809" ht="15.75" customHeight="1">
+    <row r="809" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A809" s="4"/>
       <c r="B809" s="4"/>
       <c r="C809" s="4"/>
@@ -25735,7 +25803,7 @@
       <c r="AB809" s="4"/>
       <c r="AC809" s="4"/>
     </row>
-    <row r="810" ht="15.75" customHeight="1">
+    <row r="810" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A810" s="4"/>
       <c r="B810" s="4"/>
       <c r="C810" s="4"/>
@@ -25766,7 +25834,7 @@
       <c r="AB810" s="4"/>
       <c r="AC810" s="4"/>
     </row>
-    <row r="811" ht="15.75" customHeight="1">
+    <row r="811" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A811" s="4"/>
       <c r="B811" s="4"/>
       <c r="C811" s="4"/>
@@ -25797,7 +25865,7 @@
       <c r="AB811" s="4"/>
       <c r="AC811" s="4"/>
     </row>
-    <row r="812" ht="15.75" customHeight="1">
+    <row r="812" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A812" s="4"/>
       <c r="B812" s="4"/>
       <c r="C812" s="4"/>
@@ -25828,7 +25896,7 @@
       <c r="AB812" s="4"/>
       <c r="AC812" s="4"/>
     </row>
-    <row r="813" ht="15.75" customHeight="1">
+    <row r="813" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A813" s="4"/>
       <c r="B813" s="4"/>
       <c r="C813" s="4"/>
@@ -25859,7 +25927,7 @@
       <c r="AB813" s="4"/>
       <c r="AC813" s="4"/>
     </row>
-    <row r="814" ht="15.75" customHeight="1">
+    <row r="814" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A814" s="4"/>
       <c r="B814" s="4"/>
       <c r="C814" s="4"/>
@@ -25890,7 +25958,7 @@
       <c r="AB814" s="4"/>
       <c r="AC814" s="4"/>
     </row>
-    <row r="815" ht="15.75" customHeight="1">
+    <row r="815" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A815" s="4"/>
       <c r="B815" s="4"/>
       <c r="C815" s="4"/>
@@ -25921,7 +25989,7 @@
       <c r="AB815" s="4"/>
       <c r="AC815" s="4"/>
     </row>
-    <row r="816" ht="15.75" customHeight="1">
+    <row r="816" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A816" s="4"/>
       <c r="B816" s="4"/>
       <c r="C816" s="4"/>
@@ -25952,7 +26020,7 @@
       <c r="AB816" s="4"/>
       <c r="AC816" s="4"/>
     </row>
-    <row r="817" ht="15.75" customHeight="1">
+    <row r="817" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A817" s="4"/>
       <c r="B817" s="4"/>
       <c r="C817" s="4"/>
@@ -25983,7 +26051,7 @@
       <c r="AB817" s="4"/>
       <c r="AC817" s="4"/>
     </row>
-    <row r="818" ht="15.75" customHeight="1">
+    <row r="818" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A818" s="4"/>
       <c r="B818" s="4"/>
       <c r="C818" s="4"/>
@@ -26014,7 +26082,7 @@
       <c r="AB818" s="4"/>
       <c r="AC818" s="4"/>
     </row>
-    <row r="819" ht="15.75" customHeight="1">
+    <row r="819" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A819" s="4"/>
       <c r="B819" s="4"/>
       <c r="C819" s="4"/>
@@ -26045,7 +26113,7 @@
       <c r="AB819" s="4"/>
       <c r="AC819" s="4"/>
     </row>
-    <row r="820" ht="15.75" customHeight="1">
+    <row r="820" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A820" s="4"/>
       <c r="B820" s="4"/>
       <c r="C820" s="4"/>
@@ -26076,7 +26144,7 @@
       <c r="AB820" s="4"/>
       <c r="AC820" s="4"/>
     </row>
-    <row r="821" ht="15.75" customHeight="1">
+    <row r="821" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A821" s="4"/>
       <c r="B821" s="4"/>
       <c r="C821" s="4"/>
@@ -26107,7 +26175,7 @@
       <c r="AB821" s="4"/>
       <c r="AC821" s="4"/>
     </row>
-    <row r="822" ht="15.75" customHeight="1">
+    <row r="822" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A822" s="4"/>
       <c r="B822" s="4"/>
       <c r="C822" s="4"/>
@@ -26138,7 +26206,7 @@
       <c r="AB822" s="4"/>
       <c r="AC822" s="4"/>
     </row>
-    <row r="823" ht="15.75" customHeight="1">
+    <row r="823" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A823" s="4"/>
       <c r="B823" s="4"/>
       <c r="C823" s="4"/>
@@ -26169,7 +26237,7 @@
       <c r="AB823" s="4"/>
       <c r="AC823" s="4"/>
     </row>
-    <row r="824" ht="15.75" customHeight="1">
+    <row r="824" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A824" s="4"/>
       <c r="B824" s="4"/>
       <c r="C824" s="4"/>
@@ -26200,7 +26268,7 @@
       <c r="AB824" s="4"/>
       <c r="AC824" s="4"/>
     </row>
-    <row r="825" ht="15.75" customHeight="1">
+    <row r="825" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A825" s="4"/>
       <c r="B825" s="4"/>
       <c r="C825" s="4"/>
@@ -26231,7 +26299,7 @@
       <c r="AB825" s="4"/>
       <c r="AC825" s="4"/>
     </row>
-    <row r="826" ht="15.75" customHeight="1">
+    <row r="826" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A826" s="4"/>
       <c r="B826" s="4"/>
       <c r="C826" s="4"/>
@@ -26262,7 +26330,7 @@
       <c r="AB826" s="4"/>
       <c r="AC826" s="4"/>
     </row>
-    <row r="827" ht="15.75" customHeight="1">
+    <row r="827" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A827" s="4"/>
       <c r="B827" s="4"/>
       <c r="C827" s="4"/>
@@ -26293,7 +26361,7 @@
       <c r="AB827" s="4"/>
       <c r="AC827" s="4"/>
     </row>
-    <row r="828" ht="15.75" customHeight="1">
+    <row r="828" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A828" s="4"/>
       <c r="B828" s="4"/>
       <c r="C828" s="4"/>
@@ -26324,7 +26392,7 @@
       <c r="AB828" s="4"/>
       <c r="AC828" s="4"/>
     </row>
-    <row r="829" ht="15.75" customHeight="1">
+    <row r="829" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A829" s="4"/>
       <c r="B829" s="4"/>
       <c r="C829" s="4"/>
@@ -26355,7 +26423,7 @@
       <c r="AB829" s="4"/>
       <c r="AC829" s="4"/>
     </row>
-    <row r="830" ht="15.75" customHeight="1">
+    <row r="830" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A830" s="4"/>
       <c r="B830" s="4"/>
       <c r="C830" s="4"/>
@@ -26386,7 +26454,7 @@
       <c r="AB830" s="4"/>
       <c r="AC830" s="4"/>
     </row>
-    <row r="831" ht="15.75" customHeight="1">
+    <row r="831" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A831" s="4"/>
       <c r="B831" s="4"/>
       <c r="C831" s="4"/>
@@ -26417,7 +26485,7 @@
       <c r="AB831" s="4"/>
       <c r="AC831" s="4"/>
     </row>
-    <row r="832" ht="15.75" customHeight="1">
+    <row r="832" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A832" s="4"/>
       <c r="B832" s="4"/>
       <c r="C832" s="4"/>
@@ -26448,7 +26516,7 @@
       <c r="AB832" s="4"/>
       <c r="AC832" s="4"/>
     </row>
-    <row r="833" ht="15.75" customHeight="1">
+    <row r="833" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A833" s="4"/>
       <c r="B833" s="4"/>
       <c r="C833" s="4"/>
@@ -26479,7 +26547,7 @@
       <c r="AB833" s="4"/>
       <c r="AC833" s="4"/>
     </row>
-    <row r="834" ht="15.75" customHeight="1">
+    <row r="834" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A834" s="4"/>
       <c r="B834" s="4"/>
       <c r="C834" s="4"/>
@@ -26510,7 +26578,7 @@
       <c r="AB834" s="4"/>
       <c r="AC834" s="4"/>
     </row>
-    <row r="835" ht="15.75" customHeight="1">
+    <row r="835" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A835" s="4"/>
       <c r="B835" s="4"/>
       <c r="C835" s="4"/>
@@ -26541,7 +26609,7 @@
       <c r="AB835" s="4"/>
       <c r="AC835" s="4"/>
     </row>
-    <row r="836" ht="15.75" customHeight="1">
+    <row r="836" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A836" s="4"/>
       <c r="B836" s="4"/>
       <c r="C836" s="4"/>
@@ -26572,7 +26640,7 @@
       <c r="AB836" s="4"/>
       <c r="AC836" s="4"/>
     </row>
-    <row r="837" ht="15.75" customHeight="1">
+    <row r="837" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A837" s="4"/>
       <c r="B837" s="4"/>
       <c r="C837" s="4"/>
@@ -26603,7 +26671,7 @@
       <c r="AB837" s="4"/>
       <c r="AC837" s="4"/>
     </row>
-    <row r="838" ht="15.75" customHeight="1">
+    <row r="838" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A838" s="4"/>
       <c r="B838" s="4"/>
       <c r="C838" s="4"/>
@@ -26634,7 +26702,7 @@
       <c r="AB838" s="4"/>
       <c r="AC838" s="4"/>
     </row>
-    <row r="839" ht="15.75" customHeight="1">
+    <row r="839" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A839" s="4"/>
       <c r="B839" s="4"/>
       <c r="C839" s="4"/>
@@ -26665,7 +26733,7 @@
       <c r="AB839" s="4"/>
       <c r="AC839" s="4"/>
     </row>
-    <row r="840" ht="15.75" customHeight="1">
+    <row r="840" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A840" s="4"/>
       <c r="B840" s="4"/>
       <c r="C840" s="4"/>
@@ -26696,7 +26764,7 @@
       <c r="AB840" s="4"/>
       <c r="AC840" s="4"/>
     </row>
-    <row r="841" ht="15.75" customHeight="1">
+    <row r="841" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A841" s="4"/>
       <c r="B841" s="4"/>
       <c r="C841" s="4"/>
@@ -26727,7 +26795,7 @@
       <c r="AB841" s="4"/>
       <c r="AC841" s="4"/>
     </row>
-    <row r="842" ht="15.75" customHeight="1">
+    <row r="842" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A842" s="4"/>
       <c r="B842" s="4"/>
       <c r="C842" s="4"/>
@@ -26758,7 +26826,7 @@
       <c r="AB842" s="4"/>
       <c r="AC842" s="4"/>
     </row>
-    <row r="843" ht="15.75" customHeight="1">
+    <row r="843" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A843" s="4"/>
       <c r="B843" s="4"/>
       <c r="C843" s="4"/>
@@ -26789,7 +26857,7 @@
       <c r="AB843" s="4"/>
       <c r="AC843" s="4"/>
     </row>
-    <row r="844" ht="15.75" customHeight="1">
+    <row r="844" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A844" s="4"/>
       <c r="B844" s="4"/>
       <c r="C844" s="4"/>
@@ -26820,7 +26888,7 @@
       <c r="AB844" s="4"/>
       <c r="AC844" s="4"/>
     </row>
-    <row r="845" ht="15.75" customHeight="1">
+    <row r="845" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A845" s="4"/>
       <c r="B845" s="4"/>
       <c r="C845" s="4"/>
@@ -26851,7 +26919,7 @@
       <c r="AB845" s="4"/>
       <c r="AC845" s="4"/>
     </row>
-    <row r="846" ht="15.75" customHeight="1">
+    <row r="846" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A846" s="4"/>
       <c r="B846" s="4"/>
       <c r="C846" s="4"/>
@@ -26882,7 +26950,7 @@
       <c r="AB846" s="4"/>
       <c r="AC846" s="4"/>
     </row>
-    <row r="847" ht="15.75" customHeight="1">
+    <row r="847" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A847" s="4"/>
       <c r="B847" s="4"/>
       <c r="C847" s="4"/>
@@ -26913,7 +26981,7 @@
       <c r="AB847" s="4"/>
       <c r="AC847" s="4"/>
     </row>
-    <row r="848" ht="15.75" customHeight="1">
+    <row r="848" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A848" s="4"/>
       <c r="B848" s="4"/>
       <c r="C848" s="4"/>
@@ -26944,7 +27012,7 @@
       <c r="AB848" s="4"/>
       <c r="AC848" s="4"/>
     </row>
-    <row r="849" ht="15.75" customHeight="1">
+    <row r="849" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A849" s="4"/>
       <c r="B849" s="4"/>
       <c r="C849" s="4"/>
@@ -26975,7 +27043,7 @@
       <c r="AB849" s="4"/>
       <c r="AC849" s="4"/>
     </row>
-    <row r="850" ht="15.75" customHeight="1">
+    <row r="850" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A850" s="4"/>
       <c r="B850" s="4"/>
       <c r="C850" s="4"/>
@@ -27006,7 +27074,7 @@
       <c r="AB850" s="4"/>
       <c r="AC850" s="4"/>
     </row>
-    <row r="851" ht="15.75" customHeight="1">
+    <row r="851" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A851" s="4"/>
       <c r="B851" s="4"/>
       <c r="C851" s="4"/>
@@ -27037,7 +27105,7 @@
       <c r="AB851" s="4"/>
       <c r="AC851" s="4"/>
     </row>
-    <row r="852" ht="15.75" customHeight="1">
+    <row r="852" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A852" s="4"/>
       <c r="B852" s="4"/>
       <c r="C852" s="4"/>
@@ -27068,7 +27136,7 @@
       <c r="AB852" s="4"/>
       <c r="AC852" s="4"/>
     </row>
-    <row r="853" ht="15.75" customHeight="1">
+    <row r="853" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A853" s="4"/>
       <c r="B853" s="4"/>
       <c r="C853" s="4"/>
@@ -27099,7 +27167,7 @@
       <c r="AB853" s="4"/>
       <c r="AC853" s="4"/>
     </row>
-    <row r="854" ht="15.75" customHeight="1">
+    <row r="854" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A854" s="4"/>
       <c r="B854" s="4"/>
       <c r="C854" s="4"/>
@@ -27130,7 +27198,7 @@
       <c r="AB854" s="4"/>
       <c r="AC854" s="4"/>
     </row>
-    <row r="855" ht="15.75" customHeight="1">
+    <row r="855" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A855" s="4"/>
       <c r="B855" s="4"/>
       <c r="C855" s="4"/>
@@ -27161,7 +27229,7 @@
       <c r="AB855" s="4"/>
       <c r="AC855" s="4"/>
     </row>
-    <row r="856" ht="15.75" customHeight="1">
+    <row r="856" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A856" s="4"/>
       <c r="B856" s="4"/>
       <c r="C856" s="4"/>
@@ -27192,7 +27260,7 @@
       <c r="AB856" s="4"/>
       <c r="AC856" s="4"/>
     </row>
-    <row r="857" ht="15.75" customHeight="1">
+    <row r="857" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A857" s="4"/>
       <c r="B857" s="4"/>
       <c r="C857" s="4"/>
@@ -27223,7 +27291,7 @@
       <c r="AB857" s="4"/>
       <c r="AC857" s="4"/>
     </row>
-    <row r="858" ht="15.75" customHeight="1">
+    <row r="858" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A858" s="4"/>
       <c r="B858" s="4"/>
       <c r="C858" s="4"/>
@@ -27254,7 +27322,7 @@
       <c r="AB858" s="4"/>
       <c r="AC858" s="4"/>
     </row>
-    <row r="859" ht="15.75" customHeight="1">
+    <row r="859" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A859" s="4"/>
       <c r="B859" s="4"/>
       <c r="C859" s="4"/>
@@ -27285,7 +27353,7 @@
       <c r="AB859" s="4"/>
       <c r="AC859" s="4"/>
     </row>
-    <row r="860" ht="15.75" customHeight="1">
+    <row r="860" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A860" s="4"/>
       <c r="B860" s="4"/>
       <c r="C860" s="4"/>
@@ -27316,7 +27384,7 @@
       <c r="AB860" s="4"/>
       <c r="AC860" s="4"/>
     </row>
-    <row r="861" ht="15.75" customHeight="1">
+    <row r="861" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A861" s="4"/>
       <c r="B861" s="4"/>
       <c r="C861" s="4"/>
@@ -27347,7 +27415,7 @@
       <c r="AB861" s="4"/>
       <c r="AC861" s="4"/>
     </row>
-    <row r="862" ht="15.75" customHeight="1">
+    <row r="862" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A862" s="4"/>
       <c r="B862" s="4"/>
       <c r="C862" s="4"/>
@@ -27378,7 +27446,7 @@
       <c r="AB862" s="4"/>
       <c r="AC862" s="4"/>
     </row>
-    <row r="863" ht="15.75" customHeight="1">
+    <row r="863" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A863" s="4"/>
       <c r="B863" s="4"/>
       <c r="C863" s="4"/>
@@ -27409,7 +27477,7 @@
       <c r="AB863" s="4"/>
       <c r="AC863" s="4"/>
     </row>
-    <row r="864" ht="15.75" customHeight="1">
+    <row r="864" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A864" s="4"/>
       <c r="B864" s="4"/>
       <c r="C864" s="4"/>
@@ -27440,7 +27508,7 @@
       <c r="AB864" s="4"/>
       <c r="AC864" s="4"/>
     </row>
-    <row r="865" ht="15.75" customHeight="1">
+    <row r="865" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A865" s="4"/>
       <c r="B865" s="4"/>
       <c r="C865" s="4"/>
@@ -27471,7 +27539,7 @@
       <c r="AB865" s="4"/>
       <c r="AC865" s="4"/>
     </row>
-    <row r="866" ht="15.75" customHeight="1">
+    <row r="866" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A866" s="4"/>
       <c r="B866" s="4"/>
       <c r="C866" s="4"/>
@@ -27502,7 +27570,7 @@
       <c r="AB866" s="4"/>
       <c r="AC866" s="4"/>
     </row>
-    <row r="867" ht="15.75" customHeight="1">
+    <row r="867" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A867" s="4"/>
       <c r="B867" s="4"/>
       <c r="C867" s="4"/>
@@ -27533,7 +27601,7 @@
       <c r="AB867" s="4"/>
       <c r="AC867" s="4"/>
     </row>
-    <row r="868" ht="15.75" customHeight="1">
+    <row r="868" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A868" s="4"/>
       <c r="B868" s="4"/>
       <c r="C868" s="4"/>
@@ -27564,7 +27632,7 @@
       <c r="AB868" s="4"/>
       <c r="AC868" s="4"/>
     </row>
-    <row r="869" ht="15.75" customHeight="1">
+    <row r="869" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A869" s="4"/>
       <c r="B869" s="4"/>
       <c r="C869" s="4"/>
@@ -27595,7 +27663,7 @@
       <c r="AB869" s="4"/>
       <c r="AC869" s="4"/>
     </row>
-    <row r="870" ht="15.75" customHeight="1">
+    <row r="870" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A870" s="4"/>
       <c r="B870" s="4"/>
       <c r="C870" s="4"/>
@@ -27626,7 +27694,7 @@
       <c r="AB870" s="4"/>
       <c r="AC870" s="4"/>
     </row>
-    <row r="871" ht="15.75" customHeight="1">
+    <row r="871" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A871" s="4"/>
       <c r="B871" s="4"/>
       <c r="C871" s="4"/>
@@ -27657,7 +27725,7 @@
       <c r="AB871" s="4"/>
       <c r="AC871" s="4"/>
     </row>
-    <row r="872" ht="15.75" customHeight="1">
+    <row r="872" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A872" s="4"/>
       <c r="B872" s="4"/>
       <c r="C872" s="4"/>
@@ -27688,7 +27756,7 @@
       <c r="AB872" s="4"/>
       <c r="AC872" s="4"/>
     </row>
-    <row r="873" ht="15.75" customHeight="1">
+    <row r="873" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A873" s="4"/>
       <c r="B873" s="4"/>
       <c r="C873" s="4"/>
@@ -27719,7 +27787,7 @@
       <c r="AB873" s="4"/>
       <c r="AC873" s="4"/>
     </row>
-    <row r="874" ht="15.75" customHeight="1">
+    <row r="874" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A874" s="4"/>
       <c r="B874" s="4"/>
       <c r="C874" s="4"/>
@@ -27750,7 +27818,7 @@
       <c r="AB874" s="4"/>
       <c r="AC874" s="4"/>
     </row>
-    <row r="875" ht="15.75" customHeight="1">
+    <row r="875" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A875" s="4"/>
       <c r="B875" s="4"/>
       <c r="C875" s="4"/>
@@ -27781,7 +27849,7 @@
       <c r="AB875" s="4"/>
       <c r="AC875" s="4"/>
     </row>
-    <row r="876" ht="15.75" customHeight="1">
+    <row r="876" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A876" s="4"/>
       <c r="B876" s="4"/>
       <c r="C876" s="4"/>
@@ -27812,7 +27880,7 @@
       <c r="AB876" s="4"/>
       <c r="AC876" s="4"/>
     </row>
-    <row r="877" ht="15.75" customHeight="1">
+    <row r="877" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A877" s="4"/>
       <c r="B877" s="4"/>
       <c r="C877" s="4"/>
@@ -27843,7 +27911,7 @@
       <c r="AB877" s="4"/>
       <c r="AC877" s="4"/>
     </row>
-    <row r="878" ht="15.75" customHeight="1">
+    <row r="878" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A878" s="4"/>
       <c r="B878" s="4"/>
       <c r="C878" s="4"/>
@@ -27874,7 +27942,7 @@
       <c r="AB878" s="4"/>
       <c r="AC878" s="4"/>
     </row>
-    <row r="879" ht="15.75" customHeight="1">
+    <row r="879" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A879" s="4"/>
       <c r="B879" s="4"/>
       <c r="C879" s="4"/>
@@ -27905,7 +27973,7 @@
       <c r="AB879" s="4"/>
       <c r="AC879" s="4"/>
     </row>
-    <row r="880" ht="15.75" customHeight="1">
+    <row r="880" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A880" s="4"/>
       <c r="B880" s="4"/>
       <c r="C880" s="4"/>
@@ -27936,7 +28004,7 @@
       <c r="AB880" s="4"/>
       <c r="AC880" s="4"/>
     </row>
-    <row r="881" ht="15.75" customHeight="1">
+    <row r="881" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A881" s="4"/>
       <c r="B881" s="4"/>
       <c r="C881" s="4"/>
@@ -27967,7 +28035,7 @@
       <c r="AB881" s="4"/>
       <c r="AC881" s="4"/>
     </row>
-    <row r="882" ht="15.75" customHeight="1">
+    <row r="882" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A882" s="4"/>
       <c r="B882" s="4"/>
       <c r="C882" s="4"/>
@@ -27998,7 +28066,7 @@
       <c r="AB882" s="4"/>
       <c r="AC882" s="4"/>
     </row>
-    <row r="883" ht="15.75" customHeight="1">
+    <row r="883" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A883" s="4"/>
       <c r="B883" s="4"/>
       <c r="C883" s="4"/>
@@ -28029,7 +28097,7 @@
       <c r="AB883" s="4"/>
       <c r="AC883" s="4"/>
     </row>
-    <row r="884" ht="15.75" customHeight="1">
+    <row r="884" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A884" s="4"/>
       <c r="B884" s="4"/>
       <c r="C884" s="4"/>
@@ -28060,7 +28128,7 @@
       <c r="AB884" s="4"/>
       <c r="AC884" s="4"/>
     </row>
-    <row r="885" ht="15.75" customHeight="1">
+    <row r="885" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A885" s="4"/>
       <c r="B885" s="4"/>
       <c r="C885" s="4"/>
@@ -28091,7 +28159,7 @@
       <c r="AB885" s="4"/>
       <c r="AC885" s="4"/>
     </row>
-    <row r="886" ht="15.75" customHeight="1">
+    <row r="886" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A886" s="4"/>
       <c r="B886" s="4"/>
       <c r="C886" s="4"/>
@@ -28122,7 +28190,7 @@
       <c r="AB886" s="4"/>
       <c r="AC886" s="4"/>
     </row>
-    <row r="887" ht="15.75" customHeight="1">
+    <row r="887" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A887" s="4"/>
       <c r="B887" s="4"/>
       <c r="C887" s="4"/>
@@ -28153,7 +28221,7 @@
       <c r="AB887" s="4"/>
       <c r="AC887" s="4"/>
     </row>
-    <row r="888" ht="15.75" customHeight="1">
+    <row r="888" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A888" s="4"/>
       <c r="B888" s="4"/>
       <c r="C888" s="4"/>
@@ -28184,7 +28252,7 @@
       <c r="AB888" s="4"/>
       <c r="AC888" s="4"/>
     </row>
-    <row r="889" ht="15.75" customHeight="1">
+    <row r="889" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A889" s="4"/>
       <c r="B889" s="4"/>
       <c r="C889" s="4"/>
@@ -28215,7 +28283,7 @@
       <c r="AB889" s="4"/>
       <c r="AC889" s="4"/>
     </row>
-    <row r="890" ht="15.75" customHeight="1">
+    <row r="890" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A890" s="4"/>
       <c r="B890" s="4"/>
       <c r="C890" s="4"/>
@@ -28246,7 +28314,7 @@
       <c r="AB890" s="4"/>
       <c r="AC890" s="4"/>
     </row>
-    <row r="891" ht="15.75" customHeight="1">
+    <row r="891" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A891" s="4"/>
       <c r="B891" s="4"/>
       <c r="C891" s="4"/>
@@ -28277,7 +28345,7 @@
       <c r="AB891" s="4"/>
       <c r="AC891" s="4"/>
     </row>
-    <row r="892" ht="15.75" customHeight="1">
+    <row r="892" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A892" s="4"/>
       <c r="B892" s="4"/>
       <c r="C892" s="4"/>
@@ -28308,7 +28376,7 @@
       <c r="AB892" s="4"/>
       <c r="AC892" s="4"/>
     </row>
-    <row r="893" ht="15.75" customHeight="1">
+    <row r="893" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A893" s="4"/>
       <c r="B893" s="4"/>
       <c r="C893" s="4"/>
@@ -28339,7 +28407,7 @@
       <c r="AB893" s="4"/>
       <c r="AC893" s="4"/>
     </row>
-    <row r="894" ht="15.75" customHeight="1">
+    <row r="894" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A894" s="4"/>
       <c r="B894" s="4"/>
       <c r="C894" s="4"/>
@@ -28370,7 +28438,7 @@
       <c r="AB894" s="4"/>
       <c r="AC894" s="4"/>
     </row>
-    <row r="895" ht="15.75" customHeight="1">
+    <row r="895" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A895" s="4"/>
       <c r="B895" s="4"/>
       <c r="C895" s="4"/>
@@ -28401,7 +28469,7 @@
       <c r="AB895" s="4"/>
       <c r="AC895" s="4"/>
     </row>
-    <row r="896" ht="15.75" customHeight="1">
+    <row r="896" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A896" s="4"/>
       <c r="B896" s="4"/>
       <c r="C896" s="4"/>
@@ -28432,7 +28500,7 @@
       <c r="AB896" s="4"/>
       <c r="AC896" s="4"/>
     </row>
-    <row r="897" ht="15.75" customHeight="1">
+    <row r="897" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A897" s="4"/>
       <c r="B897" s="4"/>
       <c r="C897" s="4"/>
@@ -28463,7 +28531,7 @@
       <c r="AB897" s="4"/>
       <c r="AC897" s="4"/>
     </row>
-    <row r="898" ht="15.75" customHeight="1">
+    <row r="898" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A898" s="4"/>
       <c r="B898" s="4"/>
       <c r="C898" s="4"/>
@@ -28494,7 +28562,7 @@
       <c r="AB898" s="4"/>
       <c r="AC898" s="4"/>
     </row>
-    <row r="899" ht="15.75" customHeight="1">
+    <row r="899" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A899" s="4"/>
       <c r="B899" s="4"/>
       <c r="C899" s="4"/>
@@ -28525,7 +28593,7 @@
       <c r="AB899" s="4"/>
       <c r="AC899" s="4"/>
     </row>
-    <row r="900" ht="15.75" customHeight="1">
+    <row r="900" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A900" s="4"/>
       <c r="B900" s="4"/>
       <c r="C900" s="4"/>
@@ -28556,7 +28624,7 @@
       <c r="AB900" s="4"/>
       <c r="AC900" s="4"/>
     </row>
-    <row r="901" ht="15.75" customHeight="1">
+    <row r="901" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A901" s="4"/>
       <c r="B901" s="4"/>
       <c r="C901" s="4"/>
@@ -28587,7 +28655,7 @@
       <c r="AB901" s="4"/>
       <c r="AC901" s="4"/>
     </row>
-    <row r="902" ht="15.75" customHeight="1">
+    <row r="902" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A902" s="4"/>
       <c r="B902" s="4"/>
       <c r="C902" s="4"/>
@@ -28618,7 +28686,7 @@
       <c r="AB902" s="4"/>
       <c r="AC902" s="4"/>
     </row>
-    <row r="903" ht="15.75" customHeight="1">
+    <row r="903" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A903" s="4"/>
       <c r="B903" s="4"/>
       <c r="C903" s="4"/>
@@ -28649,7 +28717,7 @@
       <c r="AB903" s="4"/>
       <c r="AC903" s="4"/>
     </row>
-    <row r="904" ht="15.75" customHeight="1">
+    <row r="904" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A904" s="4"/>
       <c r="B904" s="4"/>
       <c r="C904" s="4"/>
@@ -28680,7 +28748,7 @@
       <c r="AB904" s="4"/>
       <c r="AC904" s="4"/>
     </row>
-    <row r="905" ht="15.75" customHeight="1">
+    <row r="905" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A905" s="4"/>
       <c r="B905" s="4"/>
       <c r="C905" s="4"/>
@@ -28711,7 +28779,7 @@
       <c r="AB905" s="4"/>
       <c r="AC905" s="4"/>
     </row>
-    <row r="906" ht="15.75" customHeight="1">
+    <row r="906" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A906" s="4"/>
       <c r="B906" s="4"/>
       <c r="C906" s="4"/>
@@ -28742,7 +28810,7 @@
       <c r="AB906" s="4"/>
       <c r="AC906" s="4"/>
     </row>
-    <row r="907" ht="15.75" customHeight="1">
+    <row r="907" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A907" s="4"/>
       <c r="B907" s="4"/>
       <c r="C907" s="4"/>
@@ -28773,7 +28841,7 @@
       <c r="AB907" s="4"/>
       <c r="AC907" s="4"/>
     </row>
-    <row r="908" ht="15.75" customHeight="1">
+    <row r="908" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A908" s="4"/>
       <c r="B908" s="4"/>
       <c r="C908" s="4"/>
@@ -28804,7 +28872,7 @@
       <c r="AB908" s="4"/>
       <c r="AC908" s="4"/>
     </row>
-    <row r="909" ht="15.75" customHeight="1">
+    <row r="909" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A909" s="4"/>
       <c r="B909" s="4"/>
       <c r="C909" s="4"/>
@@ -28835,7 +28903,7 @@
       <c r="AB909" s="4"/>
       <c r="AC909" s="4"/>
     </row>
-    <row r="910" ht="15.75" customHeight="1">
+    <row r="910" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A910" s="4"/>
       <c r="B910" s="4"/>
       <c r="C910" s="4"/>
@@ -28866,7 +28934,7 @@
       <c r="AB910" s="4"/>
       <c r="AC910" s="4"/>
     </row>
-    <row r="911" ht="15.75" customHeight="1">
+    <row r="911" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A911" s="4"/>
       <c r="B911" s="4"/>
       <c r="C911" s="4"/>
@@ -28897,7 +28965,7 @@
       <c r="AB911" s="4"/>
       <c r="AC911" s="4"/>
     </row>
-    <row r="912" ht="15.75" customHeight="1">
+    <row r="912" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A912" s="4"/>
       <c r="B912" s="4"/>
       <c r="C912" s="4"/>
@@ -28928,7 +28996,7 @@
       <c r="AB912" s="4"/>
       <c r="AC912" s="4"/>
     </row>
-    <row r="913" ht="15.75" customHeight="1">
+    <row r="913" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A913" s="4"/>
       <c r="B913" s="4"/>
       <c r="C913" s="4"/>
@@ -28959,7 +29027,7 @@
       <c r="AB913" s="4"/>
       <c r="AC913" s="4"/>
     </row>
-    <row r="914" ht="15.75" customHeight="1">
+    <row r="914" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A914" s="4"/>
       <c r="B914" s="4"/>
       <c r="C914" s="4"/>
@@ -28990,7 +29058,7 @@
       <c r="AB914" s="4"/>
       <c r="AC914" s="4"/>
     </row>
-    <row r="915" ht="15.75" customHeight="1">
+    <row r="915" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A915" s="4"/>
       <c r="B915" s="4"/>
       <c r="C915" s="4"/>
@@ -29021,7 +29089,7 @@
       <c r="AB915" s="4"/>
       <c r="AC915" s="4"/>
     </row>
-    <row r="916" ht="15.75" customHeight="1">
+    <row r="916" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A916" s="4"/>
       <c r="B916" s="4"/>
       <c r="C916" s="4"/>
@@ -29052,7 +29120,7 @@
       <c r="AB916" s="4"/>
       <c r="AC916" s="4"/>
     </row>
-    <row r="917" ht="15.75" customHeight="1">
+    <row r="917" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A917" s="4"/>
       <c r="B917" s="4"/>
       <c r="C917" s="4"/>
@@ -29083,7 +29151,7 @@
       <c r="AB917" s="4"/>
       <c r="AC917" s="4"/>
     </row>
-    <row r="918" ht="15.75" customHeight="1">
+    <row r="918" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A918" s="4"/>
       <c r="B918" s="4"/>
       <c r="C918" s="4"/>
@@ -29114,7 +29182,7 @@
       <c r="AB918" s="4"/>
       <c r="AC918" s="4"/>
     </row>
-    <row r="919" ht="15.75" customHeight="1">
+    <row r="919" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A919" s="4"/>
       <c r="B919" s="4"/>
       <c r="C919" s="4"/>
@@ -29145,7 +29213,7 @@
       <c r="AB919" s="4"/>
       <c r="AC919" s="4"/>
     </row>
-    <row r="920" ht="15.75" customHeight="1">
+    <row r="920" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A920" s="4"/>
       <c r="B920" s="4"/>
       <c r="C920" s="4"/>
@@ -29176,7 +29244,7 @@
       <c r="AB920" s="4"/>
       <c r="AC920" s="4"/>
     </row>
-    <row r="921" ht="15.75" customHeight="1">
+    <row r="921" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A921" s="4"/>
       <c r="B921" s="4"/>
       <c r="C921" s="4"/>
@@ -29207,7 +29275,7 @@
       <c r="AB921" s="4"/>
       <c r="AC921" s="4"/>
     </row>
-    <row r="922" ht="15.75" customHeight="1">
+    <row r="922" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A922" s="4"/>
       <c r="B922" s="4"/>
       <c r="C922" s="4"/>
@@ -29238,7 +29306,7 @@
       <c r="AB922" s="4"/>
       <c r="AC922" s="4"/>
     </row>
-    <row r="923" ht="15.75" customHeight="1">
+    <row r="923" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A923" s="4"/>
       <c r="B923" s="4"/>
       <c r="C923" s="4"/>
@@ -29269,7 +29337,7 @@
       <c r="AB923" s="4"/>
       <c r="AC923" s="4"/>
     </row>
-    <row r="924" ht="15.75" customHeight="1">
+    <row r="924" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A924" s="4"/>
       <c r="B924" s="4"/>
       <c r="C924" s="4"/>
@@ -29300,7 +29368,7 @@
       <c r="AB924" s="4"/>
       <c r="AC924" s="4"/>
     </row>
-    <row r="925" ht="15.75" customHeight="1">
+    <row r="925" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A925" s="4"/>
       <c r="B925" s="4"/>
       <c r="C925" s="4"/>
@@ -29331,7 +29399,7 @@
       <c r="AB925" s="4"/>
       <c r="AC925" s="4"/>
     </row>
-    <row r="926" ht="15.75" customHeight="1">
+    <row r="926" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A926" s="4"/>
       <c r="B926" s="4"/>
       <c r="C926" s="4"/>
@@ -29362,7 +29430,7 @@
       <c r="AB926" s="4"/>
       <c r="AC926" s="4"/>
     </row>
-    <row r="927" ht="15.75" customHeight="1">
+    <row r="927" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A927" s="4"/>
       <c r="B927" s="4"/>
       <c r="C927" s="4"/>
@@ -29393,7 +29461,7 @@
       <c r="AB927" s="4"/>
       <c r="AC927" s="4"/>
     </row>
-    <row r="928" ht="15.75" customHeight="1">
+    <row r="928" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A928" s="4"/>
       <c r="B928" s="4"/>
       <c r="C928" s="4"/>
@@ -29424,7 +29492,7 @@
       <c r="AB928" s="4"/>
       <c r="AC928" s="4"/>
     </row>
-    <row r="929" ht="15.75" customHeight="1">
+    <row r="929" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A929" s="4"/>
       <c r="B929" s="4"/>
       <c r="C929" s="4"/>
@@ -29455,7 +29523,7 @@
       <c r="AB929" s="4"/>
       <c r="AC929" s="4"/>
     </row>
-    <row r="930" ht="15.75" customHeight="1">
+    <row r="930" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A930" s="4"/>
       <c r="B930" s="4"/>
       <c r="C930" s="4"/>
@@ -29486,7 +29554,7 @@
       <c r="AB930" s="4"/>
       <c r="AC930" s="4"/>
     </row>
-    <row r="931" ht="15.75" customHeight="1">
+    <row r="931" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A931" s="4"/>
       <c r="B931" s="4"/>
       <c r="C931" s="4"/>
@@ -29517,7 +29585,7 @@
       <c r="AB931" s="4"/>
       <c r="AC931" s="4"/>
     </row>
-    <row r="932" ht="15.75" customHeight="1">
+    <row r="932" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A932" s="4"/>
       <c r="B932" s="4"/>
       <c r="C932" s="4"/>
@@ -29548,7 +29616,7 @@
       <c r="AB932" s="4"/>
       <c r="AC932" s="4"/>
     </row>
-    <row r="933" ht="15.75" customHeight="1">
+    <row r="933" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A933" s="4"/>
       <c r="B933" s="4"/>
       <c r="C933" s="4"/>
@@ -29579,7 +29647,7 @@
       <c r="AB933" s="4"/>
       <c r="AC933" s="4"/>
     </row>
-    <row r="934" ht="15.75" customHeight="1">
+    <row r="934" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A934" s="4"/>
       <c r="B934" s="4"/>
       <c r="C934" s="4"/>
@@ -29610,7 +29678,7 @@
       <c r="AB934" s="4"/>
       <c r="AC934" s="4"/>
     </row>
-    <row r="935" ht="15.75" customHeight="1">
+    <row r="935" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A935" s="4"/>
       <c r="B935" s="4"/>
       <c r="C935" s="4"/>
@@ -29641,7 +29709,7 @@
       <c r="AB935" s="4"/>
       <c r="AC935" s="4"/>
     </row>
-    <row r="936" ht="15.75" customHeight="1">
+    <row r="936" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A936" s="4"/>
       <c r="B936" s="4"/>
       <c r="C936" s="4"/>
@@ -29672,7 +29740,7 @@
       <c r="AB936" s="4"/>
       <c r="AC936" s="4"/>
     </row>
-    <row r="937" ht="15.75" customHeight="1">
+    <row r="937" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A937" s="4"/>
       <c r="B937" s="4"/>
       <c r="C937" s="4"/>
@@ -29703,7 +29771,7 @@
       <c r="AB937" s="4"/>
       <c r="AC937" s="4"/>
     </row>
-    <row r="938" ht="15.75" customHeight="1">
+    <row r="938" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A938" s="4"/>
       <c r="B938" s="4"/>
       <c r="C938" s="4"/>
@@ -29734,7 +29802,7 @@
       <c r="AB938" s="4"/>
       <c r="AC938" s="4"/>
     </row>
-    <row r="939" ht="15.75" customHeight="1">
+    <row r="939" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A939" s="4"/>
       <c r="B939" s="4"/>
       <c r="C939" s="4"/>
@@ -29765,7 +29833,7 @@
       <c r="AB939" s="4"/>
       <c r="AC939" s="4"/>
     </row>
-    <row r="940" ht="15.75" customHeight="1">
+    <row r="940" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A940" s="4"/>
       <c r="B940" s="4"/>
       <c r="C940" s="4"/>
@@ -29796,7 +29864,7 @@
       <c r="AB940" s="4"/>
       <c r="AC940" s="4"/>
     </row>
-    <row r="941" ht="15.75" customHeight="1">
+    <row r="941" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A941" s="4"/>
       <c r="B941" s="4"/>
       <c r="C941" s="4"/>
@@ -29827,7 +29895,7 @@
       <c r="AB941" s="4"/>
       <c r="AC941" s="4"/>
     </row>
-    <row r="942" ht="15.75" customHeight="1">
+    <row r="942" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A942" s="4"/>
       <c r="B942" s="4"/>
       <c r="C942" s="4"/>
@@ -29858,7 +29926,7 @@
       <c r="AB942" s="4"/>
       <c r="AC942" s="4"/>
     </row>
-    <row r="943" ht="15.75" customHeight="1">
+    <row r="943" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A943" s="4"/>
       <c r="B943" s="4"/>
       <c r="C943" s="4"/>
@@ -29889,7 +29957,7 @@
       <c r="AB943" s="4"/>
       <c r="AC943" s="4"/>
     </row>
-    <row r="944" ht="15.75" customHeight="1">
+    <row r="944" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A944" s="4"/>
       <c r="B944" s="4"/>
       <c r="C944" s="4"/>
@@ -29920,7 +29988,7 @@
       <c r="AB944" s="4"/>
       <c r="AC944" s="4"/>
     </row>
-    <row r="945" ht="15.75" customHeight="1">
+    <row r="945" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A945" s="4"/>
       <c r="B945" s="4"/>
       <c r="C945" s="4"/>
@@ -29951,7 +30019,7 @@
       <c r="AB945" s="4"/>
       <c r="AC945" s="4"/>
     </row>
-    <row r="946" ht="15.75" customHeight="1">
+    <row r="946" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A946" s="4"/>
       <c r="B946" s="4"/>
       <c r="C946" s="4"/>
@@ -29982,7 +30050,7 @@
       <c r="AB946" s="4"/>
       <c r="AC946" s="4"/>
     </row>
-    <row r="947" ht="15.75" customHeight="1">
+    <row r="947" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A947" s="4"/>
       <c r="B947" s="4"/>
       <c r="C947" s="4"/>
@@ -30013,7 +30081,7 @@
       <c r="AB947" s="4"/>
       <c r="AC947" s="4"/>
     </row>
-    <row r="948" ht="15.75" customHeight="1">
+    <row r="948" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A948" s="4"/>
       <c r="B948" s="4"/>
       <c r="C948" s="4"/>
@@ -30044,7 +30112,7 @@
       <c r="AB948" s="4"/>
       <c r="AC948" s="4"/>
     </row>
-    <row r="949" ht="15.75" customHeight="1">
+    <row r="949" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A949" s="4"/>
       <c r="B949" s="4"/>
       <c r="C949" s="4"/>
@@ -30075,7 +30143,7 @@
       <c r="AB949" s="4"/>
       <c r="AC949" s="4"/>
     </row>
-    <row r="950" ht="15.75" customHeight="1">
+    <row r="950" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A950" s="4"/>
       <c r="B950" s="4"/>
       <c r="C950" s="4"/>
@@ -30106,7 +30174,7 @@
       <c r="AB950" s="4"/>
       <c r="AC950" s="4"/>
     </row>
-    <row r="951" ht="15.75" customHeight="1">
+    <row r="951" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A951" s="4"/>
       <c r="B951" s="4"/>
       <c r="C951" s="4"/>
@@ -30137,7 +30205,7 @@
       <c r="AB951" s="4"/>
       <c r="AC951" s="4"/>
     </row>
-    <row r="952" ht="15.75" customHeight="1">
+    <row r="952" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A952" s="4"/>
       <c r="B952" s="4"/>
       <c r="C952" s="4"/>
@@ -30168,7 +30236,7 @@
       <c r="AB952" s="4"/>
       <c r="AC952" s="4"/>
     </row>
-    <row r="953" ht="15.75" customHeight="1">
+    <row r="953" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A953" s="4"/>
       <c r="B953" s="4"/>
       <c r="C953" s="4"/>
@@ -30199,7 +30267,7 @@
       <c r="AB953" s="4"/>
       <c r="AC953" s="4"/>
     </row>
-    <row r="954" ht="15.75" customHeight="1">
+    <row r="954" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A954" s="4"/>
       <c r="B954" s="4"/>
       <c r="C954" s="4"/>
@@ -30230,7 +30298,7 @@
       <c r="AB954" s="4"/>
       <c r="AC954" s="4"/>
     </row>
-    <row r="955" ht="15.75" customHeight="1">
+    <row r="955" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A955" s="4"/>
       <c r="B955" s="4"/>
       <c r="C955" s="4"/>
@@ -30261,7 +30329,7 @@
       <c r="AB955" s="4"/>
       <c r="AC955" s="4"/>
     </row>
-    <row r="956" ht="15.75" customHeight="1">
+    <row r="956" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A956" s="4"/>
       <c r="B956" s="4"/>
       <c r="C956" s="4"/>
@@ -30292,7 +30360,7 @@
       <c r="AB956" s="4"/>
       <c r="AC956" s="4"/>
     </row>
-    <row r="957" ht="15.75" customHeight="1">
+    <row r="957" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A957" s="4"/>
       <c r="B957" s="4"/>
       <c r="C957" s="4"/>
@@ -30323,7 +30391,7 @@
       <c r="AB957" s="4"/>
       <c r="AC957" s="4"/>
     </row>
-    <row r="958" ht="15.75" customHeight="1">
+    <row r="958" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A958" s="4"/>
       <c r="B958" s="4"/>
       <c r="C958" s="4"/>
@@ -30354,7 +30422,7 @@
       <c r="AB958" s="4"/>
       <c r="AC958" s="4"/>
     </row>
-    <row r="959" ht="15.75" customHeight="1">
+    <row r="959" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A959" s="4"/>
       <c r="B959" s="4"/>
       <c r="C959" s="4"/>
@@ -30385,7 +30453,7 @@
       <c r="AB959" s="4"/>
       <c r="AC959" s="4"/>
     </row>
-    <row r="960" ht="15.75" customHeight="1">
+    <row r="960" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A960" s="4"/>
       <c r="B960" s="4"/>
       <c r="C960" s="4"/>
@@ -30416,7 +30484,7 @@
       <c r="AB960" s="4"/>
       <c r="AC960" s="4"/>
     </row>
-    <row r="961" ht="15.75" customHeight="1">
+    <row r="961" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A961" s="4"/>
       <c r="B961" s="4"/>
       <c r="C961" s="4"/>
@@ -30447,7 +30515,7 @@
       <c r="AB961" s="4"/>
       <c r="AC961" s="4"/>
     </row>
-    <row r="962" ht="15.75" customHeight="1">
+    <row r="962" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A962" s="4"/>
       <c r="B962" s="4"/>
       <c r="C962" s="4"/>
@@ -30478,7 +30546,7 @@
       <c r="AB962" s="4"/>
       <c r="AC962" s="4"/>
     </row>
-    <row r="963" ht="15.75" customHeight="1">
+    <row r="963" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A963" s="4"/>
       <c r="B963" s="4"/>
       <c r="C963" s="4"/>
@@ -30509,7 +30577,7 @@
       <c r="AB963" s="4"/>
       <c r="AC963" s="4"/>
     </row>
-    <row r="964" ht="15.75" customHeight="1">
+    <row r="964" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A964" s="4"/>
       <c r="B964" s="4"/>
       <c r="C964" s="4"/>
@@ -30540,7 +30608,7 @@
       <c r="AB964" s="4"/>
       <c r="AC964" s="4"/>
     </row>
-    <row r="965" ht="15.75" customHeight="1">
+    <row r="965" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A965" s="4"/>
       <c r="B965" s="4"/>
       <c r="C965" s="4"/>
@@ -30571,7 +30639,7 @@
       <c r="AB965" s="4"/>
       <c r="AC965" s="4"/>
     </row>
-    <row r="966" ht="15.75" customHeight="1">
+    <row r="966" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A966" s="4"/>
       <c r="B966" s="4"/>
       <c r="C966" s="4"/>
@@ -30602,7 +30670,7 @@
       <c r="AB966" s="4"/>
       <c r="AC966" s="4"/>
     </row>
-    <row r="967" ht="15.75" customHeight="1">
+    <row r="967" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A967" s="4"/>
       <c r="B967" s="4"/>
       <c r="C967" s="4"/>
@@ -30633,7 +30701,7 @@
       <c r="AB967" s="4"/>
       <c r="AC967" s="4"/>
     </row>
-    <row r="968" ht="15.75" customHeight="1">
+    <row r="968" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A968" s="4"/>
       <c r="B968" s="4"/>
       <c r="C968" s="4"/>
@@ -30664,7 +30732,7 @@
       <c r="AB968" s="4"/>
       <c r="AC968" s="4"/>
     </row>
-    <row r="969" ht="15.75" customHeight="1">
+    <row r="969" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A969" s="4"/>
       <c r="B969" s="4"/>
       <c r="C969" s="4"/>
@@ -30695,7 +30763,7 @@
       <c r="AB969" s="4"/>
       <c r="AC969" s="4"/>
     </row>
-    <row r="970" ht="15.75" customHeight="1">
+    <row r="970" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A970" s="4"/>
       <c r="B970" s="4"/>
       <c r="C970" s="4"/>
@@ -30726,7 +30794,7 @@
       <c r="AB970" s="4"/>
       <c r="AC970" s="4"/>
     </row>
-    <row r="971" ht="15.75" customHeight="1">
+    <row r="971" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A971" s="4"/>
       <c r="B971" s="4"/>
       <c r="C971" s="4"/>
@@ -30757,7 +30825,7 @@
       <c r="AB971" s="4"/>
       <c r="AC971" s="4"/>
     </row>
-    <row r="972" ht="15.75" customHeight="1">
+    <row r="972" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A972" s="4"/>
       <c r="B972" s="4"/>
       <c r="C972" s="4"/>
@@ -30788,7 +30856,7 @@
       <c r="AB972" s="4"/>
       <c r="AC972" s="4"/>
     </row>
-    <row r="973" ht="15.75" customHeight="1">
+    <row r="973" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A973" s="4"/>
       <c r="B973" s="4"/>
       <c r="C973" s="4"/>
@@ -30819,7 +30887,7 @@
       <c r="AB973" s="4"/>
       <c r="AC973" s="4"/>
     </row>
-    <row r="974" ht="15.75" customHeight="1">
+    <row r="974" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A974" s="4"/>
       <c r="B974" s="4"/>
       <c r="C974" s="4"/>
@@ -30850,7 +30918,7 @@
       <c r="AB974" s="4"/>
       <c r="AC974" s="4"/>
     </row>
-    <row r="975" ht="15.75" customHeight="1">
+    <row r="975" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A975" s="4"/>
       <c r="B975" s="4"/>
       <c r="C975" s="4"/>
@@ -30881,7 +30949,7 @@
       <c r="AB975" s="4"/>
       <c r="AC975" s="4"/>
     </row>
-    <row r="976" ht="15.75" customHeight="1">
+    <row r="976" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A976" s="4"/>
       <c r="B976" s="4"/>
       <c r="C976" s="4"/>
@@ -30912,7 +30980,7 @@
       <c r="AB976" s="4"/>
       <c r="AC976" s="4"/>
     </row>
-    <row r="977" ht="15.75" customHeight="1">
+    <row r="977" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A977" s="4"/>
       <c r="B977" s="4"/>
       <c r="C977" s="4"/>
@@ -30943,7 +31011,7 @@
       <c r="AB977" s="4"/>
       <c r="AC977" s="4"/>
     </row>
-    <row r="978" ht="15.75" customHeight="1">
+    <row r="978" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A978" s="4"/>
       <c r="B978" s="4"/>
       <c r="C978" s="4"/>
@@ -30974,7 +31042,7 @@
       <c r="AB978" s="4"/>
       <c r="AC978" s="4"/>
     </row>
-    <row r="979" ht="15.75" customHeight="1">
+    <row r="979" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A979" s="4"/>
       <c r="B979" s="4"/>
       <c r="C979" s="4"/>
@@ -31005,7 +31073,7 @@
       <c r="AB979" s="4"/>
       <c r="AC979" s="4"/>
     </row>
-    <row r="980" ht="15.75" customHeight="1">
+    <row r="980" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A980" s="4"/>
       <c r="B980" s="4"/>
       <c r="C980" s="4"/>
@@ -31036,7 +31104,7 @@
       <c r="AB980" s="4"/>
       <c r="AC980" s="4"/>
     </row>
-    <row r="981" ht="15.75" customHeight="1">
+    <row r="981" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A981" s="4"/>
       <c r="B981" s="4"/>
       <c r="C981" s="4"/>
@@ -31067,7 +31135,7 @@
       <c r="AB981" s="4"/>
       <c r="AC981" s="4"/>
     </row>
-    <row r="982" ht="15.75" customHeight="1">
+    <row r="982" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A982" s="4"/>
       <c r="B982" s="4"/>
       <c r="C982" s="4"/>
@@ -31098,7 +31166,7 @@
       <c r="AB982" s="4"/>
       <c r="AC982" s="4"/>
     </row>
-    <row r="983" ht="15.75" customHeight="1">
+    <row r="983" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A983" s="4"/>
       <c r="B983" s="4"/>
       <c r="C983" s="4"/>
@@ -31129,7 +31197,7 @@
       <c r="AB983" s="4"/>
       <c r="AC983" s="4"/>
     </row>
-    <row r="984" ht="15.75" customHeight="1">
+    <row r="984" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A984" s="4"/>
       <c r="B984" s="4"/>
       <c r="C984" s="4"/>
@@ -31160,7 +31228,7 @@
       <c r="AB984" s="4"/>
       <c r="AC984" s="4"/>
     </row>
-    <row r="985" ht="15.75" customHeight="1">
+    <row r="985" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A985" s="4"/>
       <c r="B985" s="4"/>
       <c r="C985" s="4"/>
@@ -31191,7 +31259,7 @@
       <c r="AB985" s="4"/>
       <c r="AC985" s="4"/>
     </row>
-    <row r="986" ht="15.75" customHeight="1">
+    <row r="986" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A986" s="4"/>
       <c r="B986" s="4"/>
       <c r="C986" s="4"/>
@@ -31222,7 +31290,7 @@
       <c r="AB986" s="4"/>
       <c r="AC986" s="4"/>
     </row>
-    <row r="987" ht="15.75" customHeight="1">
+    <row r="987" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A987" s="4"/>
       <c r="B987" s="4"/>
       <c r="C987" s="4"/>
@@ -31253,7 +31321,7 @@
       <c r="AB987" s="4"/>
       <c r="AC987" s="4"/>
     </row>
-    <row r="988" ht="15.75" customHeight="1">
+    <row r="988" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A988" s="4"/>
       <c r="B988" s="4"/>
       <c r="C988" s="4"/>
@@ -31284,7 +31352,7 @@
       <c r="AB988" s="4"/>
       <c r="AC988" s="4"/>
     </row>
-    <row r="989" ht="15.75" customHeight="1">
+    <row r="989" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A989" s="4"/>
       <c r="B989" s="4"/>
       <c r="C989" s="4"/>
@@ -31315,7 +31383,7 @@
       <c r="AB989" s="4"/>
       <c r="AC989" s="4"/>
     </row>
-    <row r="990" ht="15.75" customHeight="1">
+    <row r="990" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A990" s="4"/>
       <c r="B990" s="4"/>
       <c r="C990" s="4"/>
@@ -31346,7 +31414,7 @@
       <c r="AB990" s="4"/>
       <c r="AC990" s="4"/>
     </row>
-    <row r="991" ht="15.75" customHeight="1">
+    <row r="991" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A991" s="4"/>
       <c r="B991" s="4"/>
       <c r="C991" s="4"/>
@@ -31377,7 +31445,7 @@
       <c r="AB991" s="4"/>
       <c r="AC991" s="4"/>
     </row>
-    <row r="992" ht="15.75" customHeight="1">
+    <row r="992" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A992" s="4"/>
       <c r="B992" s="4"/>
       <c r="C992" s="4"/>
@@ -31408,7 +31476,7 @@
       <c r="AB992" s="4"/>
       <c r="AC992" s="4"/>
     </row>
-    <row r="993" ht="15.75" customHeight="1">
+    <row r="993" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A993" s="4"/>
       <c r="B993" s="4"/>
       <c r="C993" s="4"/>
@@ -31439,7 +31507,7 @@
       <c r="AB993" s="4"/>
       <c r="AC993" s="4"/>
     </row>
-    <row r="994" ht="15.75" customHeight="1">
+    <row r="994" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A994" s="4"/>
       <c r="B994" s="4"/>
       <c r="C994" s="4"/>
@@ -31470,7 +31538,7 @@
       <c r="AB994" s="4"/>
       <c r="AC994" s="4"/>
     </row>
-    <row r="995" ht="15.75" customHeight="1">
+    <row r="995" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A995" s="4"/>
       <c r="B995" s="4"/>
       <c r="C995" s="4"/>
@@ -31501,7 +31569,7 @@
       <c r="AB995" s="4"/>
       <c r="AC995" s="4"/>
     </row>
-    <row r="996" ht="15.75" customHeight="1">
+    <row r="996" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A996" s="4"/>
       <c r="B996" s="4"/>
       <c r="C996" s="4"/>
@@ -31532,7 +31600,7 @@
       <c r="AB996" s="4"/>
       <c r="AC996" s="4"/>
     </row>
-    <row r="997" ht="15.75" customHeight="1">
+    <row r="997" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A997" s="4"/>
       <c r="B997" s="4"/>
       <c r="C997" s="4"/>
@@ -31563,7 +31631,7 @@
       <c r="AB997" s="4"/>
       <c r="AC997" s="4"/>
     </row>
-    <row r="998" ht="15.75" customHeight="1">
+    <row r="998" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A998" s="4"/>
       <c r="B998" s="4"/>
       <c r="C998" s="4"/>
@@ -31594,7 +31662,7 @@
       <c r="AB998" s="4"/>
       <c r="AC998" s="4"/>
     </row>
-    <row r="999" ht="15.75" customHeight="1">
+    <row r="999" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A999" s="4"/>
       <c r="B999" s="4"/>
       <c r="C999" s="4"/>
@@ -31625,7 +31693,7 @@
       <c r="AB999" s="4"/>
       <c r="AC999" s="4"/>
     </row>
-    <row r="1000" ht="15.75" customHeight="1">
+    <row r="1000" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1000" s="4"/>
       <c r="B1000" s="4"/>
       <c r="C1000" s="4"/>
@@ -31656,7 +31724,7 @@
       <c r="AB1000" s="4"/>
       <c r="AC1000" s="4"/>
     </row>
-    <row r="1001" ht="15.75" customHeight="1">
+    <row r="1001" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1001" s="4"/>
       <c r="B1001" s="4"/>
       <c r="C1001" s="4"/>
@@ -31687,7 +31755,7 @@
       <c r="AB1001" s="4"/>
       <c r="AC1001" s="4"/>
     </row>
-    <row r="1002" ht="15.75" customHeight="1">
+    <row r="1002" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1002" s="4"/>
       <c r="B1002" s="4"/>
       <c r="C1002" s="4"/>
@@ -31718,7 +31786,7 @@
       <c r="AB1002" s="4"/>
       <c r="AC1002" s="4"/>
     </row>
-    <row r="1003" ht="15.75" customHeight="1">
+    <row r="1003" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1003" s="4"/>
       <c r="B1003" s="4"/>
       <c r="C1003" s="4"/>
@@ -31749,7 +31817,7 @@
       <c r="AB1003" s="4"/>
       <c r="AC1003" s="4"/>
     </row>
-    <row r="1004" ht="15.75" customHeight="1">
+    <row r="1004" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1004" s="4"/>
       <c r="B1004" s="4"/>
       <c r="C1004" s="4"/>
@@ -31780,7 +31848,7 @@
       <c r="AB1004" s="4"/>
       <c r="AC1004" s="4"/>
     </row>
-    <row r="1005" ht="15.75" customHeight="1">
+    <row r="1005" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1005" s="4"/>
       <c r="B1005" s="4"/>
       <c r="C1005" s="4"/>
@@ -31811,7 +31879,7 @@
       <c r="AB1005" s="4"/>
       <c r="AC1005" s="4"/>
     </row>
-    <row r="1006" ht="15.75" customHeight="1">
+    <row r="1006" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1006" s="4"/>
       <c r="B1006" s="4"/>
       <c r="C1006" s="4"/>
@@ -31842,7 +31910,7 @@
       <c r="AB1006" s="4"/>
       <c r="AC1006" s="4"/>
     </row>
-    <row r="1007" ht="15.75" customHeight="1">
+    <row r="1007" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1007" s="4"/>
       <c r="B1007" s="4"/>
       <c r="C1007" s="4"/>
@@ -31873,7 +31941,7 @@
       <c r="AB1007" s="4"/>
       <c r="AC1007" s="4"/>
     </row>
-    <row r="1008" ht="15.75" customHeight="1">
+    <row r="1008" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1008" s="4"/>
       <c r="B1008" s="4"/>
       <c r="C1008" s="4"/>
@@ -31904,7 +31972,7 @@
       <c r="AB1008" s="4"/>
       <c r="AC1008" s="4"/>
     </row>
-    <row r="1009" ht="15.75" customHeight="1">
+    <row r="1009" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1009" s="4"/>
       <c r="B1009" s="4"/>
       <c r="C1009" s="4"/>
@@ -31935,7 +32003,7 @@
       <c r="AB1009" s="4"/>
       <c r="AC1009" s="4"/>
     </row>
-    <row r="1010" ht="15.75" customHeight="1">
+    <row r="1010" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1010" s="4"/>
       <c r="B1010" s="4"/>
       <c r="C1010" s="4"/>
@@ -31967,10 +32035,9 @@
       <c r="AC1010" s="4"/>
     </row>
   </sheetData>
-  <printOptions/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
+  <phoneticPr fontId="5" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <drawing r:id="rId2"/>
-  <legacyDrawing r:id="rId3"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/Data/CombatInputPanel.xlsx
+++ b/Data/CombatInputPanel.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\CombatCalculatorTest\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21B9DB26-E924-41B0-AB2D-9DFB20F6268B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52DC344D-2BE9-4094-9DE8-2C5AB2C79D28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,6 +37,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Arial"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>從0開始
@@ -51,11 +52,57 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Arial"/>
+            <family val="3"/>
+            <charset val="136"/>
             <scheme val="minor"/>
           </rPr>
-          <t>角色搭配的夥伴是否符合角色職業
+          <t xml:space="preserve">角色搭配的夥伴是否符合角色職業
 有的話才會應用額外的能力加成
-======</t>
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">======
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+            <family val="3"/>
+            <charset val="136"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>可移除，相同職業用</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>class</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+            <family val="3"/>
+            <charset val="136"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">欄位判斷
+</t>
         </r>
       </text>
     </comment>
@@ -66,6 +113,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Arial"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>從1開始
@@ -80,6 +128,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Arial"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>最多裝6個
@@ -95,6 +144,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Arial"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>0~5
@@ -109,6 +159,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Arial"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>最多裝3個
@@ -136,9 +187,6 @@
   </si>
   <si>
     <t>PartnerStackCount</t>
-  </si>
-  <si>
-    <t>IsPartnerBonusApplied</t>
   </si>
   <si>
     <t>AffectionLevel</t>
@@ -204,17 +252,22 @@
     <t>Cassius</t>
   </si>
   <si>
-    <t>Partner002</t>
+    <t>Mika</t>
   </si>
   <si>
-    <t>Mika</t>
+    <t>Partner003</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>IsPartnerBonusApplied</t>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -225,21 +278,25 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -249,8 +306,23 @@
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="3"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -273,6 +345,18 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFB7B7B7"/>
         <bgColor rgb="FFB7B7B7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor rgb="FFFCE5CD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -303,7 +387,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -317,6 +401,10 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -541,7 +629,7 @@
     <col min="1" max="3" width="9.5703125" customWidth="1"/>
     <col min="4" max="4" width="11.42578125" customWidth="1"/>
     <col min="5" max="5" width="20.5703125" customWidth="1"/>
-    <col min="6" max="6" width="22.85546875" customWidth="1"/>
+    <col min="6" max="6" width="22.85546875" style="16" customWidth="1"/>
     <col min="7" max="7" width="12.7109375" customWidth="1"/>
     <col min="8" max="8" width="22.42578125" customWidth="1"/>
     <col min="9" max="9" width="20.28515625" customWidth="1"/>
@@ -570,41 +658,41 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="K1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="L1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="N1" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="O1" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="P1" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="Q1" s="3" t="s">
         <v>15</v>
-      </c>
-      <c r="Q1" s="3" t="s">
-        <v>16</v>
       </c>
       <c r="R1" s="4"/>
       <c r="S1" s="4"/>
@@ -621,13 +709,13 @@
     </row>
     <row r="2" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B2" s="5">
         <v>10</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D2" s="5">
         <v>5</v>
@@ -635,26 +723,26 @@
       <c r="E2" s="5">
         <v>4</v>
       </c>
-      <c r="F2" s="6" t="b">
+      <c r="F2" s="14" t="b">
         <v>0</v>
       </c>
       <c r="G2" s="5">
         <v>1</v>
       </c>
       <c r="H2" s="7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I2" s="5">
         <v>0</v>
       </c>
       <c r="J2" s="7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K2" s="8">
         <v>1</v>
       </c>
       <c r="L2" s="9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="M2" s="5"/>
       <c r="N2" s="5"/>
@@ -680,18 +768,18 @@
       <c r="C3" s="6"/>
       <c r="D3" s="5"/>
       <c r="E3" s="5"/>
-      <c r="F3" s="6"/>
+      <c r="F3" s="14"/>
       <c r="G3" s="5"/>
       <c r="H3" s="7"/>
       <c r="I3" s="8"/>
       <c r="J3" s="7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K3" s="8">
         <v>1</v>
       </c>
       <c r="L3" s="10" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="M3" s="5"/>
       <c r="N3" s="5"/>
@@ -717,18 +805,18 @@
       <c r="C4" s="6"/>
       <c r="D4" s="5"/>
       <c r="E4" s="5"/>
-      <c r="F4" s="6"/>
+      <c r="F4" s="14"/>
       <c r="G4" s="5"/>
       <c r="H4" s="7"/>
       <c r="I4" s="8"/>
       <c r="J4" s="7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K4" s="8">
         <v>1</v>
       </c>
       <c r="L4" s="10" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="M4" s="5"/>
       <c r="N4" s="5"/>
@@ -754,16 +842,16 @@
       <c r="C5" s="6"/>
       <c r="D5" s="5"/>
       <c r="E5" s="5"/>
-      <c r="F5" s="6"/>
+      <c r="F5" s="14"/>
       <c r="G5" s="5"/>
       <c r="H5" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I5" s="8">
         <v>5</v>
       </c>
       <c r="J5" s="7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K5" s="8">
         <v>1</v>
@@ -793,12 +881,12 @@
       <c r="C6" s="6"/>
       <c r="D6" s="5"/>
       <c r="E6" s="5"/>
-      <c r="F6" s="6"/>
+      <c r="F6" s="14"/>
       <c r="G6" s="5"/>
       <c r="H6" s="11"/>
       <c r="I6" s="8"/>
       <c r="J6" s="12" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K6" s="8">
         <v>1</v>
@@ -828,12 +916,12 @@
       <c r="C7" s="6"/>
       <c r="D7" s="5"/>
       <c r="E7" s="5"/>
-      <c r="F7" s="6"/>
+      <c r="F7" s="14"/>
       <c r="G7" s="5"/>
       <c r="H7" s="11"/>
       <c r="I7" s="8"/>
       <c r="J7" s="12" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K7" s="8">
         <v>1</v>
@@ -863,12 +951,12 @@
       <c r="C8" s="6"/>
       <c r="D8" s="5"/>
       <c r="E8" s="5"/>
-      <c r="F8" s="6"/>
+      <c r="F8" s="14"/>
       <c r="G8" s="5"/>
       <c r="H8" s="11"/>
       <c r="I8" s="8"/>
       <c r="J8" s="12" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K8" s="8">
         <v>1</v>
@@ -898,16 +986,16 @@
       <c r="C9" s="6"/>
       <c r="D9" s="5"/>
       <c r="E9" s="5"/>
-      <c r="F9" s="6"/>
+      <c r="F9" s="14"/>
       <c r="G9" s="5"/>
       <c r="H9" s="10" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I9" s="10">
         <v>0</v>
       </c>
       <c r="J9" s="10" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K9" s="10">
         <v>0</v>
@@ -937,16 +1025,16 @@
       <c r="C10" s="6"/>
       <c r="D10" s="5"/>
       <c r="E10" s="5"/>
-      <c r="F10" s="6"/>
+      <c r="F10" s="14"/>
       <c r="G10" s="5"/>
       <c r="H10" s="10" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I10" s="10">
         <v>0</v>
       </c>
       <c r="J10" s="10" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K10" s="10">
         <v>0</v>
@@ -976,16 +1064,16 @@
       <c r="C11" s="6"/>
       <c r="D11" s="5"/>
       <c r="E11" s="5"/>
-      <c r="F11" s="6"/>
+      <c r="F11" s="14"/>
       <c r="G11" s="5"/>
       <c r="H11" s="10" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I11" s="10">
         <v>0</v>
       </c>
       <c r="J11" s="10" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K11" s="10">
         <v>0</v>
@@ -1015,16 +1103,16 @@
       <c r="C12" s="6"/>
       <c r="D12" s="5"/>
       <c r="E12" s="5"/>
-      <c r="F12" s="6"/>
+      <c r="F12" s="14"/>
       <c r="G12" s="5"/>
       <c r="H12" s="10" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I12" s="10">
         <v>0</v>
       </c>
       <c r="J12" s="10" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K12" s="10">
         <v>0</v>
@@ -1050,7 +1138,7 @@
     </row>
     <row r="13" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B13" s="5">
         <v>10.5</v>
@@ -1062,28 +1150,28 @@
         <v>2</v>
       </c>
       <c r="E13" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
-      <c r="F13" s="6" t="b">
+      <c r="F13" s="14" t="b">
         <v>0</v>
       </c>
       <c r="G13" s="5">
         <v>1</v>
       </c>
       <c r="H13" s="10" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I13" s="5">
         <v>0</v>
       </c>
       <c r="J13" s="10" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K13" s="5">
         <v>0</v>
       </c>
       <c r="L13" s="10" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="M13" s="5"/>
       <c r="N13" s="5"/>
@@ -1105,13 +1193,13 @@
     </row>
     <row r="14" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="5" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B14" s="5">
         <v>1</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D14" s="5">
         <v>1</v>
@@ -1119,26 +1207,26 @@
       <c r="E14" s="5">
         <v>5</v>
       </c>
-      <c r="F14" s="6" t="b">
+      <c r="F14" s="14" t="b">
         <v>1</v>
       </c>
       <c r="G14" s="5">
         <v>2</v>
       </c>
       <c r="H14" s="10" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I14" s="5">
         <v>0</v>
       </c>
       <c r="J14" s="10" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K14" s="5">
         <v>0</v>
       </c>
       <c r="L14" s="10" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="M14" s="5"/>
       <c r="N14" s="5"/>
@@ -1164,7 +1252,7 @@
       <c r="C15" s="4"/>
       <c r="D15" s="4"/>
       <c r="E15" s="4"/>
-      <c r="F15" s="4"/>
+      <c r="F15" s="15"/>
       <c r="G15" s="4"/>
       <c r="H15" s="4"/>
       <c r="I15" s="4"/>
@@ -1195,7 +1283,7 @@
       <c r="C16" s="4"/>
       <c r="D16" s="4"/>
       <c r="E16" s="4"/>
-      <c r="F16" s="4"/>
+      <c r="F16" s="15"/>
       <c r="G16" s="4"/>
       <c r="H16" s="4"/>
       <c r="I16" s="4"/>
@@ -1226,7 +1314,7 @@
       <c r="C17" s="4"/>
       <c r="D17" s="4"/>
       <c r="E17" s="4"/>
-      <c r="F17" s="4"/>
+      <c r="F17" s="15"/>
       <c r="G17" s="4"/>
       <c r="H17" s="4"/>
       <c r="I17" s="4"/>
@@ -1257,7 +1345,7 @@
       <c r="C18" s="4"/>
       <c r="D18" s="4"/>
       <c r="E18" s="4"/>
-      <c r="F18" s="4"/>
+      <c r="F18" s="15"/>
       <c r="G18" s="4"/>
       <c r="H18" s="4"/>
       <c r="I18" s="4"/>
@@ -1288,7 +1376,7 @@
       <c r="C19" s="4"/>
       <c r="D19" s="4"/>
       <c r="E19" s="4"/>
-      <c r="F19" s="4"/>
+      <c r="F19" s="15"/>
       <c r="G19" s="4"/>
       <c r="H19" s="4"/>
       <c r="I19" s="4"/>
@@ -1319,7 +1407,7 @@
       <c r="C20" s="4"/>
       <c r="D20" s="4"/>
       <c r="E20" s="4"/>
-      <c r="F20" s="4"/>
+      <c r="F20" s="15"/>
       <c r="G20" s="4"/>
       <c r="H20" s="4"/>
       <c r="I20" s="4"/>
@@ -1350,7 +1438,7 @@
       <c r="C21" s="4"/>
       <c r="D21" s="4"/>
       <c r="E21" s="4"/>
-      <c r="F21" s="4"/>
+      <c r="F21" s="15"/>
       <c r="G21" s="4"/>
       <c r="H21" s="4"/>
       <c r="I21" s="4"/>
@@ -1381,7 +1469,7 @@
       <c r="C22" s="4"/>
       <c r="D22" s="4"/>
       <c r="E22" s="4"/>
-      <c r="F22" s="4"/>
+      <c r="F22" s="15"/>
       <c r="G22" s="4"/>
       <c r="H22" s="4"/>
       <c r="I22" s="4"/>
@@ -1412,7 +1500,7 @@
       <c r="C23" s="4"/>
       <c r="D23" s="4"/>
       <c r="E23" s="4"/>
-      <c r="F23" s="4"/>
+      <c r="F23" s="15"/>
       <c r="G23" s="4"/>
       <c r="H23" s="4"/>
       <c r="I23" s="4"/>
@@ -1443,7 +1531,7 @@
       <c r="C24" s="4"/>
       <c r="D24" s="4"/>
       <c r="E24" s="4"/>
-      <c r="F24" s="4"/>
+      <c r="F24" s="15"/>
       <c r="G24" s="4"/>
       <c r="H24" s="4"/>
       <c r="I24" s="4"/>
@@ -1474,7 +1562,7 @@
       <c r="C25" s="4"/>
       <c r="D25" s="4"/>
       <c r="E25" s="4"/>
-      <c r="F25" s="4"/>
+      <c r="F25" s="15"/>
       <c r="G25" s="4"/>
       <c r="H25" s="4"/>
       <c r="I25" s="4"/>
@@ -1505,7 +1593,7 @@
       <c r="C26" s="4"/>
       <c r="D26" s="4"/>
       <c r="E26" s="4"/>
-      <c r="F26" s="4"/>
+      <c r="F26" s="15"/>
       <c r="G26" s="4"/>
       <c r="H26" s="4"/>
       <c r="I26" s="4"/>
@@ -1536,7 +1624,7 @@
       <c r="C27" s="4"/>
       <c r="D27" s="4"/>
       <c r="E27" s="4"/>
-      <c r="F27" s="4"/>
+      <c r="F27" s="15"/>
       <c r="G27" s="4"/>
       <c r="H27" s="4"/>
       <c r="I27" s="4"/>
@@ -1567,7 +1655,7 @@
       <c r="C28" s="4"/>
       <c r="D28" s="4"/>
       <c r="E28" s="4"/>
-      <c r="F28" s="4"/>
+      <c r="F28" s="15"/>
       <c r="G28" s="4"/>
       <c r="H28" s="4"/>
       <c r="I28" s="4"/>
@@ -1598,7 +1686,7 @@
       <c r="C29" s="4"/>
       <c r="D29" s="4"/>
       <c r="E29" s="4"/>
-      <c r="F29" s="4"/>
+      <c r="F29" s="15"/>
       <c r="G29" s="4"/>
       <c r="H29" s="4"/>
       <c r="I29" s="4"/>
@@ -1629,7 +1717,7 @@
       <c r="C30" s="4"/>
       <c r="D30" s="4"/>
       <c r="E30" s="4"/>
-      <c r="F30" s="4"/>
+      <c r="F30" s="15"/>
       <c r="G30" s="4"/>
       <c r="H30" s="4"/>
       <c r="I30" s="4"/>
@@ -1660,7 +1748,7 @@
       <c r="C31" s="4"/>
       <c r="D31" s="4"/>
       <c r="E31" s="4"/>
-      <c r="F31" s="4"/>
+      <c r="F31" s="15"/>
       <c r="G31" s="4"/>
       <c r="H31" s="4"/>
       <c r="I31" s="4"/>
@@ -1691,7 +1779,7 @@
       <c r="C32" s="4"/>
       <c r="D32" s="4"/>
       <c r="E32" s="4"/>
-      <c r="F32" s="4"/>
+      <c r="F32" s="15"/>
       <c r="G32" s="4"/>
       <c r="H32" s="4"/>
       <c r="I32" s="4"/>
@@ -1722,7 +1810,7 @@
       <c r="C33" s="4"/>
       <c r="D33" s="4"/>
       <c r="E33" s="4"/>
-      <c r="F33" s="4"/>
+      <c r="F33" s="15"/>
       <c r="G33" s="4"/>
       <c r="H33" s="4"/>
       <c r="I33" s="4"/>
@@ -1753,7 +1841,7 @@
       <c r="C34" s="4"/>
       <c r="D34" s="4"/>
       <c r="E34" s="4"/>
-      <c r="F34" s="4"/>
+      <c r="F34" s="15"/>
       <c r="G34" s="4"/>
       <c r="H34" s="4"/>
       <c r="I34" s="4"/>
@@ -1784,7 +1872,7 @@
       <c r="C35" s="4"/>
       <c r="D35" s="4"/>
       <c r="E35" s="4"/>
-      <c r="F35" s="4"/>
+      <c r="F35" s="15"/>
       <c r="G35" s="4"/>
       <c r="H35" s="4"/>
       <c r="I35" s="4"/>
@@ -1815,7 +1903,7 @@
       <c r="C36" s="4"/>
       <c r="D36" s="4"/>
       <c r="E36" s="4"/>
-      <c r="F36" s="4"/>
+      <c r="F36" s="15"/>
       <c r="G36" s="4"/>
       <c r="H36" s="4"/>
       <c r="I36" s="4"/>
@@ -1846,7 +1934,7 @@
       <c r="C37" s="4"/>
       <c r="D37" s="4"/>
       <c r="E37" s="4"/>
-      <c r="F37" s="4"/>
+      <c r="F37" s="15"/>
       <c r="G37" s="4"/>
       <c r="H37" s="4"/>
       <c r="I37" s="4"/>
@@ -1877,7 +1965,7 @@
       <c r="C38" s="4"/>
       <c r="D38" s="4"/>
       <c r="E38" s="4"/>
-      <c r="F38" s="4"/>
+      <c r="F38" s="15"/>
       <c r="G38" s="4"/>
       <c r="H38" s="4"/>
       <c r="I38" s="4"/>
@@ -1908,7 +1996,7 @@
       <c r="C39" s="4"/>
       <c r="D39" s="4"/>
       <c r="E39" s="4"/>
-      <c r="F39" s="4"/>
+      <c r="F39" s="15"/>
       <c r="G39" s="4"/>
       <c r="H39" s="4"/>
       <c r="I39" s="4"/>
@@ -1939,7 +2027,7 @@
       <c r="C40" s="4"/>
       <c r="D40" s="4"/>
       <c r="E40" s="4"/>
-      <c r="F40" s="4"/>
+      <c r="F40" s="15"/>
       <c r="G40" s="4"/>
       <c r="H40" s="4"/>
       <c r="I40" s="4"/>
@@ -1970,7 +2058,7 @@
       <c r="C41" s="4"/>
       <c r="D41" s="4"/>
       <c r="E41" s="4"/>
-      <c r="F41" s="4"/>
+      <c r="F41" s="15"/>
       <c r="G41" s="4"/>
       <c r="H41" s="4"/>
       <c r="I41" s="4"/>
@@ -2001,7 +2089,7 @@
       <c r="C42" s="4"/>
       <c r="D42" s="4"/>
       <c r="E42" s="4"/>
-      <c r="F42" s="4"/>
+      <c r="F42" s="15"/>
       <c r="G42" s="4"/>
       <c r="H42" s="4"/>
       <c r="I42" s="4"/>
@@ -2032,7 +2120,7 @@
       <c r="C43" s="4"/>
       <c r="D43" s="4"/>
       <c r="E43" s="4"/>
-      <c r="F43" s="4"/>
+      <c r="F43" s="15"/>
       <c r="G43" s="4"/>
       <c r="H43" s="4"/>
       <c r="I43" s="4"/>
@@ -2063,7 +2151,7 @@
       <c r="C44" s="4"/>
       <c r="D44" s="4"/>
       <c r="E44" s="4"/>
-      <c r="F44" s="4"/>
+      <c r="F44" s="15"/>
       <c r="G44" s="4"/>
       <c r="H44" s="4"/>
       <c r="I44" s="4"/>
@@ -2094,7 +2182,7 @@
       <c r="C45" s="4"/>
       <c r="D45" s="4"/>
       <c r="E45" s="4"/>
-      <c r="F45" s="4"/>
+      <c r="F45" s="15"/>
       <c r="G45" s="4"/>
       <c r="H45" s="4"/>
       <c r="I45" s="4"/>
@@ -2125,7 +2213,7 @@
       <c r="C46" s="4"/>
       <c r="D46" s="4"/>
       <c r="E46" s="4"/>
-      <c r="F46" s="4"/>
+      <c r="F46" s="15"/>
       <c r="G46" s="4"/>
       <c r="H46" s="4"/>
       <c r="I46" s="4"/>
@@ -2156,7 +2244,7 @@
       <c r="C47" s="4"/>
       <c r="D47" s="4"/>
       <c r="E47" s="4"/>
-      <c r="F47" s="4"/>
+      <c r="F47" s="15"/>
       <c r="G47" s="4"/>
       <c r="H47" s="4"/>
       <c r="I47" s="4"/>
@@ -2187,7 +2275,7 @@
       <c r="C48" s="4"/>
       <c r="D48" s="4"/>
       <c r="E48" s="4"/>
-      <c r="F48" s="4"/>
+      <c r="F48" s="15"/>
       <c r="G48" s="4"/>
       <c r="H48" s="4"/>
       <c r="I48" s="4"/>
@@ -2218,7 +2306,7 @@
       <c r="C49" s="4"/>
       <c r="D49" s="4"/>
       <c r="E49" s="4"/>
-      <c r="F49" s="4"/>
+      <c r="F49" s="15"/>
       <c r="G49" s="4"/>
       <c r="H49" s="4"/>
       <c r="I49" s="4"/>
@@ -2249,7 +2337,7 @@
       <c r="C50" s="4"/>
       <c r="D50" s="4"/>
       <c r="E50" s="4"/>
-      <c r="F50" s="4"/>
+      <c r="F50" s="15"/>
       <c r="G50" s="4"/>
       <c r="H50" s="4"/>
       <c r="I50" s="4"/>
@@ -2280,7 +2368,7 @@
       <c r="C51" s="4"/>
       <c r="D51" s="4"/>
       <c r="E51" s="4"/>
-      <c r="F51" s="4"/>
+      <c r="F51" s="15"/>
       <c r="G51" s="4"/>
       <c r="H51" s="4"/>
       <c r="I51" s="4"/>
@@ -2311,7 +2399,7 @@
       <c r="C52" s="4"/>
       <c r="D52" s="4"/>
       <c r="E52" s="4"/>
-      <c r="F52" s="4"/>
+      <c r="F52" s="15"/>
       <c r="G52" s="4"/>
       <c r="H52" s="4"/>
       <c r="I52" s="4"/>
@@ -2342,7 +2430,7 @@
       <c r="C53" s="4"/>
       <c r="D53" s="4"/>
       <c r="E53" s="4"/>
-      <c r="F53" s="4"/>
+      <c r="F53" s="15"/>
       <c r="G53" s="4"/>
       <c r="H53" s="4"/>
       <c r="I53" s="4"/>
@@ -2373,7 +2461,7 @@
       <c r="C54" s="4"/>
       <c r="D54" s="4"/>
       <c r="E54" s="4"/>
-      <c r="F54" s="4"/>
+      <c r="F54" s="15"/>
       <c r="G54" s="4"/>
       <c r="H54" s="4"/>
       <c r="I54" s="4"/>
@@ -2404,7 +2492,7 @@
       <c r="C55" s="4"/>
       <c r="D55" s="4"/>
       <c r="E55" s="4"/>
-      <c r="F55" s="4"/>
+      <c r="F55" s="15"/>
       <c r="G55" s="4"/>
       <c r="H55" s="4"/>
       <c r="I55" s="4"/>
@@ -2435,7 +2523,7 @@
       <c r="C56" s="4"/>
       <c r="D56" s="4"/>
       <c r="E56" s="4"/>
-      <c r="F56" s="4"/>
+      <c r="F56" s="15"/>
       <c r="G56" s="4"/>
       <c r="H56" s="4"/>
       <c r="I56" s="4"/>
@@ -2466,7 +2554,7 @@
       <c r="C57" s="4"/>
       <c r="D57" s="4"/>
       <c r="E57" s="4"/>
-      <c r="F57" s="4"/>
+      <c r="F57" s="15"/>
       <c r="G57" s="4"/>
       <c r="H57" s="4"/>
       <c r="I57" s="4"/>
@@ -2497,7 +2585,7 @@
       <c r="C58" s="4"/>
       <c r="D58" s="4"/>
       <c r="E58" s="4"/>
-      <c r="F58" s="4"/>
+      <c r="F58" s="15"/>
       <c r="G58" s="4"/>
       <c r="H58" s="4"/>
       <c r="I58" s="4"/>
@@ -2528,7 +2616,7 @@
       <c r="C59" s="4"/>
       <c r="D59" s="4"/>
       <c r="E59" s="4"/>
-      <c r="F59" s="4"/>
+      <c r="F59" s="15"/>
       <c r="G59" s="4"/>
       <c r="H59" s="4"/>
       <c r="I59" s="4"/>
@@ -2559,7 +2647,7 @@
       <c r="C60" s="4"/>
       <c r="D60" s="4"/>
       <c r="E60" s="4"/>
-      <c r="F60" s="4"/>
+      <c r="F60" s="15"/>
       <c r="G60" s="4"/>
       <c r="H60" s="4"/>
       <c r="I60" s="4"/>
@@ -2590,7 +2678,7 @@
       <c r="C61" s="4"/>
       <c r="D61" s="4"/>
       <c r="E61" s="4"/>
-      <c r="F61" s="4"/>
+      <c r="F61" s="15"/>
       <c r="G61" s="4"/>
       <c r="H61" s="4"/>
       <c r="I61" s="4"/>
@@ -2621,7 +2709,7 @@
       <c r="C62" s="4"/>
       <c r="D62" s="4"/>
       <c r="E62" s="4"/>
-      <c r="F62" s="4"/>
+      <c r="F62" s="15"/>
       <c r="G62" s="4"/>
       <c r="H62" s="4"/>
       <c r="I62" s="4"/>
@@ -2652,7 +2740,7 @@
       <c r="C63" s="4"/>
       <c r="D63" s="4"/>
       <c r="E63" s="4"/>
-      <c r="F63" s="4"/>
+      <c r="F63" s="15"/>
       <c r="G63" s="4"/>
       <c r="H63" s="4"/>
       <c r="I63" s="4"/>
@@ -2683,7 +2771,7 @@
       <c r="C64" s="4"/>
       <c r="D64" s="4"/>
       <c r="E64" s="4"/>
-      <c r="F64" s="4"/>
+      <c r="F64" s="15"/>
       <c r="G64" s="4"/>
       <c r="H64" s="4"/>
       <c r="I64" s="4"/>
@@ -2714,7 +2802,7 @@
       <c r="C65" s="4"/>
       <c r="D65" s="4"/>
       <c r="E65" s="4"/>
-      <c r="F65" s="4"/>
+      <c r="F65" s="15"/>
       <c r="G65" s="4"/>
       <c r="H65" s="4"/>
       <c r="I65" s="4"/>
@@ -2745,7 +2833,7 @@
       <c r="C66" s="4"/>
       <c r="D66" s="4"/>
       <c r="E66" s="4"/>
-      <c r="F66" s="4"/>
+      <c r="F66" s="15"/>
       <c r="G66" s="4"/>
       <c r="H66" s="4"/>
       <c r="I66" s="4"/>
@@ -2776,7 +2864,7 @@
       <c r="C67" s="4"/>
       <c r="D67" s="4"/>
       <c r="E67" s="4"/>
-      <c r="F67" s="4"/>
+      <c r="F67" s="15"/>
       <c r="G67" s="4"/>
       <c r="H67" s="4"/>
       <c r="I67" s="4"/>
@@ -2807,7 +2895,7 @@
       <c r="C68" s="4"/>
       <c r="D68" s="4"/>
       <c r="E68" s="4"/>
-      <c r="F68" s="4"/>
+      <c r="F68" s="15"/>
       <c r="G68" s="4"/>
       <c r="H68" s="4"/>
       <c r="I68" s="4"/>
@@ -2838,7 +2926,7 @@
       <c r="C69" s="4"/>
       <c r="D69" s="4"/>
       <c r="E69" s="4"/>
-      <c r="F69" s="4"/>
+      <c r="F69" s="15"/>
       <c r="G69" s="4"/>
       <c r="H69" s="4"/>
       <c r="I69" s="4"/>
@@ -2869,7 +2957,7 @@
       <c r="C70" s="4"/>
       <c r="D70" s="4"/>
       <c r="E70" s="4"/>
-      <c r="F70" s="4"/>
+      <c r="F70" s="15"/>
       <c r="G70" s="4"/>
       <c r="H70" s="4"/>
       <c r="I70" s="4"/>
@@ -2900,7 +2988,7 @@
       <c r="C71" s="4"/>
       <c r="D71" s="4"/>
       <c r="E71" s="4"/>
-      <c r="F71" s="4"/>
+      <c r="F71" s="15"/>
       <c r="G71" s="4"/>
       <c r="H71" s="4"/>
       <c r="I71" s="4"/>
@@ -2931,7 +3019,7 @@
       <c r="C72" s="4"/>
       <c r="D72" s="4"/>
       <c r="E72" s="4"/>
-      <c r="F72" s="4"/>
+      <c r="F72" s="15"/>
       <c r="G72" s="4"/>
       <c r="H72" s="4"/>
       <c r="I72" s="4"/>
@@ -2962,7 +3050,7 @@
       <c r="C73" s="4"/>
       <c r="D73" s="4"/>
       <c r="E73" s="4"/>
-      <c r="F73" s="4"/>
+      <c r="F73" s="15"/>
       <c r="G73" s="4"/>
       <c r="H73" s="4"/>
       <c r="I73" s="4"/>
@@ -2993,7 +3081,7 @@
       <c r="C74" s="4"/>
       <c r="D74" s="4"/>
       <c r="E74" s="4"/>
-      <c r="F74" s="4"/>
+      <c r="F74" s="15"/>
       <c r="G74" s="4"/>
       <c r="H74" s="4"/>
       <c r="I74" s="4"/>
@@ -3024,7 +3112,7 @@
       <c r="C75" s="4"/>
       <c r="D75" s="4"/>
       <c r="E75" s="4"/>
-      <c r="F75" s="4"/>
+      <c r="F75" s="15"/>
       <c r="G75" s="4"/>
       <c r="H75" s="4"/>
       <c r="I75" s="4"/>
@@ -3055,7 +3143,7 @@
       <c r="C76" s="4"/>
       <c r="D76" s="4"/>
       <c r="E76" s="4"/>
-      <c r="F76" s="4"/>
+      <c r="F76" s="15"/>
       <c r="G76" s="4"/>
       <c r="H76" s="4"/>
       <c r="I76" s="4"/>
@@ -3086,7 +3174,7 @@
       <c r="C77" s="4"/>
       <c r="D77" s="4"/>
       <c r="E77" s="4"/>
-      <c r="F77" s="4"/>
+      <c r="F77" s="15"/>
       <c r="G77" s="4"/>
       <c r="H77" s="4"/>
       <c r="I77" s="4"/>
@@ -3117,7 +3205,7 @@
       <c r="C78" s="4"/>
       <c r="D78" s="4"/>
       <c r="E78" s="4"/>
-      <c r="F78" s="4"/>
+      <c r="F78" s="15"/>
       <c r="G78" s="4"/>
       <c r="H78" s="4"/>
       <c r="I78" s="4"/>
@@ -3148,7 +3236,7 @@
       <c r="C79" s="4"/>
       <c r="D79" s="4"/>
       <c r="E79" s="4"/>
-      <c r="F79" s="4"/>
+      <c r="F79" s="15"/>
       <c r="G79" s="4"/>
       <c r="H79" s="4"/>
       <c r="I79" s="4"/>
@@ -3179,7 +3267,7 @@
       <c r="C80" s="4"/>
       <c r="D80" s="4"/>
       <c r="E80" s="4"/>
-      <c r="F80" s="4"/>
+      <c r="F80" s="15"/>
       <c r="G80" s="4"/>
       <c r="H80" s="4"/>
       <c r="I80" s="4"/>
@@ -3210,7 +3298,7 @@
       <c r="C81" s="4"/>
       <c r="D81" s="4"/>
       <c r="E81" s="4"/>
-      <c r="F81" s="4"/>
+      <c r="F81" s="15"/>
       <c r="G81" s="4"/>
       <c r="H81" s="4"/>
       <c r="I81" s="4"/>
@@ -3241,7 +3329,7 @@
       <c r="C82" s="4"/>
       <c r="D82" s="4"/>
       <c r="E82" s="4"/>
-      <c r="F82" s="4"/>
+      <c r="F82" s="15"/>
       <c r="G82" s="4"/>
       <c r="H82" s="4"/>
       <c r="I82" s="4"/>
@@ -3272,7 +3360,7 @@
       <c r="C83" s="4"/>
       <c r="D83" s="4"/>
       <c r="E83" s="4"/>
-      <c r="F83" s="4"/>
+      <c r="F83" s="15"/>
       <c r="G83" s="4"/>
       <c r="H83" s="4"/>
       <c r="I83" s="4"/>
@@ -3303,7 +3391,7 @@
       <c r="C84" s="4"/>
       <c r="D84" s="4"/>
       <c r="E84" s="4"/>
-      <c r="F84" s="4"/>
+      <c r="F84" s="15"/>
       <c r="G84" s="4"/>
       <c r="H84" s="4"/>
       <c r="I84" s="4"/>
@@ -3334,7 +3422,7 @@
       <c r="C85" s="4"/>
       <c r="D85" s="4"/>
       <c r="E85" s="4"/>
-      <c r="F85" s="4"/>
+      <c r="F85" s="15"/>
       <c r="G85" s="4"/>
       <c r="H85" s="4"/>
       <c r="I85" s="4"/>
@@ -3365,7 +3453,7 @@
       <c r="C86" s="4"/>
       <c r="D86" s="4"/>
       <c r="E86" s="4"/>
-      <c r="F86" s="4"/>
+      <c r="F86" s="15"/>
       <c r="G86" s="4"/>
       <c r="H86" s="4"/>
       <c r="I86" s="4"/>
@@ -3396,7 +3484,7 @@
       <c r="C87" s="4"/>
       <c r="D87" s="4"/>
       <c r="E87" s="4"/>
-      <c r="F87" s="4"/>
+      <c r="F87" s="15"/>
       <c r="G87" s="4"/>
       <c r="H87" s="4"/>
       <c r="I87" s="4"/>
@@ -3427,7 +3515,7 @@
       <c r="C88" s="4"/>
       <c r="D88" s="4"/>
       <c r="E88" s="4"/>
-      <c r="F88" s="4"/>
+      <c r="F88" s="15"/>
       <c r="G88" s="4"/>
       <c r="H88" s="4"/>
       <c r="I88" s="4"/>
@@ -3458,7 +3546,7 @@
       <c r="C89" s="4"/>
       <c r="D89" s="4"/>
       <c r="E89" s="4"/>
-      <c r="F89" s="4"/>
+      <c r="F89" s="15"/>
       <c r="G89" s="4"/>
       <c r="H89" s="4"/>
       <c r="I89" s="4"/>
@@ -3489,7 +3577,7 @@
       <c r="C90" s="4"/>
       <c r="D90" s="4"/>
       <c r="E90" s="4"/>
-      <c r="F90" s="4"/>
+      <c r="F90" s="15"/>
       <c r="G90" s="4"/>
       <c r="H90" s="4"/>
       <c r="I90" s="4"/>
@@ -3520,7 +3608,7 @@
       <c r="C91" s="4"/>
       <c r="D91" s="4"/>
       <c r="E91" s="4"/>
-      <c r="F91" s="4"/>
+      <c r="F91" s="15"/>
       <c r="G91" s="4"/>
       <c r="H91" s="4"/>
       <c r="I91" s="4"/>
@@ -3551,7 +3639,7 @@
       <c r="C92" s="4"/>
       <c r="D92" s="4"/>
       <c r="E92" s="4"/>
-      <c r="F92" s="4"/>
+      <c r="F92" s="15"/>
       <c r="G92" s="4"/>
       <c r="H92" s="4"/>
       <c r="I92" s="4"/>
@@ -3582,7 +3670,7 @@
       <c r="C93" s="4"/>
       <c r="D93" s="4"/>
       <c r="E93" s="4"/>
-      <c r="F93" s="4"/>
+      <c r="F93" s="15"/>
       <c r="G93" s="4"/>
       <c r="H93" s="4"/>
       <c r="I93" s="4"/>
@@ -3613,7 +3701,7 @@
       <c r="C94" s="4"/>
       <c r="D94" s="4"/>
       <c r="E94" s="4"/>
-      <c r="F94" s="4"/>
+      <c r="F94" s="15"/>
       <c r="G94" s="4"/>
       <c r="H94" s="4"/>
       <c r="I94" s="4"/>
@@ -3644,7 +3732,7 @@
       <c r="C95" s="4"/>
       <c r="D95" s="4"/>
       <c r="E95" s="4"/>
-      <c r="F95" s="4"/>
+      <c r="F95" s="15"/>
       <c r="G95" s="4"/>
       <c r="H95" s="4"/>
       <c r="I95" s="4"/>
@@ -3675,7 +3763,7 @@
       <c r="C96" s="4"/>
       <c r="D96" s="4"/>
       <c r="E96" s="4"/>
-      <c r="F96" s="4"/>
+      <c r="F96" s="15"/>
       <c r="G96" s="4"/>
       <c r="H96" s="4"/>
       <c r="I96" s="4"/>
@@ -3706,7 +3794,7 @@
       <c r="C97" s="4"/>
       <c r="D97" s="4"/>
       <c r="E97" s="4"/>
-      <c r="F97" s="4"/>
+      <c r="F97" s="15"/>
       <c r="G97" s="4"/>
       <c r="H97" s="4"/>
       <c r="I97" s="4"/>
@@ -3737,7 +3825,7 @@
       <c r="C98" s="4"/>
       <c r="D98" s="4"/>
       <c r="E98" s="4"/>
-      <c r="F98" s="4"/>
+      <c r="F98" s="15"/>
       <c r="G98" s="4"/>
       <c r="H98" s="4"/>
       <c r="I98" s="4"/>
@@ -3768,7 +3856,7 @@
       <c r="C99" s="4"/>
       <c r="D99" s="4"/>
       <c r="E99" s="4"/>
-      <c r="F99" s="4"/>
+      <c r="F99" s="15"/>
       <c r="G99" s="4"/>
       <c r="H99" s="4"/>
       <c r="I99" s="4"/>
@@ -3799,7 +3887,7 @@
       <c r="C100" s="4"/>
       <c r="D100" s="4"/>
       <c r="E100" s="4"/>
-      <c r="F100" s="4"/>
+      <c r="F100" s="15"/>
       <c r="G100" s="4"/>
       <c r="H100" s="4"/>
       <c r="I100" s="4"/>
@@ -3830,7 +3918,7 @@
       <c r="C101" s="4"/>
       <c r="D101" s="4"/>
       <c r="E101" s="4"/>
-      <c r="F101" s="4"/>
+      <c r="F101" s="15"/>
       <c r="G101" s="4"/>
       <c r="H101" s="4"/>
       <c r="I101" s="4"/>
@@ -3861,7 +3949,7 @@
       <c r="C102" s="4"/>
       <c r="D102" s="4"/>
       <c r="E102" s="4"/>
-      <c r="F102" s="4"/>
+      <c r="F102" s="15"/>
       <c r="G102" s="4"/>
       <c r="H102" s="4"/>
       <c r="I102" s="4"/>
@@ -3892,7 +3980,7 @@
       <c r="C103" s="4"/>
       <c r="D103" s="4"/>
       <c r="E103" s="4"/>
-      <c r="F103" s="4"/>
+      <c r="F103" s="15"/>
       <c r="G103" s="4"/>
       <c r="H103" s="4"/>
       <c r="I103" s="4"/>
@@ -3923,7 +4011,7 @@
       <c r="C104" s="4"/>
       <c r="D104" s="4"/>
       <c r="E104" s="4"/>
-      <c r="F104" s="4"/>
+      <c r="F104" s="15"/>
       <c r="G104" s="4"/>
       <c r="H104" s="4"/>
       <c r="I104" s="4"/>
@@ -3954,7 +4042,7 @@
       <c r="C105" s="4"/>
       <c r="D105" s="4"/>
       <c r="E105" s="4"/>
-      <c r="F105" s="4"/>
+      <c r="F105" s="15"/>
       <c r="G105" s="4"/>
       <c r="H105" s="4"/>
       <c r="I105" s="4"/>
@@ -3985,7 +4073,7 @@
       <c r="C106" s="4"/>
       <c r="D106" s="4"/>
       <c r="E106" s="4"/>
-      <c r="F106" s="4"/>
+      <c r="F106" s="15"/>
       <c r="G106" s="4"/>
       <c r="H106" s="4"/>
       <c r="I106" s="4"/>
@@ -4016,7 +4104,7 @@
       <c r="C107" s="4"/>
       <c r="D107" s="4"/>
       <c r="E107" s="4"/>
-      <c r="F107" s="4"/>
+      <c r="F107" s="15"/>
       <c r="G107" s="4"/>
       <c r="H107" s="4"/>
       <c r="I107" s="4"/>
@@ -4047,7 +4135,7 @@
       <c r="C108" s="4"/>
       <c r="D108" s="4"/>
       <c r="E108" s="4"/>
-      <c r="F108" s="4"/>
+      <c r="F108" s="15"/>
       <c r="G108" s="4"/>
       <c r="H108" s="4"/>
       <c r="I108" s="4"/>
@@ -4078,7 +4166,7 @@
       <c r="C109" s="4"/>
       <c r="D109" s="4"/>
       <c r="E109" s="4"/>
-      <c r="F109" s="4"/>
+      <c r="F109" s="15"/>
       <c r="G109" s="4"/>
       <c r="H109" s="4"/>
       <c r="I109" s="4"/>
@@ -4109,7 +4197,7 @@
       <c r="C110" s="4"/>
       <c r="D110" s="4"/>
       <c r="E110" s="4"/>
-      <c r="F110" s="4"/>
+      <c r="F110" s="15"/>
       <c r="G110" s="4"/>
       <c r="H110" s="4"/>
       <c r="I110" s="4"/>
@@ -4140,7 +4228,7 @@
       <c r="C111" s="4"/>
       <c r="D111" s="4"/>
       <c r="E111" s="4"/>
-      <c r="F111" s="4"/>
+      <c r="F111" s="15"/>
       <c r="G111" s="4"/>
       <c r="H111" s="4"/>
       <c r="I111" s="4"/>
@@ -4171,7 +4259,7 @@
       <c r="C112" s="4"/>
       <c r="D112" s="4"/>
       <c r="E112" s="4"/>
-      <c r="F112" s="4"/>
+      <c r="F112" s="15"/>
       <c r="G112" s="4"/>
       <c r="H112" s="4"/>
       <c r="I112" s="4"/>
@@ -4202,7 +4290,7 @@
       <c r="C113" s="4"/>
       <c r="D113" s="4"/>
       <c r="E113" s="4"/>
-      <c r="F113" s="4"/>
+      <c r="F113" s="15"/>
       <c r="G113" s="4"/>
       <c r="H113" s="4"/>
       <c r="I113" s="4"/>
@@ -4233,7 +4321,7 @@
       <c r="C114" s="4"/>
       <c r="D114" s="4"/>
       <c r="E114" s="4"/>
-      <c r="F114" s="4"/>
+      <c r="F114" s="15"/>
       <c r="G114" s="4"/>
       <c r="H114" s="4"/>
       <c r="I114" s="4"/>
@@ -4264,7 +4352,7 @@
       <c r="C115" s="4"/>
       <c r="D115" s="4"/>
       <c r="E115" s="4"/>
-      <c r="F115" s="4"/>
+      <c r="F115" s="15"/>
       <c r="G115" s="4"/>
       <c r="H115" s="4"/>
       <c r="I115" s="4"/>
@@ -4295,7 +4383,7 @@
       <c r="C116" s="4"/>
       <c r="D116" s="4"/>
       <c r="E116" s="4"/>
-      <c r="F116" s="4"/>
+      <c r="F116" s="15"/>
       <c r="G116" s="4"/>
       <c r="H116" s="4"/>
       <c r="I116" s="4"/>
@@ -4326,7 +4414,7 @@
       <c r="C117" s="4"/>
       <c r="D117" s="4"/>
       <c r="E117" s="4"/>
-      <c r="F117" s="4"/>
+      <c r="F117" s="15"/>
       <c r="G117" s="4"/>
       <c r="H117" s="4"/>
       <c r="I117" s="4"/>
@@ -4357,7 +4445,7 @@
       <c r="C118" s="4"/>
       <c r="D118" s="4"/>
       <c r="E118" s="4"/>
-      <c r="F118" s="4"/>
+      <c r="F118" s="15"/>
       <c r="G118" s="4"/>
       <c r="H118" s="4"/>
       <c r="I118" s="4"/>
@@ -4388,7 +4476,7 @@
       <c r="C119" s="4"/>
       <c r="D119" s="4"/>
       <c r="E119" s="4"/>
-      <c r="F119" s="4"/>
+      <c r="F119" s="15"/>
       <c r="G119" s="4"/>
       <c r="H119" s="4"/>
       <c r="I119" s="4"/>
@@ -4419,7 +4507,7 @@
       <c r="C120" s="4"/>
       <c r="D120" s="4"/>
       <c r="E120" s="4"/>
-      <c r="F120" s="4"/>
+      <c r="F120" s="15"/>
       <c r="G120" s="4"/>
       <c r="H120" s="4"/>
       <c r="I120" s="4"/>
@@ -4450,7 +4538,7 @@
       <c r="C121" s="4"/>
       <c r="D121" s="4"/>
       <c r="E121" s="4"/>
-      <c r="F121" s="4"/>
+      <c r="F121" s="15"/>
       <c r="G121" s="4"/>
       <c r="H121" s="4"/>
       <c r="I121" s="4"/>
@@ -4481,7 +4569,7 @@
       <c r="C122" s="4"/>
       <c r="D122" s="4"/>
       <c r="E122" s="4"/>
-      <c r="F122" s="4"/>
+      <c r="F122" s="15"/>
       <c r="G122" s="4"/>
       <c r="H122" s="4"/>
       <c r="I122" s="4"/>
@@ -4512,7 +4600,7 @@
       <c r="C123" s="4"/>
       <c r="D123" s="4"/>
       <c r="E123" s="4"/>
-      <c r="F123" s="4"/>
+      <c r="F123" s="15"/>
       <c r="G123" s="4"/>
       <c r="H123" s="4"/>
       <c r="I123" s="4"/>
@@ -4543,7 +4631,7 @@
       <c r="C124" s="4"/>
       <c r="D124" s="4"/>
       <c r="E124" s="4"/>
-      <c r="F124" s="4"/>
+      <c r="F124" s="15"/>
       <c r="G124" s="4"/>
       <c r="H124" s="4"/>
       <c r="I124" s="4"/>
@@ -4574,7 +4662,7 @@
       <c r="C125" s="4"/>
       <c r="D125" s="4"/>
       <c r="E125" s="4"/>
-      <c r="F125" s="4"/>
+      <c r="F125" s="15"/>
       <c r="G125" s="4"/>
       <c r="H125" s="4"/>
       <c r="I125" s="4"/>
@@ -4605,7 +4693,7 @@
       <c r="C126" s="4"/>
       <c r="D126" s="4"/>
       <c r="E126" s="4"/>
-      <c r="F126" s="4"/>
+      <c r="F126" s="15"/>
       <c r="G126" s="4"/>
       <c r="H126" s="4"/>
       <c r="I126" s="4"/>
@@ -4636,7 +4724,7 @@
       <c r="C127" s="4"/>
       <c r="D127" s="4"/>
       <c r="E127" s="4"/>
-      <c r="F127" s="4"/>
+      <c r="F127" s="15"/>
       <c r="G127" s="4"/>
       <c r="H127" s="4"/>
       <c r="I127" s="4"/>
@@ -4667,7 +4755,7 @@
       <c r="C128" s="4"/>
       <c r="D128" s="4"/>
       <c r="E128" s="4"/>
-      <c r="F128" s="4"/>
+      <c r="F128" s="15"/>
       <c r="G128" s="4"/>
       <c r="H128" s="4"/>
       <c r="I128" s="4"/>
@@ -4698,7 +4786,7 @@
       <c r="C129" s="4"/>
       <c r="D129" s="4"/>
       <c r="E129" s="4"/>
-      <c r="F129" s="4"/>
+      <c r="F129" s="15"/>
       <c r="G129" s="4"/>
       <c r="H129" s="4"/>
       <c r="I129" s="4"/>
@@ -4729,7 +4817,7 @@
       <c r="C130" s="4"/>
       <c r="D130" s="4"/>
       <c r="E130" s="4"/>
-      <c r="F130" s="4"/>
+      <c r="F130" s="15"/>
       <c r="G130" s="4"/>
       <c r="H130" s="4"/>
       <c r="I130" s="4"/>
@@ -4760,7 +4848,7 @@
       <c r="C131" s="4"/>
       <c r="D131" s="4"/>
       <c r="E131" s="4"/>
-      <c r="F131" s="4"/>
+      <c r="F131" s="15"/>
       <c r="G131" s="4"/>
       <c r="H131" s="4"/>
       <c r="I131" s="4"/>
@@ -4791,7 +4879,7 @@
       <c r="C132" s="4"/>
       <c r="D132" s="4"/>
       <c r="E132" s="4"/>
-      <c r="F132" s="4"/>
+      <c r="F132" s="15"/>
       <c r="G132" s="4"/>
       <c r="H132" s="4"/>
       <c r="I132" s="4"/>
@@ -4822,7 +4910,7 @@
       <c r="C133" s="4"/>
       <c r="D133" s="4"/>
       <c r="E133" s="4"/>
-      <c r="F133" s="4"/>
+      <c r="F133" s="15"/>
       <c r="G133" s="4"/>
       <c r="H133" s="4"/>
       <c r="I133" s="4"/>
@@ -4853,7 +4941,7 @@
       <c r="C134" s="4"/>
       <c r="D134" s="4"/>
       <c r="E134" s="4"/>
-      <c r="F134" s="4"/>
+      <c r="F134" s="15"/>
       <c r="G134" s="4"/>
       <c r="H134" s="4"/>
       <c r="I134" s="4"/>
@@ -4884,7 +4972,7 @@
       <c r="C135" s="4"/>
       <c r="D135" s="4"/>
       <c r="E135" s="4"/>
-      <c r="F135" s="4"/>
+      <c r="F135" s="15"/>
       <c r="G135" s="4"/>
       <c r="H135" s="4"/>
       <c r="I135" s="4"/>
@@ -4915,7 +5003,7 @@
       <c r="C136" s="4"/>
       <c r="D136" s="4"/>
       <c r="E136" s="4"/>
-      <c r="F136" s="4"/>
+      <c r="F136" s="15"/>
       <c r="G136" s="4"/>
       <c r="H136" s="4"/>
       <c r="I136" s="4"/>
@@ -4946,7 +5034,7 @@
       <c r="C137" s="4"/>
       <c r="D137" s="4"/>
       <c r="E137" s="4"/>
-      <c r="F137" s="4"/>
+      <c r="F137" s="15"/>
       <c r="G137" s="4"/>
       <c r="H137" s="4"/>
       <c r="I137" s="4"/>
@@ -4977,7 +5065,7 @@
       <c r="C138" s="4"/>
       <c r="D138" s="4"/>
       <c r="E138" s="4"/>
-      <c r="F138" s="4"/>
+      <c r="F138" s="15"/>
       <c r="G138" s="4"/>
       <c r="H138" s="4"/>
       <c r="I138" s="4"/>
@@ -5008,7 +5096,7 @@
       <c r="C139" s="4"/>
       <c r="D139" s="4"/>
       <c r="E139" s="4"/>
-      <c r="F139" s="4"/>
+      <c r="F139" s="15"/>
       <c r="G139" s="4"/>
       <c r="H139" s="4"/>
       <c r="I139" s="4"/>
@@ -5039,7 +5127,7 @@
       <c r="C140" s="4"/>
       <c r="D140" s="4"/>
       <c r="E140" s="4"/>
-      <c r="F140" s="4"/>
+      <c r="F140" s="15"/>
       <c r="G140" s="4"/>
       <c r="H140" s="4"/>
       <c r="I140" s="4"/>
@@ -5070,7 +5158,7 @@
       <c r="C141" s="4"/>
       <c r="D141" s="4"/>
       <c r="E141" s="4"/>
-      <c r="F141" s="4"/>
+      <c r="F141" s="15"/>
       <c r="G141" s="4"/>
       <c r="H141" s="4"/>
       <c r="I141" s="4"/>
@@ -5101,7 +5189,7 @@
       <c r="C142" s="4"/>
       <c r="D142" s="4"/>
       <c r="E142" s="4"/>
-      <c r="F142" s="4"/>
+      <c r="F142" s="15"/>
       <c r="G142" s="4"/>
       <c r="H142" s="4"/>
       <c r="I142" s="4"/>
@@ -5132,7 +5220,7 @@
       <c r="C143" s="4"/>
       <c r="D143" s="4"/>
       <c r="E143" s="4"/>
-      <c r="F143" s="4"/>
+      <c r="F143" s="15"/>
       <c r="G143" s="4"/>
       <c r="H143" s="4"/>
       <c r="I143" s="4"/>
@@ -5163,7 +5251,7 @@
       <c r="C144" s="4"/>
       <c r="D144" s="4"/>
       <c r="E144" s="4"/>
-      <c r="F144" s="4"/>
+      <c r="F144" s="15"/>
       <c r="G144" s="4"/>
       <c r="H144" s="4"/>
       <c r="I144" s="4"/>
@@ -5194,7 +5282,7 @@
       <c r="C145" s="4"/>
       <c r="D145" s="4"/>
       <c r="E145" s="4"/>
-      <c r="F145" s="4"/>
+      <c r="F145" s="15"/>
       <c r="G145" s="4"/>
       <c r="H145" s="4"/>
       <c r="I145" s="4"/>
@@ -5225,7 +5313,7 @@
       <c r="C146" s="4"/>
       <c r="D146" s="4"/>
       <c r="E146" s="4"/>
-      <c r="F146" s="4"/>
+      <c r="F146" s="15"/>
       <c r="G146" s="4"/>
       <c r="H146" s="4"/>
       <c r="I146" s="4"/>
@@ -5256,7 +5344,7 @@
       <c r="C147" s="4"/>
       <c r="D147" s="4"/>
       <c r="E147" s="4"/>
-      <c r="F147" s="4"/>
+      <c r="F147" s="15"/>
       <c r="G147" s="4"/>
       <c r="H147" s="4"/>
       <c r="I147" s="4"/>
@@ -5287,7 +5375,7 @@
       <c r="C148" s="4"/>
       <c r="D148" s="4"/>
       <c r="E148" s="4"/>
-      <c r="F148" s="4"/>
+      <c r="F148" s="15"/>
       <c r="G148" s="4"/>
       <c r="H148" s="4"/>
       <c r="I148" s="4"/>
@@ -5318,7 +5406,7 @@
       <c r="C149" s="4"/>
       <c r="D149" s="4"/>
       <c r="E149" s="4"/>
-      <c r="F149" s="4"/>
+      <c r="F149" s="15"/>
       <c r="G149" s="4"/>
       <c r="H149" s="4"/>
       <c r="I149" s="4"/>
@@ -5349,7 +5437,7 @@
       <c r="C150" s="4"/>
       <c r="D150" s="4"/>
       <c r="E150" s="4"/>
-      <c r="F150" s="4"/>
+      <c r="F150" s="15"/>
       <c r="G150" s="4"/>
       <c r="H150" s="4"/>
       <c r="I150" s="4"/>
@@ -5380,7 +5468,7 @@
       <c r="C151" s="4"/>
       <c r="D151" s="4"/>
       <c r="E151" s="4"/>
-      <c r="F151" s="4"/>
+      <c r="F151" s="15"/>
       <c r="G151" s="4"/>
       <c r="H151" s="4"/>
       <c r="I151" s="4"/>
@@ -5411,7 +5499,7 @@
       <c r="C152" s="4"/>
       <c r="D152" s="4"/>
       <c r="E152" s="4"/>
-      <c r="F152" s="4"/>
+      <c r="F152" s="15"/>
       <c r="G152" s="4"/>
       <c r="H152" s="4"/>
       <c r="I152" s="4"/>
@@ -5442,7 +5530,7 @@
       <c r="C153" s="4"/>
       <c r="D153" s="4"/>
       <c r="E153" s="4"/>
-      <c r="F153" s="4"/>
+      <c r="F153" s="15"/>
       <c r="G153" s="4"/>
       <c r="H153" s="4"/>
       <c r="I153" s="4"/>
@@ -5473,7 +5561,7 @@
       <c r="C154" s="4"/>
       <c r="D154" s="4"/>
       <c r="E154" s="4"/>
-      <c r="F154" s="4"/>
+      <c r="F154" s="15"/>
       <c r="G154" s="4"/>
       <c r="H154" s="4"/>
       <c r="I154" s="4"/>
@@ -5504,7 +5592,7 @@
       <c r="C155" s="4"/>
       <c r="D155" s="4"/>
       <c r="E155" s="4"/>
-      <c r="F155" s="4"/>
+      <c r="F155" s="15"/>
       <c r="G155" s="4"/>
       <c r="H155" s="4"/>
       <c r="I155" s="4"/>
@@ -5535,7 +5623,7 @@
       <c r="C156" s="4"/>
       <c r="D156" s="4"/>
       <c r="E156" s="4"/>
-      <c r="F156" s="4"/>
+      <c r="F156" s="15"/>
       <c r="G156" s="4"/>
       <c r="H156" s="4"/>
       <c r="I156" s="4"/>
@@ -5566,7 +5654,7 @@
       <c r="C157" s="4"/>
       <c r="D157" s="4"/>
       <c r="E157" s="4"/>
-      <c r="F157" s="4"/>
+      <c r="F157" s="15"/>
       <c r="G157" s="4"/>
       <c r="H157" s="4"/>
       <c r="I157" s="4"/>
@@ -5597,7 +5685,7 @@
       <c r="C158" s="4"/>
       <c r="D158" s="4"/>
       <c r="E158" s="4"/>
-      <c r="F158" s="4"/>
+      <c r="F158" s="15"/>
       <c r="G158" s="4"/>
       <c r="H158" s="4"/>
       <c r="I158" s="4"/>
@@ -5628,7 +5716,7 @@
       <c r="C159" s="4"/>
       <c r="D159" s="4"/>
       <c r="E159" s="4"/>
-      <c r="F159" s="4"/>
+      <c r="F159" s="15"/>
       <c r="G159" s="4"/>
       <c r="H159" s="4"/>
       <c r="I159" s="4"/>
@@ -5659,7 +5747,7 @@
       <c r="C160" s="4"/>
       <c r="D160" s="4"/>
       <c r="E160" s="4"/>
-      <c r="F160" s="4"/>
+      <c r="F160" s="15"/>
       <c r="G160" s="4"/>
       <c r="H160" s="4"/>
       <c r="I160" s="4"/>
@@ -5690,7 +5778,7 @@
       <c r="C161" s="4"/>
       <c r="D161" s="4"/>
       <c r="E161" s="4"/>
-      <c r="F161" s="4"/>
+      <c r="F161" s="15"/>
       <c r="G161" s="4"/>
       <c r="H161" s="4"/>
       <c r="I161" s="4"/>
@@ -5721,7 +5809,7 @@
       <c r="C162" s="4"/>
       <c r="D162" s="4"/>
       <c r="E162" s="4"/>
-      <c r="F162" s="4"/>
+      <c r="F162" s="15"/>
       <c r="G162" s="4"/>
       <c r="H162" s="4"/>
       <c r="I162" s="4"/>
@@ -5752,7 +5840,7 @@
       <c r="C163" s="4"/>
       <c r="D163" s="4"/>
       <c r="E163" s="4"/>
-      <c r="F163" s="4"/>
+      <c r="F163" s="15"/>
       <c r="G163" s="4"/>
       <c r="H163" s="4"/>
       <c r="I163" s="4"/>
@@ -5783,7 +5871,7 @@
       <c r="C164" s="4"/>
       <c r="D164" s="4"/>
       <c r="E164" s="4"/>
-      <c r="F164" s="4"/>
+      <c r="F164" s="15"/>
       <c r="G164" s="4"/>
       <c r="H164" s="4"/>
       <c r="I164" s="4"/>
@@ -5814,7 +5902,7 @@
       <c r="C165" s="4"/>
       <c r="D165" s="4"/>
       <c r="E165" s="4"/>
-      <c r="F165" s="4"/>
+      <c r="F165" s="15"/>
       <c r="G165" s="4"/>
       <c r="H165" s="4"/>
       <c r="I165" s="4"/>
@@ -5845,7 +5933,7 @@
       <c r="C166" s="4"/>
       <c r="D166" s="4"/>
       <c r="E166" s="4"/>
-      <c r="F166" s="4"/>
+      <c r="F166" s="15"/>
       <c r="G166" s="4"/>
       <c r="H166" s="4"/>
       <c r="I166" s="4"/>
@@ -5876,7 +5964,7 @@
       <c r="C167" s="4"/>
       <c r="D167" s="4"/>
       <c r="E167" s="4"/>
-      <c r="F167" s="4"/>
+      <c r="F167" s="15"/>
       <c r="G167" s="4"/>
       <c r="H167" s="4"/>
       <c r="I167" s="4"/>
@@ -5907,7 +5995,7 @@
       <c r="C168" s="4"/>
       <c r="D168" s="4"/>
       <c r="E168" s="4"/>
-      <c r="F168" s="4"/>
+      <c r="F168" s="15"/>
       <c r="G168" s="4"/>
       <c r="H168" s="4"/>
       <c r="I168" s="4"/>
@@ -5938,7 +6026,7 @@
       <c r="C169" s="4"/>
       <c r="D169" s="4"/>
       <c r="E169" s="4"/>
-      <c r="F169" s="4"/>
+      <c r="F169" s="15"/>
       <c r="G169" s="4"/>
       <c r="H169" s="4"/>
       <c r="I169" s="4"/>
@@ -5969,7 +6057,7 @@
       <c r="C170" s="4"/>
       <c r="D170" s="4"/>
       <c r="E170" s="4"/>
-      <c r="F170" s="4"/>
+      <c r="F170" s="15"/>
       <c r="G170" s="4"/>
       <c r="H170" s="4"/>
       <c r="I170" s="4"/>
@@ -6000,7 +6088,7 @@
       <c r="C171" s="4"/>
       <c r="D171" s="4"/>
       <c r="E171" s="4"/>
-      <c r="F171" s="4"/>
+      <c r="F171" s="15"/>
       <c r="G171" s="4"/>
       <c r="H171" s="4"/>
       <c r="I171" s="4"/>
@@ -6031,7 +6119,7 @@
       <c r="C172" s="4"/>
       <c r="D172" s="4"/>
       <c r="E172" s="4"/>
-      <c r="F172" s="4"/>
+      <c r="F172" s="15"/>
       <c r="G172" s="4"/>
       <c r="H172" s="4"/>
       <c r="I172" s="4"/>
@@ -6062,7 +6150,7 @@
       <c r="C173" s="4"/>
       <c r="D173" s="4"/>
       <c r="E173" s="4"/>
-      <c r="F173" s="4"/>
+      <c r="F173" s="15"/>
       <c r="G173" s="4"/>
       <c r="H173" s="4"/>
       <c r="I173" s="4"/>
@@ -6093,7 +6181,7 @@
       <c r="C174" s="4"/>
       <c r="D174" s="4"/>
       <c r="E174" s="4"/>
-      <c r="F174" s="4"/>
+      <c r="F174" s="15"/>
       <c r="G174" s="4"/>
       <c r="H174" s="4"/>
       <c r="I174" s="4"/>
@@ -6124,7 +6212,7 @@
       <c r="C175" s="4"/>
       <c r="D175" s="4"/>
       <c r="E175" s="4"/>
-      <c r="F175" s="4"/>
+      <c r="F175" s="15"/>
       <c r="G175" s="4"/>
       <c r="H175" s="4"/>
       <c r="I175" s="4"/>
@@ -6155,7 +6243,7 @@
       <c r="C176" s="4"/>
       <c r="D176" s="4"/>
       <c r="E176" s="4"/>
-      <c r="F176" s="4"/>
+      <c r="F176" s="15"/>
       <c r="G176" s="4"/>
       <c r="H176" s="4"/>
       <c r="I176" s="4"/>
@@ -6186,7 +6274,7 @@
       <c r="C177" s="4"/>
       <c r="D177" s="4"/>
       <c r="E177" s="4"/>
-      <c r="F177" s="4"/>
+      <c r="F177" s="15"/>
       <c r="G177" s="4"/>
       <c r="H177" s="4"/>
       <c r="I177" s="4"/>
@@ -6217,7 +6305,7 @@
       <c r="C178" s="4"/>
       <c r="D178" s="4"/>
       <c r="E178" s="4"/>
-      <c r="F178" s="4"/>
+      <c r="F178" s="15"/>
       <c r="G178" s="4"/>
       <c r="H178" s="4"/>
       <c r="I178" s="4"/>
@@ -6248,7 +6336,7 @@
       <c r="C179" s="4"/>
       <c r="D179" s="4"/>
       <c r="E179" s="4"/>
-      <c r="F179" s="4"/>
+      <c r="F179" s="15"/>
       <c r="G179" s="4"/>
       <c r="H179" s="4"/>
       <c r="I179" s="4"/>
@@ -6279,7 +6367,7 @@
       <c r="C180" s="4"/>
       <c r="D180" s="4"/>
       <c r="E180" s="4"/>
-      <c r="F180" s="4"/>
+      <c r="F180" s="15"/>
       <c r="G180" s="4"/>
       <c r="H180" s="4"/>
       <c r="I180" s="4"/>
@@ -6310,7 +6398,7 @@
       <c r="C181" s="4"/>
       <c r="D181" s="4"/>
       <c r="E181" s="4"/>
-      <c r="F181" s="4"/>
+      <c r="F181" s="15"/>
       <c r="G181" s="4"/>
       <c r="H181" s="4"/>
       <c r="I181" s="4"/>
@@ -6341,7 +6429,7 @@
       <c r="C182" s="4"/>
       <c r="D182" s="4"/>
       <c r="E182" s="4"/>
-      <c r="F182" s="4"/>
+      <c r="F182" s="15"/>
       <c r="G182" s="4"/>
       <c r="H182" s="4"/>
       <c r="I182" s="4"/>
@@ -6372,7 +6460,7 @@
       <c r="C183" s="4"/>
       <c r="D183" s="4"/>
       <c r="E183" s="4"/>
-      <c r="F183" s="4"/>
+      <c r="F183" s="15"/>
       <c r="G183" s="4"/>
       <c r="H183" s="4"/>
       <c r="I183" s="4"/>
@@ -6403,7 +6491,7 @@
       <c r="C184" s="4"/>
       <c r="D184" s="4"/>
       <c r="E184" s="4"/>
-      <c r="F184" s="4"/>
+      <c r="F184" s="15"/>
       <c r="G184" s="4"/>
       <c r="H184" s="4"/>
       <c r="I184" s="4"/>
@@ -6434,7 +6522,7 @@
       <c r="C185" s="4"/>
       <c r="D185" s="4"/>
       <c r="E185" s="4"/>
-      <c r="F185" s="4"/>
+      <c r="F185" s="15"/>
       <c r="G185" s="4"/>
       <c r="H185" s="4"/>
       <c r="I185" s="4"/>
@@ -6465,7 +6553,7 @@
       <c r="C186" s="4"/>
       <c r="D186" s="4"/>
       <c r="E186" s="4"/>
-      <c r="F186" s="4"/>
+      <c r="F186" s="15"/>
       <c r="G186" s="4"/>
       <c r="H186" s="4"/>
       <c r="I186" s="4"/>
@@ -6496,7 +6584,7 @@
       <c r="C187" s="4"/>
       <c r="D187" s="4"/>
       <c r="E187" s="4"/>
-      <c r="F187" s="4"/>
+      <c r="F187" s="15"/>
       <c r="G187" s="4"/>
       <c r="H187" s="4"/>
       <c r="I187" s="4"/>
@@ -6527,7 +6615,7 @@
       <c r="C188" s="4"/>
       <c r="D188" s="4"/>
       <c r="E188" s="4"/>
-      <c r="F188" s="4"/>
+      <c r="F188" s="15"/>
       <c r="G188" s="4"/>
       <c r="H188" s="4"/>
       <c r="I188" s="4"/>
@@ -6558,7 +6646,7 @@
       <c r="C189" s="4"/>
       <c r="D189" s="4"/>
       <c r="E189" s="4"/>
-      <c r="F189" s="4"/>
+      <c r="F189" s="15"/>
       <c r="G189" s="4"/>
       <c r="H189" s="4"/>
       <c r="I189" s="4"/>
@@ -6589,7 +6677,7 @@
       <c r="C190" s="4"/>
       <c r="D190" s="4"/>
       <c r="E190" s="4"/>
-      <c r="F190" s="4"/>
+      <c r="F190" s="15"/>
       <c r="G190" s="4"/>
       <c r="H190" s="4"/>
       <c r="I190" s="4"/>
@@ -6620,7 +6708,7 @@
       <c r="C191" s="4"/>
       <c r="D191" s="4"/>
       <c r="E191" s="4"/>
-      <c r="F191" s="4"/>
+      <c r="F191" s="15"/>
       <c r="G191" s="4"/>
       <c r="H191" s="4"/>
       <c r="I191" s="4"/>
@@ -6651,7 +6739,7 @@
       <c r="C192" s="4"/>
       <c r="D192" s="4"/>
       <c r="E192" s="4"/>
-      <c r="F192" s="4"/>
+      <c r="F192" s="15"/>
       <c r="G192" s="4"/>
       <c r="H192" s="4"/>
       <c r="I192" s="4"/>
@@ -6682,7 +6770,7 @@
       <c r="C193" s="4"/>
       <c r="D193" s="4"/>
       <c r="E193" s="4"/>
-      <c r="F193" s="4"/>
+      <c r="F193" s="15"/>
       <c r="G193" s="4"/>
       <c r="H193" s="4"/>
       <c r="I193" s="4"/>
@@ -6713,7 +6801,7 @@
       <c r="C194" s="4"/>
       <c r="D194" s="4"/>
       <c r="E194" s="4"/>
-      <c r="F194" s="4"/>
+      <c r="F194" s="15"/>
       <c r="G194" s="4"/>
       <c r="H194" s="4"/>
       <c r="I194" s="4"/>
@@ -6744,7 +6832,7 @@
       <c r="C195" s="4"/>
       <c r="D195" s="4"/>
       <c r="E195" s="4"/>
-      <c r="F195" s="4"/>
+      <c r="F195" s="15"/>
       <c r="G195" s="4"/>
       <c r="H195" s="4"/>
       <c r="I195" s="4"/>
@@ -6775,7 +6863,7 @@
       <c r="C196" s="4"/>
       <c r="D196" s="4"/>
       <c r="E196" s="4"/>
-      <c r="F196" s="4"/>
+      <c r="F196" s="15"/>
       <c r="G196" s="4"/>
       <c r="H196" s="4"/>
       <c r="I196" s="4"/>
@@ -6806,7 +6894,7 @@
       <c r="C197" s="4"/>
       <c r="D197" s="4"/>
       <c r="E197" s="4"/>
-      <c r="F197" s="4"/>
+      <c r="F197" s="15"/>
       <c r="G197" s="4"/>
       <c r="H197" s="4"/>
       <c r="I197" s="4"/>
@@ -6837,7 +6925,7 @@
       <c r="C198" s="4"/>
       <c r="D198" s="4"/>
       <c r="E198" s="4"/>
-      <c r="F198" s="4"/>
+      <c r="F198" s="15"/>
       <c r="G198" s="4"/>
       <c r="H198" s="4"/>
       <c r="I198" s="4"/>
@@ -6868,7 +6956,7 @@
       <c r="C199" s="4"/>
       <c r="D199" s="4"/>
       <c r="E199" s="4"/>
-      <c r="F199" s="4"/>
+      <c r="F199" s="15"/>
       <c r="G199" s="4"/>
       <c r="H199" s="4"/>
       <c r="I199" s="4"/>
@@ -6899,7 +6987,7 @@
       <c r="C200" s="4"/>
       <c r="D200" s="4"/>
       <c r="E200" s="4"/>
-      <c r="F200" s="4"/>
+      <c r="F200" s="15"/>
       <c r="G200" s="4"/>
       <c r="H200" s="4"/>
       <c r="I200" s="4"/>
@@ -6930,7 +7018,7 @@
       <c r="C201" s="4"/>
       <c r="D201" s="4"/>
       <c r="E201" s="4"/>
-      <c r="F201" s="4"/>
+      <c r="F201" s="15"/>
       <c r="G201" s="4"/>
       <c r="H201" s="4"/>
       <c r="I201" s="4"/>
@@ -6961,7 +7049,7 @@
       <c r="C202" s="4"/>
       <c r="D202" s="4"/>
       <c r="E202" s="4"/>
-      <c r="F202" s="4"/>
+      <c r="F202" s="15"/>
       <c r="G202" s="4"/>
       <c r="H202" s="4"/>
       <c r="I202" s="4"/>
@@ -6992,7 +7080,7 @@
       <c r="C203" s="4"/>
       <c r="D203" s="4"/>
       <c r="E203" s="4"/>
-      <c r="F203" s="4"/>
+      <c r="F203" s="15"/>
       <c r="G203" s="4"/>
       <c r="H203" s="4"/>
       <c r="I203" s="4"/>
@@ -7023,7 +7111,7 @@
       <c r="C204" s="4"/>
       <c r="D204" s="4"/>
       <c r="E204" s="4"/>
-      <c r="F204" s="4"/>
+      <c r="F204" s="15"/>
       <c r="G204" s="4"/>
       <c r="H204" s="4"/>
       <c r="I204" s="4"/>
@@ -7054,7 +7142,7 @@
       <c r="C205" s="4"/>
       <c r="D205" s="4"/>
       <c r="E205" s="4"/>
-      <c r="F205" s="4"/>
+      <c r="F205" s="15"/>
       <c r="G205" s="4"/>
       <c r="H205" s="4"/>
       <c r="I205" s="4"/>
@@ -7085,7 +7173,7 @@
       <c r="C206" s="4"/>
       <c r="D206" s="4"/>
       <c r="E206" s="4"/>
-      <c r="F206" s="4"/>
+      <c r="F206" s="15"/>
       <c r="G206" s="4"/>
       <c r="H206" s="4"/>
       <c r="I206" s="4"/>
@@ -7116,7 +7204,7 @@
       <c r="C207" s="4"/>
       <c r="D207" s="4"/>
       <c r="E207" s="4"/>
-      <c r="F207" s="4"/>
+      <c r="F207" s="15"/>
       <c r="G207" s="4"/>
       <c r="H207" s="4"/>
       <c r="I207" s="4"/>
@@ -7147,7 +7235,7 @@
       <c r="C208" s="4"/>
       <c r="D208" s="4"/>
       <c r="E208" s="4"/>
-      <c r="F208" s="4"/>
+      <c r="F208" s="15"/>
       <c r="G208" s="4"/>
       <c r="H208" s="4"/>
       <c r="I208" s="4"/>
@@ -7178,7 +7266,7 @@
       <c r="C209" s="4"/>
       <c r="D209" s="4"/>
       <c r="E209" s="4"/>
-      <c r="F209" s="4"/>
+      <c r="F209" s="15"/>
       <c r="G209" s="4"/>
       <c r="H209" s="4"/>
       <c r="I209" s="4"/>
@@ -7209,7 +7297,7 @@
       <c r="C210" s="4"/>
       <c r="D210" s="4"/>
       <c r="E210" s="4"/>
-      <c r="F210" s="4"/>
+      <c r="F210" s="15"/>
       <c r="G210" s="4"/>
       <c r="H210" s="4"/>
       <c r="I210" s="4"/>
@@ -7240,7 +7328,7 @@
       <c r="C211" s="4"/>
       <c r="D211" s="4"/>
       <c r="E211" s="4"/>
-      <c r="F211" s="4"/>
+      <c r="F211" s="15"/>
       <c r="G211" s="4"/>
       <c r="H211" s="4"/>
       <c r="I211" s="4"/>
@@ -7271,7 +7359,7 @@
       <c r="C212" s="4"/>
       <c r="D212" s="4"/>
       <c r="E212" s="4"/>
-      <c r="F212" s="4"/>
+      <c r="F212" s="15"/>
       <c r="G212" s="4"/>
       <c r="H212" s="4"/>
       <c r="I212" s="4"/>
@@ -7302,7 +7390,7 @@
       <c r="C213" s="4"/>
       <c r="D213" s="4"/>
       <c r="E213" s="4"/>
-      <c r="F213" s="4"/>
+      <c r="F213" s="15"/>
       <c r="G213" s="4"/>
       <c r="H213" s="4"/>
       <c r="I213" s="4"/>
@@ -7333,7 +7421,7 @@
       <c r="C214" s="4"/>
       <c r="D214" s="4"/>
       <c r="E214" s="4"/>
-      <c r="F214" s="4"/>
+      <c r="F214" s="15"/>
       <c r="G214" s="4"/>
       <c r="H214" s="4"/>
       <c r="I214" s="4"/>
@@ -7364,7 +7452,7 @@
       <c r="C215" s="4"/>
       <c r="D215" s="4"/>
       <c r="E215" s="4"/>
-      <c r="F215" s="4"/>
+      <c r="F215" s="15"/>
       <c r="G215" s="4"/>
       <c r="H215" s="4"/>
       <c r="I215" s="4"/>
@@ -7395,7 +7483,7 @@
       <c r="C216" s="4"/>
       <c r="D216" s="4"/>
       <c r="E216" s="4"/>
-      <c r="F216" s="4"/>
+      <c r="F216" s="15"/>
       <c r="G216" s="4"/>
       <c r="H216" s="4"/>
       <c r="I216" s="4"/>
@@ -7426,7 +7514,7 @@
       <c r="C217" s="4"/>
       <c r="D217" s="4"/>
       <c r="E217" s="4"/>
-      <c r="F217" s="4"/>
+      <c r="F217" s="15"/>
       <c r="G217" s="4"/>
       <c r="H217" s="4"/>
       <c r="I217" s="4"/>
@@ -7457,7 +7545,7 @@
       <c r="C218" s="4"/>
       <c r="D218" s="4"/>
       <c r="E218" s="4"/>
-      <c r="F218" s="4"/>
+      <c r="F218" s="15"/>
       <c r="G218" s="4"/>
       <c r="H218" s="4"/>
       <c r="I218" s="4"/>
@@ -7488,7 +7576,7 @@
       <c r="C219" s="4"/>
       <c r="D219" s="4"/>
       <c r="E219" s="4"/>
-      <c r="F219" s="4"/>
+      <c r="F219" s="15"/>
       <c r="G219" s="4"/>
       <c r="H219" s="4"/>
       <c r="I219" s="4"/>
@@ -7519,7 +7607,7 @@
       <c r="C220" s="4"/>
       <c r="D220" s="4"/>
       <c r="E220" s="4"/>
-      <c r="F220" s="4"/>
+      <c r="F220" s="15"/>
       <c r="G220" s="4"/>
       <c r="H220" s="4"/>
       <c r="I220" s="4"/>
@@ -7550,7 +7638,7 @@
       <c r="C221" s="4"/>
       <c r="D221" s="4"/>
       <c r="E221" s="4"/>
-      <c r="F221" s="4"/>
+      <c r="F221" s="15"/>
       <c r="G221" s="4"/>
       <c r="H221" s="4"/>
       <c r="I221" s="4"/>
@@ -7581,7 +7669,7 @@
       <c r="C222" s="4"/>
       <c r="D222" s="4"/>
       <c r="E222" s="4"/>
-      <c r="F222" s="4"/>
+      <c r="F222" s="15"/>
       <c r="G222" s="4"/>
       <c r="H222" s="4"/>
       <c r="I222" s="4"/>
@@ -7612,7 +7700,7 @@
       <c r="C223" s="4"/>
       <c r="D223" s="4"/>
       <c r="E223" s="4"/>
-      <c r="F223" s="4"/>
+      <c r="F223" s="15"/>
       <c r="G223" s="4"/>
       <c r="H223" s="4"/>
       <c r="I223" s="4"/>
@@ -7643,7 +7731,7 @@
       <c r="C224" s="4"/>
       <c r="D224" s="4"/>
       <c r="E224" s="4"/>
-      <c r="F224" s="4"/>
+      <c r="F224" s="15"/>
       <c r="G224" s="4"/>
       <c r="H224" s="4"/>
       <c r="I224" s="4"/>
@@ -7674,7 +7762,7 @@
       <c r="C225" s="4"/>
       <c r="D225" s="4"/>
       <c r="E225" s="4"/>
-      <c r="F225" s="4"/>
+      <c r="F225" s="15"/>
       <c r="G225" s="4"/>
       <c r="H225" s="4"/>
       <c r="I225" s="4"/>
@@ -7705,7 +7793,7 @@
       <c r="C226" s="4"/>
       <c r="D226" s="4"/>
       <c r="E226" s="4"/>
-      <c r="F226" s="4"/>
+      <c r="F226" s="15"/>
       <c r="G226" s="4"/>
       <c r="H226" s="4"/>
       <c r="I226" s="4"/>
@@ -7736,7 +7824,7 @@
       <c r="C227" s="4"/>
       <c r="D227" s="4"/>
       <c r="E227" s="4"/>
-      <c r="F227" s="4"/>
+      <c r="F227" s="15"/>
       <c r="G227" s="4"/>
       <c r="H227" s="4"/>
       <c r="I227" s="4"/>
@@ -7767,7 +7855,7 @@
       <c r="C228" s="4"/>
       <c r="D228" s="4"/>
       <c r="E228" s="4"/>
-      <c r="F228" s="4"/>
+      <c r="F228" s="15"/>
       <c r="G228" s="4"/>
       <c r="H228" s="4"/>
       <c r="I228" s="4"/>
@@ -7798,7 +7886,7 @@
       <c r="C229" s="4"/>
       <c r="D229" s="4"/>
       <c r="E229" s="4"/>
-      <c r="F229" s="4"/>
+      <c r="F229" s="15"/>
       <c r="G229" s="4"/>
       <c r="H229" s="4"/>
       <c r="I229" s="4"/>
@@ -7829,7 +7917,7 @@
       <c r="C230" s="4"/>
       <c r="D230" s="4"/>
       <c r="E230" s="4"/>
-      <c r="F230" s="4"/>
+      <c r="F230" s="15"/>
       <c r="G230" s="4"/>
       <c r="H230" s="4"/>
       <c r="I230" s="4"/>
@@ -7860,7 +7948,7 @@
       <c r="C231" s="4"/>
       <c r="D231" s="4"/>
       <c r="E231" s="4"/>
-      <c r="F231" s="4"/>
+      <c r="F231" s="15"/>
       <c r="G231" s="4"/>
       <c r="H231" s="4"/>
       <c r="I231" s="4"/>
@@ -7891,7 +7979,7 @@
       <c r="C232" s="4"/>
       <c r="D232" s="4"/>
       <c r="E232" s="4"/>
-      <c r="F232" s="4"/>
+      <c r="F232" s="15"/>
       <c r="G232" s="4"/>
       <c r="H232" s="4"/>
       <c r="I232" s="4"/>
@@ -7922,7 +8010,7 @@
       <c r="C233" s="4"/>
       <c r="D233" s="4"/>
       <c r="E233" s="4"/>
-      <c r="F233" s="4"/>
+      <c r="F233" s="15"/>
       <c r="G233" s="4"/>
       <c r="H233" s="4"/>
       <c r="I233" s="4"/>
@@ -7953,7 +8041,7 @@
       <c r="C234" s="4"/>
       <c r="D234" s="4"/>
       <c r="E234" s="4"/>
-      <c r="F234" s="4"/>
+      <c r="F234" s="15"/>
       <c r="G234" s="4"/>
       <c r="H234" s="4"/>
       <c r="I234" s="4"/>
@@ -7984,7 +8072,7 @@
       <c r="C235" s="4"/>
       <c r="D235" s="4"/>
       <c r="E235" s="4"/>
-      <c r="F235" s="4"/>
+      <c r="F235" s="15"/>
       <c r="G235" s="4"/>
       <c r="H235" s="4"/>
       <c r="I235" s="4"/>
@@ -8015,7 +8103,7 @@
       <c r="C236" s="4"/>
       <c r="D236" s="4"/>
       <c r="E236" s="4"/>
-      <c r="F236" s="4"/>
+      <c r="F236" s="15"/>
       <c r="G236" s="4"/>
       <c r="H236" s="4"/>
       <c r="I236" s="4"/>
@@ -8046,7 +8134,7 @@
       <c r="C237" s="4"/>
       <c r="D237" s="4"/>
       <c r="E237" s="4"/>
-      <c r="F237" s="4"/>
+      <c r="F237" s="15"/>
       <c r="G237" s="4"/>
       <c r="H237" s="4"/>
       <c r="I237" s="4"/>
@@ -8077,7 +8165,7 @@
       <c r="C238" s="4"/>
       <c r="D238" s="4"/>
       <c r="E238" s="4"/>
-      <c r="F238" s="4"/>
+      <c r="F238" s="15"/>
       <c r="G238" s="4"/>
       <c r="H238" s="4"/>
       <c r="I238" s="4"/>
@@ -8108,7 +8196,7 @@
       <c r="C239" s="4"/>
       <c r="D239" s="4"/>
       <c r="E239" s="4"/>
-      <c r="F239" s="4"/>
+      <c r="F239" s="15"/>
       <c r="G239" s="4"/>
       <c r="H239" s="4"/>
       <c r="I239" s="4"/>
@@ -8139,7 +8227,7 @@
       <c r="C240" s="4"/>
       <c r="D240" s="4"/>
       <c r="E240" s="4"/>
-      <c r="F240" s="4"/>
+      <c r="F240" s="15"/>
       <c r="G240" s="4"/>
       <c r="H240" s="4"/>
       <c r="I240" s="4"/>
@@ -8170,7 +8258,7 @@
       <c r="C241" s="4"/>
       <c r="D241" s="4"/>
       <c r="E241" s="4"/>
-      <c r="F241" s="4"/>
+      <c r="F241" s="15"/>
       <c r="G241" s="4"/>
       <c r="H241" s="4"/>
       <c r="I241" s="4"/>
@@ -8201,7 +8289,7 @@
       <c r="C242" s="4"/>
       <c r="D242" s="4"/>
       <c r="E242" s="4"/>
-      <c r="F242" s="4"/>
+      <c r="F242" s="15"/>
       <c r="G242" s="4"/>
       <c r="H242" s="4"/>
       <c r="I242" s="4"/>
@@ -8232,7 +8320,7 @@
       <c r="C243" s="4"/>
       <c r="D243" s="4"/>
       <c r="E243" s="4"/>
-      <c r="F243" s="4"/>
+      <c r="F243" s="15"/>
       <c r="G243" s="4"/>
       <c r="H243" s="4"/>
       <c r="I243" s="4"/>
@@ -8263,7 +8351,7 @@
       <c r="C244" s="4"/>
       <c r="D244" s="4"/>
       <c r="E244" s="4"/>
-      <c r="F244" s="4"/>
+      <c r="F244" s="15"/>
       <c r="G244" s="4"/>
       <c r="H244" s="4"/>
       <c r="I244" s="4"/>
@@ -8294,7 +8382,7 @@
       <c r="C245" s="4"/>
       <c r="D245" s="4"/>
       <c r="E245" s="4"/>
-      <c r="F245" s="4"/>
+      <c r="F245" s="15"/>
       <c r="G245" s="4"/>
       <c r="H245" s="4"/>
       <c r="I245" s="4"/>
@@ -8325,7 +8413,7 @@
       <c r="C246" s="4"/>
       <c r="D246" s="4"/>
       <c r="E246" s="4"/>
-      <c r="F246" s="4"/>
+      <c r="F246" s="15"/>
       <c r="G246" s="4"/>
       <c r="H246" s="4"/>
       <c r="I246" s="4"/>
@@ -8356,7 +8444,7 @@
       <c r="C247" s="4"/>
       <c r="D247" s="4"/>
       <c r="E247" s="4"/>
-      <c r="F247" s="4"/>
+      <c r="F247" s="15"/>
       <c r="G247" s="4"/>
       <c r="H247" s="4"/>
       <c r="I247" s="4"/>
@@ -8387,7 +8475,7 @@
       <c r="C248" s="4"/>
       <c r="D248" s="4"/>
       <c r="E248" s="4"/>
-      <c r="F248" s="4"/>
+      <c r="F248" s="15"/>
       <c r="G248" s="4"/>
       <c r="H248" s="4"/>
       <c r="I248" s="4"/>
@@ -8418,7 +8506,7 @@
       <c r="C249" s="4"/>
       <c r="D249" s="4"/>
       <c r="E249" s="4"/>
-      <c r="F249" s="4"/>
+      <c r="F249" s="15"/>
       <c r="G249" s="4"/>
       <c r="H249" s="4"/>
       <c r="I249" s="4"/>
@@ -8449,7 +8537,7 @@
       <c r="C250" s="4"/>
       <c r="D250" s="4"/>
       <c r="E250" s="4"/>
-      <c r="F250" s="4"/>
+      <c r="F250" s="15"/>
       <c r="G250" s="4"/>
       <c r="H250" s="4"/>
       <c r="I250" s="4"/>
@@ -8480,7 +8568,7 @@
       <c r="C251" s="4"/>
       <c r="D251" s="4"/>
       <c r="E251" s="4"/>
-      <c r="F251" s="4"/>
+      <c r="F251" s="15"/>
       <c r="G251" s="4"/>
       <c r="H251" s="4"/>
       <c r="I251" s="4"/>
@@ -8511,7 +8599,7 @@
       <c r="C252" s="4"/>
       <c r="D252" s="4"/>
       <c r="E252" s="4"/>
-      <c r="F252" s="4"/>
+      <c r="F252" s="15"/>
       <c r="G252" s="4"/>
       <c r="H252" s="4"/>
       <c r="I252" s="4"/>
@@ -8542,7 +8630,7 @@
       <c r="C253" s="4"/>
       <c r="D253" s="4"/>
       <c r="E253" s="4"/>
-      <c r="F253" s="4"/>
+      <c r="F253" s="15"/>
       <c r="G253" s="4"/>
       <c r="H253" s="4"/>
       <c r="I253" s="4"/>
@@ -8573,7 +8661,7 @@
       <c r="C254" s="4"/>
       <c r="D254" s="4"/>
       <c r="E254" s="4"/>
-      <c r="F254" s="4"/>
+      <c r="F254" s="15"/>
       <c r="G254" s="4"/>
       <c r="H254" s="4"/>
       <c r="I254" s="4"/>
@@ -8604,7 +8692,7 @@
       <c r="C255" s="4"/>
       <c r="D255" s="4"/>
       <c r="E255" s="4"/>
-      <c r="F255" s="4"/>
+      <c r="F255" s="15"/>
       <c r="G255" s="4"/>
       <c r="H255" s="4"/>
       <c r="I255" s="4"/>
@@ -8635,7 +8723,7 @@
       <c r="C256" s="4"/>
       <c r="D256" s="4"/>
       <c r="E256" s="4"/>
-      <c r="F256" s="4"/>
+      <c r="F256" s="15"/>
       <c r="G256" s="4"/>
       <c r="H256" s="4"/>
       <c r="I256" s="4"/>
@@ -8666,7 +8754,7 @@
       <c r="C257" s="4"/>
       <c r="D257" s="4"/>
       <c r="E257" s="4"/>
-      <c r="F257" s="4"/>
+      <c r="F257" s="15"/>
       <c r="G257" s="4"/>
       <c r="H257" s="4"/>
       <c r="I257" s="4"/>
@@ -8697,7 +8785,7 @@
       <c r="C258" s="4"/>
       <c r="D258" s="4"/>
       <c r="E258" s="4"/>
-      <c r="F258" s="4"/>
+      <c r="F258" s="15"/>
       <c r="G258" s="4"/>
       <c r="H258" s="4"/>
       <c r="I258" s="4"/>
@@ -8728,7 +8816,7 @@
       <c r="C259" s="4"/>
       <c r="D259" s="4"/>
       <c r="E259" s="4"/>
-      <c r="F259" s="4"/>
+      <c r="F259" s="15"/>
       <c r="G259" s="4"/>
       <c r="H259" s="4"/>
       <c r="I259" s="4"/>
@@ -8759,7 +8847,7 @@
       <c r="C260" s="4"/>
       <c r="D260" s="4"/>
       <c r="E260" s="4"/>
-      <c r="F260" s="4"/>
+      <c r="F260" s="15"/>
       <c r="G260" s="4"/>
       <c r="H260" s="4"/>
       <c r="I260" s="4"/>
@@ -8790,7 +8878,7 @@
       <c r="C261" s="4"/>
       <c r="D261" s="4"/>
       <c r="E261" s="4"/>
-      <c r="F261" s="4"/>
+      <c r="F261" s="15"/>
       <c r="G261" s="4"/>
       <c r="H261" s="4"/>
       <c r="I261" s="4"/>
@@ -8821,7 +8909,7 @@
       <c r="C262" s="4"/>
       <c r="D262" s="4"/>
       <c r="E262" s="4"/>
-      <c r="F262" s="4"/>
+      <c r="F262" s="15"/>
       <c r="G262" s="4"/>
       <c r="H262" s="4"/>
       <c r="I262" s="4"/>
@@ -8852,7 +8940,7 @@
       <c r="C263" s="4"/>
       <c r="D263" s="4"/>
       <c r="E263" s="4"/>
-      <c r="F263" s="4"/>
+      <c r="F263" s="15"/>
       <c r="G263" s="4"/>
       <c r="H263" s="4"/>
       <c r="I263" s="4"/>
@@ -8883,7 +8971,7 @@
       <c r="C264" s="4"/>
       <c r="D264" s="4"/>
       <c r="E264" s="4"/>
-      <c r="F264" s="4"/>
+      <c r="F264" s="15"/>
       <c r="G264" s="4"/>
       <c r="H264" s="4"/>
       <c r="I264" s="4"/>
@@ -8914,7 +9002,7 @@
       <c r="C265" s="4"/>
       <c r="D265" s="4"/>
       <c r="E265" s="4"/>
-      <c r="F265" s="4"/>
+      <c r="F265" s="15"/>
       <c r="G265" s="4"/>
       <c r="H265" s="4"/>
       <c r="I265" s="4"/>
@@ -8945,7 +9033,7 @@
       <c r="C266" s="4"/>
       <c r="D266" s="4"/>
       <c r="E266" s="4"/>
-      <c r="F266" s="4"/>
+      <c r="F266" s="15"/>
       <c r="G266" s="4"/>
       <c r="H266" s="4"/>
       <c r="I266" s="4"/>
@@ -8976,7 +9064,7 @@
       <c r="C267" s="4"/>
       <c r="D267" s="4"/>
       <c r="E267" s="4"/>
-      <c r="F267" s="4"/>
+      <c r="F267" s="15"/>
       <c r="G267" s="4"/>
       <c r="H267" s="4"/>
       <c r="I267" s="4"/>
@@ -9007,7 +9095,7 @@
       <c r="C268" s="4"/>
       <c r="D268" s="4"/>
       <c r="E268" s="4"/>
-      <c r="F268" s="4"/>
+      <c r="F268" s="15"/>
       <c r="G268" s="4"/>
       <c r="H268" s="4"/>
       <c r="I268" s="4"/>
@@ -9038,7 +9126,7 @@
       <c r="C269" s="4"/>
       <c r="D269" s="4"/>
       <c r="E269" s="4"/>
-      <c r="F269" s="4"/>
+      <c r="F269" s="15"/>
       <c r="G269" s="4"/>
       <c r="H269" s="4"/>
       <c r="I269" s="4"/>
@@ -9069,7 +9157,7 @@
       <c r="C270" s="4"/>
       <c r="D270" s="4"/>
       <c r="E270" s="4"/>
-      <c r="F270" s="4"/>
+      <c r="F270" s="15"/>
       <c r="G270" s="4"/>
       <c r="H270" s="4"/>
       <c r="I270" s="4"/>
@@ -9100,7 +9188,7 @@
       <c r="C271" s="4"/>
       <c r="D271" s="4"/>
       <c r="E271" s="4"/>
-      <c r="F271" s="4"/>
+      <c r="F271" s="15"/>
       <c r="G271" s="4"/>
       <c r="H271" s="4"/>
       <c r="I271" s="4"/>
@@ -9131,7 +9219,7 @@
       <c r="C272" s="4"/>
       <c r="D272" s="4"/>
       <c r="E272" s="4"/>
-      <c r="F272" s="4"/>
+      <c r="F272" s="15"/>
       <c r="G272" s="4"/>
       <c r="H272" s="4"/>
       <c r="I272" s="4"/>
@@ -9162,7 +9250,7 @@
       <c r="C273" s="4"/>
       <c r="D273" s="4"/>
       <c r="E273" s="4"/>
-      <c r="F273" s="4"/>
+      <c r="F273" s="15"/>
       <c r="G273" s="4"/>
       <c r="H273" s="4"/>
       <c r="I273" s="4"/>
@@ -9193,7 +9281,7 @@
       <c r="C274" s="4"/>
       <c r="D274" s="4"/>
       <c r="E274" s="4"/>
-      <c r="F274" s="4"/>
+      <c r="F274" s="15"/>
       <c r="G274" s="4"/>
       <c r="H274" s="4"/>
       <c r="I274" s="4"/>
@@ -9224,7 +9312,7 @@
       <c r="C275" s="4"/>
       <c r="D275" s="4"/>
       <c r="E275" s="4"/>
-      <c r="F275" s="4"/>
+      <c r="F275" s="15"/>
       <c r="G275" s="4"/>
       <c r="H275" s="4"/>
       <c r="I275" s="4"/>
@@ -9255,7 +9343,7 @@
       <c r="C276" s="4"/>
       <c r="D276" s="4"/>
       <c r="E276" s="4"/>
-      <c r="F276" s="4"/>
+      <c r="F276" s="15"/>
       <c r="G276" s="4"/>
       <c r="H276" s="4"/>
       <c r="I276" s="4"/>
@@ -9286,7 +9374,7 @@
       <c r="C277" s="4"/>
       <c r="D277" s="4"/>
       <c r="E277" s="4"/>
-      <c r="F277" s="4"/>
+      <c r="F277" s="15"/>
       <c r="G277" s="4"/>
       <c r="H277" s="4"/>
       <c r="I277" s="4"/>
@@ -9317,7 +9405,7 @@
       <c r="C278" s="4"/>
       <c r="D278" s="4"/>
       <c r="E278" s="4"/>
-      <c r="F278" s="4"/>
+      <c r="F278" s="15"/>
       <c r="G278" s="4"/>
       <c r="H278" s="4"/>
       <c r="I278" s="4"/>
@@ -9348,7 +9436,7 @@
       <c r="C279" s="4"/>
       <c r="D279" s="4"/>
       <c r="E279" s="4"/>
-      <c r="F279" s="4"/>
+      <c r="F279" s="15"/>
       <c r="G279" s="4"/>
       <c r="H279" s="4"/>
       <c r="I279" s="4"/>
@@ -9379,7 +9467,7 @@
       <c r="C280" s="4"/>
       <c r="D280" s="4"/>
       <c r="E280" s="4"/>
-      <c r="F280" s="4"/>
+      <c r="F280" s="15"/>
       <c r="G280" s="4"/>
       <c r="H280" s="4"/>
       <c r="I280" s="4"/>
@@ -9410,7 +9498,7 @@
       <c r="C281" s="4"/>
       <c r="D281" s="4"/>
       <c r="E281" s="4"/>
-      <c r="F281" s="4"/>
+      <c r="F281" s="15"/>
       <c r="G281" s="4"/>
       <c r="H281" s="4"/>
       <c r="I281" s="4"/>
@@ -9441,7 +9529,7 @@
       <c r="C282" s="4"/>
       <c r="D282" s="4"/>
       <c r="E282" s="4"/>
-      <c r="F282" s="4"/>
+      <c r="F282" s="15"/>
       <c r="G282" s="4"/>
       <c r="H282" s="4"/>
       <c r="I282" s="4"/>
@@ -9472,7 +9560,7 @@
       <c r="C283" s="4"/>
       <c r="D283" s="4"/>
       <c r="E283" s="4"/>
-      <c r="F283" s="4"/>
+      <c r="F283" s="15"/>
       <c r="G283" s="4"/>
       <c r="H283" s="4"/>
       <c r="I283" s="4"/>
@@ -9503,7 +9591,7 @@
       <c r="C284" s="4"/>
       <c r="D284" s="4"/>
       <c r="E284" s="4"/>
-      <c r="F284" s="4"/>
+      <c r="F284" s="15"/>
       <c r="G284" s="4"/>
       <c r="H284" s="4"/>
       <c r="I284" s="4"/>
@@ -9534,7 +9622,7 @@
       <c r="C285" s="4"/>
       <c r="D285" s="4"/>
       <c r="E285" s="4"/>
-      <c r="F285" s="4"/>
+      <c r="F285" s="15"/>
       <c r="G285" s="4"/>
       <c r="H285" s="4"/>
       <c r="I285" s="4"/>
@@ -9565,7 +9653,7 @@
       <c r="C286" s="4"/>
       <c r="D286" s="4"/>
       <c r="E286" s="4"/>
-      <c r="F286" s="4"/>
+      <c r="F286" s="15"/>
       <c r="G286" s="4"/>
       <c r="H286" s="4"/>
       <c r="I286" s="4"/>
@@ -9596,7 +9684,7 @@
       <c r="C287" s="4"/>
       <c r="D287" s="4"/>
       <c r="E287" s="4"/>
-      <c r="F287" s="4"/>
+      <c r="F287" s="15"/>
       <c r="G287" s="4"/>
       <c r="H287" s="4"/>
       <c r="I287" s="4"/>
@@ -9627,7 +9715,7 @@
       <c r="C288" s="4"/>
       <c r="D288" s="4"/>
       <c r="E288" s="4"/>
-      <c r="F288" s="4"/>
+      <c r="F288" s="15"/>
       <c r="G288" s="4"/>
       <c r="H288" s="4"/>
       <c r="I288" s="4"/>
@@ -9658,7 +9746,7 @@
       <c r="C289" s="4"/>
       <c r="D289" s="4"/>
       <c r="E289" s="4"/>
-      <c r="F289" s="4"/>
+      <c r="F289" s="15"/>
       <c r="G289" s="4"/>
       <c r="H289" s="4"/>
       <c r="I289" s="4"/>
@@ -9689,7 +9777,7 @@
       <c r="C290" s="4"/>
       <c r="D290" s="4"/>
       <c r="E290" s="4"/>
-      <c r="F290" s="4"/>
+      <c r="F290" s="15"/>
       <c r="G290" s="4"/>
       <c r="H290" s="4"/>
       <c r="I290" s="4"/>
@@ -9720,7 +9808,7 @@
       <c r="C291" s="4"/>
       <c r="D291" s="4"/>
       <c r="E291" s="4"/>
-      <c r="F291" s="4"/>
+      <c r="F291" s="15"/>
       <c r="G291" s="4"/>
       <c r="H291" s="4"/>
       <c r="I291" s="4"/>
@@ -9751,7 +9839,7 @@
       <c r="C292" s="4"/>
       <c r="D292" s="4"/>
       <c r="E292" s="4"/>
-      <c r="F292" s="4"/>
+      <c r="F292" s="15"/>
       <c r="G292" s="4"/>
       <c r="H292" s="4"/>
       <c r="I292" s="4"/>
@@ -9782,7 +9870,7 @@
       <c r="C293" s="4"/>
       <c r="D293" s="4"/>
       <c r="E293" s="4"/>
-      <c r="F293" s="4"/>
+      <c r="F293" s="15"/>
       <c r="G293" s="4"/>
       <c r="H293" s="4"/>
       <c r="I293" s="4"/>
@@ -9813,7 +9901,7 @@
       <c r="C294" s="4"/>
       <c r="D294" s="4"/>
       <c r="E294" s="4"/>
-      <c r="F294" s="4"/>
+      <c r="F294" s="15"/>
       <c r="G294" s="4"/>
       <c r="H294" s="4"/>
       <c r="I294" s="4"/>
@@ -9844,7 +9932,7 @@
       <c r="C295" s="4"/>
       <c r="D295" s="4"/>
       <c r="E295" s="4"/>
-      <c r="F295" s="4"/>
+      <c r="F295" s="15"/>
       <c r="G295" s="4"/>
       <c r="H295" s="4"/>
       <c r="I295" s="4"/>
@@ -9875,7 +9963,7 @@
       <c r="C296" s="4"/>
       <c r="D296" s="4"/>
       <c r="E296" s="4"/>
-      <c r="F296" s="4"/>
+      <c r="F296" s="15"/>
       <c r="G296" s="4"/>
       <c r="H296" s="4"/>
       <c r="I296" s="4"/>
@@ -9906,7 +9994,7 @@
       <c r="C297" s="4"/>
       <c r="D297" s="4"/>
       <c r="E297" s="4"/>
-      <c r="F297" s="4"/>
+      <c r="F297" s="15"/>
       <c r="G297" s="4"/>
       <c r="H297" s="4"/>
       <c r="I297" s="4"/>
@@ -9937,7 +10025,7 @@
       <c r="C298" s="4"/>
       <c r="D298" s="4"/>
       <c r="E298" s="4"/>
-      <c r="F298" s="4"/>
+      <c r="F298" s="15"/>
       <c r="G298" s="4"/>
       <c r="H298" s="4"/>
       <c r="I298" s="4"/>
@@ -9968,7 +10056,7 @@
       <c r="C299" s="4"/>
       <c r="D299" s="4"/>
       <c r="E299" s="4"/>
-      <c r="F299" s="4"/>
+      <c r="F299" s="15"/>
       <c r="G299" s="4"/>
       <c r="H299" s="4"/>
       <c r="I299" s="4"/>
@@ -9999,7 +10087,7 @@
       <c r="C300" s="4"/>
       <c r="D300" s="4"/>
       <c r="E300" s="4"/>
-      <c r="F300" s="4"/>
+      <c r="F300" s="15"/>
       <c r="G300" s="4"/>
       <c r="H300" s="4"/>
       <c r="I300" s="4"/>
@@ -10030,7 +10118,7 @@
       <c r="C301" s="4"/>
       <c r="D301" s="4"/>
       <c r="E301" s="4"/>
-      <c r="F301" s="4"/>
+      <c r="F301" s="15"/>
       <c r="G301" s="4"/>
       <c r="H301" s="4"/>
       <c r="I301" s="4"/>
@@ -10061,7 +10149,7 @@
       <c r="C302" s="4"/>
       <c r="D302" s="4"/>
       <c r="E302" s="4"/>
-      <c r="F302" s="4"/>
+      <c r="F302" s="15"/>
       <c r="G302" s="4"/>
       <c r="H302" s="4"/>
       <c r="I302" s="4"/>
@@ -10092,7 +10180,7 @@
       <c r="C303" s="4"/>
       <c r="D303" s="4"/>
       <c r="E303" s="4"/>
-      <c r="F303" s="4"/>
+      <c r="F303" s="15"/>
       <c r="G303" s="4"/>
       <c r="H303" s="4"/>
       <c r="I303" s="4"/>
@@ -10123,7 +10211,7 @@
       <c r="C304" s="4"/>
       <c r="D304" s="4"/>
       <c r="E304" s="4"/>
-      <c r="F304" s="4"/>
+      <c r="F304" s="15"/>
       <c r="G304" s="4"/>
       <c r="H304" s="4"/>
       <c r="I304" s="4"/>
@@ -10154,7 +10242,7 @@
       <c r="C305" s="4"/>
       <c r="D305" s="4"/>
       <c r="E305" s="4"/>
-      <c r="F305" s="4"/>
+      <c r="F305" s="15"/>
       <c r="G305" s="4"/>
       <c r="H305" s="4"/>
       <c r="I305" s="4"/>
@@ -10185,7 +10273,7 @@
       <c r="C306" s="4"/>
       <c r="D306" s="4"/>
       <c r="E306" s="4"/>
-      <c r="F306" s="4"/>
+      <c r="F306" s="15"/>
       <c r="G306" s="4"/>
       <c r="H306" s="4"/>
       <c r="I306" s="4"/>
@@ -10216,7 +10304,7 @@
       <c r="C307" s="4"/>
       <c r="D307" s="4"/>
       <c r="E307" s="4"/>
-      <c r="F307" s="4"/>
+      <c r="F307" s="15"/>
       <c r="G307" s="4"/>
       <c r="H307" s="4"/>
       <c r="I307" s="4"/>
@@ -10247,7 +10335,7 @@
       <c r="C308" s="4"/>
       <c r="D308" s="4"/>
       <c r="E308" s="4"/>
-      <c r="F308" s="4"/>
+      <c r="F308" s="15"/>
       <c r="G308" s="4"/>
       <c r="H308" s="4"/>
       <c r="I308" s="4"/>
@@ -10278,7 +10366,7 @@
       <c r="C309" s="4"/>
       <c r="D309" s="4"/>
       <c r="E309" s="4"/>
-      <c r="F309" s="4"/>
+      <c r="F309" s="15"/>
       <c r="G309" s="4"/>
       <c r="H309" s="4"/>
       <c r="I309" s="4"/>
@@ -10309,7 +10397,7 @@
       <c r="C310" s="4"/>
       <c r="D310" s="4"/>
       <c r="E310" s="4"/>
-      <c r="F310" s="4"/>
+      <c r="F310" s="15"/>
       <c r="G310" s="4"/>
       <c r="H310" s="4"/>
       <c r="I310" s="4"/>
@@ -10340,7 +10428,7 @@
       <c r="C311" s="4"/>
       <c r="D311" s="4"/>
       <c r="E311" s="4"/>
-      <c r="F311" s="4"/>
+      <c r="F311" s="15"/>
       <c r="G311" s="4"/>
       <c r="H311" s="4"/>
       <c r="I311" s="4"/>
@@ -10371,7 +10459,7 @@
       <c r="C312" s="4"/>
       <c r="D312" s="4"/>
       <c r="E312" s="4"/>
-      <c r="F312" s="4"/>
+      <c r="F312" s="15"/>
       <c r="G312" s="4"/>
       <c r="H312" s="4"/>
       <c r="I312" s="4"/>
@@ -10402,7 +10490,7 @@
       <c r="C313" s="4"/>
       <c r="D313" s="4"/>
       <c r="E313" s="4"/>
-      <c r="F313" s="4"/>
+      <c r="F313" s="15"/>
       <c r="G313" s="4"/>
       <c r="H313" s="4"/>
       <c r="I313" s="4"/>
@@ -10433,7 +10521,7 @@
       <c r="C314" s="4"/>
       <c r="D314" s="4"/>
       <c r="E314" s="4"/>
-      <c r="F314" s="4"/>
+      <c r="F314" s="15"/>
       <c r="G314" s="4"/>
       <c r="H314" s="4"/>
       <c r="I314" s="4"/>
@@ -10464,7 +10552,7 @@
       <c r="C315" s="4"/>
       <c r="D315" s="4"/>
       <c r="E315" s="4"/>
-      <c r="F315" s="4"/>
+      <c r="F315" s="15"/>
       <c r="G315" s="4"/>
       <c r="H315" s="4"/>
       <c r="I315" s="4"/>
@@ -10495,7 +10583,7 @@
       <c r="C316" s="4"/>
       <c r="D316" s="4"/>
       <c r="E316" s="4"/>
-      <c r="F316" s="4"/>
+      <c r="F316" s="15"/>
       <c r="G316" s="4"/>
       <c r="H316" s="4"/>
       <c r="I316" s="4"/>
@@ -10526,7 +10614,7 @@
       <c r="C317" s="4"/>
       <c r="D317" s="4"/>
       <c r="E317" s="4"/>
-      <c r="F317" s="4"/>
+      <c r="F317" s="15"/>
       <c r="G317" s="4"/>
       <c r="H317" s="4"/>
       <c r="I317" s="4"/>
@@ -10557,7 +10645,7 @@
       <c r="C318" s="4"/>
       <c r="D318" s="4"/>
       <c r="E318" s="4"/>
-      <c r="F318" s="4"/>
+      <c r="F318" s="15"/>
       <c r="G318" s="4"/>
       <c r="H318" s="4"/>
       <c r="I318" s="4"/>
@@ -10588,7 +10676,7 @@
       <c r="C319" s="4"/>
       <c r="D319" s="4"/>
       <c r="E319" s="4"/>
-      <c r="F319" s="4"/>
+      <c r="F319" s="15"/>
       <c r="G319" s="4"/>
       <c r="H319" s="4"/>
       <c r="I319" s="4"/>
@@ -10619,7 +10707,7 @@
       <c r="C320" s="4"/>
       <c r="D320" s="4"/>
       <c r="E320" s="4"/>
-      <c r="F320" s="4"/>
+      <c r="F320" s="15"/>
       <c r="G320" s="4"/>
       <c r="H320" s="4"/>
       <c r="I320" s="4"/>
@@ -10650,7 +10738,7 @@
       <c r="C321" s="4"/>
       <c r="D321" s="4"/>
       <c r="E321" s="4"/>
-      <c r="F321" s="4"/>
+      <c r="F321" s="15"/>
       <c r="G321" s="4"/>
       <c r="H321" s="4"/>
       <c r="I321" s="4"/>
@@ -10681,7 +10769,7 @@
       <c r="C322" s="4"/>
       <c r="D322" s="4"/>
       <c r="E322" s="4"/>
-      <c r="F322" s="4"/>
+      <c r="F322" s="15"/>
       <c r="G322" s="4"/>
       <c r="H322" s="4"/>
       <c r="I322" s="4"/>
@@ -10712,7 +10800,7 @@
       <c r="C323" s="4"/>
       <c r="D323" s="4"/>
       <c r="E323" s="4"/>
-      <c r="F323" s="4"/>
+      <c r="F323" s="15"/>
       <c r="G323" s="4"/>
       <c r="H323" s="4"/>
       <c r="I323" s="4"/>
@@ -10743,7 +10831,7 @@
       <c r="C324" s="4"/>
       <c r="D324" s="4"/>
       <c r="E324" s="4"/>
-      <c r="F324" s="4"/>
+      <c r="F324" s="15"/>
       <c r="G324" s="4"/>
       <c r="H324" s="4"/>
       <c r="I324" s="4"/>
@@ -10774,7 +10862,7 @@
       <c r="C325" s="4"/>
       <c r="D325" s="4"/>
       <c r="E325" s="4"/>
-      <c r="F325" s="4"/>
+      <c r="F325" s="15"/>
       <c r="G325" s="4"/>
       <c r="H325" s="4"/>
       <c r="I325" s="4"/>
@@ -10805,7 +10893,7 @@
       <c r="C326" s="4"/>
       <c r="D326" s="4"/>
       <c r="E326" s="4"/>
-      <c r="F326" s="4"/>
+      <c r="F326" s="15"/>
       <c r="G326" s="4"/>
       <c r="H326" s="4"/>
       <c r="I326" s="4"/>
@@ -10836,7 +10924,7 @@
       <c r="C327" s="4"/>
       <c r="D327" s="4"/>
       <c r="E327" s="4"/>
-      <c r="F327" s="4"/>
+      <c r="F327" s="15"/>
       <c r="G327" s="4"/>
       <c r="H327" s="4"/>
       <c r="I327" s="4"/>
@@ -10867,7 +10955,7 @@
       <c r="C328" s="4"/>
       <c r="D328" s="4"/>
       <c r="E328" s="4"/>
-      <c r="F328" s="4"/>
+      <c r="F328" s="15"/>
       <c r="G328" s="4"/>
       <c r="H328" s="4"/>
       <c r="I328" s="4"/>
@@ -10898,7 +10986,7 @@
       <c r="C329" s="4"/>
       <c r="D329" s="4"/>
       <c r="E329" s="4"/>
-      <c r="F329" s="4"/>
+      <c r="F329" s="15"/>
       <c r="G329" s="4"/>
       <c r="H329" s="4"/>
       <c r="I329" s="4"/>
@@ -10929,7 +11017,7 @@
       <c r="C330" s="4"/>
       <c r="D330" s="4"/>
       <c r="E330" s="4"/>
-      <c r="F330" s="4"/>
+      <c r="F330" s="15"/>
       <c r="G330" s="4"/>
       <c r="H330" s="4"/>
       <c r="I330" s="4"/>
@@ -10960,7 +11048,7 @@
       <c r="C331" s="4"/>
       <c r="D331" s="4"/>
       <c r="E331" s="4"/>
-      <c r="F331" s="4"/>
+      <c r="F331" s="15"/>
       <c r="G331" s="4"/>
       <c r="H331" s="4"/>
       <c r="I331" s="4"/>
@@ -10991,7 +11079,7 @@
       <c r="C332" s="4"/>
       <c r="D332" s="4"/>
       <c r="E332" s="4"/>
-      <c r="F332" s="4"/>
+      <c r="F332" s="15"/>
       <c r="G332" s="4"/>
       <c r="H332" s="4"/>
       <c r="I332" s="4"/>
@@ -11022,7 +11110,7 @@
       <c r="C333" s="4"/>
       <c r="D333" s="4"/>
       <c r="E333" s="4"/>
-      <c r="F333" s="4"/>
+      <c r="F333" s="15"/>
       <c r="G333" s="4"/>
       <c r="H333" s="4"/>
       <c r="I333" s="4"/>
@@ -11053,7 +11141,7 @@
       <c r="C334" s="4"/>
       <c r="D334" s="4"/>
       <c r="E334" s="4"/>
-      <c r="F334" s="4"/>
+      <c r="F334" s="15"/>
       <c r="G334" s="4"/>
       <c r="H334" s="4"/>
       <c r="I334" s="4"/>
@@ -11084,7 +11172,7 @@
       <c r="C335" s="4"/>
       <c r="D335" s="4"/>
       <c r="E335" s="4"/>
-      <c r="F335" s="4"/>
+      <c r="F335" s="15"/>
       <c r="G335" s="4"/>
       <c r="H335" s="4"/>
       <c r="I335" s="4"/>
@@ -11115,7 +11203,7 @@
       <c r="C336" s="4"/>
       <c r="D336" s="4"/>
       <c r="E336" s="4"/>
-      <c r="F336" s="4"/>
+      <c r="F336" s="15"/>
       <c r="G336" s="4"/>
       <c r="H336" s="4"/>
       <c r="I336" s="4"/>
@@ -11146,7 +11234,7 @@
       <c r="C337" s="4"/>
       <c r="D337" s="4"/>
       <c r="E337" s="4"/>
-      <c r="F337" s="4"/>
+      <c r="F337" s="15"/>
       <c r="G337" s="4"/>
       <c r="H337" s="4"/>
       <c r="I337" s="4"/>
@@ -11177,7 +11265,7 @@
       <c r="C338" s="4"/>
       <c r="D338" s="4"/>
       <c r="E338" s="4"/>
-      <c r="F338" s="4"/>
+      <c r="F338" s="15"/>
       <c r="G338" s="4"/>
       <c r="H338" s="4"/>
       <c r="I338" s="4"/>
@@ -11208,7 +11296,7 @@
       <c r="C339" s="4"/>
       <c r="D339" s="4"/>
       <c r="E339" s="4"/>
-      <c r="F339" s="4"/>
+      <c r="F339" s="15"/>
       <c r="G339" s="4"/>
       <c r="H339" s="4"/>
       <c r="I339" s="4"/>
@@ -11239,7 +11327,7 @@
       <c r="C340" s="4"/>
       <c r="D340" s="4"/>
       <c r="E340" s="4"/>
-      <c r="F340" s="4"/>
+      <c r="F340" s="15"/>
       <c r="G340" s="4"/>
       <c r="H340" s="4"/>
       <c r="I340" s="4"/>
@@ -11270,7 +11358,7 @@
       <c r="C341" s="4"/>
       <c r="D341" s="4"/>
       <c r="E341" s="4"/>
-      <c r="F341" s="4"/>
+      <c r="F341" s="15"/>
       <c r="G341" s="4"/>
       <c r="H341" s="4"/>
       <c r="I341" s="4"/>
@@ -11301,7 +11389,7 @@
       <c r="C342" s="4"/>
       <c r="D342" s="4"/>
       <c r="E342" s="4"/>
-      <c r="F342" s="4"/>
+      <c r="F342" s="15"/>
       <c r="G342" s="4"/>
       <c r="H342" s="4"/>
       <c r="I342" s="4"/>
@@ -11332,7 +11420,7 @@
       <c r="C343" s="4"/>
       <c r="D343" s="4"/>
       <c r="E343" s="4"/>
-      <c r="F343" s="4"/>
+      <c r="F343" s="15"/>
       <c r="G343" s="4"/>
       <c r="H343" s="4"/>
       <c r="I343" s="4"/>
@@ -11363,7 +11451,7 @@
       <c r="C344" s="4"/>
       <c r="D344" s="4"/>
       <c r="E344" s="4"/>
-      <c r="F344" s="4"/>
+      <c r="F344" s="15"/>
       <c r="G344" s="4"/>
       <c r="H344" s="4"/>
       <c r="I344" s="4"/>
@@ -11394,7 +11482,7 @@
       <c r="C345" s="4"/>
       <c r="D345" s="4"/>
       <c r="E345" s="4"/>
-      <c r="F345" s="4"/>
+      <c r="F345" s="15"/>
       <c r="G345" s="4"/>
       <c r="H345" s="4"/>
       <c r="I345" s="4"/>
@@ -11425,7 +11513,7 @@
       <c r="C346" s="4"/>
       <c r="D346" s="4"/>
       <c r="E346" s="4"/>
-      <c r="F346" s="4"/>
+      <c r="F346" s="15"/>
       <c r="G346" s="4"/>
       <c r="H346" s="4"/>
       <c r="I346" s="4"/>
@@ -11456,7 +11544,7 @@
       <c r="C347" s="4"/>
       <c r="D347" s="4"/>
       <c r="E347" s="4"/>
-      <c r="F347" s="4"/>
+      <c r="F347" s="15"/>
       <c r="G347" s="4"/>
       <c r="H347" s="4"/>
       <c r="I347" s="4"/>
@@ -11487,7 +11575,7 @@
       <c r="C348" s="4"/>
       <c r="D348" s="4"/>
       <c r="E348" s="4"/>
-      <c r="F348" s="4"/>
+      <c r="F348" s="15"/>
       <c r="G348" s="4"/>
       <c r="H348" s="4"/>
       <c r="I348" s="4"/>
@@ -11518,7 +11606,7 @@
       <c r="C349" s="4"/>
       <c r="D349" s="4"/>
       <c r="E349" s="4"/>
-      <c r="F349" s="4"/>
+      <c r="F349" s="15"/>
       <c r="G349" s="4"/>
       <c r="H349" s="4"/>
       <c r="I349" s="4"/>
@@ -11549,7 +11637,7 @@
       <c r="C350" s="4"/>
       <c r="D350" s="4"/>
       <c r="E350" s="4"/>
-      <c r="F350" s="4"/>
+      <c r="F350" s="15"/>
       <c r="G350" s="4"/>
       <c r="H350" s="4"/>
       <c r="I350" s="4"/>
@@ -11580,7 +11668,7 @@
       <c r="C351" s="4"/>
       <c r="D351" s="4"/>
       <c r="E351" s="4"/>
-      <c r="F351" s="4"/>
+      <c r="F351" s="15"/>
       <c r="G351" s="4"/>
       <c r="H351" s="4"/>
       <c r="I351" s="4"/>
@@ -11611,7 +11699,7 @@
       <c r="C352" s="4"/>
       <c r="D352" s="4"/>
       <c r="E352" s="4"/>
-      <c r="F352" s="4"/>
+      <c r="F352" s="15"/>
       <c r="G352" s="4"/>
       <c r="H352" s="4"/>
       <c r="I352" s="4"/>
@@ -11642,7 +11730,7 @@
       <c r="C353" s="4"/>
       <c r="D353" s="4"/>
       <c r="E353" s="4"/>
-      <c r="F353" s="4"/>
+      <c r="F353" s="15"/>
       <c r="G353" s="4"/>
       <c r="H353" s="4"/>
       <c r="I353" s="4"/>
@@ -11673,7 +11761,7 @@
       <c r="C354" s="4"/>
       <c r="D354" s="4"/>
       <c r="E354" s="4"/>
-      <c r="F354" s="4"/>
+      <c r="F354" s="15"/>
       <c r="G354" s="4"/>
       <c r="H354" s="4"/>
       <c r="I354" s="4"/>
@@ -11704,7 +11792,7 @@
       <c r="C355" s="4"/>
       <c r="D355" s="4"/>
       <c r="E355" s="4"/>
-      <c r="F355" s="4"/>
+      <c r="F355" s="15"/>
       <c r="G355" s="4"/>
       <c r="H355" s="4"/>
       <c r="I355" s="4"/>
@@ -11735,7 +11823,7 @@
       <c r="C356" s="4"/>
       <c r="D356" s="4"/>
       <c r="E356" s="4"/>
-      <c r="F356" s="4"/>
+      <c r="F356" s="15"/>
       <c r="G356" s="4"/>
       <c r="H356" s="4"/>
       <c r="I356" s="4"/>
@@ -11766,7 +11854,7 @@
       <c r="C357" s="4"/>
       <c r="D357" s="4"/>
       <c r="E357" s="4"/>
-      <c r="F357" s="4"/>
+      <c r="F357" s="15"/>
       <c r="G357" s="4"/>
       <c r="H357" s="4"/>
       <c r="I357" s="4"/>
@@ -11797,7 +11885,7 @@
       <c r="C358" s="4"/>
       <c r="D358" s="4"/>
       <c r="E358" s="4"/>
-      <c r="F358" s="4"/>
+      <c r="F358" s="15"/>
       <c r="G358" s="4"/>
       <c r="H358" s="4"/>
       <c r="I358" s="4"/>
@@ -11828,7 +11916,7 @@
       <c r="C359" s="4"/>
       <c r="D359" s="4"/>
       <c r="E359" s="4"/>
-      <c r="F359" s="4"/>
+      <c r="F359" s="15"/>
       <c r="G359" s="4"/>
       <c r="H359" s="4"/>
       <c r="I359" s="4"/>
@@ -11859,7 +11947,7 @@
       <c r="C360" s="4"/>
       <c r="D360" s="4"/>
       <c r="E360" s="4"/>
-      <c r="F360" s="4"/>
+      <c r="F360" s="15"/>
       <c r="G360" s="4"/>
       <c r="H360" s="4"/>
       <c r="I360" s="4"/>
@@ -11890,7 +11978,7 @@
       <c r="C361" s="4"/>
       <c r="D361" s="4"/>
       <c r="E361" s="4"/>
-      <c r="F361" s="4"/>
+      <c r="F361" s="15"/>
       <c r="G361" s="4"/>
       <c r="H361" s="4"/>
       <c r="I361" s="4"/>
@@ -11921,7 +12009,7 @@
       <c r="C362" s="4"/>
       <c r="D362" s="4"/>
       <c r="E362" s="4"/>
-      <c r="F362" s="4"/>
+      <c r="F362" s="15"/>
       <c r="G362" s="4"/>
       <c r="H362" s="4"/>
       <c r="I362" s="4"/>
@@ -11952,7 +12040,7 @@
       <c r="C363" s="4"/>
       <c r="D363" s="4"/>
       <c r="E363" s="4"/>
-      <c r="F363" s="4"/>
+      <c r="F363" s="15"/>
       <c r="G363" s="4"/>
       <c r="H363" s="4"/>
       <c r="I363" s="4"/>
@@ -11983,7 +12071,7 @@
       <c r="C364" s="4"/>
       <c r="D364" s="4"/>
       <c r="E364" s="4"/>
-      <c r="F364" s="4"/>
+      <c r="F364" s="15"/>
       <c r="G364" s="4"/>
       <c r="H364" s="4"/>
       <c r="I364" s="4"/>
@@ -12014,7 +12102,7 @@
       <c r="C365" s="4"/>
       <c r="D365" s="4"/>
       <c r="E365" s="4"/>
-      <c r="F365" s="4"/>
+      <c r="F365" s="15"/>
       <c r="G365" s="4"/>
       <c r="H365" s="4"/>
       <c r="I365" s="4"/>
@@ -12045,7 +12133,7 @@
       <c r="C366" s="4"/>
       <c r="D366" s="4"/>
       <c r="E366" s="4"/>
-      <c r="F366" s="4"/>
+      <c r="F366" s="15"/>
       <c r="G366" s="4"/>
       <c r="H366" s="4"/>
       <c r="I366" s="4"/>
@@ -12076,7 +12164,7 @@
       <c r="C367" s="4"/>
       <c r="D367" s="4"/>
       <c r="E367" s="4"/>
-      <c r="F367" s="4"/>
+      <c r="F367" s="15"/>
       <c r="G367" s="4"/>
       <c r="H367" s="4"/>
       <c r="I367" s="4"/>
@@ -12107,7 +12195,7 @@
       <c r="C368" s="4"/>
       <c r="D368" s="4"/>
       <c r="E368" s="4"/>
-      <c r="F368" s="4"/>
+      <c r="F368" s="15"/>
       <c r="G368" s="4"/>
       <c r="H368" s="4"/>
       <c r="I368" s="4"/>
@@ -12138,7 +12226,7 @@
       <c r="C369" s="4"/>
       <c r="D369" s="4"/>
       <c r="E369" s="4"/>
-      <c r="F369" s="4"/>
+      <c r="F369" s="15"/>
       <c r="G369" s="4"/>
       <c r="H369" s="4"/>
       <c r="I369" s="4"/>
@@ -12169,7 +12257,7 @@
       <c r="C370" s="4"/>
       <c r="D370" s="4"/>
       <c r="E370" s="4"/>
-      <c r="F370" s="4"/>
+      <c r="F370" s="15"/>
       <c r="G370" s="4"/>
       <c r="H370" s="4"/>
       <c r="I370" s="4"/>
@@ -12200,7 +12288,7 @@
       <c r="C371" s="4"/>
       <c r="D371" s="4"/>
       <c r="E371" s="4"/>
-      <c r="F371" s="4"/>
+      <c r="F371" s="15"/>
       <c r="G371" s="4"/>
       <c r="H371" s="4"/>
       <c r="I371" s="4"/>
@@ -12231,7 +12319,7 @@
       <c r="C372" s="4"/>
       <c r="D372" s="4"/>
       <c r="E372" s="4"/>
-      <c r="F372" s="4"/>
+      <c r="F372" s="15"/>
       <c r="G372" s="4"/>
       <c r="H372" s="4"/>
       <c r="I372" s="4"/>
@@ -12262,7 +12350,7 @@
       <c r="C373" s="4"/>
       <c r="D373" s="4"/>
       <c r="E373" s="4"/>
-      <c r="F373" s="4"/>
+      <c r="F373" s="15"/>
       <c r="G373" s="4"/>
       <c r="H373" s="4"/>
       <c r="I373" s="4"/>
@@ -12293,7 +12381,7 @@
       <c r="C374" s="4"/>
       <c r="D374" s="4"/>
       <c r="E374" s="4"/>
-      <c r="F374" s="4"/>
+      <c r="F374" s="15"/>
       <c r="G374" s="4"/>
       <c r="H374" s="4"/>
       <c r="I374" s="4"/>
@@ -12324,7 +12412,7 @@
       <c r="C375" s="4"/>
       <c r="D375" s="4"/>
       <c r="E375" s="4"/>
-      <c r="F375" s="4"/>
+      <c r="F375" s="15"/>
       <c r="G375" s="4"/>
       <c r="H375" s="4"/>
       <c r="I375" s="4"/>
@@ -12355,7 +12443,7 @@
       <c r="C376" s="4"/>
       <c r="D376" s="4"/>
       <c r="E376" s="4"/>
-      <c r="F376" s="4"/>
+      <c r="F376" s="15"/>
       <c r="G376" s="4"/>
       <c r="H376" s="4"/>
       <c r="I376" s="4"/>
@@ -12386,7 +12474,7 @@
       <c r="C377" s="4"/>
       <c r="D377" s="4"/>
       <c r="E377" s="4"/>
-      <c r="F377" s="4"/>
+      <c r="F377" s="15"/>
       <c r="G377" s="4"/>
       <c r="H377" s="4"/>
       <c r="I377" s="4"/>
@@ -12417,7 +12505,7 @@
       <c r="C378" s="4"/>
       <c r="D378" s="4"/>
       <c r="E378" s="4"/>
-      <c r="F378" s="4"/>
+      <c r="F378" s="15"/>
       <c r="G378" s="4"/>
       <c r="H378" s="4"/>
       <c r="I378" s="4"/>
@@ -12448,7 +12536,7 @@
       <c r="C379" s="4"/>
       <c r="D379" s="4"/>
       <c r="E379" s="4"/>
-      <c r="F379" s="4"/>
+      <c r="F379" s="15"/>
       <c r="G379" s="4"/>
       <c r="H379" s="4"/>
       <c r="I379" s="4"/>
@@ -12479,7 +12567,7 @@
       <c r="C380" s="4"/>
       <c r="D380" s="4"/>
       <c r="E380" s="4"/>
-      <c r="F380" s="4"/>
+      <c r="F380" s="15"/>
       <c r="G380" s="4"/>
       <c r="H380" s="4"/>
       <c r="I380" s="4"/>
@@ -12510,7 +12598,7 @@
       <c r="C381" s="4"/>
       <c r="D381" s="4"/>
       <c r="E381" s="4"/>
-      <c r="F381" s="4"/>
+      <c r="F381" s="15"/>
       <c r="G381" s="4"/>
       <c r="H381" s="4"/>
       <c r="I381" s="4"/>
@@ -12541,7 +12629,7 @@
       <c r="C382" s="4"/>
       <c r="D382" s="4"/>
       <c r="E382" s="4"/>
-      <c r="F382" s="4"/>
+      <c r="F382" s="15"/>
       <c r="G382" s="4"/>
       <c r="H382" s="4"/>
       <c r="I382" s="4"/>
@@ -12572,7 +12660,7 @@
       <c r="C383" s="4"/>
       <c r="D383" s="4"/>
       <c r="E383" s="4"/>
-      <c r="F383" s="4"/>
+      <c r="F383" s="15"/>
       <c r="G383" s="4"/>
       <c r="H383" s="4"/>
       <c r="I383" s="4"/>
@@ -12603,7 +12691,7 @@
       <c r="C384" s="4"/>
       <c r="D384" s="4"/>
       <c r="E384" s="4"/>
-      <c r="F384" s="4"/>
+      <c r="F384" s="15"/>
       <c r="G384" s="4"/>
       <c r="H384" s="4"/>
       <c r="I384" s="4"/>
@@ -12634,7 +12722,7 @@
       <c r="C385" s="4"/>
       <c r="D385" s="4"/>
       <c r="E385" s="4"/>
-      <c r="F385" s="4"/>
+      <c r="F385" s="15"/>
       <c r="G385" s="4"/>
       <c r="H385" s="4"/>
       <c r="I385" s="4"/>
@@ -12665,7 +12753,7 @@
       <c r="C386" s="4"/>
       <c r="D386" s="4"/>
       <c r="E386" s="4"/>
-      <c r="F386" s="4"/>
+      <c r="F386" s="15"/>
       <c r="G386" s="4"/>
       <c r="H386" s="4"/>
       <c r="I386" s="4"/>
@@ -12696,7 +12784,7 @@
       <c r="C387" s="4"/>
       <c r="D387" s="4"/>
       <c r="E387" s="4"/>
-      <c r="F387" s="4"/>
+      <c r="F387" s="15"/>
       <c r="G387" s="4"/>
       <c r="H387" s="4"/>
       <c r="I387" s="4"/>
@@ -12727,7 +12815,7 @@
       <c r="C388" s="4"/>
       <c r="D388" s="4"/>
       <c r="E388" s="4"/>
-      <c r="F388" s="4"/>
+      <c r="F388" s="15"/>
       <c r="G388" s="4"/>
       <c r="H388" s="4"/>
       <c r="I388" s="4"/>
@@ -12758,7 +12846,7 @@
       <c r="C389" s="4"/>
       <c r="D389" s="4"/>
       <c r="E389" s="4"/>
-      <c r="F389" s="4"/>
+      <c r="F389" s="15"/>
       <c r="G389" s="4"/>
       <c r="H389" s="4"/>
       <c r="I389" s="4"/>
@@ -12789,7 +12877,7 @@
       <c r="C390" s="4"/>
       <c r="D390" s="4"/>
       <c r="E390" s="4"/>
-      <c r="F390" s="4"/>
+      <c r="F390" s="15"/>
       <c r="G390" s="4"/>
       <c r="H390" s="4"/>
       <c r="I390" s="4"/>
@@ -12820,7 +12908,7 @@
       <c r="C391" s="4"/>
       <c r="D391" s="4"/>
       <c r="E391" s="4"/>
-      <c r="F391" s="4"/>
+      <c r="F391" s="15"/>
       <c r="G391" s="4"/>
       <c r="H391" s="4"/>
       <c r="I391" s="4"/>
@@ -12851,7 +12939,7 @@
       <c r="C392" s="4"/>
       <c r="D392" s="4"/>
       <c r="E392" s="4"/>
-      <c r="F392" s="4"/>
+      <c r="F392" s="15"/>
       <c r="G392" s="4"/>
       <c r="H392" s="4"/>
       <c r="I392" s="4"/>
@@ -12882,7 +12970,7 @@
       <c r="C393" s="4"/>
       <c r="D393" s="4"/>
       <c r="E393" s="4"/>
-      <c r="F393" s="4"/>
+      <c r="F393" s="15"/>
       <c r="G393" s="4"/>
       <c r="H393" s="4"/>
       <c r="I393" s="4"/>
@@ -12913,7 +13001,7 @@
       <c r="C394" s="4"/>
       <c r="D394" s="4"/>
       <c r="E394" s="4"/>
-      <c r="F394" s="4"/>
+      <c r="F394" s="15"/>
       <c r="G394" s="4"/>
       <c r="H394" s="4"/>
       <c r="I394" s="4"/>
@@ -12944,7 +13032,7 @@
       <c r="C395" s="4"/>
       <c r="D395" s="4"/>
       <c r="E395" s="4"/>
-      <c r="F395" s="4"/>
+      <c r="F395" s="15"/>
       <c r="G395" s="4"/>
       <c r="H395" s="4"/>
       <c r="I395" s="4"/>
@@ -12975,7 +13063,7 @@
       <c r="C396" s="4"/>
       <c r="D396" s="4"/>
       <c r="E396" s="4"/>
-      <c r="F396" s="4"/>
+      <c r="F396" s="15"/>
       <c r="G396" s="4"/>
       <c r="H396" s="4"/>
       <c r="I396" s="4"/>
@@ -13006,7 +13094,7 @@
       <c r="C397" s="4"/>
       <c r="D397" s="4"/>
       <c r="E397" s="4"/>
-      <c r="F397" s="4"/>
+      <c r="F397" s="15"/>
       <c r="G397" s="4"/>
       <c r="H397" s="4"/>
       <c r="I397" s="4"/>
@@ -13037,7 +13125,7 @@
       <c r="C398" s="4"/>
       <c r="D398" s="4"/>
       <c r="E398" s="4"/>
-      <c r="F398" s="4"/>
+      <c r="F398" s="15"/>
       <c r="G398" s="4"/>
       <c r="H398" s="4"/>
       <c r="I398" s="4"/>
@@ -13068,7 +13156,7 @@
       <c r="C399" s="4"/>
       <c r="D399" s="4"/>
       <c r="E399" s="4"/>
-      <c r="F399" s="4"/>
+      <c r="F399" s="15"/>
       <c r="G399" s="4"/>
       <c r="H399" s="4"/>
       <c r="I399" s="4"/>
@@ -13099,7 +13187,7 @@
       <c r="C400" s="4"/>
       <c r="D400" s="4"/>
       <c r="E400" s="4"/>
-      <c r="F400" s="4"/>
+      <c r="F400" s="15"/>
       <c r="G400" s="4"/>
       <c r="H400" s="4"/>
       <c r="I400" s="4"/>
@@ -13130,7 +13218,7 @@
       <c r="C401" s="4"/>
       <c r="D401" s="4"/>
       <c r="E401" s="4"/>
-      <c r="F401" s="4"/>
+      <c r="F401" s="15"/>
       <c r="G401" s="4"/>
       <c r="H401" s="4"/>
       <c r="I401" s="4"/>
@@ -13161,7 +13249,7 @@
       <c r="C402" s="4"/>
       <c r="D402" s="4"/>
       <c r="E402" s="4"/>
-      <c r="F402" s="4"/>
+      <c r="F402" s="15"/>
       <c r="G402" s="4"/>
       <c r="H402" s="4"/>
       <c r="I402" s="4"/>
@@ -13192,7 +13280,7 @@
       <c r="C403" s="4"/>
       <c r="D403" s="4"/>
       <c r="E403" s="4"/>
-      <c r="F403" s="4"/>
+      <c r="F403" s="15"/>
       <c r="G403" s="4"/>
       <c r="H403" s="4"/>
       <c r="I403" s="4"/>
@@ -13223,7 +13311,7 @@
       <c r="C404" s="4"/>
       <c r="D404" s="4"/>
       <c r="E404" s="4"/>
-      <c r="F404" s="4"/>
+      <c r="F404" s="15"/>
       <c r="G404" s="4"/>
       <c r="H404" s="4"/>
       <c r="I404" s="4"/>
@@ -13254,7 +13342,7 @@
       <c r="C405" s="4"/>
       <c r="D405" s="4"/>
       <c r="E405" s="4"/>
-      <c r="F405" s="4"/>
+      <c r="F405" s="15"/>
       <c r="G405" s="4"/>
       <c r="H405" s="4"/>
       <c r="I405" s="4"/>
@@ -13285,7 +13373,7 @@
       <c r="C406" s="4"/>
       <c r="D406" s="4"/>
       <c r="E406" s="4"/>
-      <c r="F406" s="4"/>
+      <c r="F406" s="15"/>
       <c r="G406" s="4"/>
       <c r="H406" s="4"/>
       <c r="I406" s="4"/>
@@ -13316,7 +13404,7 @@
       <c r="C407" s="4"/>
       <c r="D407" s="4"/>
       <c r="E407" s="4"/>
-      <c r="F407" s="4"/>
+      <c r="F407" s="15"/>
       <c r="G407" s="4"/>
       <c r="H407" s="4"/>
       <c r="I407" s="4"/>
@@ -13347,7 +13435,7 @@
       <c r="C408" s="4"/>
       <c r="D408" s="4"/>
       <c r="E408" s="4"/>
-      <c r="F408" s="4"/>
+      <c r="F408" s="15"/>
       <c r="G408" s="4"/>
       <c r="H408" s="4"/>
       <c r="I408" s="4"/>
@@ -13378,7 +13466,7 @@
       <c r="C409" s="4"/>
       <c r="D409" s="4"/>
       <c r="E409" s="4"/>
-      <c r="F409" s="4"/>
+      <c r="F409" s="15"/>
       <c r="G409" s="4"/>
       <c r="H409" s="4"/>
       <c r="I409" s="4"/>
@@ -13409,7 +13497,7 @@
       <c r="C410" s="4"/>
       <c r="D410" s="4"/>
       <c r="E410" s="4"/>
-      <c r="F410" s="4"/>
+      <c r="F410" s="15"/>
       <c r="G410" s="4"/>
       <c r="H410" s="4"/>
       <c r="I410" s="4"/>
@@ -13440,7 +13528,7 @@
       <c r="C411" s="4"/>
       <c r="D411" s="4"/>
       <c r="E411" s="4"/>
-      <c r="F411" s="4"/>
+      <c r="F411" s="15"/>
       <c r="G411" s="4"/>
       <c r="H411" s="4"/>
       <c r="I411" s="4"/>
@@ -13471,7 +13559,7 @@
       <c r="C412" s="4"/>
       <c r="D412" s="4"/>
       <c r="E412" s="4"/>
-      <c r="F412" s="4"/>
+      <c r="F412" s="15"/>
       <c r="G412" s="4"/>
       <c r="H412" s="4"/>
       <c r="I412" s="4"/>
@@ -13502,7 +13590,7 @@
       <c r="C413" s="4"/>
       <c r="D413" s="4"/>
       <c r="E413" s="4"/>
-      <c r="F413" s="4"/>
+      <c r="F413" s="15"/>
       <c r="G413" s="4"/>
       <c r="H413" s="4"/>
       <c r="I413" s="4"/>
@@ -13533,7 +13621,7 @@
       <c r="C414" s="4"/>
       <c r="D414" s="4"/>
       <c r="E414" s="4"/>
-      <c r="F414" s="4"/>
+      <c r="F414" s="15"/>
       <c r="G414" s="4"/>
       <c r="H414" s="4"/>
       <c r="I414" s="4"/>
@@ -13564,7 +13652,7 @@
       <c r="C415" s="4"/>
       <c r="D415" s="4"/>
       <c r="E415" s="4"/>
-      <c r="F415" s="4"/>
+      <c r="F415" s="15"/>
       <c r="G415" s="4"/>
       <c r="H415" s="4"/>
       <c r="I415" s="4"/>
@@ -13595,7 +13683,7 @@
       <c r="C416" s="4"/>
       <c r="D416" s="4"/>
       <c r="E416" s="4"/>
-      <c r="F416" s="4"/>
+      <c r="F416" s="15"/>
       <c r="G416" s="4"/>
       <c r="H416" s="4"/>
       <c r="I416" s="4"/>
@@ -13626,7 +13714,7 @@
       <c r="C417" s="4"/>
       <c r="D417" s="4"/>
       <c r="E417" s="4"/>
-      <c r="F417" s="4"/>
+      <c r="F417" s="15"/>
       <c r="G417" s="4"/>
       <c r="H417" s="4"/>
       <c r="I417" s="4"/>
@@ -13657,7 +13745,7 @@
       <c r="C418" s="4"/>
       <c r="D418" s="4"/>
       <c r="E418" s="4"/>
-      <c r="F418" s="4"/>
+      <c r="F418" s="15"/>
       <c r="G418" s="4"/>
       <c r="H418" s="4"/>
       <c r="I418" s="4"/>
@@ -13688,7 +13776,7 @@
       <c r="C419" s="4"/>
       <c r="D419" s="4"/>
       <c r="E419" s="4"/>
-      <c r="F419" s="4"/>
+      <c r="F419" s="15"/>
       <c r="G419" s="4"/>
       <c r="H419" s="4"/>
       <c r="I419" s="4"/>
@@ -13719,7 +13807,7 @@
       <c r="C420" s="4"/>
       <c r="D420" s="4"/>
       <c r="E420" s="4"/>
-      <c r="F420" s="4"/>
+      <c r="F420" s="15"/>
       <c r="G420" s="4"/>
       <c r="H420" s="4"/>
       <c r="I420" s="4"/>
@@ -13750,7 +13838,7 @@
       <c r="C421" s="4"/>
       <c r="D421" s="4"/>
       <c r="E421" s="4"/>
-      <c r="F421" s="4"/>
+      <c r="F421" s="15"/>
       <c r="G421" s="4"/>
       <c r="H421" s="4"/>
       <c r="I421" s="4"/>
@@ -13781,7 +13869,7 @@
       <c r="C422" s="4"/>
       <c r="D422" s="4"/>
       <c r="E422" s="4"/>
-      <c r="F422" s="4"/>
+      <c r="F422" s="15"/>
       <c r="G422" s="4"/>
       <c r="H422" s="4"/>
       <c r="I422" s="4"/>
@@ -13812,7 +13900,7 @@
       <c r="C423" s="4"/>
       <c r="D423" s="4"/>
       <c r="E423" s="4"/>
-      <c r="F423" s="4"/>
+      <c r="F423" s="15"/>
       <c r="G423" s="4"/>
       <c r="H423" s="4"/>
       <c r="I423" s="4"/>
@@ -13843,7 +13931,7 @@
       <c r="C424" s="4"/>
       <c r="D424" s="4"/>
       <c r="E424" s="4"/>
-      <c r="F424" s="4"/>
+      <c r="F424" s="15"/>
       <c r="G424" s="4"/>
       <c r="H424" s="4"/>
       <c r="I424" s="4"/>
@@ -13874,7 +13962,7 @@
       <c r="C425" s="4"/>
       <c r="D425" s="4"/>
       <c r="E425" s="4"/>
-      <c r="F425" s="4"/>
+      <c r="F425" s="15"/>
       <c r="G425" s="4"/>
       <c r="H425" s="4"/>
       <c r="I425" s="4"/>
@@ -13905,7 +13993,7 @@
       <c r="C426" s="4"/>
       <c r="D426" s="4"/>
       <c r="E426" s="4"/>
-      <c r="F426" s="4"/>
+      <c r="F426" s="15"/>
       <c r="G426" s="4"/>
       <c r="H426" s="4"/>
       <c r="I426" s="4"/>
@@ -13936,7 +14024,7 @@
       <c r="C427" s="4"/>
       <c r="D427" s="4"/>
       <c r="E427" s="4"/>
-      <c r="F427" s="4"/>
+      <c r="F427" s="15"/>
       <c r="G427" s="4"/>
       <c r="H427" s="4"/>
       <c r="I427" s="4"/>
@@ -13967,7 +14055,7 @@
       <c r="C428" s="4"/>
       <c r="D428" s="4"/>
       <c r="E428" s="4"/>
-      <c r="F428" s="4"/>
+      <c r="F428" s="15"/>
       <c r="G428" s="4"/>
       <c r="H428" s="4"/>
       <c r="I428" s="4"/>
@@ -13998,7 +14086,7 @@
       <c r="C429" s="4"/>
       <c r="D429" s="4"/>
       <c r="E429" s="4"/>
-      <c r="F429" s="4"/>
+      <c r="F429" s="15"/>
       <c r="G429" s="4"/>
       <c r="H429" s="4"/>
       <c r="I429" s="4"/>
@@ -14029,7 +14117,7 @@
       <c r="C430" s="4"/>
       <c r="D430" s="4"/>
       <c r="E430" s="4"/>
-      <c r="F430" s="4"/>
+      <c r="F430" s="15"/>
       <c r="G430" s="4"/>
       <c r="H430" s="4"/>
       <c r="I430" s="4"/>
@@ -14060,7 +14148,7 @@
       <c r="C431" s="4"/>
       <c r="D431" s="4"/>
       <c r="E431" s="4"/>
-      <c r="F431" s="4"/>
+      <c r="F431" s="15"/>
       <c r="G431" s="4"/>
       <c r="H431" s="4"/>
       <c r="I431" s="4"/>
@@ -14091,7 +14179,7 @@
       <c r="C432" s="4"/>
       <c r="D432" s="4"/>
       <c r="E432" s="4"/>
-      <c r="F432" s="4"/>
+      <c r="F432" s="15"/>
       <c r="G432" s="4"/>
       <c r="H432" s="4"/>
       <c r="I432" s="4"/>
@@ -14122,7 +14210,7 @@
       <c r="C433" s="4"/>
       <c r="D433" s="4"/>
       <c r="E433" s="4"/>
-      <c r="F433" s="4"/>
+      <c r="F433" s="15"/>
       <c r="G433" s="4"/>
       <c r="H433" s="4"/>
       <c r="I433" s="4"/>
@@ -14153,7 +14241,7 @@
       <c r="C434" s="4"/>
       <c r="D434" s="4"/>
       <c r="E434" s="4"/>
-      <c r="F434" s="4"/>
+      <c r="F434" s="15"/>
       <c r="G434" s="4"/>
       <c r="H434" s="4"/>
       <c r="I434" s="4"/>
@@ -14184,7 +14272,7 @@
       <c r="C435" s="4"/>
       <c r="D435" s="4"/>
       <c r="E435" s="4"/>
-      <c r="F435" s="4"/>
+      <c r="F435" s="15"/>
       <c r="G435" s="4"/>
       <c r="H435" s="4"/>
       <c r="I435" s="4"/>
@@ -14215,7 +14303,7 @@
       <c r="C436" s="4"/>
       <c r="D436" s="4"/>
       <c r="E436" s="4"/>
-      <c r="F436" s="4"/>
+      <c r="F436" s="15"/>
       <c r="G436" s="4"/>
       <c r="H436" s="4"/>
       <c r="I436" s="4"/>
@@ -14246,7 +14334,7 @@
       <c r="C437" s="4"/>
       <c r="D437" s="4"/>
       <c r="E437" s="4"/>
-      <c r="F437" s="4"/>
+      <c r="F437" s="15"/>
       <c r="G437" s="4"/>
       <c r="H437" s="4"/>
       <c r="I437" s="4"/>
@@ -14277,7 +14365,7 @@
       <c r="C438" s="4"/>
       <c r="D438" s="4"/>
       <c r="E438" s="4"/>
-      <c r="F438" s="4"/>
+      <c r="F438" s="15"/>
       <c r="G438" s="4"/>
       <c r="H438" s="4"/>
       <c r="I438" s="4"/>
@@ -14308,7 +14396,7 @@
       <c r="C439" s="4"/>
       <c r="D439" s="4"/>
       <c r="E439" s="4"/>
-      <c r="F439" s="4"/>
+      <c r="F439" s="15"/>
       <c r="G439" s="4"/>
       <c r="H439" s="4"/>
       <c r="I439" s="4"/>
@@ -14339,7 +14427,7 @@
       <c r="C440" s="4"/>
       <c r="D440" s="4"/>
       <c r="E440" s="4"/>
-      <c r="F440" s="4"/>
+      <c r="F440" s="15"/>
       <c r="G440" s="4"/>
       <c r="H440" s="4"/>
       <c r="I440" s="4"/>
@@ -14370,7 +14458,7 @@
       <c r="C441" s="4"/>
       <c r="D441" s="4"/>
       <c r="E441" s="4"/>
-      <c r="F441" s="4"/>
+      <c r="F441" s="15"/>
       <c r="G441" s="4"/>
       <c r="H441" s="4"/>
       <c r="I441" s="4"/>
@@ -14401,7 +14489,7 @@
       <c r="C442" s="4"/>
       <c r="D442" s="4"/>
       <c r="E442" s="4"/>
-      <c r="F442" s="4"/>
+      <c r="F442" s="15"/>
       <c r="G442" s="4"/>
       <c r="H442" s="4"/>
       <c r="I442" s="4"/>
@@ -14432,7 +14520,7 @@
       <c r="C443" s="4"/>
       <c r="D443" s="4"/>
       <c r="E443" s="4"/>
-      <c r="F443" s="4"/>
+      <c r="F443" s="15"/>
       <c r="G443" s="4"/>
       <c r="H443" s="4"/>
       <c r="I443" s="4"/>
@@ -14463,7 +14551,7 @@
       <c r="C444" s="4"/>
       <c r="D444" s="4"/>
       <c r="E444" s="4"/>
-      <c r="F444" s="4"/>
+      <c r="F444" s="15"/>
       <c r="G444" s="4"/>
       <c r="H444" s="4"/>
       <c r="I444" s="4"/>
@@ -14494,7 +14582,7 @@
       <c r="C445" s="4"/>
       <c r="D445" s="4"/>
       <c r="E445" s="4"/>
-      <c r="F445" s="4"/>
+      <c r="F445" s="15"/>
       <c r="G445" s="4"/>
       <c r="H445" s="4"/>
       <c r="I445" s="4"/>
@@ -14525,7 +14613,7 @@
       <c r="C446" s="4"/>
       <c r="D446" s="4"/>
       <c r="E446" s="4"/>
-      <c r="F446" s="4"/>
+      <c r="F446" s="15"/>
       <c r="G446" s="4"/>
       <c r="H446" s="4"/>
       <c r="I446" s="4"/>
@@ -14556,7 +14644,7 @@
       <c r="C447" s="4"/>
       <c r="D447" s="4"/>
       <c r="E447" s="4"/>
-      <c r="F447" s="4"/>
+      <c r="F447" s="15"/>
       <c r="G447" s="4"/>
       <c r="H447" s="4"/>
       <c r="I447" s="4"/>
@@ -14587,7 +14675,7 @@
       <c r="C448" s="4"/>
       <c r="D448" s="4"/>
       <c r="E448" s="4"/>
-      <c r="F448" s="4"/>
+      <c r="F448" s="15"/>
       <c r="G448" s="4"/>
       <c r="H448" s="4"/>
       <c r="I448" s="4"/>
@@ -14618,7 +14706,7 @@
       <c r="C449" s="4"/>
       <c r="D449" s="4"/>
       <c r="E449" s="4"/>
-      <c r="F449" s="4"/>
+      <c r="F449" s="15"/>
       <c r="G449" s="4"/>
       <c r="H449" s="4"/>
       <c r="I449" s="4"/>
@@ -14649,7 +14737,7 @@
       <c r="C450" s="4"/>
       <c r="D450" s="4"/>
       <c r="E450" s="4"/>
-      <c r="F450" s="4"/>
+      <c r="F450" s="15"/>
       <c r="G450" s="4"/>
       <c r="H450" s="4"/>
       <c r="I450" s="4"/>
@@ -14680,7 +14768,7 @@
       <c r="C451" s="4"/>
       <c r="D451" s="4"/>
       <c r="E451" s="4"/>
-      <c r="F451" s="4"/>
+      <c r="F451" s="15"/>
       <c r="G451" s="4"/>
       <c r="H451" s="4"/>
       <c r="I451" s="4"/>
@@ -14711,7 +14799,7 @@
       <c r="C452" s="4"/>
       <c r="D452" s="4"/>
       <c r="E452" s="4"/>
-      <c r="F452" s="4"/>
+      <c r="F452" s="15"/>
       <c r="G452" s="4"/>
       <c r="H452" s="4"/>
       <c r="I452" s="4"/>
@@ -14742,7 +14830,7 @@
       <c r="C453" s="4"/>
       <c r="D453" s="4"/>
       <c r="E453" s="4"/>
-      <c r="F453" s="4"/>
+      <c r="F453" s="15"/>
       <c r="G453" s="4"/>
       <c r="H453" s="4"/>
       <c r="I453" s="4"/>
@@ -14773,7 +14861,7 @@
       <c r="C454" s="4"/>
       <c r="D454" s="4"/>
       <c r="E454" s="4"/>
-      <c r="F454" s="4"/>
+      <c r="F454" s="15"/>
       <c r="G454" s="4"/>
       <c r="H454" s="4"/>
       <c r="I454" s="4"/>
@@ -14804,7 +14892,7 @@
       <c r="C455" s="4"/>
       <c r="D455" s="4"/>
       <c r="E455" s="4"/>
-      <c r="F455" s="4"/>
+      <c r="F455" s="15"/>
       <c r="G455" s="4"/>
       <c r="H455" s="4"/>
       <c r="I455" s="4"/>
@@ -14835,7 +14923,7 @@
       <c r="C456" s="4"/>
       <c r="D456" s="4"/>
       <c r="E456" s="4"/>
-      <c r="F456" s="4"/>
+      <c r="F456" s="15"/>
       <c r="G456" s="4"/>
       <c r="H456" s="4"/>
       <c r="I456" s="4"/>
@@ -14866,7 +14954,7 @@
       <c r="C457" s="4"/>
       <c r="D457" s="4"/>
       <c r="E457" s="4"/>
-      <c r="F457" s="4"/>
+      <c r="F457" s="15"/>
       <c r="G457" s="4"/>
       <c r="H457" s="4"/>
       <c r="I457" s="4"/>
@@ -14897,7 +14985,7 @@
       <c r="C458" s="4"/>
       <c r="D458" s="4"/>
       <c r="E458" s="4"/>
-      <c r="F458" s="4"/>
+      <c r="F458" s="15"/>
       <c r="G458" s="4"/>
       <c r="H458" s="4"/>
       <c r="I458" s="4"/>
@@ -14928,7 +15016,7 @@
       <c r="C459" s="4"/>
       <c r="D459" s="4"/>
       <c r="E459" s="4"/>
-      <c r="F459" s="4"/>
+      <c r="F459" s="15"/>
       <c r="G459" s="4"/>
       <c r="H459" s="4"/>
       <c r="I459" s="4"/>
@@ -14959,7 +15047,7 @@
       <c r="C460" s="4"/>
       <c r="D460" s="4"/>
       <c r="E460" s="4"/>
-      <c r="F460" s="4"/>
+      <c r="F460" s="15"/>
       <c r="G460" s="4"/>
       <c r="H460" s="4"/>
       <c r="I460" s="4"/>
@@ -14990,7 +15078,7 @@
       <c r="C461" s="4"/>
       <c r="D461" s="4"/>
       <c r="E461" s="4"/>
-      <c r="F461" s="4"/>
+      <c r="F461" s="15"/>
       <c r="G461" s="4"/>
       <c r="H461" s="4"/>
       <c r="I461" s="4"/>
@@ -15021,7 +15109,7 @@
       <c r="C462" s="4"/>
       <c r="D462" s="4"/>
       <c r="E462" s="4"/>
-      <c r="F462" s="4"/>
+      <c r="F462" s="15"/>
       <c r="G462" s="4"/>
       <c r="H462" s="4"/>
       <c r="I462" s="4"/>
@@ -15052,7 +15140,7 @@
       <c r="C463" s="4"/>
       <c r="D463" s="4"/>
       <c r="E463" s="4"/>
-      <c r="F463" s="4"/>
+      <c r="F463" s="15"/>
       <c r="G463" s="4"/>
       <c r="H463" s="4"/>
       <c r="I463" s="4"/>
@@ -15083,7 +15171,7 @@
       <c r="C464" s="4"/>
       <c r="D464" s="4"/>
       <c r="E464" s="4"/>
-      <c r="F464" s="4"/>
+      <c r="F464" s="15"/>
       <c r="G464" s="4"/>
       <c r="H464" s="4"/>
       <c r="I464" s="4"/>
@@ -15114,7 +15202,7 @@
       <c r="C465" s="4"/>
       <c r="D465" s="4"/>
       <c r="E465" s="4"/>
-      <c r="F465" s="4"/>
+      <c r="F465" s="15"/>
       <c r="G465" s="4"/>
       <c r="H465" s="4"/>
       <c r="I465" s="4"/>
@@ -15145,7 +15233,7 @@
       <c r="C466" s="4"/>
       <c r="D466" s="4"/>
       <c r="E466" s="4"/>
-      <c r="F466" s="4"/>
+      <c r="F466" s="15"/>
       <c r="G466" s="4"/>
       <c r="H466" s="4"/>
       <c r="I466" s="4"/>
@@ -15176,7 +15264,7 @@
       <c r="C467" s="4"/>
       <c r="D467" s="4"/>
       <c r="E467" s="4"/>
-      <c r="F467" s="4"/>
+      <c r="F467" s="15"/>
       <c r="G467" s="4"/>
       <c r="H467" s="4"/>
       <c r="I467" s="4"/>
@@ -15207,7 +15295,7 @@
       <c r="C468" s="4"/>
       <c r="D468" s="4"/>
       <c r="E468" s="4"/>
-      <c r="F468" s="4"/>
+      <c r="F468" s="15"/>
       <c r="G468" s="4"/>
       <c r="H468" s="4"/>
       <c r="I468" s="4"/>
@@ -15238,7 +15326,7 @@
       <c r="C469" s="4"/>
       <c r="D469" s="4"/>
       <c r="E469" s="4"/>
-      <c r="F469" s="4"/>
+      <c r="F469" s="15"/>
       <c r="G469" s="4"/>
       <c r="H469" s="4"/>
       <c r="I469" s="4"/>
@@ -15269,7 +15357,7 @@
       <c r="C470" s="4"/>
       <c r="D470" s="4"/>
       <c r="E470" s="4"/>
-      <c r="F470" s="4"/>
+      <c r="F470" s="15"/>
       <c r="G470" s="4"/>
       <c r="H470" s="4"/>
       <c r="I470" s="4"/>
@@ -15300,7 +15388,7 @@
       <c r="C471" s="4"/>
       <c r="D471" s="4"/>
       <c r="E471" s="4"/>
-      <c r="F471" s="4"/>
+      <c r="F471" s="15"/>
       <c r="G471" s="4"/>
       <c r="H471" s="4"/>
       <c r="I471" s="4"/>
@@ -15331,7 +15419,7 @@
       <c r="C472" s="4"/>
       <c r="D472" s="4"/>
       <c r="E472" s="4"/>
-      <c r="F472" s="4"/>
+      <c r="F472" s="15"/>
       <c r="G472" s="4"/>
       <c r="H472" s="4"/>
       <c r="I472" s="4"/>
@@ -15362,7 +15450,7 @@
       <c r="C473" s="4"/>
       <c r="D473" s="4"/>
       <c r="E473" s="4"/>
-      <c r="F473" s="4"/>
+      <c r="F473" s="15"/>
       <c r="G473" s="4"/>
       <c r="H473" s="4"/>
       <c r="I473" s="4"/>
@@ -15393,7 +15481,7 @@
       <c r="C474" s="4"/>
       <c r="D474" s="4"/>
       <c r="E474" s="4"/>
-      <c r="F474" s="4"/>
+      <c r="F474" s="15"/>
       <c r="G474" s="4"/>
       <c r="H474" s="4"/>
       <c r="I474" s="4"/>
@@ -15424,7 +15512,7 @@
       <c r="C475" s="4"/>
       <c r="D475" s="4"/>
       <c r="E475" s="4"/>
-      <c r="F475" s="4"/>
+      <c r="F475" s="15"/>
       <c r="G475" s="4"/>
       <c r="H475" s="4"/>
       <c r="I475" s="4"/>
@@ -15455,7 +15543,7 @@
       <c r="C476" s="4"/>
       <c r="D476" s="4"/>
       <c r="E476" s="4"/>
-      <c r="F476" s="4"/>
+      <c r="F476" s="15"/>
       <c r="G476" s="4"/>
       <c r="H476" s="4"/>
       <c r="I476" s="4"/>
@@ -15486,7 +15574,7 @@
       <c r="C477" s="4"/>
       <c r="D477" s="4"/>
       <c r="E477" s="4"/>
-      <c r="F477" s="4"/>
+      <c r="F477" s="15"/>
       <c r="G477" s="4"/>
       <c r="H477" s="4"/>
       <c r="I477" s="4"/>
@@ -15517,7 +15605,7 @@
       <c r="C478" s="4"/>
       <c r="D478" s="4"/>
       <c r="E478" s="4"/>
-      <c r="F478" s="4"/>
+      <c r="F478" s="15"/>
       <c r="G478" s="4"/>
       <c r="H478" s="4"/>
       <c r="I478" s="4"/>
@@ -15548,7 +15636,7 @@
       <c r="C479" s="4"/>
       <c r="D479" s="4"/>
       <c r="E479" s="4"/>
-      <c r="F479" s="4"/>
+      <c r="F479" s="15"/>
       <c r="G479" s="4"/>
       <c r="H479" s="4"/>
       <c r="I479" s="4"/>
@@ -15579,7 +15667,7 @@
       <c r="C480" s="4"/>
       <c r="D480" s="4"/>
       <c r="E480" s="4"/>
-      <c r="F480" s="4"/>
+      <c r="F480" s="15"/>
       <c r="G480" s="4"/>
       <c r="H480" s="4"/>
       <c r="I480" s="4"/>
@@ -15610,7 +15698,7 @@
       <c r="C481" s="4"/>
       <c r="D481" s="4"/>
       <c r="E481" s="4"/>
-      <c r="F481" s="4"/>
+      <c r="F481" s="15"/>
       <c r="G481" s="4"/>
       <c r="H481" s="4"/>
       <c r="I481" s="4"/>
@@ -15641,7 +15729,7 @@
       <c r="C482" s="4"/>
       <c r="D482" s="4"/>
       <c r="E482" s="4"/>
-      <c r="F482" s="4"/>
+      <c r="F482" s="15"/>
       <c r="G482" s="4"/>
       <c r="H482" s="4"/>
       <c r="I482" s="4"/>
@@ -15672,7 +15760,7 @@
       <c r="C483" s="4"/>
       <c r="D483" s="4"/>
       <c r="E483" s="4"/>
-      <c r="F483" s="4"/>
+      <c r="F483" s="15"/>
       <c r="G483" s="4"/>
       <c r="H483" s="4"/>
       <c r="I483" s="4"/>
@@ -15703,7 +15791,7 @@
       <c r="C484" s="4"/>
       <c r="D484" s="4"/>
       <c r="E484" s="4"/>
-      <c r="F484" s="4"/>
+      <c r="F484" s="15"/>
       <c r="G484" s="4"/>
       <c r="H484" s="4"/>
       <c r="I484" s="4"/>
@@ -15734,7 +15822,7 @@
       <c r="C485" s="4"/>
       <c r="D485" s="4"/>
       <c r="E485" s="4"/>
-      <c r="F485" s="4"/>
+      <c r="F485" s="15"/>
       <c r="G485" s="4"/>
       <c r="H485" s="4"/>
       <c r="I485" s="4"/>
@@ -15765,7 +15853,7 @@
       <c r="C486" s="4"/>
       <c r="D486" s="4"/>
       <c r="E486" s="4"/>
-      <c r="F486" s="4"/>
+      <c r="F486" s="15"/>
       <c r="G486" s="4"/>
       <c r="H486" s="4"/>
       <c r="I486" s="4"/>
@@ -15796,7 +15884,7 @@
       <c r="C487" s="4"/>
       <c r="D487" s="4"/>
       <c r="E487" s="4"/>
-      <c r="F487" s="4"/>
+      <c r="F487" s="15"/>
       <c r="G487" s="4"/>
       <c r="H487" s="4"/>
       <c r="I487" s="4"/>
@@ -15827,7 +15915,7 @@
       <c r="C488" s="4"/>
       <c r="D488" s="4"/>
       <c r="E488" s="4"/>
-      <c r="F488" s="4"/>
+      <c r="F488" s="15"/>
       <c r="G488" s="4"/>
       <c r="H488" s="4"/>
       <c r="I488" s="4"/>
@@ -15858,7 +15946,7 @@
       <c r="C489" s="4"/>
       <c r="D489" s="4"/>
       <c r="E489" s="4"/>
-      <c r="F489" s="4"/>
+      <c r="F489" s="15"/>
       <c r="G489" s="4"/>
       <c r="H489" s="4"/>
       <c r="I489" s="4"/>
@@ -15889,7 +15977,7 @@
       <c r="C490" s="4"/>
       <c r="D490" s="4"/>
       <c r="E490" s="4"/>
-      <c r="F490" s="4"/>
+      <c r="F490" s="15"/>
       <c r="G490" s="4"/>
       <c r="H490" s="4"/>
       <c r="I490" s="4"/>
@@ -15920,7 +16008,7 @@
       <c r="C491" s="4"/>
       <c r="D491" s="4"/>
       <c r="E491" s="4"/>
-      <c r="F491" s="4"/>
+      <c r="F491" s="15"/>
       <c r="G491" s="4"/>
       <c r="H491" s="4"/>
       <c r="I491" s="4"/>
@@ -15951,7 +16039,7 @@
       <c r="C492" s="4"/>
       <c r="D492" s="4"/>
       <c r="E492" s="4"/>
-      <c r="F492" s="4"/>
+      <c r="F492" s="15"/>
       <c r="G492" s="4"/>
       <c r="H492" s="4"/>
       <c r="I492" s="4"/>
@@ -15982,7 +16070,7 @@
       <c r="C493" s="4"/>
       <c r="D493" s="4"/>
       <c r="E493" s="4"/>
-      <c r="F493" s="4"/>
+      <c r="F493" s="15"/>
       <c r="G493" s="4"/>
       <c r="H493" s="4"/>
       <c r="I493" s="4"/>
@@ -16013,7 +16101,7 @@
       <c r="C494" s="4"/>
       <c r="D494" s="4"/>
       <c r="E494" s="4"/>
-      <c r="F494" s="4"/>
+      <c r="F494" s="15"/>
       <c r="G494" s="4"/>
       <c r="H494" s="4"/>
       <c r="I494" s="4"/>
@@ -16044,7 +16132,7 @@
       <c r="C495" s="4"/>
       <c r="D495" s="4"/>
       <c r="E495" s="4"/>
-      <c r="F495" s="4"/>
+      <c r="F495" s="15"/>
       <c r="G495" s="4"/>
       <c r="H495" s="4"/>
       <c r="I495" s="4"/>
@@ -16075,7 +16163,7 @@
       <c r="C496" s="4"/>
       <c r="D496" s="4"/>
       <c r="E496" s="4"/>
-      <c r="F496" s="4"/>
+      <c r="F496" s="15"/>
       <c r="G496" s="4"/>
       <c r="H496" s="4"/>
       <c r="I496" s="4"/>
@@ -16106,7 +16194,7 @@
       <c r="C497" s="4"/>
       <c r="D497" s="4"/>
       <c r="E497" s="4"/>
-      <c r="F497" s="4"/>
+      <c r="F497" s="15"/>
       <c r="G497" s="4"/>
       <c r="H497" s="4"/>
       <c r="I497" s="4"/>
@@ -16137,7 +16225,7 @@
       <c r="C498" s="4"/>
       <c r="D498" s="4"/>
       <c r="E498" s="4"/>
-      <c r="F498" s="4"/>
+      <c r="F498" s="15"/>
       <c r="G498" s="4"/>
       <c r="H498" s="4"/>
       <c r="I498" s="4"/>
@@ -16168,7 +16256,7 @@
       <c r="C499" s="4"/>
       <c r="D499" s="4"/>
       <c r="E499" s="4"/>
-      <c r="F499" s="4"/>
+      <c r="F499" s="15"/>
       <c r="G499" s="4"/>
       <c r="H499" s="4"/>
       <c r="I499" s="4"/>
@@ -16199,7 +16287,7 @@
       <c r="C500" s="4"/>
       <c r="D500" s="4"/>
       <c r="E500" s="4"/>
-      <c r="F500" s="4"/>
+      <c r="F500" s="15"/>
       <c r="G500" s="4"/>
       <c r="H500" s="4"/>
       <c r="I500" s="4"/>
@@ -16230,7 +16318,7 @@
       <c r="C501" s="4"/>
       <c r="D501" s="4"/>
       <c r="E501" s="4"/>
-      <c r="F501" s="4"/>
+      <c r="F501" s="15"/>
       <c r="G501" s="4"/>
       <c r="H501" s="4"/>
       <c r="I501" s="4"/>
@@ -16261,7 +16349,7 @@
       <c r="C502" s="4"/>
       <c r="D502" s="4"/>
       <c r="E502" s="4"/>
-      <c r="F502" s="4"/>
+      <c r="F502" s="15"/>
       <c r="G502" s="4"/>
       <c r="H502" s="4"/>
       <c r="I502" s="4"/>
@@ -16292,7 +16380,7 @@
       <c r="C503" s="4"/>
       <c r="D503" s="4"/>
       <c r="E503" s="4"/>
-      <c r="F503" s="4"/>
+      <c r="F503" s="15"/>
       <c r="G503" s="4"/>
       <c r="H503" s="4"/>
       <c r="I503" s="4"/>
@@ -16323,7 +16411,7 @@
       <c r="C504" s="4"/>
       <c r="D504" s="4"/>
       <c r="E504" s="4"/>
-      <c r="F504" s="4"/>
+      <c r="F504" s="15"/>
       <c r="G504" s="4"/>
       <c r="H504" s="4"/>
       <c r="I504" s="4"/>
@@ -16354,7 +16442,7 @@
       <c r="C505" s="4"/>
       <c r="D505" s="4"/>
       <c r="E505" s="4"/>
-      <c r="F505" s="4"/>
+      <c r="F505" s="15"/>
       <c r="G505" s="4"/>
       <c r="H505" s="4"/>
       <c r="I505" s="4"/>
@@ -16385,7 +16473,7 @@
       <c r="C506" s="4"/>
       <c r="D506" s="4"/>
       <c r="E506" s="4"/>
-      <c r="F506" s="4"/>
+      <c r="F506" s="15"/>
       <c r="G506" s="4"/>
       <c r="H506" s="4"/>
       <c r="I506" s="4"/>
@@ -16416,7 +16504,7 @@
       <c r="C507" s="4"/>
       <c r="D507" s="4"/>
       <c r="E507" s="4"/>
-      <c r="F507" s="4"/>
+      <c r="F507" s="15"/>
       <c r="G507" s="4"/>
       <c r="H507" s="4"/>
       <c r="I507" s="4"/>
@@ -16447,7 +16535,7 @@
       <c r="C508" s="4"/>
       <c r="D508" s="4"/>
       <c r="E508" s="4"/>
-      <c r="F508" s="4"/>
+      <c r="F508" s="15"/>
       <c r="G508" s="4"/>
       <c r="H508" s="4"/>
       <c r="I508" s="4"/>
@@ -16478,7 +16566,7 @@
       <c r="C509" s="4"/>
       <c r="D509" s="4"/>
       <c r="E509" s="4"/>
-      <c r="F509" s="4"/>
+      <c r="F509" s="15"/>
       <c r="G509" s="4"/>
       <c r="H509" s="4"/>
       <c r="I509" s="4"/>
@@ -16509,7 +16597,7 @@
       <c r="C510" s="4"/>
       <c r="D510" s="4"/>
       <c r="E510" s="4"/>
-      <c r="F510" s="4"/>
+      <c r="F510" s="15"/>
       <c r="G510" s="4"/>
       <c r="H510" s="4"/>
       <c r="I510" s="4"/>
@@ -16540,7 +16628,7 @@
       <c r="C511" s="4"/>
       <c r="D511" s="4"/>
       <c r="E511" s="4"/>
-      <c r="F511" s="4"/>
+      <c r="F511" s="15"/>
       <c r="G511" s="4"/>
       <c r="H511" s="4"/>
       <c r="I511" s="4"/>
@@ -16571,7 +16659,7 @@
       <c r="C512" s="4"/>
       <c r="D512" s="4"/>
       <c r="E512" s="4"/>
-      <c r="F512" s="4"/>
+      <c r="F512" s="15"/>
       <c r="G512" s="4"/>
       <c r="H512" s="4"/>
       <c r="I512" s="4"/>
@@ -16602,7 +16690,7 @@
       <c r="C513" s="4"/>
       <c r="D513" s="4"/>
       <c r="E513" s="4"/>
-      <c r="F513" s="4"/>
+      <c r="F513" s="15"/>
       <c r="G513" s="4"/>
       <c r="H513" s="4"/>
       <c r="I513" s="4"/>
@@ -16633,7 +16721,7 @@
       <c r="C514" s="4"/>
       <c r="D514" s="4"/>
       <c r="E514" s="4"/>
-      <c r="F514" s="4"/>
+      <c r="F514" s="15"/>
       <c r="G514" s="4"/>
       <c r="H514" s="4"/>
       <c r="I514" s="4"/>
@@ -16664,7 +16752,7 @@
       <c r="C515" s="4"/>
       <c r="D515" s="4"/>
       <c r="E515" s="4"/>
-      <c r="F515" s="4"/>
+      <c r="F515" s="15"/>
       <c r="G515" s="4"/>
       <c r="H515" s="4"/>
       <c r="I515" s="4"/>
@@ -16695,7 +16783,7 @@
       <c r="C516" s="4"/>
       <c r="D516" s="4"/>
       <c r="E516" s="4"/>
-      <c r="F516" s="4"/>
+      <c r="F516" s="15"/>
       <c r="G516" s="4"/>
       <c r="H516" s="4"/>
       <c r="I516" s="4"/>
@@ -16726,7 +16814,7 @@
       <c r="C517" s="4"/>
       <c r="D517" s="4"/>
       <c r="E517" s="4"/>
-      <c r="F517" s="4"/>
+      <c r="F517" s="15"/>
       <c r="G517" s="4"/>
       <c r="H517" s="4"/>
       <c r="I517" s="4"/>
@@ -16757,7 +16845,7 @@
       <c r="C518" s="4"/>
       <c r="D518" s="4"/>
       <c r="E518" s="4"/>
-      <c r="F518" s="4"/>
+      <c r="F518" s="15"/>
       <c r="G518" s="4"/>
       <c r="H518" s="4"/>
       <c r="I518" s="4"/>
@@ -16788,7 +16876,7 @@
       <c r="C519" s="4"/>
       <c r="D519" s="4"/>
       <c r="E519" s="4"/>
-      <c r="F519" s="4"/>
+      <c r="F519" s="15"/>
       <c r="G519" s="4"/>
       <c r="H519" s="4"/>
       <c r="I519" s="4"/>
@@ -16819,7 +16907,7 @@
       <c r="C520" s="4"/>
       <c r="D520" s="4"/>
       <c r="E520" s="4"/>
-      <c r="F520" s="4"/>
+      <c r="F520" s="15"/>
       <c r="G520" s="4"/>
       <c r="H520" s="4"/>
       <c r="I520" s="4"/>
@@ -16850,7 +16938,7 @@
       <c r="C521" s="4"/>
       <c r="D521" s="4"/>
       <c r="E521" s="4"/>
-      <c r="F521" s="4"/>
+      <c r="F521" s="15"/>
       <c r="G521" s="4"/>
       <c r="H521" s="4"/>
       <c r="I521" s="4"/>
@@ -16881,7 +16969,7 @@
       <c r="C522" s="4"/>
       <c r="D522" s="4"/>
       <c r="E522" s="4"/>
-      <c r="F522" s="4"/>
+      <c r="F522" s="15"/>
       <c r="G522" s="4"/>
       <c r="H522" s="4"/>
       <c r="I522" s="4"/>
@@ -16912,7 +17000,7 @@
       <c r="C523" s="4"/>
       <c r="D523" s="4"/>
       <c r="E523" s="4"/>
-      <c r="F523" s="4"/>
+      <c r="F523" s="15"/>
       <c r="G523" s="4"/>
       <c r="H523" s="4"/>
       <c r="I523" s="4"/>
@@ -16943,7 +17031,7 @@
       <c r="C524" s="4"/>
       <c r="D524" s="4"/>
       <c r="E524" s="4"/>
-      <c r="F524" s="4"/>
+      <c r="F524" s="15"/>
       <c r="G524" s="4"/>
       <c r="H524" s="4"/>
       <c r="I524" s="4"/>
@@ -16974,7 +17062,7 @@
       <c r="C525" s="4"/>
       <c r="D525" s="4"/>
       <c r="E525" s="4"/>
-      <c r="F525" s="4"/>
+      <c r="F525" s="15"/>
       <c r="G525" s="4"/>
       <c r="H525" s="4"/>
       <c r="I525" s="4"/>
@@ -17005,7 +17093,7 @@
       <c r="C526" s="4"/>
       <c r="D526" s="4"/>
       <c r="E526" s="4"/>
-      <c r="F526" s="4"/>
+      <c r="F526" s="15"/>
       <c r="G526" s="4"/>
       <c r="H526" s="4"/>
       <c r="I526" s="4"/>
@@ -17036,7 +17124,7 @@
       <c r="C527" s="4"/>
       <c r="D527" s="4"/>
       <c r="E527" s="4"/>
-      <c r="F527" s="4"/>
+      <c r="F527" s="15"/>
       <c r="G527" s="4"/>
       <c r="H527" s="4"/>
       <c r="I527" s="4"/>
@@ -17067,7 +17155,7 @@
       <c r="C528" s="4"/>
       <c r="D528" s="4"/>
       <c r="E528" s="4"/>
-      <c r="F528" s="4"/>
+      <c r="F528" s="15"/>
       <c r="G528" s="4"/>
       <c r="H528" s="4"/>
       <c r="I528" s="4"/>
@@ -17098,7 +17186,7 @@
       <c r="C529" s="4"/>
       <c r="D529" s="4"/>
       <c r="E529" s="4"/>
-      <c r="F529" s="4"/>
+      <c r="F529" s="15"/>
       <c r="G529" s="4"/>
       <c r="H529" s="4"/>
       <c r="I529" s="4"/>
@@ -17129,7 +17217,7 @@
       <c r="C530" s="4"/>
       <c r="D530" s="4"/>
       <c r="E530" s="4"/>
-      <c r="F530" s="4"/>
+      <c r="F530" s="15"/>
       <c r="G530" s="4"/>
       <c r="H530" s="4"/>
       <c r="I530" s="4"/>
@@ -17160,7 +17248,7 @@
       <c r="C531" s="4"/>
       <c r="D531" s="4"/>
       <c r="E531" s="4"/>
-      <c r="F531" s="4"/>
+      <c r="F531" s="15"/>
       <c r="G531" s="4"/>
       <c r="H531" s="4"/>
       <c r="I531" s="4"/>
@@ -17191,7 +17279,7 @@
       <c r="C532" s="4"/>
       <c r="D532" s="4"/>
       <c r="E532" s="4"/>
-      <c r="F532" s="4"/>
+      <c r="F532" s="15"/>
       <c r="G532" s="4"/>
       <c r="H532" s="4"/>
       <c r="I532" s="4"/>
@@ -17222,7 +17310,7 @@
       <c r="C533" s="4"/>
       <c r="D533" s="4"/>
       <c r="E533" s="4"/>
-      <c r="F533" s="4"/>
+      <c r="F533" s="15"/>
       <c r="G533" s="4"/>
       <c r="H533" s="4"/>
       <c r="I533" s="4"/>
@@ -17253,7 +17341,7 @@
       <c r="C534" s="4"/>
       <c r="D534" s="4"/>
       <c r="E534" s="4"/>
-      <c r="F534" s="4"/>
+      <c r="F534" s="15"/>
       <c r="G534" s="4"/>
       <c r="H534" s="4"/>
       <c r="I534" s="4"/>
@@ -17284,7 +17372,7 @@
       <c r="C535" s="4"/>
       <c r="D535" s="4"/>
       <c r="E535" s="4"/>
-      <c r="F535" s="4"/>
+      <c r="F535" s="15"/>
       <c r="G535" s="4"/>
       <c r="H535" s="4"/>
       <c r="I535" s="4"/>
@@ -17315,7 +17403,7 @@
       <c r="C536" s="4"/>
       <c r="D536" s="4"/>
       <c r="E536" s="4"/>
-      <c r="F536" s="4"/>
+      <c r="F536" s="15"/>
       <c r="G536" s="4"/>
       <c r="H536" s="4"/>
       <c r="I536" s="4"/>
@@ -17346,7 +17434,7 @@
       <c r="C537" s="4"/>
       <c r="D537" s="4"/>
       <c r="E537" s="4"/>
-      <c r="F537" s="4"/>
+      <c r="F537" s="15"/>
       <c r="G537" s="4"/>
       <c r="H537" s="4"/>
       <c r="I537" s="4"/>
@@ -17377,7 +17465,7 @@
       <c r="C538" s="4"/>
       <c r="D538" s="4"/>
       <c r="E538" s="4"/>
-      <c r="F538" s="4"/>
+      <c r="F538" s="15"/>
       <c r="G538" s="4"/>
       <c r="H538" s="4"/>
       <c r="I538" s="4"/>
@@ -17408,7 +17496,7 @@
       <c r="C539" s="4"/>
       <c r="D539" s="4"/>
       <c r="E539" s="4"/>
-      <c r="F539" s="4"/>
+      <c r="F539" s="15"/>
       <c r="G539" s="4"/>
       <c r="H539" s="4"/>
       <c r="I539" s="4"/>
@@ -17439,7 +17527,7 @@
       <c r="C540" s="4"/>
       <c r="D540" s="4"/>
       <c r="E540" s="4"/>
-      <c r="F540" s="4"/>
+      <c r="F540" s="15"/>
       <c r="G540" s="4"/>
       <c r="H540" s="4"/>
       <c r="I540" s="4"/>
@@ -17470,7 +17558,7 @@
       <c r="C541" s="4"/>
       <c r="D541" s="4"/>
       <c r="E541" s="4"/>
-      <c r="F541" s="4"/>
+      <c r="F541" s="15"/>
       <c r="G541" s="4"/>
       <c r="H541" s="4"/>
       <c r="I541" s="4"/>
@@ -17501,7 +17589,7 @@
       <c r="C542" s="4"/>
       <c r="D542" s="4"/>
       <c r="E542" s="4"/>
-      <c r="F542" s="4"/>
+      <c r="F542" s="15"/>
       <c r="G542" s="4"/>
       <c r="H542" s="4"/>
       <c r="I542" s="4"/>
@@ -17532,7 +17620,7 @@
       <c r="C543" s="4"/>
       <c r="D543" s="4"/>
       <c r="E543" s="4"/>
-      <c r="F543" s="4"/>
+      <c r="F543" s="15"/>
       <c r="G543" s="4"/>
       <c r="H543" s="4"/>
       <c r="I543" s="4"/>
@@ -17563,7 +17651,7 @@
       <c r="C544" s="4"/>
       <c r="D544" s="4"/>
       <c r="E544" s="4"/>
-      <c r="F544" s="4"/>
+      <c r="F544" s="15"/>
       <c r="G544" s="4"/>
       <c r="H544" s="4"/>
       <c r="I544" s="4"/>
@@ -17594,7 +17682,7 @@
       <c r="C545" s="4"/>
       <c r="D545" s="4"/>
       <c r="E545" s="4"/>
-      <c r="F545" s="4"/>
+      <c r="F545" s="15"/>
       <c r="G545" s="4"/>
       <c r="H545" s="4"/>
       <c r="I545" s="4"/>
@@ -17625,7 +17713,7 @@
       <c r="C546" s="4"/>
       <c r="D546" s="4"/>
       <c r="E546" s="4"/>
-      <c r="F546" s="4"/>
+      <c r="F546" s="15"/>
       <c r="G546" s="4"/>
       <c r="H546" s="4"/>
       <c r="I546" s="4"/>
@@ -17656,7 +17744,7 @@
       <c r="C547" s="4"/>
       <c r="D547" s="4"/>
       <c r="E547" s="4"/>
-      <c r="F547" s="4"/>
+      <c r="F547" s="15"/>
       <c r="G547" s="4"/>
       <c r="H547" s="4"/>
       <c r="I547" s="4"/>
@@ -17687,7 +17775,7 @@
       <c r="C548" s="4"/>
       <c r="D548" s="4"/>
       <c r="E548" s="4"/>
-      <c r="F548" s="4"/>
+      <c r="F548" s="15"/>
       <c r="G548" s="4"/>
       <c r="H548" s="4"/>
       <c r="I548" s="4"/>
@@ -17718,7 +17806,7 @@
       <c r="C549" s="4"/>
       <c r="D549" s="4"/>
       <c r="E549" s="4"/>
-      <c r="F549" s="4"/>
+      <c r="F549" s="15"/>
       <c r="G549" s="4"/>
       <c r="H549" s="4"/>
       <c r="I549" s="4"/>
@@ -17749,7 +17837,7 @@
       <c r="C550" s="4"/>
       <c r="D550" s="4"/>
       <c r="E550" s="4"/>
-      <c r="F550" s="4"/>
+      <c r="F550" s="15"/>
       <c r="G550" s="4"/>
       <c r="H550" s="4"/>
       <c r="I550" s="4"/>
@@ -17780,7 +17868,7 @@
       <c r="C551" s="4"/>
       <c r="D551" s="4"/>
       <c r="E551" s="4"/>
-      <c r="F551" s="4"/>
+      <c r="F551" s="15"/>
       <c r="G551" s="4"/>
       <c r="H551" s="4"/>
       <c r="I551" s="4"/>
@@ -17811,7 +17899,7 @@
       <c r="C552" s="4"/>
       <c r="D552" s="4"/>
       <c r="E552" s="4"/>
-      <c r="F552" s="4"/>
+      <c r="F552" s="15"/>
       <c r="G552" s="4"/>
       <c r="H552" s="4"/>
       <c r="I552" s="4"/>
@@ -17842,7 +17930,7 @@
       <c r="C553" s="4"/>
       <c r="D553" s="4"/>
       <c r="E553" s="4"/>
-      <c r="F553" s="4"/>
+      <c r="F553" s="15"/>
       <c r="G553" s="4"/>
       <c r="H553" s="4"/>
       <c r="I553" s="4"/>
@@ -17873,7 +17961,7 @@
       <c r="C554" s="4"/>
       <c r="D554" s="4"/>
       <c r="E554" s="4"/>
-      <c r="F554" s="4"/>
+      <c r="F554" s="15"/>
       <c r="G554" s="4"/>
       <c r="H554" s="4"/>
       <c r="I554" s="4"/>
@@ -17904,7 +17992,7 @@
       <c r="C555" s="4"/>
       <c r="D555" s="4"/>
       <c r="E555" s="4"/>
-      <c r="F555" s="4"/>
+      <c r="F555" s="15"/>
       <c r="G555" s="4"/>
       <c r="H555" s="4"/>
       <c r="I555" s="4"/>
@@ -17935,7 +18023,7 @@
       <c r="C556" s="4"/>
       <c r="D556" s="4"/>
       <c r="E556" s="4"/>
-      <c r="F556" s="4"/>
+      <c r="F556" s="15"/>
       <c r="G556" s="4"/>
       <c r="H556" s="4"/>
       <c r="I556" s="4"/>
@@ -17966,7 +18054,7 @@
       <c r="C557" s="4"/>
       <c r="D557" s="4"/>
       <c r="E557" s="4"/>
-      <c r="F557" s="4"/>
+      <c r="F557" s="15"/>
       <c r="G557" s="4"/>
       <c r="H557" s="4"/>
       <c r="I557" s="4"/>
@@ -17997,7 +18085,7 @@
       <c r="C558" s="4"/>
       <c r="D558" s="4"/>
       <c r="E558" s="4"/>
-      <c r="F558" s="4"/>
+      <c r="F558" s="15"/>
       <c r="G558" s="4"/>
       <c r="H558" s="4"/>
       <c r="I558" s="4"/>
@@ -18028,7 +18116,7 @@
       <c r="C559" s="4"/>
       <c r="D559" s="4"/>
       <c r="E559" s="4"/>
-      <c r="F559" s="4"/>
+      <c r="F559" s="15"/>
       <c r="G559" s="4"/>
       <c r="H559" s="4"/>
       <c r="I559" s="4"/>
@@ -18059,7 +18147,7 @@
       <c r="C560" s="4"/>
       <c r="D560" s="4"/>
       <c r="E560" s="4"/>
-      <c r="F560" s="4"/>
+      <c r="F560" s="15"/>
       <c r="G560" s="4"/>
       <c r="H560" s="4"/>
       <c r="I560" s="4"/>
@@ -18090,7 +18178,7 @@
       <c r="C561" s="4"/>
       <c r="D561" s="4"/>
       <c r="E561" s="4"/>
-      <c r="F561" s="4"/>
+      <c r="F561" s="15"/>
       <c r="G561" s="4"/>
       <c r="H561" s="4"/>
       <c r="I561" s="4"/>
@@ -18121,7 +18209,7 @@
       <c r="C562" s="4"/>
       <c r="D562" s="4"/>
       <c r="E562" s="4"/>
-      <c r="F562" s="4"/>
+      <c r="F562" s="15"/>
       <c r="G562" s="4"/>
       <c r="H562" s="4"/>
       <c r="I562" s="4"/>
@@ -18152,7 +18240,7 @@
       <c r="C563" s="4"/>
       <c r="D563" s="4"/>
       <c r="E563" s="4"/>
-      <c r="F563" s="4"/>
+      <c r="F563" s="15"/>
       <c r="G563" s="4"/>
       <c r="H563" s="4"/>
       <c r="I563" s="4"/>
@@ -18183,7 +18271,7 @@
       <c r="C564" s="4"/>
       <c r="D564" s="4"/>
       <c r="E564" s="4"/>
-      <c r="F564" s="4"/>
+      <c r="F564" s="15"/>
       <c r="G564" s="4"/>
       <c r="H564" s="4"/>
       <c r="I564" s="4"/>
@@ -18214,7 +18302,7 @@
       <c r="C565" s="4"/>
       <c r="D565" s="4"/>
       <c r="E565" s="4"/>
-      <c r="F565" s="4"/>
+      <c r="F565" s="15"/>
       <c r="G565" s="4"/>
       <c r="H565" s="4"/>
       <c r="I565" s="4"/>
@@ -18245,7 +18333,7 @@
       <c r="C566" s="4"/>
       <c r="D566" s="4"/>
       <c r="E566" s="4"/>
-      <c r="F566" s="4"/>
+      <c r="F566" s="15"/>
       <c r="G566" s="4"/>
       <c r="H566" s="4"/>
       <c r="I566" s="4"/>
@@ -18276,7 +18364,7 @@
       <c r="C567" s="4"/>
       <c r="D567" s="4"/>
       <c r="E567" s="4"/>
-      <c r="F567" s="4"/>
+      <c r="F567" s="15"/>
       <c r="G567" s="4"/>
       <c r="H567" s="4"/>
       <c r="I567" s="4"/>
@@ -18307,7 +18395,7 @@
       <c r="C568" s="4"/>
       <c r="D568" s="4"/>
       <c r="E568" s="4"/>
-      <c r="F568" s="4"/>
+      <c r="F568" s="15"/>
       <c r="G568" s="4"/>
       <c r="H568" s="4"/>
       <c r="I568" s="4"/>
@@ -18338,7 +18426,7 @@
       <c r="C569" s="4"/>
       <c r="D569" s="4"/>
       <c r="E569" s="4"/>
-      <c r="F569" s="4"/>
+      <c r="F569" s="15"/>
       <c r="G569" s="4"/>
       <c r="H569" s="4"/>
       <c r="I569" s="4"/>
@@ -18369,7 +18457,7 @@
       <c r="C570" s="4"/>
       <c r="D570" s="4"/>
       <c r="E570" s="4"/>
-      <c r="F570" s="4"/>
+      <c r="F570" s="15"/>
       <c r="G570" s="4"/>
       <c r="H570" s="4"/>
       <c r="I570" s="4"/>
@@ -18400,7 +18488,7 @@
       <c r="C571" s="4"/>
       <c r="D571" s="4"/>
       <c r="E571" s="4"/>
-      <c r="F571" s="4"/>
+      <c r="F571" s="15"/>
       <c r="G571" s="4"/>
       <c r="H571" s="4"/>
       <c r="I571" s="4"/>
@@ -18431,7 +18519,7 @@
       <c r="C572" s="4"/>
       <c r="D572" s="4"/>
       <c r="E572" s="4"/>
-      <c r="F572" s="4"/>
+      <c r="F572" s="15"/>
       <c r="G572" s="4"/>
       <c r="H572" s="4"/>
       <c r="I572" s="4"/>
@@ -18462,7 +18550,7 @@
       <c r="C573" s="4"/>
       <c r="D573" s="4"/>
       <c r="E573" s="4"/>
-      <c r="F573" s="4"/>
+      <c r="F573" s="15"/>
       <c r="G573" s="4"/>
       <c r="H573" s="4"/>
       <c r="I573" s="4"/>
@@ -18493,7 +18581,7 @@
       <c r="C574" s="4"/>
       <c r="D574" s="4"/>
       <c r="E574" s="4"/>
-      <c r="F574" s="4"/>
+      <c r="F574" s="15"/>
       <c r="G574" s="4"/>
       <c r="H574" s="4"/>
       <c r="I574" s="4"/>
@@ -18524,7 +18612,7 @@
       <c r="C575" s="4"/>
       <c r="D575" s="4"/>
       <c r="E575" s="4"/>
-      <c r="F575" s="4"/>
+      <c r="F575" s="15"/>
       <c r="G575" s="4"/>
       <c r="H575" s="4"/>
       <c r="I575" s="4"/>
@@ -18555,7 +18643,7 @@
       <c r="C576" s="4"/>
       <c r="D576" s="4"/>
       <c r="E576" s="4"/>
-      <c r="F576" s="4"/>
+      <c r="F576" s="15"/>
       <c r="G576" s="4"/>
       <c r="H576" s="4"/>
       <c r="I576" s="4"/>
@@ -18586,7 +18674,7 @@
       <c r="C577" s="4"/>
       <c r="D577" s="4"/>
       <c r="E577" s="4"/>
-      <c r="F577" s="4"/>
+      <c r="F577" s="15"/>
       <c r="G577" s="4"/>
       <c r="H577" s="4"/>
       <c r="I577" s="4"/>
@@ -18617,7 +18705,7 @@
       <c r="C578" s="4"/>
       <c r="D578" s="4"/>
       <c r="E578" s="4"/>
-      <c r="F578" s="4"/>
+      <c r="F578" s="15"/>
       <c r="G578" s="4"/>
       <c r="H578" s="4"/>
       <c r="I578" s="4"/>
@@ -18648,7 +18736,7 @@
       <c r="C579" s="4"/>
       <c r="D579" s="4"/>
       <c r="E579" s="4"/>
-      <c r="F579" s="4"/>
+      <c r="F579" s="15"/>
       <c r="G579" s="4"/>
       <c r="H579" s="4"/>
       <c r="I579" s="4"/>
@@ -18679,7 +18767,7 @@
       <c r="C580" s="4"/>
       <c r="D580" s="4"/>
       <c r="E580" s="4"/>
-      <c r="F580" s="4"/>
+      <c r="F580" s="15"/>
       <c r="G580" s="4"/>
       <c r="H580" s="4"/>
       <c r="I580" s="4"/>
@@ -18710,7 +18798,7 @@
       <c r="C581" s="4"/>
       <c r="D581" s="4"/>
       <c r="E581" s="4"/>
-      <c r="F581" s="4"/>
+      <c r="F581" s="15"/>
       <c r="G581" s="4"/>
       <c r="H581" s="4"/>
       <c r="I581" s="4"/>
@@ -18741,7 +18829,7 @@
       <c r="C582" s="4"/>
       <c r="D582" s="4"/>
       <c r="E582" s="4"/>
-      <c r="F582" s="4"/>
+      <c r="F582" s="15"/>
       <c r="G582" s="4"/>
       <c r="H582" s="4"/>
       <c r="I582" s="4"/>
@@ -18772,7 +18860,7 @@
       <c r="C583" s="4"/>
       <c r="D583" s="4"/>
       <c r="E583" s="4"/>
-      <c r="F583" s="4"/>
+      <c r="F583" s="15"/>
       <c r="G583" s="4"/>
       <c r="H583" s="4"/>
       <c r="I583" s="4"/>
@@ -18803,7 +18891,7 @@
       <c r="C584" s="4"/>
       <c r="D584" s="4"/>
       <c r="E584" s="4"/>
-      <c r="F584" s="4"/>
+      <c r="F584" s="15"/>
       <c r="G584" s="4"/>
       <c r="H584" s="4"/>
       <c r="I584" s="4"/>
@@ -18834,7 +18922,7 @@
       <c r="C585" s="4"/>
       <c r="D585" s="4"/>
       <c r="E585" s="4"/>
-      <c r="F585" s="4"/>
+      <c r="F585" s="15"/>
       <c r="G585" s="4"/>
       <c r="H585" s="4"/>
       <c r="I585" s="4"/>
@@ -18865,7 +18953,7 @@
       <c r="C586" s="4"/>
       <c r="D586" s="4"/>
       <c r="E586" s="4"/>
-      <c r="F586" s="4"/>
+      <c r="F586" s="15"/>
       <c r="G586" s="4"/>
       <c r="H586" s="4"/>
       <c r="I586" s="4"/>
@@ -18896,7 +18984,7 @@
       <c r="C587" s="4"/>
       <c r="D587" s="4"/>
       <c r="E587" s="4"/>
-      <c r="F587" s="4"/>
+      <c r="F587" s="15"/>
       <c r="G587" s="4"/>
       <c r="H587" s="4"/>
       <c r="I587" s="4"/>
@@ -18927,7 +19015,7 @@
       <c r="C588" s="4"/>
       <c r="D588" s="4"/>
       <c r="E588" s="4"/>
-      <c r="F588" s="4"/>
+      <c r="F588" s="15"/>
       <c r="G588" s="4"/>
       <c r="H588" s="4"/>
       <c r="I588" s="4"/>
@@ -18958,7 +19046,7 @@
       <c r="C589" s="4"/>
       <c r="D589" s="4"/>
       <c r="E589" s="4"/>
-      <c r="F589" s="4"/>
+      <c r="F589" s="15"/>
       <c r="G589" s="4"/>
       <c r="H589" s="4"/>
       <c r="I589" s="4"/>
@@ -18989,7 +19077,7 @@
       <c r="C590" s="4"/>
       <c r="D590" s="4"/>
       <c r="E590" s="4"/>
-      <c r="F590" s="4"/>
+      <c r="F590" s="15"/>
       <c r="G590" s="4"/>
       <c r="H590" s="4"/>
       <c r="I590" s="4"/>
@@ -19020,7 +19108,7 @@
       <c r="C591" s="4"/>
       <c r="D591" s="4"/>
       <c r="E591" s="4"/>
-      <c r="F591" s="4"/>
+      <c r="F591" s="15"/>
       <c r="G591" s="4"/>
       <c r="H591" s="4"/>
       <c r="I591" s="4"/>
@@ -19051,7 +19139,7 @@
       <c r="C592" s="4"/>
       <c r="D592" s="4"/>
       <c r="E592" s="4"/>
-      <c r="F592" s="4"/>
+      <c r="F592" s="15"/>
       <c r="G592" s="4"/>
       <c r="H592" s="4"/>
       <c r="I592" s="4"/>
@@ -19082,7 +19170,7 @@
       <c r="C593" s="4"/>
       <c r="D593" s="4"/>
       <c r="E593" s="4"/>
-      <c r="F593" s="4"/>
+      <c r="F593" s="15"/>
       <c r="G593" s="4"/>
       <c r="H593" s="4"/>
       <c r="I593" s="4"/>
@@ -19113,7 +19201,7 @@
       <c r="C594" s="4"/>
       <c r="D594" s="4"/>
       <c r="E594" s="4"/>
-      <c r="F594" s="4"/>
+      <c r="F594" s="15"/>
       <c r="G594" s="4"/>
       <c r="H594" s="4"/>
       <c r="I594" s="4"/>
@@ -19144,7 +19232,7 @@
       <c r="C595" s="4"/>
       <c r="D595" s="4"/>
       <c r="E595" s="4"/>
-      <c r="F595" s="4"/>
+      <c r="F595" s="15"/>
       <c r="G595" s="4"/>
       <c r="H595" s="4"/>
       <c r="I595" s="4"/>
@@ -19175,7 +19263,7 @@
       <c r="C596" s="4"/>
       <c r="D596" s="4"/>
       <c r="E596" s="4"/>
-      <c r="F596" s="4"/>
+      <c r="F596" s="15"/>
       <c r="G596" s="4"/>
       <c r="H596" s="4"/>
       <c r="I596" s="4"/>
@@ -19206,7 +19294,7 @@
       <c r="C597" s="4"/>
       <c r="D597" s="4"/>
       <c r="E597" s="4"/>
-      <c r="F597" s="4"/>
+      <c r="F597" s="15"/>
       <c r="G597" s="4"/>
       <c r="H597" s="4"/>
       <c r="I597" s="4"/>
@@ -19237,7 +19325,7 @@
       <c r="C598" s="4"/>
       <c r="D598" s="4"/>
       <c r="E598" s="4"/>
-      <c r="F598" s="4"/>
+      <c r="F598" s="15"/>
       <c r="G598" s="4"/>
       <c r="H598" s="4"/>
       <c r="I598" s="4"/>
@@ -19268,7 +19356,7 @@
       <c r="C599" s="4"/>
       <c r="D599" s="4"/>
       <c r="E599" s="4"/>
-      <c r="F599" s="4"/>
+      <c r="F599" s="15"/>
       <c r="G599" s="4"/>
       <c r="H599" s="4"/>
       <c r="I599" s="4"/>
@@ -19299,7 +19387,7 @@
       <c r="C600" s="4"/>
       <c r="D600" s="4"/>
       <c r="E600" s="4"/>
-      <c r="F600" s="4"/>
+      <c r="F600" s="15"/>
       <c r="G600" s="4"/>
       <c r="H600" s="4"/>
       <c r="I600" s="4"/>
@@ -19330,7 +19418,7 @@
       <c r="C601" s="4"/>
       <c r="D601" s="4"/>
       <c r="E601" s="4"/>
-      <c r="F601" s="4"/>
+      <c r="F601" s="15"/>
       <c r="G601" s="4"/>
       <c r="H601" s="4"/>
       <c r="I601" s="4"/>
@@ -19361,7 +19449,7 @@
       <c r="C602" s="4"/>
       <c r="D602" s="4"/>
       <c r="E602" s="4"/>
-      <c r="F602" s="4"/>
+      <c r="F602" s="15"/>
       <c r="G602" s="4"/>
       <c r="H602" s="4"/>
       <c r="I602" s="4"/>
@@ -19392,7 +19480,7 @@
       <c r="C603" s="4"/>
       <c r="D603" s="4"/>
       <c r="E603" s="4"/>
-      <c r="F603" s="4"/>
+      <c r="F603" s="15"/>
       <c r="G603" s="4"/>
       <c r="H603" s="4"/>
       <c r="I603" s="4"/>
@@ -19423,7 +19511,7 @@
       <c r="C604" s="4"/>
       <c r="D604" s="4"/>
       <c r="E604" s="4"/>
-      <c r="F604" s="4"/>
+      <c r="F604" s="15"/>
       <c r="G604" s="4"/>
       <c r="H604" s="4"/>
       <c r="I604" s="4"/>
@@ -19454,7 +19542,7 @@
       <c r="C605" s="4"/>
       <c r="D605" s="4"/>
       <c r="E605" s="4"/>
-      <c r="F605" s="4"/>
+      <c r="F605" s="15"/>
       <c r="G605" s="4"/>
       <c r="H605" s="4"/>
       <c r="I605" s="4"/>
@@ -19485,7 +19573,7 @@
       <c r="C606" s="4"/>
       <c r="D606" s="4"/>
       <c r="E606" s="4"/>
-      <c r="F606" s="4"/>
+      <c r="F606" s="15"/>
       <c r="G606" s="4"/>
       <c r="H606" s="4"/>
       <c r="I606" s="4"/>
@@ -19516,7 +19604,7 @@
       <c r="C607" s="4"/>
       <c r="D607" s="4"/>
       <c r="E607" s="4"/>
-      <c r="F607" s="4"/>
+      <c r="F607" s="15"/>
       <c r="G607" s="4"/>
       <c r="H607" s="4"/>
       <c r="I607" s="4"/>
@@ -19547,7 +19635,7 @@
       <c r="C608" s="4"/>
       <c r="D608" s="4"/>
       <c r="E608" s="4"/>
-      <c r="F608" s="4"/>
+      <c r="F608" s="15"/>
       <c r="G608" s="4"/>
       <c r="H608" s="4"/>
       <c r="I608" s="4"/>
@@ -19578,7 +19666,7 @@
       <c r="C609" s="4"/>
       <c r="D609" s="4"/>
       <c r="E609" s="4"/>
-      <c r="F609" s="4"/>
+      <c r="F609" s="15"/>
       <c r="G609" s="4"/>
       <c r="H609" s="4"/>
       <c r="I609" s="4"/>
@@ -19609,7 +19697,7 @@
       <c r="C610" s="4"/>
       <c r="D610" s="4"/>
       <c r="E610" s="4"/>
-      <c r="F610" s="4"/>
+      <c r="F610" s="15"/>
       <c r="G610" s="4"/>
       <c r="H610" s="4"/>
       <c r="I610" s="4"/>
@@ -19640,7 +19728,7 @@
       <c r="C611" s="4"/>
       <c r="D611" s="4"/>
       <c r="E611" s="4"/>
-      <c r="F611" s="4"/>
+      <c r="F611" s="15"/>
       <c r="G611" s="4"/>
       <c r="H611" s="4"/>
       <c r="I611" s="4"/>
@@ -19671,7 +19759,7 @@
       <c r="C612" s="4"/>
       <c r="D612" s="4"/>
       <c r="E612" s="4"/>
-      <c r="F612" s="4"/>
+      <c r="F612" s="15"/>
       <c r="G612" s="4"/>
       <c r="H612" s="4"/>
       <c r="I612" s="4"/>
@@ -19702,7 +19790,7 @@
       <c r="C613" s="4"/>
       <c r="D613" s="4"/>
       <c r="E613" s="4"/>
-      <c r="F613" s="4"/>
+      <c r="F613" s="15"/>
       <c r="G613" s="4"/>
       <c r="H613" s="4"/>
       <c r="I613" s="4"/>
@@ -19733,7 +19821,7 @@
       <c r="C614" s="4"/>
       <c r="D614" s="4"/>
       <c r="E614" s="4"/>
-      <c r="F614" s="4"/>
+      <c r="F614" s="15"/>
       <c r="G614" s="4"/>
       <c r="H614" s="4"/>
       <c r="I614" s="4"/>
@@ -19764,7 +19852,7 @@
       <c r="C615" s="4"/>
       <c r="D615" s="4"/>
       <c r="E615" s="4"/>
-      <c r="F615" s="4"/>
+      <c r="F615" s="15"/>
       <c r="G615" s="4"/>
       <c r="H615" s="4"/>
       <c r="I615" s="4"/>
@@ -19795,7 +19883,7 @@
       <c r="C616" s="4"/>
       <c r="D616" s="4"/>
       <c r="E616" s="4"/>
-      <c r="F616" s="4"/>
+      <c r="F616" s="15"/>
       <c r="G616" s="4"/>
       <c r="H616" s="4"/>
       <c r="I616" s="4"/>
@@ -19826,7 +19914,7 @@
       <c r="C617" s="4"/>
       <c r="D617" s="4"/>
       <c r="E617" s="4"/>
-      <c r="F617" s="4"/>
+      <c r="F617" s="15"/>
       <c r="G617" s="4"/>
       <c r="H617" s="4"/>
       <c r="I617" s="4"/>
@@ -19857,7 +19945,7 @@
       <c r="C618" s="4"/>
       <c r="D618" s="4"/>
       <c r="E618" s="4"/>
-      <c r="F618" s="4"/>
+      <c r="F618" s="15"/>
       <c r="G618" s="4"/>
       <c r="H618" s="4"/>
       <c r="I618" s="4"/>
@@ -19888,7 +19976,7 @@
       <c r="C619" s="4"/>
       <c r="D619" s="4"/>
       <c r="E619" s="4"/>
-      <c r="F619" s="4"/>
+      <c r="F619" s="15"/>
       <c r="G619" s="4"/>
       <c r="H619" s="4"/>
       <c r="I619" s="4"/>
@@ -19919,7 +20007,7 @@
       <c r="C620" s="4"/>
       <c r="D620" s="4"/>
       <c r="E620" s="4"/>
-      <c r="F620" s="4"/>
+      <c r="F620" s="15"/>
       <c r="G620" s="4"/>
       <c r="H620" s="4"/>
       <c r="I620" s="4"/>
@@ -19950,7 +20038,7 @@
       <c r="C621" s="4"/>
       <c r="D621" s="4"/>
       <c r="E621" s="4"/>
-      <c r="F621" s="4"/>
+      <c r="F621" s="15"/>
       <c r="G621" s="4"/>
       <c r="H621" s="4"/>
       <c r="I621" s="4"/>
@@ -19981,7 +20069,7 @@
       <c r="C622" s="4"/>
       <c r="D622" s="4"/>
       <c r="E622" s="4"/>
-      <c r="F622" s="4"/>
+      <c r="F622" s="15"/>
       <c r="G622" s="4"/>
       <c r="H622" s="4"/>
       <c r="I622" s="4"/>
@@ -20012,7 +20100,7 @@
       <c r="C623" s="4"/>
       <c r="D623" s="4"/>
       <c r="E623" s="4"/>
-      <c r="F623" s="4"/>
+      <c r="F623" s="15"/>
       <c r="G623" s="4"/>
       <c r="H623" s="4"/>
       <c r="I623" s="4"/>
@@ -20043,7 +20131,7 @@
       <c r="C624" s="4"/>
       <c r="D624" s="4"/>
       <c r="E624" s="4"/>
-      <c r="F624" s="4"/>
+      <c r="F624" s="15"/>
       <c r="G624" s="4"/>
       <c r="H624" s="4"/>
       <c r="I624" s="4"/>
@@ -20074,7 +20162,7 @@
       <c r="C625" s="4"/>
       <c r="D625" s="4"/>
       <c r="E625" s="4"/>
-      <c r="F625" s="4"/>
+      <c r="F625" s="15"/>
       <c r="G625" s="4"/>
       <c r="H625" s="4"/>
       <c r="I625" s="4"/>
@@ -20105,7 +20193,7 @@
       <c r="C626" s="4"/>
       <c r="D626" s="4"/>
       <c r="E626" s="4"/>
-      <c r="F626" s="4"/>
+      <c r="F626" s="15"/>
       <c r="G626" s="4"/>
       <c r="H626" s="4"/>
       <c r="I626" s="4"/>
@@ -20136,7 +20224,7 @@
       <c r="C627" s="4"/>
       <c r="D627" s="4"/>
       <c r="E627" s="4"/>
-      <c r="F627" s="4"/>
+      <c r="F627" s="15"/>
       <c r="G627" s="4"/>
       <c r="H627" s="4"/>
       <c r="I627" s="4"/>
@@ -20167,7 +20255,7 @@
       <c r="C628" s="4"/>
       <c r="D628" s="4"/>
       <c r="E628" s="4"/>
-      <c r="F628" s="4"/>
+      <c r="F628" s="15"/>
       <c r="G628" s="4"/>
       <c r="H628" s="4"/>
       <c r="I628" s="4"/>
@@ -20198,7 +20286,7 @@
       <c r="C629" s="4"/>
       <c r="D629" s="4"/>
       <c r="E629" s="4"/>
-      <c r="F629" s="4"/>
+      <c r="F629" s="15"/>
       <c r="G629" s="4"/>
       <c r="H629" s="4"/>
       <c r="I629" s="4"/>
@@ -20229,7 +20317,7 @@
       <c r="C630" s="4"/>
       <c r="D630" s="4"/>
       <c r="E630" s="4"/>
-      <c r="F630" s="4"/>
+      <c r="F630" s="15"/>
       <c r="G630" s="4"/>
       <c r="H630" s="4"/>
       <c r="I630" s="4"/>
@@ -20260,7 +20348,7 @@
       <c r="C631" s="4"/>
       <c r="D631" s="4"/>
       <c r="E631" s="4"/>
-      <c r="F631" s="4"/>
+      <c r="F631" s="15"/>
       <c r="G631" s="4"/>
       <c r="H631" s="4"/>
       <c r="I631" s="4"/>
@@ -20291,7 +20379,7 @@
       <c r="C632" s="4"/>
       <c r="D632" s="4"/>
       <c r="E632" s="4"/>
-      <c r="F632" s="4"/>
+      <c r="F632" s="15"/>
       <c r="G632" s="4"/>
       <c r="H632" s="4"/>
       <c r="I632" s="4"/>
@@ -20322,7 +20410,7 @@
       <c r="C633" s="4"/>
       <c r="D633" s="4"/>
       <c r="E633" s="4"/>
-      <c r="F633" s="4"/>
+      <c r="F633" s="15"/>
       <c r="G633" s="4"/>
       <c r="H633" s="4"/>
       <c r="I633" s="4"/>
@@ -20353,7 +20441,7 @@
       <c r="C634" s="4"/>
       <c r="D634" s="4"/>
       <c r="E634" s="4"/>
-      <c r="F634" s="4"/>
+      <c r="F634" s="15"/>
       <c r="G634" s="4"/>
       <c r="H634" s="4"/>
       <c r="I634" s="4"/>
@@ -20384,7 +20472,7 @@
       <c r="C635" s="4"/>
       <c r="D635" s="4"/>
       <c r="E635" s="4"/>
-      <c r="F635" s="4"/>
+      <c r="F635" s="15"/>
       <c r="G635" s="4"/>
       <c r="H635" s="4"/>
       <c r="I635" s="4"/>
@@ -20415,7 +20503,7 @@
       <c r="C636" s="4"/>
       <c r="D636" s="4"/>
       <c r="E636" s="4"/>
-      <c r="F636" s="4"/>
+      <c r="F636" s="15"/>
       <c r="G636" s="4"/>
       <c r="H636" s="4"/>
       <c r="I636" s="4"/>
@@ -20446,7 +20534,7 @@
       <c r="C637" s="4"/>
       <c r="D637" s="4"/>
       <c r="E637" s="4"/>
-      <c r="F637" s="4"/>
+      <c r="F637" s="15"/>
       <c r="G637" s="4"/>
       <c r="H637" s="4"/>
       <c r="I637" s="4"/>
@@ -20477,7 +20565,7 @@
       <c r="C638" s="4"/>
       <c r="D638" s="4"/>
       <c r="E638" s="4"/>
-      <c r="F638" s="4"/>
+      <c r="F638" s="15"/>
       <c r="G638" s="4"/>
       <c r="H638" s="4"/>
       <c r="I638" s="4"/>
@@ -20508,7 +20596,7 @@
       <c r="C639" s="4"/>
       <c r="D639" s="4"/>
       <c r="E639" s="4"/>
-      <c r="F639" s="4"/>
+      <c r="F639" s="15"/>
       <c r="G639" s="4"/>
       <c r="H639" s="4"/>
       <c r="I639" s="4"/>
@@ -20539,7 +20627,7 @@
       <c r="C640" s="4"/>
       <c r="D640" s="4"/>
       <c r="E640" s="4"/>
-      <c r="F640" s="4"/>
+      <c r="F640" s="15"/>
       <c r="G640" s="4"/>
       <c r="H640" s="4"/>
       <c r="I640" s="4"/>
@@ -20570,7 +20658,7 @@
       <c r="C641" s="4"/>
       <c r="D641" s="4"/>
       <c r="E641" s="4"/>
-      <c r="F641" s="4"/>
+      <c r="F641" s="15"/>
       <c r="G641" s="4"/>
       <c r="H641" s="4"/>
       <c r="I641" s="4"/>
@@ -20601,7 +20689,7 @@
       <c r="C642" s="4"/>
       <c r="D642" s="4"/>
       <c r="E642" s="4"/>
-      <c r="F642" s="4"/>
+      <c r="F642" s="15"/>
       <c r="G642" s="4"/>
       <c r="H642" s="4"/>
       <c r="I642" s="4"/>
@@ -20632,7 +20720,7 @@
       <c r="C643" s="4"/>
       <c r="D643" s="4"/>
       <c r="E643" s="4"/>
-      <c r="F643" s="4"/>
+      <c r="F643" s="15"/>
       <c r="G643" s="4"/>
       <c r="H643" s="4"/>
       <c r="I643" s="4"/>
@@ -20663,7 +20751,7 @@
       <c r="C644" s="4"/>
       <c r="D644" s="4"/>
       <c r="E644" s="4"/>
-      <c r="F644" s="4"/>
+      <c r="F644" s="15"/>
       <c r="G644" s="4"/>
       <c r="H644" s="4"/>
       <c r="I644" s="4"/>
@@ -20694,7 +20782,7 @@
       <c r="C645" s="4"/>
       <c r="D645" s="4"/>
       <c r="E645" s="4"/>
-      <c r="F645" s="4"/>
+      <c r="F645" s="15"/>
       <c r="G645" s="4"/>
       <c r="H645" s="4"/>
       <c r="I645" s="4"/>
@@ -20725,7 +20813,7 @@
       <c r="C646" s="4"/>
       <c r="D646" s="4"/>
       <c r="E646" s="4"/>
-      <c r="F646" s="4"/>
+      <c r="F646" s="15"/>
       <c r="G646" s="4"/>
       <c r="H646" s="4"/>
       <c r="I646" s="4"/>
@@ -20756,7 +20844,7 @@
       <c r="C647" s="4"/>
       <c r="D647" s="4"/>
       <c r="E647" s="4"/>
-      <c r="F647" s="4"/>
+      <c r="F647" s="15"/>
       <c r="G647" s="4"/>
       <c r="H647" s="4"/>
       <c r="I647" s="4"/>
@@ -20787,7 +20875,7 @@
       <c r="C648" s="4"/>
       <c r="D648" s="4"/>
       <c r="E648" s="4"/>
-      <c r="F648" s="4"/>
+      <c r="F648" s="15"/>
       <c r="G648" s="4"/>
       <c r="H648" s="4"/>
       <c r="I648" s="4"/>
@@ -20818,7 +20906,7 @@
       <c r="C649" s="4"/>
       <c r="D649" s="4"/>
       <c r="E649" s="4"/>
-      <c r="F649" s="4"/>
+      <c r="F649" s="15"/>
       <c r="G649" s="4"/>
       <c r="H649" s="4"/>
       <c r="I649" s="4"/>
@@ -20849,7 +20937,7 @@
       <c r="C650" s="4"/>
       <c r="D650" s="4"/>
       <c r="E650" s="4"/>
-      <c r="F650" s="4"/>
+      <c r="F650" s="15"/>
       <c r="G650" s="4"/>
       <c r="H650" s="4"/>
       <c r="I650" s="4"/>
@@ -20880,7 +20968,7 @@
       <c r="C651" s="4"/>
       <c r="D651" s="4"/>
       <c r="E651" s="4"/>
-      <c r="F651" s="4"/>
+      <c r="F651" s="15"/>
       <c r="G651" s="4"/>
       <c r="H651" s="4"/>
       <c r="I651" s="4"/>
@@ -20911,7 +20999,7 @@
       <c r="C652" s="4"/>
       <c r="D652" s="4"/>
       <c r="E652" s="4"/>
-      <c r="F652" s="4"/>
+      <c r="F652" s="15"/>
       <c r="G652" s="4"/>
       <c r="H652" s="4"/>
       <c r="I652" s="4"/>
@@ -20942,7 +21030,7 @@
       <c r="C653" s="4"/>
       <c r="D653" s="4"/>
       <c r="E653" s="4"/>
-      <c r="F653" s="4"/>
+      <c r="F653" s="15"/>
       <c r="G653" s="4"/>
       <c r="H653" s="4"/>
       <c r="I653" s="4"/>
@@ -20973,7 +21061,7 @@
       <c r="C654" s="4"/>
       <c r="D654" s="4"/>
       <c r="E654" s="4"/>
-      <c r="F654" s="4"/>
+      <c r="F654" s="15"/>
       <c r="G654" s="4"/>
       <c r="H654" s="4"/>
       <c r="I654" s="4"/>
@@ -21004,7 +21092,7 @@
       <c r="C655" s="4"/>
       <c r="D655" s="4"/>
       <c r="E655" s="4"/>
-      <c r="F655" s="4"/>
+      <c r="F655" s="15"/>
       <c r="G655" s="4"/>
       <c r="H655" s="4"/>
       <c r="I655" s="4"/>
@@ -21035,7 +21123,7 @@
       <c r="C656" s="4"/>
       <c r="D656" s="4"/>
       <c r="E656" s="4"/>
-      <c r="F656" s="4"/>
+      <c r="F656" s="15"/>
       <c r="G656" s="4"/>
       <c r="H656" s="4"/>
       <c r="I656" s="4"/>
@@ -21066,7 +21154,7 @@
       <c r="C657" s="4"/>
       <c r="D657" s="4"/>
       <c r="E657" s="4"/>
-      <c r="F657" s="4"/>
+      <c r="F657" s="15"/>
       <c r="G657" s="4"/>
       <c r="H657" s="4"/>
       <c r="I657" s="4"/>
@@ -21097,7 +21185,7 @@
       <c r="C658" s="4"/>
       <c r="D658" s="4"/>
       <c r="E658" s="4"/>
-      <c r="F658" s="4"/>
+      <c r="F658" s="15"/>
       <c r="G658" s="4"/>
       <c r="H658" s="4"/>
       <c r="I658" s="4"/>
@@ -21128,7 +21216,7 @@
       <c r="C659" s="4"/>
       <c r="D659" s="4"/>
       <c r="E659" s="4"/>
-      <c r="F659" s="4"/>
+      <c r="F659" s="15"/>
       <c r="G659" s="4"/>
       <c r="H659" s="4"/>
       <c r="I659" s="4"/>
@@ -21159,7 +21247,7 @@
       <c r="C660" s="4"/>
       <c r="D660" s="4"/>
       <c r="E660" s="4"/>
-      <c r="F660" s="4"/>
+      <c r="F660" s="15"/>
       <c r="G660" s="4"/>
       <c r="H660" s="4"/>
       <c r="I660" s="4"/>
@@ -21190,7 +21278,7 @@
       <c r="C661" s="4"/>
       <c r="D661" s="4"/>
       <c r="E661" s="4"/>
-      <c r="F661" s="4"/>
+      <c r="F661" s="15"/>
       <c r="G661" s="4"/>
       <c r="H661" s="4"/>
       <c r="I661" s="4"/>
@@ -21221,7 +21309,7 @@
       <c r="C662" s="4"/>
       <c r="D662" s="4"/>
       <c r="E662" s="4"/>
-      <c r="F662" s="4"/>
+      <c r="F662" s="15"/>
       <c r="G662" s="4"/>
       <c r="H662" s="4"/>
       <c r="I662" s="4"/>
@@ -21252,7 +21340,7 @@
       <c r="C663" s="4"/>
       <c r="D663" s="4"/>
       <c r="E663" s="4"/>
-      <c r="F663" s="4"/>
+      <c r="F663" s="15"/>
       <c r="G663" s="4"/>
       <c r="H663" s="4"/>
       <c r="I663" s="4"/>
@@ -21283,7 +21371,7 @@
       <c r="C664" s="4"/>
       <c r="D664" s="4"/>
       <c r="E664" s="4"/>
-      <c r="F664" s="4"/>
+      <c r="F664" s="15"/>
       <c r="G664" s="4"/>
       <c r="H664" s="4"/>
       <c r="I664" s="4"/>
@@ -21314,7 +21402,7 @@
       <c r="C665" s="4"/>
       <c r="D665" s="4"/>
       <c r="E665" s="4"/>
-      <c r="F665" s="4"/>
+      <c r="F665" s="15"/>
       <c r="G665" s="4"/>
       <c r="H665" s="4"/>
       <c r="I665" s="4"/>
@@ -21345,7 +21433,7 @@
       <c r="C666" s="4"/>
       <c r="D666" s="4"/>
       <c r="E666" s="4"/>
-      <c r="F666" s="4"/>
+      <c r="F666" s="15"/>
       <c r="G666" s="4"/>
       <c r="H666" s="4"/>
       <c r="I666" s="4"/>
@@ -21376,7 +21464,7 @@
       <c r="C667" s="4"/>
       <c r="D667" s="4"/>
       <c r="E667" s="4"/>
-      <c r="F667" s="4"/>
+      <c r="F667" s="15"/>
       <c r="G667" s="4"/>
       <c r="H667" s="4"/>
       <c r="I667" s="4"/>
@@ -21407,7 +21495,7 @@
       <c r="C668" s="4"/>
       <c r="D668" s="4"/>
       <c r="E668" s="4"/>
-      <c r="F668" s="4"/>
+      <c r="F668" s="15"/>
       <c r="G668" s="4"/>
       <c r="H668" s="4"/>
       <c r="I668" s="4"/>
@@ -21438,7 +21526,7 @@
       <c r="C669" s="4"/>
       <c r="D669" s="4"/>
       <c r="E669" s="4"/>
-      <c r="F669" s="4"/>
+      <c r="F669" s="15"/>
       <c r="G669" s="4"/>
       <c r="H669" s="4"/>
       <c r="I669" s="4"/>
@@ -21469,7 +21557,7 @@
       <c r="C670" s="4"/>
       <c r="D670" s="4"/>
       <c r="E670" s="4"/>
-      <c r="F670" s="4"/>
+      <c r="F670" s="15"/>
       <c r="G670" s="4"/>
       <c r="H670" s="4"/>
       <c r="I670" s="4"/>
@@ -21500,7 +21588,7 @@
       <c r="C671" s="4"/>
       <c r="D671" s="4"/>
       <c r="E671" s="4"/>
-      <c r="F671" s="4"/>
+      <c r="F671" s="15"/>
       <c r="G671" s="4"/>
       <c r="H671" s="4"/>
       <c r="I671" s="4"/>
@@ -21531,7 +21619,7 @@
       <c r="C672" s="4"/>
       <c r="D672" s="4"/>
       <c r="E672" s="4"/>
-      <c r="F672" s="4"/>
+      <c r="F672" s="15"/>
       <c r="G672" s="4"/>
       <c r="H672" s="4"/>
       <c r="I672" s="4"/>
@@ -21562,7 +21650,7 @@
       <c r="C673" s="4"/>
       <c r="D673" s="4"/>
       <c r="E673" s="4"/>
-      <c r="F673" s="4"/>
+      <c r="F673" s="15"/>
       <c r="G673" s="4"/>
       <c r="H673" s="4"/>
       <c r="I673" s="4"/>
@@ -21593,7 +21681,7 @@
       <c r="C674" s="4"/>
       <c r="D674" s="4"/>
       <c r="E674" s="4"/>
-      <c r="F674" s="4"/>
+      <c r="F674" s="15"/>
       <c r="G674" s="4"/>
       <c r="H674" s="4"/>
       <c r="I674" s="4"/>
@@ -21624,7 +21712,7 @@
       <c r="C675" s="4"/>
       <c r="D675" s="4"/>
       <c r="E675" s="4"/>
-      <c r="F675" s="4"/>
+      <c r="F675" s="15"/>
       <c r="G675" s="4"/>
       <c r="H675" s="4"/>
       <c r="I675" s="4"/>
@@ -21655,7 +21743,7 @@
       <c r="C676" s="4"/>
       <c r="D676" s="4"/>
       <c r="E676" s="4"/>
-      <c r="F676" s="4"/>
+      <c r="F676" s="15"/>
       <c r="G676" s="4"/>
       <c r="H676" s="4"/>
       <c r="I676" s="4"/>
@@ -21686,7 +21774,7 @@
       <c r="C677" s="4"/>
       <c r="D677" s="4"/>
       <c r="E677" s="4"/>
-      <c r="F677" s="4"/>
+      <c r="F677" s="15"/>
       <c r="G677" s="4"/>
       <c r="H677" s="4"/>
       <c r="I677" s="4"/>
@@ -21717,7 +21805,7 @@
       <c r="C678" s="4"/>
       <c r="D678" s="4"/>
       <c r="E678" s="4"/>
-      <c r="F678" s="4"/>
+      <c r="F678" s="15"/>
       <c r="G678" s="4"/>
       <c r="H678" s="4"/>
       <c r="I678" s="4"/>
@@ -21748,7 +21836,7 @@
       <c r="C679" s="4"/>
       <c r="D679" s="4"/>
       <c r="E679" s="4"/>
-      <c r="F679" s="4"/>
+      <c r="F679" s="15"/>
       <c r="G679" s="4"/>
       <c r="H679" s="4"/>
       <c r="I679" s="4"/>
@@ -21779,7 +21867,7 @@
       <c r="C680" s="4"/>
       <c r="D680" s="4"/>
       <c r="E680" s="4"/>
-      <c r="F680" s="4"/>
+      <c r="F680" s="15"/>
       <c r="G680" s="4"/>
       <c r="H680" s="4"/>
       <c r="I680" s="4"/>
@@ -21810,7 +21898,7 @@
       <c r="C681" s="4"/>
       <c r="D681" s="4"/>
       <c r="E681" s="4"/>
-      <c r="F681" s="4"/>
+      <c r="F681" s="15"/>
       <c r="G681" s="4"/>
       <c r="H681" s="4"/>
       <c r="I681" s="4"/>
@@ -21841,7 +21929,7 @@
       <c r="C682" s="4"/>
       <c r="D682" s="4"/>
       <c r="E682" s="4"/>
-      <c r="F682" s="4"/>
+      <c r="F682" s="15"/>
       <c r="G682" s="4"/>
       <c r="H682" s="4"/>
       <c r="I682" s="4"/>
@@ -21872,7 +21960,7 @@
       <c r="C683" s="4"/>
       <c r="D683" s="4"/>
       <c r="E683" s="4"/>
-      <c r="F683" s="4"/>
+      <c r="F683" s="15"/>
       <c r="G683" s="4"/>
       <c r="H683" s="4"/>
       <c r="I683" s="4"/>
@@ -21903,7 +21991,7 @@
       <c r="C684" s="4"/>
       <c r="D684" s="4"/>
       <c r="E684" s="4"/>
-      <c r="F684" s="4"/>
+      <c r="F684" s="15"/>
       <c r="G684" s="4"/>
       <c r="H684" s="4"/>
       <c r="I684" s="4"/>
@@ -21934,7 +22022,7 @@
       <c r="C685" s="4"/>
       <c r="D685" s="4"/>
       <c r="E685" s="4"/>
-      <c r="F685" s="4"/>
+      <c r="F685" s="15"/>
       <c r="G685" s="4"/>
       <c r="H685" s="4"/>
       <c r="I685" s="4"/>
@@ -21965,7 +22053,7 @@
       <c r="C686" s="4"/>
       <c r="D686" s="4"/>
       <c r="E686" s="4"/>
-      <c r="F686" s="4"/>
+      <c r="F686" s="15"/>
       <c r="G686" s="4"/>
       <c r="H686" s="4"/>
       <c r="I686" s="4"/>
@@ -21996,7 +22084,7 @@
       <c r="C687" s="4"/>
       <c r="D687" s="4"/>
       <c r="E687" s="4"/>
-      <c r="F687" s="4"/>
+      <c r="F687" s="15"/>
       <c r="G687" s="4"/>
       <c r="H687" s="4"/>
       <c r="I687" s="4"/>
@@ -22027,7 +22115,7 @@
       <c r="C688" s="4"/>
       <c r="D688" s="4"/>
       <c r="E688" s="4"/>
-      <c r="F688" s="4"/>
+      <c r="F688" s="15"/>
       <c r="G688" s="4"/>
       <c r="H688" s="4"/>
       <c r="I688" s="4"/>
@@ -22058,7 +22146,7 @@
       <c r="C689" s="4"/>
       <c r="D689" s="4"/>
       <c r="E689" s="4"/>
-      <c r="F689" s="4"/>
+      <c r="F689" s="15"/>
       <c r="G689" s="4"/>
       <c r="H689" s="4"/>
       <c r="I689" s="4"/>
@@ -22089,7 +22177,7 @@
       <c r="C690" s="4"/>
       <c r="D690" s="4"/>
       <c r="E690" s="4"/>
-      <c r="F690" s="4"/>
+      <c r="F690" s="15"/>
       <c r="G690" s="4"/>
       <c r="H690" s="4"/>
       <c r="I690" s="4"/>
@@ -22120,7 +22208,7 @@
       <c r="C691" s="4"/>
       <c r="D691" s="4"/>
       <c r="E691" s="4"/>
-      <c r="F691" s="4"/>
+      <c r="F691" s="15"/>
       <c r="G691" s="4"/>
       <c r="H691" s="4"/>
       <c r="I691" s="4"/>
@@ -22151,7 +22239,7 @@
       <c r="C692" s="4"/>
       <c r="D692" s="4"/>
       <c r="E692" s="4"/>
-      <c r="F692" s="4"/>
+      <c r="F692" s="15"/>
       <c r="G692" s="4"/>
       <c r="H692" s="4"/>
       <c r="I692" s="4"/>
@@ -22182,7 +22270,7 @@
       <c r="C693" s="4"/>
       <c r="D693" s="4"/>
       <c r="E693" s="4"/>
-      <c r="F693" s="4"/>
+      <c r="F693" s="15"/>
       <c r="G693" s="4"/>
       <c r="H693" s="4"/>
       <c r="I693" s="4"/>
@@ -22213,7 +22301,7 @@
       <c r="C694" s="4"/>
       <c r="D694" s="4"/>
       <c r="E694" s="4"/>
-      <c r="F694" s="4"/>
+      <c r="F694" s="15"/>
       <c r="G694" s="4"/>
       <c r="H694" s="4"/>
       <c r="I694" s="4"/>
@@ -22244,7 +22332,7 @@
       <c r="C695" s="4"/>
       <c r="D695" s="4"/>
       <c r="E695" s="4"/>
-      <c r="F695" s="4"/>
+      <c r="F695" s="15"/>
       <c r="G695" s="4"/>
       <c r="H695" s="4"/>
       <c r="I695" s="4"/>
@@ -22275,7 +22363,7 @@
       <c r="C696" s="4"/>
       <c r="D696" s="4"/>
       <c r="E696" s="4"/>
-      <c r="F696" s="4"/>
+      <c r="F696" s="15"/>
       <c r="G696" s="4"/>
       <c r="H696" s="4"/>
       <c r="I696" s="4"/>
@@ -22306,7 +22394,7 @@
       <c r="C697" s="4"/>
       <c r="D697" s="4"/>
       <c r="E697" s="4"/>
-      <c r="F697" s="4"/>
+      <c r="F697" s="15"/>
       <c r="G697" s="4"/>
       <c r="H697" s="4"/>
       <c r="I697" s="4"/>
@@ -22337,7 +22425,7 @@
       <c r="C698" s="4"/>
       <c r="D698" s="4"/>
       <c r="E698" s="4"/>
-      <c r="F698" s="4"/>
+      <c r="F698" s="15"/>
       <c r="G698" s="4"/>
       <c r="H698" s="4"/>
       <c r="I698" s="4"/>
@@ -22368,7 +22456,7 @@
       <c r="C699" s="4"/>
       <c r="D699" s="4"/>
       <c r="E699" s="4"/>
-      <c r="F699" s="4"/>
+      <c r="F699" s="15"/>
       <c r="G699" s="4"/>
       <c r="H699" s="4"/>
       <c r="I699" s="4"/>
@@ -22399,7 +22487,7 @@
       <c r="C700" s="4"/>
       <c r="D700" s="4"/>
       <c r="E700" s="4"/>
-      <c r="F700" s="4"/>
+      <c r="F700" s="15"/>
       <c r="G700" s="4"/>
       <c r="H700" s="4"/>
       <c r="I700" s="4"/>
@@ -22430,7 +22518,7 @@
       <c r="C701" s="4"/>
       <c r="D701" s="4"/>
       <c r="E701" s="4"/>
-      <c r="F701" s="4"/>
+      <c r="F701" s="15"/>
       <c r="G701" s="4"/>
       <c r="H701" s="4"/>
       <c r="I701" s="4"/>
@@ -22461,7 +22549,7 @@
       <c r="C702" s="4"/>
       <c r="D702" s="4"/>
       <c r="E702" s="4"/>
-      <c r="F702" s="4"/>
+      <c r="F702" s="15"/>
       <c r="G702" s="4"/>
       <c r="H702" s="4"/>
       <c r="I702" s="4"/>
@@ -22492,7 +22580,7 @@
       <c r="C703" s="4"/>
       <c r="D703" s="4"/>
       <c r="E703" s="4"/>
-      <c r="F703" s="4"/>
+      <c r="F703" s="15"/>
       <c r="G703" s="4"/>
       <c r="H703" s="4"/>
       <c r="I703" s="4"/>
@@ -22523,7 +22611,7 @@
       <c r="C704" s="4"/>
       <c r="D704" s="4"/>
       <c r="E704" s="4"/>
-      <c r="F704" s="4"/>
+      <c r="F704" s="15"/>
       <c r="G704" s="4"/>
       <c r="H704" s="4"/>
       <c r="I704" s="4"/>
@@ -22554,7 +22642,7 @@
       <c r="C705" s="4"/>
       <c r="D705" s="4"/>
       <c r="E705" s="4"/>
-      <c r="F705" s="4"/>
+      <c r="F705" s="15"/>
       <c r="G705" s="4"/>
       <c r="H705" s="4"/>
       <c r="I705" s="4"/>
@@ -22585,7 +22673,7 @@
       <c r="C706" s="4"/>
       <c r="D706" s="4"/>
       <c r="E706" s="4"/>
-      <c r="F706" s="4"/>
+      <c r="F706" s="15"/>
       <c r="G706" s="4"/>
       <c r="H706" s="4"/>
       <c r="I706" s="4"/>
@@ -22616,7 +22704,7 @@
       <c r="C707" s="4"/>
       <c r="D707" s="4"/>
       <c r="E707" s="4"/>
-      <c r="F707" s="4"/>
+      <c r="F707" s="15"/>
       <c r="G707" s="4"/>
       <c r="H707" s="4"/>
       <c r="I707" s="4"/>
@@ -22647,7 +22735,7 @@
       <c r="C708" s="4"/>
       <c r="D708" s="4"/>
       <c r="E708" s="4"/>
-      <c r="F708" s="4"/>
+      <c r="F708" s="15"/>
       <c r="G708" s="4"/>
       <c r="H708" s="4"/>
       <c r="I708" s="4"/>
@@ -22678,7 +22766,7 @@
       <c r="C709" s="4"/>
       <c r="D709" s="4"/>
       <c r="E709" s="4"/>
-      <c r="F709" s="4"/>
+      <c r="F709" s="15"/>
       <c r="G709" s="4"/>
       <c r="H709" s="4"/>
       <c r="I709" s="4"/>
@@ -22709,7 +22797,7 @@
       <c r="C710" s="4"/>
       <c r="D710" s="4"/>
       <c r="E710" s="4"/>
-      <c r="F710" s="4"/>
+      <c r="F710" s="15"/>
       <c r="G710" s="4"/>
       <c r="H710" s="4"/>
       <c r="I710" s="4"/>
@@ -22740,7 +22828,7 @@
       <c r="C711" s="4"/>
       <c r="D711" s="4"/>
       <c r="E711" s="4"/>
-      <c r="F711" s="4"/>
+      <c r="F711" s="15"/>
       <c r="G711" s="4"/>
       <c r="H711" s="4"/>
       <c r="I711" s="4"/>
@@ -22771,7 +22859,7 @@
       <c r="C712" s="4"/>
       <c r="D712" s="4"/>
       <c r="E712" s="4"/>
-      <c r="F712" s="4"/>
+      <c r="F712" s="15"/>
       <c r="G712" s="4"/>
       <c r="H712" s="4"/>
       <c r="I712" s="4"/>
@@ -22802,7 +22890,7 @@
       <c r="C713" s="4"/>
       <c r="D713" s="4"/>
       <c r="E713" s="4"/>
-      <c r="F713" s="4"/>
+      <c r="F713" s="15"/>
       <c r="G713" s="4"/>
       <c r="H713" s="4"/>
       <c r="I713" s="4"/>
@@ -22833,7 +22921,7 @@
       <c r="C714" s="4"/>
       <c r="D714" s="4"/>
       <c r="E714" s="4"/>
-      <c r="F714" s="4"/>
+      <c r="F714" s="15"/>
       <c r="G714" s="4"/>
       <c r="H714" s="4"/>
       <c r="I714" s="4"/>
@@ -22864,7 +22952,7 @@
       <c r="C715" s="4"/>
       <c r="D715" s="4"/>
       <c r="E715" s="4"/>
-      <c r="F715" s="4"/>
+      <c r="F715" s="15"/>
       <c r="G715" s="4"/>
       <c r="H715" s="4"/>
       <c r="I715" s="4"/>
@@ -22895,7 +22983,7 @@
       <c r="C716" s="4"/>
       <c r="D716" s="4"/>
       <c r="E716" s="4"/>
-      <c r="F716" s="4"/>
+      <c r="F716" s="15"/>
       <c r="G716" s="4"/>
       <c r="H716" s="4"/>
       <c r="I716" s="4"/>
@@ -22926,7 +23014,7 @@
       <c r="C717" s="4"/>
       <c r="D717" s="4"/>
       <c r="E717" s="4"/>
-      <c r="F717" s="4"/>
+      <c r="F717" s="15"/>
       <c r="G717" s="4"/>
       <c r="H717" s="4"/>
       <c r="I717" s="4"/>
@@ -22957,7 +23045,7 @@
       <c r="C718" s="4"/>
       <c r="D718" s="4"/>
       <c r="E718" s="4"/>
-      <c r="F718" s="4"/>
+      <c r="F718" s="15"/>
       <c r="G718" s="4"/>
       <c r="H718" s="4"/>
       <c r="I718" s="4"/>
@@ -22988,7 +23076,7 @@
       <c r="C719" s="4"/>
       <c r="D719" s="4"/>
       <c r="E719" s="4"/>
-      <c r="F719" s="4"/>
+      <c r="F719" s="15"/>
       <c r="G719" s="4"/>
       <c r="H719" s="4"/>
       <c r="I719" s="4"/>
@@ -23019,7 +23107,7 @@
       <c r="C720" s="4"/>
       <c r="D720" s="4"/>
       <c r="E720" s="4"/>
-      <c r="F720" s="4"/>
+      <c r="F720" s="15"/>
       <c r="G720" s="4"/>
       <c r="H720" s="4"/>
       <c r="I720" s="4"/>
@@ -23050,7 +23138,7 @@
       <c r="C721" s="4"/>
       <c r="D721" s="4"/>
       <c r="E721" s="4"/>
-      <c r="F721" s="4"/>
+      <c r="F721" s="15"/>
       <c r="G721" s="4"/>
       <c r="H721" s="4"/>
       <c r="I721" s="4"/>
@@ -23081,7 +23169,7 @@
       <c r="C722" s="4"/>
       <c r="D722" s="4"/>
       <c r="E722" s="4"/>
-      <c r="F722" s="4"/>
+      <c r="F722" s="15"/>
       <c r="G722" s="4"/>
       <c r="H722" s="4"/>
       <c r="I722" s="4"/>
@@ -23112,7 +23200,7 @@
       <c r="C723" s="4"/>
       <c r="D723" s="4"/>
       <c r="E723" s="4"/>
-      <c r="F723" s="4"/>
+      <c r="F723" s="15"/>
       <c r="G723" s="4"/>
       <c r="H723" s="4"/>
       <c r="I723" s="4"/>
@@ -23143,7 +23231,7 @@
       <c r="C724" s="4"/>
       <c r="D724" s="4"/>
       <c r="E724" s="4"/>
-      <c r="F724" s="4"/>
+      <c r="F724" s="15"/>
       <c r="G724" s="4"/>
       <c r="H724" s="4"/>
       <c r="I724" s="4"/>
@@ -23174,7 +23262,7 @@
       <c r="C725" s="4"/>
       <c r="D725" s="4"/>
       <c r="E725" s="4"/>
-      <c r="F725" s="4"/>
+      <c r="F725" s="15"/>
       <c r="G725" s="4"/>
       <c r="H725" s="4"/>
       <c r="I725" s="4"/>
@@ -23205,7 +23293,7 @@
       <c r="C726" s="4"/>
       <c r="D726" s="4"/>
       <c r="E726" s="4"/>
-      <c r="F726" s="4"/>
+      <c r="F726" s="15"/>
       <c r="G726" s="4"/>
       <c r="H726" s="4"/>
       <c r="I726" s="4"/>
@@ -23236,7 +23324,7 @@
       <c r="C727" s="4"/>
       <c r="D727" s="4"/>
       <c r="E727" s="4"/>
-      <c r="F727" s="4"/>
+      <c r="F727" s="15"/>
       <c r="G727" s="4"/>
       <c r="H727" s="4"/>
       <c r="I727" s="4"/>
@@ -23267,7 +23355,7 @@
       <c r="C728" s="4"/>
       <c r="D728" s="4"/>
       <c r="E728" s="4"/>
-      <c r="F728" s="4"/>
+      <c r="F728" s="15"/>
       <c r="G728" s="4"/>
       <c r="H728" s="4"/>
       <c r="I728" s="4"/>
@@ -23298,7 +23386,7 @@
       <c r="C729" s="4"/>
       <c r="D729" s="4"/>
       <c r="E729" s="4"/>
-      <c r="F729" s="4"/>
+      <c r="F729" s="15"/>
       <c r="G729" s="4"/>
       <c r="H729" s="4"/>
       <c r="I729" s="4"/>
@@ -23329,7 +23417,7 @@
       <c r="C730" s="4"/>
       <c r="D730" s="4"/>
       <c r="E730" s="4"/>
-      <c r="F730" s="4"/>
+      <c r="F730" s="15"/>
       <c r="G730" s="4"/>
       <c r="H730" s="4"/>
       <c r="I730" s="4"/>
@@ -23360,7 +23448,7 @@
       <c r="C731" s="4"/>
       <c r="D731" s="4"/>
       <c r="E731" s="4"/>
-      <c r="F731" s="4"/>
+      <c r="F731" s="15"/>
       <c r="G731" s="4"/>
       <c r="H731" s="4"/>
       <c r="I731" s="4"/>
@@ -23391,7 +23479,7 @@
       <c r="C732" s="4"/>
       <c r="D732" s="4"/>
       <c r="E732" s="4"/>
-      <c r="F732" s="4"/>
+      <c r="F732" s="15"/>
       <c r="G732" s="4"/>
       <c r="H732" s="4"/>
       <c r="I732" s="4"/>
@@ -23422,7 +23510,7 @@
       <c r="C733" s="4"/>
       <c r="D733" s="4"/>
       <c r="E733" s="4"/>
-      <c r="F733" s="4"/>
+      <c r="F733" s="15"/>
       <c r="G733" s="4"/>
       <c r="H733" s="4"/>
       <c r="I733" s="4"/>
@@ -23453,7 +23541,7 @@
       <c r="C734" s="4"/>
       <c r="D734" s="4"/>
       <c r="E734" s="4"/>
-      <c r="F734" s="4"/>
+      <c r="F734" s="15"/>
       <c r="G734" s="4"/>
       <c r="H734" s="4"/>
       <c r="I734" s="4"/>
@@ -23484,7 +23572,7 @@
       <c r="C735" s="4"/>
       <c r="D735" s="4"/>
       <c r="E735" s="4"/>
-      <c r="F735" s="4"/>
+      <c r="F735" s="15"/>
       <c r="G735" s="4"/>
       <c r="H735" s="4"/>
       <c r="I735" s="4"/>
@@ -23515,7 +23603,7 @@
       <c r="C736" s="4"/>
       <c r="D736" s="4"/>
       <c r="E736" s="4"/>
-      <c r="F736" s="4"/>
+      <c r="F736" s="15"/>
       <c r="G736" s="4"/>
       <c r="H736" s="4"/>
       <c r="I736" s="4"/>
@@ -23546,7 +23634,7 @@
       <c r="C737" s="4"/>
       <c r="D737" s="4"/>
       <c r="E737" s="4"/>
-      <c r="F737" s="4"/>
+      <c r="F737" s="15"/>
       <c r="G737" s="4"/>
       <c r="H737" s="4"/>
       <c r="I737" s="4"/>
@@ -23577,7 +23665,7 @@
       <c r="C738" s="4"/>
       <c r="D738" s="4"/>
       <c r="E738" s="4"/>
-      <c r="F738" s="4"/>
+      <c r="F738" s="15"/>
       <c r="G738" s="4"/>
       <c r="H738" s="4"/>
       <c r="I738" s="4"/>
@@ -23608,7 +23696,7 @@
       <c r="C739" s="4"/>
       <c r="D739" s="4"/>
       <c r="E739" s="4"/>
-      <c r="F739" s="4"/>
+      <c r="F739" s="15"/>
       <c r="G739" s="4"/>
       <c r="H739" s="4"/>
       <c r="I739" s="4"/>
@@ -23639,7 +23727,7 @@
       <c r="C740" s="4"/>
       <c r="D740" s="4"/>
       <c r="E740" s="4"/>
-      <c r="F740" s="4"/>
+      <c r="F740" s="15"/>
       <c r="G740" s="4"/>
       <c r="H740" s="4"/>
       <c r="I740" s="4"/>
@@ -23670,7 +23758,7 @@
       <c r="C741" s="4"/>
       <c r="D741" s="4"/>
       <c r="E741" s="4"/>
-      <c r="F741" s="4"/>
+      <c r="F741" s="15"/>
       <c r="G741" s="4"/>
       <c r="H741" s="4"/>
       <c r="I741" s="4"/>
@@ -23701,7 +23789,7 @@
       <c r="C742" s="4"/>
       <c r="D742" s="4"/>
       <c r="E742" s="4"/>
-      <c r="F742" s="4"/>
+      <c r="F742" s="15"/>
       <c r="G742" s="4"/>
       <c r="H742" s="4"/>
       <c r="I742" s="4"/>
@@ -23732,7 +23820,7 @@
       <c r="C743" s="4"/>
       <c r="D743" s="4"/>
       <c r="E743" s="4"/>
-      <c r="F743" s="4"/>
+      <c r="F743" s="15"/>
       <c r="G743" s="4"/>
       <c r="H743" s="4"/>
       <c r="I743" s="4"/>
@@ -23763,7 +23851,7 @@
       <c r="C744" s="4"/>
       <c r="D744" s="4"/>
       <c r="E744" s="4"/>
-      <c r="F744" s="4"/>
+      <c r="F744" s="15"/>
       <c r="G744" s="4"/>
       <c r="H744" s="4"/>
       <c r="I744" s="4"/>
@@ -23794,7 +23882,7 @@
       <c r="C745" s="4"/>
       <c r="D745" s="4"/>
       <c r="E745" s="4"/>
-      <c r="F745" s="4"/>
+      <c r="F745" s="15"/>
       <c r="G745" s="4"/>
       <c r="H745" s="4"/>
       <c r="I745" s="4"/>
@@ -23825,7 +23913,7 @@
       <c r="C746" s="4"/>
       <c r="D746" s="4"/>
       <c r="E746" s="4"/>
-      <c r="F746" s="4"/>
+      <c r="F746" s="15"/>
       <c r="G746" s="4"/>
       <c r="H746" s="4"/>
       <c r="I746" s="4"/>
@@ -23856,7 +23944,7 @@
       <c r="C747" s="4"/>
       <c r="D747" s="4"/>
       <c r="E747" s="4"/>
-      <c r="F747" s="4"/>
+      <c r="F747" s="15"/>
       <c r="G747" s="4"/>
       <c r="H747" s="4"/>
       <c r="I747" s="4"/>
@@ -23887,7 +23975,7 @@
       <c r="C748" s="4"/>
       <c r="D748" s="4"/>
       <c r="E748" s="4"/>
-      <c r="F748" s="4"/>
+      <c r="F748" s="15"/>
       <c r="G748" s="4"/>
       <c r="H748" s="4"/>
       <c r="I748" s="4"/>
@@ -23918,7 +24006,7 @@
       <c r="C749" s="4"/>
       <c r="D749" s="4"/>
       <c r="E749" s="4"/>
-      <c r="F749" s="4"/>
+      <c r="F749" s="15"/>
       <c r="G749" s="4"/>
       <c r="H749" s="4"/>
       <c r="I749" s="4"/>
@@ -23949,7 +24037,7 @@
       <c r="C750" s="4"/>
       <c r="D750" s="4"/>
       <c r="E750" s="4"/>
-      <c r="F750" s="4"/>
+      <c r="F750" s="15"/>
       <c r="G750" s="4"/>
       <c r="H750" s="4"/>
       <c r="I750" s="4"/>
@@ -23980,7 +24068,7 @@
       <c r="C751" s="4"/>
       <c r="D751" s="4"/>
       <c r="E751" s="4"/>
-      <c r="F751" s="4"/>
+      <c r="F751" s="15"/>
       <c r="G751" s="4"/>
       <c r="H751" s="4"/>
       <c r="I751" s="4"/>
@@ -24011,7 +24099,7 @@
       <c r="C752" s="4"/>
       <c r="D752" s="4"/>
       <c r="E752" s="4"/>
-      <c r="F752" s="4"/>
+      <c r="F752" s="15"/>
       <c r="G752" s="4"/>
       <c r="H752" s="4"/>
       <c r="I752" s="4"/>
@@ -24042,7 +24130,7 @@
       <c r="C753" s="4"/>
       <c r="D753" s="4"/>
       <c r="E753" s="4"/>
-      <c r="F753" s="4"/>
+      <c r="F753" s="15"/>
       <c r="G753" s="4"/>
       <c r="H753" s="4"/>
       <c r="I753" s="4"/>
@@ -24073,7 +24161,7 @@
       <c r="C754" s="4"/>
       <c r="D754" s="4"/>
       <c r="E754" s="4"/>
-      <c r="F754" s="4"/>
+      <c r="F754" s="15"/>
       <c r="G754" s="4"/>
       <c r="H754" s="4"/>
       <c r="I754" s="4"/>
@@ -24104,7 +24192,7 @@
       <c r="C755" s="4"/>
       <c r="D755" s="4"/>
       <c r="E755" s="4"/>
-      <c r="F755" s="4"/>
+      <c r="F755" s="15"/>
       <c r="G755" s="4"/>
       <c r="H755" s="4"/>
       <c r="I755" s="4"/>
@@ -24135,7 +24223,7 @@
       <c r="C756" s="4"/>
       <c r="D756" s="4"/>
       <c r="E756" s="4"/>
-      <c r="F756" s="4"/>
+      <c r="F756" s="15"/>
       <c r="G756" s="4"/>
       <c r="H756" s="4"/>
       <c r="I756" s="4"/>
@@ -24166,7 +24254,7 @@
       <c r="C757" s="4"/>
       <c r="D757" s="4"/>
       <c r="E757" s="4"/>
-      <c r="F757" s="4"/>
+      <c r="F757" s="15"/>
       <c r="G757" s="4"/>
       <c r="H757" s="4"/>
       <c r="I757" s="4"/>
@@ -24197,7 +24285,7 @@
       <c r="C758" s="4"/>
       <c r="D758" s="4"/>
       <c r="E758" s="4"/>
-      <c r="F758" s="4"/>
+      <c r="F758" s="15"/>
       <c r="G758" s="4"/>
       <c r="H758" s="4"/>
       <c r="I758" s="4"/>
@@ -24228,7 +24316,7 @@
       <c r="C759" s="4"/>
       <c r="D759" s="4"/>
       <c r="E759" s="4"/>
-      <c r="F759" s="4"/>
+      <c r="F759" s="15"/>
       <c r="G759" s="4"/>
       <c r="H759" s="4"/>
       <c r="I759" s="4"/>
@@ -24259,7 +24347,7 @@
       <c r="C760" s="4"/>
       <c r="D760" s="4"/>
       <c r="E760" s="4"/>
-      <c r="F760" s="4"/>
+      <c r="F760" s="15"/>
       <c r="G760" s="4"/>
       <c r="H760" s="4"/>
       <c r="I760" s="4"/>
@@ -24290,7 +24378,7 @@
       <c r="C761" s="4"/>
       <c r="D761" s="4"/>
       <c r="E761" s="4"/>
-      <c r="F761" s="4"/>
+      <c r="F761" s="15"/>
       <c r="G761" s="4"/>
       <c r="H761" s="4"/>
       <c r="I761" s="4"/>
@@ -24321,7 +24409,7 @@
       <c r="C762" s="4"/>
       <c r="D762" s="4"/>
       <c r="E762" s="4"/>
-      <c r="F762" s="4"/>
+      <c r="F762" s="15"/>
       <c r="G762" s="4"/>
       <c r="H762" s="4"/>
       <c r="I762" s="4"/>
@@ -24352,7 +24440,7 @@
       <c r="C763" s="4"/>
       <c r="D763" s="4"/>
       <c r="E763" s="4"/>
-      <c r="F763" s="4"/>
+      <c r="F763" s="15"/>
       <c r="G763" s="4"/>
       <c r="H763" s="4"/>
       <c r="I763" s="4"/>
@@ -24383,7 +24471,7 @@
       <c r="C764" s="4"/>
       <c r="D764" s="4"/>
       <c r="E764" s="4"/>
-      <c r="F764" s="4"/>
+      <c r="F764" s="15"/>
       <c r="G764" s="4"/>
       <c r="H764" s="4"/>
       <c r="I764" s="4"/>
@@ -24414,7 +24502,7 @@
       <c r="C765" s="4"/>
       <c r="D765" s="4"/>
       <c r="E765" s="4"/>
-      <c r="F765" s="4"/>
+      <c r="F765" s="15"/>
       <c r="G765" s="4"/>
       <c r="H765" s="4"/>
       <c r="I765" s="4"/>
@@ -24445,7 +24533,7 @@
       <c r="C766" s="4"/>
       <c r="D766" s="4"/>
       <c r="E766" s="4"/>
-      <c r="F766" s="4"/>
+      <c r="F766" s="15"/>
       <c r="G766" s="4"/>
       <c r="H766" s="4"/>
       <c r="I766" s="4"/>
@@ -24476,7 +24564,7 @@
       <c r="C767" s="4"/>
       <c r="D767" s="4"/>
       <c r="E767" s="4"/>
-      <c r="F767" s="4"/>
+      <c r="F767" s="15"/>
       <c r="G767" s="4"/>
       <c r="H767" s="4"/>
       <c r="I767" s="4"/>
@@ -24507,7 +24595,7 @@
       <c r="C768" s="4"/>
       <c r="D768" s="4"/>
       <c r="E768" s="4"/>
-      <c r="F768" s="4"/>
+      <c r="F768" s="15"/>
       <c r="G768" s="4"/>
       <c r="H768" s="4"/>
       <c r="I768" s="4"/>
@@ -24538,7 +24626,7 @@
       <c r="C769" s="4"/>
       <c r="D769" s="4"/>
       <c r="E769" s="4"/>
-      <c r="F769" s="4"/>
+      <c r="F769" s="15"/>
       <c r="G769" s="4"/>
       <c r="H769" s="4"/>
       <c r="I769" s="4"/>
@@ -24569,7 +24657,7 @@
       <c r="C770" s="4"/>
       <c r="D770" s="4"/>
       <c r="E770" s="4"/>
-      <c r="F770" s="4"/>
+      <c r="F770" s="15"/>
       <c r="G770" s="4"/>
       <c r="H770" s="4"/>
       <c r="I770" s="4"/>
@@ -24600,7 +24688,7 @@
       <c r="C771" s="4"/>
       <c r="D771" s="4"/>
       <c r="E771" s="4"/>
-      <c r="F771" s="4"/>
+      <c r="F771" s="15"/>
       <c r="G771" s="4"/>
       <c r="H771" s="4"/>
       <c r="I771" s="4"/>
@@ -24631,7 +24719,7 @@
       <c r="C772" s="4"/>
       <c r="D772" s="4"/>
       <c r="E772" s="4"/>
-      <c r="F772" s="4"/>
+      <c r="F772" s="15"/>
       <c r="G772" s="4"/>
       <c r="H772" s="4"/>
       <c r="I772" s="4"/>
@@ -24662,7 +24750,7 @@
       <c r="C773" s="4"/>
       <c r="D773" s="4"/>
       <c r="E773" s="4"/>
-      <c r="F773" s="4"/>
+      <c r="F773" s="15"/>
       <c r="G773" s="4"/>
       <c r="H773" s="4"/>
       <c r="I773" s="4"/>
@@ -24693,7 +24781,7 @@
       <c r="C774" s="4"/>
       <c r="D774" s="4"/>
       <c r="E774" s="4"/>
-      <c r="F774" s="4"/>
+      <c r="F774" s="15"/>
       <c r="G774" s="4"/>
       <c r="H774" s="4"/>
       <c r="I774" s="4"/>
@@ -24724,7 +24812,7 @@
       <c r="C775" s="4"/>
       <c r="D775" s="4"/>
       <c r="E775" s="4"/>
-      <c r="F775" s="4"/>
+      <c r="F775" s="15"/>
       <c r="G775" s="4"/>
       <c r="H775" s="4"/>
       <c r="I775" s="4"/>
@@ -24755,7 +24843,7 @@
       <c r="C776" s="4"/>
       <c r="D776" s="4"/>
       <c r="E776" s="4"/>
-      <c r="F776" s="4"/>
+      <c r="F776" s="15"/>
       <c r="G776" s="4"/>
       <c r="H776" s="4"/>
       <c r="I776" s="4"/>
@@ -24786,7 +24874,7 @@
       <c r="C777" s="4"/>
       <c r="D777" s="4"/>
       <c r="E777" s="4"/>
-      <c r="F777" s="4"/>
+      <c r="F777" s="15"/>
       <c r="G777" s="4"/>
       <c r="H777" s="4"/>
       <c r="I777" s="4"/>
@@ -24817,7 +24905,7 @@
       <c r="C778" s="4"/>
       <c r="D778" s="4"/>
       <c r="E778" s="4"/>
-      <c r="F778" s="4"/>
+      <c r="F778" s="15"/>
       <c r="G778" s="4"/>
       <c r="H778" s="4"/>
       <c r="I778" s="4"/>
@@ -24848,7 +24936,7 @@
       <c r="C779" s="4"/>
       <c r="D779" s="4"/>
       <c r="E779" s="4"/>
-      <c r="F779" s="4"/>
+      <c r="F779" s="15"/>
       <c r="G779" s="4"/>
       <c r="H779" s="4"/>
       <c r="I779" s="4"/>
@@ -24879,7 +24967,7 @@
       <c r="C780" s="4"/>
       <c r="D780" s="4"/>
       <c r="E780" s="4"/>
-      <c r="F780" s="4"/>
+      <c r="F780" s="15"/>
       <c r="G780" s="4"/>
       <c r="H780" s="4"/>
       <c r="I780" s="4"/>
@@ -24910,7 +24998,7 @@
       <c r="C781" s="4"/>
       <c r="D781" s="4"/>
       <c r="E781" s="4"/>
-      <c r="F781" s="4"/>
+      <c r="F781" s="15"/>
       <c r="G781" s="4"/>
       <c r="H781" s="4"/>
       <c r="I781" s="4"/>
@@ -24941,7 +25029,7 @@
       <c r="C782" s="4"/>
       <c r="D782" s="4"/>
       <c r="E782" s="4"/>
-      <c r="F782" s="4"/>
+      <c r="F782" s="15"/>
       <c r="G782" s="4"/>
       <c r="H782" s="4"/>
       <c r="I782" s="4"/>
@@ -24972,7 +25060,7 @@
       <c r="C783" s="4"/>
       <c r="D783" s="4"/>
       <c r="E783" s="4"/>
-      <c r="F783" s="4"/>
+      <c r="F783" s="15"/>
       <c r="G783" s="4"/>
       <c r="H783" s="4"/>
       <c r="I783" s="4"/>
@@ -25003,7 +25091,7 @@
       <c r="C784" s="4"/>
       <c r="D784" s="4"/>
       <c r="E784" s="4"/>
-      <c r="F784" s="4"/>
+      <c r="F784" s="15"/>
       <c r="G784" s="4"/>
       <c r="H784" s="4"/>
       <c r="I784" s="4"/>
@@ -25034,7 +25122,7 @@
       <c r="C785" s="4"/>
       <c r="D785" s="4"/>
       <c r="E785" s="4"/>
-      <c r="F785" s="4"/>
+      <c r="F785" s="15"/>
       <c r="G785" s="4"/>
       <c r="H785" s="4"/>
       <c r="I785" s="4"/>
@@ -25065,7 +25153,7 @@
       <c r="C786" s="4"/>
       <c r="D786" s="4"/>
       <c r="E786" s="4"/>
-      <c r="F786" s="4"/>
+      <c r="F786" s="15"/>
       <c r="G786" s="4"/>
       <c r="H786" s="4"/>
       <c r="I786" s="4"/>
@@ -25096,7 +25184,7 @@
       <c r="C787" s="4"/>
       <c r="D787" s="4"/>
       <c r="E787" s="4"/>
-      <c r="F787" s="4"/>
+      <c r="F787" s="15"/>
       <c r="G787" s="4"/>
       <c r="H787" s="4"/>
       <c r="I787" s="4"/>
@@ -25127,7 +25215,7 @@
       <c r="C788" s="4"/>
       <c r="D788" s="4"/>
       <c r="E788" s="4"/>
-      <c r="F788" s="4"/>
+      <c r="F788" s="15"/>
       <c r="G788" s="4"/>
       <c r="H788" s="4"/>
       <c r="I788" s="4"/>
@@ -25158,7 +25246,7 @@
       <c r="C789" s="4"/>
       <c r="D789" s="4"/>
       <c r="E789" s="4"/>
-      <c r="F789" s="4"/>
+      <c r="F789" s="15"/>
       <c r="G789" s="4"/>
       <c r="H789" s="4"/>
       <c r="I789" s="4"/>
@@ -25189,7 +25277,7 @@
       <c r="C790" s="4"/>
       <c r="D790" s="4"/>
       <c r="E790" s="4"/>
-      <c r="F790" s="4"/>
+      <c r="F790" s="15"/>
       <c r="G790" s="4"/>
       <c r="H790" s="4"/>
       <c r="I790" s="4"/>
@@ -25220,7 +25308,7 @@
       <c r="C791" s="4"/>
       <c r="D791" s="4"/>
       <c r="E791" s="4"/>
-      <c r="F791" s="4"/>
+      <c r="F791" s="15"/>
       <c r="G791" s="4"/>
       <c r="H791" s="4"/>
       <c r="I791" s="4"/>
@@ -25251,7 +25339,7 @@
       <c r="C792" s="4"/>
       <c r="D792" s="4"/>
       <c r="E792" s="4"/>
-      <c r="F792" s="4"/>
+      <c r="F792" s="15"/>
       <c r="G792" s="4"/>
       <c r="H792" s="4"/>
       <c r="I792" s="4"/>
@@ -25282,7 +25370,7 @@
       <c r="C793" s="4"/>
       <c r="D793" s="4"/>
       <c r="E793" s="4"/>
-      <c r="F793" s="4"/>
+      <c r="F793" s="15"/>
       <c r="G793" s="4"/>
       <c r="H793" s="4"/>
       <c r="I793" s="4"/>
@@ -25313,7 +25401,7 @@
       <c r="C794" s="4"/>
       <c r="D794" s="4"/>
       <c r="E794" s="4"/>
-      <c r="F794" s="4"/>
+      <c r="F794" s="15"/>
       <c r="G794" s="4"/>
       <c r="H794" s="4"/>
       <c r="I794" s="4"/>
@@ -25344,7 +25432,7 @@
       <c r="C795" s="4"/>
       <c r="D795" s="4"/>
       <c r="E795" s="4"/>
-      <c r="F795" s="4"/>
+      <c r="F795" s="15"/>
       <c r="G795" s="4"/>
       <c r="H795" s="4"/>
       <c r="I795" s="4"/>
@@ -25375,7 +25463,7 @@
       <c r="C796" s="4"/>
       <c r="D796" s="4"/>
       <c r="E796" s="4"/>
-      <c r="F796" s="4"/>
+      <c r="F796" s="15"/>
       <c r="G796" s="4"/>
       <c r="H796" s="4"/>
       <c r="I796" s="4"/>
@@ -25406,7 +25494,7 @@
       <c r="C797" s="4"/>
       <c r="D797" s="4"/>
       <c r="E797" s="4"/>
-      <c r="F797" s="4"/>
+      <c r="F797" s="15"/>
       <c r="G797" s="4"/>
       <c r="H797" s="4"/>
       <c r="I797" s="4"/>
@@ -25437,7 +25525,7 @@
       <c r="C798" s="4"/>
       <c r="D798" s="4"/>
       <c r="E798" s="4"/>
-      <c r="F798" s="4"/>
+      <c r="F798" s="15"/>
       <c r="G798" s="4"/>
       <c r="H798" s="4"/>
       <c r="I798" s="4"/>
@@ -25468,7 +25556,7 @@
       <c r="C799" s="4"/>
       <c r="D799" s="4"/>
       <c r="E799" s="4"/>
-      <c r="F799" s="4"/>
+      <c r="F799" s="15"/>
       <c r="G799" s="4"/>
       <c r="H799" s="4"/>
       <c r="I799" s="4"/>
@@ -25499,7 +25587,7 @@
       <c r="C800" s="4"/>
       <c r="D800" s="4"/>
       <c r="E800" s="4"/>
-      <c r="F800" s="4"/>
+      <c r="F800" s="15"/>
       <c r="G800" s="4"/>
       <c r="H800" s="4"/>
       <c r="I800" s="4"/>
@@ -25530,7 +25618,7 @@
       <c r="C801" s="4"/>
       <c r="D801" s="4"/>
       <c r="E801" s="4"/>
-      <c r="F801" s="4"/>
+      <c r="F801" s="15"/>
       <c r="G801" s="4"/>
       <c r="H801" s="4"/>
       <c r="I801" s="4"/>
@@ -25561,7 +25649,7 @@
       <c r="C802" s="4"/>
       <c r="D802" s="4"/>
       <c r="E802" s="4"/>
-      <c r="F802" s="4"/>
+      <c r="F802" s="15"/>
       <c r="G802" s="4"/>
       <c r="H802" s="4"/>
       <c r="I802" s="4"/>
@@ -25592,7 +25680,7 @@
       <c r="C803" s="4"/>
       <c r="D803" s="4"/>
       <c r="E803" s="4"/>
-      <c r="F803" s="4"/>
+      <c r="F803" s="15"/>
       <c r="G803" s="4"/>
       <c r="H803" s="4"/>
       <c r="I803" s="4"/>
@@ -25623,7 +25711,7 @@
       <c r="C804" s="4"/>
       <c r="D804" s="4"/>
       <c r="E804" s="4"/>
-      <c r="F804" s="4"/>
+      <c r="F804" s="15"/>
       <c r="G804" s="4"/>
       <c r="H804" s="4"/>
       <c r="I804" s="4"/>
@@ -25654,7 +25742,7 @@
       <c r="C805" s="4"/>
       <c r="D805" s="4"/>
       <c r="E805" s="4"/>
-      <c r="F805" s="4"/>
+      <c r="F805" s="15"/>
       <c r="G805" s="4"/>
       <c r="H805" s="4"/>
       <c r="I805" s="4"/>
@@ -25685,7 +25773,7 @@
       <c r="C806" s="4"/>
       <c r="D806" s="4"/>
       <c r="E806" s="4"/>
-      <c r="F806" s="4"/>
+      <c r="F806" s="15"/>
       <c r="G806" s="4"/>
       <c r="H806" s="4"/>
       <c r="I806" s="4"/>
@@ -25716,7 +25804,7 @@
       <c r="C807" s="4"/>
       <c r="D807" s="4"/>
       <c r="E807" s="4"/>
-      <c r="F807" s="4"/>
+      <c r="F807" s="15"/>
       <c r="G807" s="4"/>
       <c r="H807" s="4"/>
       <c r="I807" s="4"/>
@@ -25747,7 +25835,7 @@
       <c r="C808" s="4"/>
       <c r="D808" s="4"/>
       <c r="E808" s="4"/>
-      <c r="F808" s="4"/>
+      <c r="F808" s="15"/>
       <c r="G808" s="4"/>
       <c r="H808" s="4"/>
       <c r="I808" s="4"/>
@@ -25778,7 +25866,7 @@
       <c r="C809" s="4"/>
       <c r="D809" s="4"/>
       <c r="E809" s="4"/>
-      <c r="F809" s="4"/>
+      <c r="F809" s="15"/>
       <c r="G809" s="4"/>
       <c r="H809" s="4"/>
       <c r="I809" s="4"/>
@@ -25809,7 +25897,7 @@
       <c r="C810" s="4"/>
       <c r="D810" s="4"/>
       <c r="E810" s="4"/>
-      <c r="F810" s="4"/>
+      <c r="F810" s="15"/>
       <c r="G810" s="4"/>
       <c r="H810" s="4"/>
       <c r="I810" s="4"/>
@@ -25840,7 +25928,7 @@
       <c r="C811" s="4"/>
       <c r="D811" s="4"/>
       <c r="E811" s="4"/>
-      <c r="F811" s="4"/>
+      <c r="F811" s="15"/>
       <c r="G811" s="4"/>
       <c r="H811" s="4"/>
       <c r="I811" s="4"/>
@@ -25871,7 +25959,7 @@
       <c r="C812" s="4"/>
       <c r="D812" s="4"/>
       <c r="E812" s="4"/>
-      <c r="F812" s="4"/>
+      <c r="F812" s="15"/>
       <c r="G812" s="4"/>
       <c r="H812" s="4"/>
       <c r="I812" s="4"/>
@@ -25902,7 +25990,7 @@
       <c r="C813" s="4"/>
       <c r="D813" s="4"/>
       <c r="E813" s="4"/>
-      <c r="F813" s="4"/>
+      <c r="F813" s="15"/>
       <c r="G813" s="4"/>
       <c r="H813" s="4"/>
       <c r="I813" s="4"/>
@@ -25933,7 +26021,7 @@
       <c r="C814" s="4"/>
       <c r="D814" s="4"/>
       <c r="E814" s="4"/>
-      <c r="F814" s="4"/>
+      <c r="F814" s="15"/>
       <c r="G814" s="4"/>
       <c r="H814" s="4"/>
       <c r="I814" s="4"/>
@@ -25964,7 +26052,7 @@
       <c r="C815" s="4"/>
       <c r="D815" s="4"/>
       <c r="E815" s="4"/>
-      <c r="F815" s="4"/>
+      <c r="F815" s="15"/>
       <c r="G815" s="4"/>
       <c r="H815" s="4"/>
       <c r="I815" s="4"/>
@@ -25995,7 +26083,7 @@
       <c r="C816" s="4"/>
       <c r="D816" s="4"/>
       <c r="E816" s="4"/>
-      <c r="F816" s="4"/>
+      <c r="F816" s="15"/>
       <c r="G816" s="4"/>
       <c r="H816" s="4"/>
       <c r="I816" s="4"/>
@@ -26026,7 +26114,7 @@
       <c r="C817" s="4"/>
       <c r="D817" s="4"/>
       <c r="E817" s="4"/>
-      <c r="F817" s="4"/>
+      <c r="F817" s="15"/>
       <c r="G817" s="4"/>
       <c r="H817" s="4"/>
       <c r="I817" s="4"/>
@@ -26057,7 +26145,7 @@
       <c r="C818" s="4"/>
       <c r="D818" s="4"/>
       <c r="E818" s="4"/>
-      <c r="F818" s="4"/>
+      <c r="F818" s="15"/>
       <c r="G818" s="4"/>
       <c r="H818" s="4"/>
       <c r="I818" s="4"/>
@@ -26088,7 +26176,7 @@
       <c r="C819" s="4"/>
       <c r="D819" s="4"/>
       <c r="E819" s="4"/>
-      <c r="F819" s="4"/>
+      <c r="F819" s="15"/>
       <c r="G819" s="4"/>
       <c r="H819" s="4"/>
       <c r="I819" s="4"/>
@@ -26119,7 +26207,7 @@
       <c r="C820" s="4"/>
       <c r="D820" s="4"/>
       <c r="E820" s="4"/>
-      <c r="F820" s="4"/>
+      <c r="F820" s="15"/>
       <c r="G820" s="4"/>
       <c r="H820" s="4"/>
       <c r="I820" s="4"/>
@@ -26150,7 +26238,7 @@
       <c r="C821" s="4"/>
       <c r="D821" s="4"/>
       <c r="E821" s="4"/>
-      <c r="F821" s="4"/>
+      <c r="F821" s="15"/>
       <c r="G821" s="4"/>
       <c r="H821" s="4"/>
       <c r="I821" s="4"/>
@@ -26181,7 +26269,7 @@
       <c r="C822" s="4"/>
       <c r="D822" s="4"/>
       <c r="E822" s="4"/>
-      <c r="F822" s="4"/>
+      <c r="F822" s="15"/>
       <c r="G822" s="4"/>
       <c r="H822" s="4"/>
       <c r="I822" s="4"/>
@@ -26212,7 +26300,7 @@
       <c r="C823" s="4"/>
       <c r="D823" s="4"/>
       <c r="E823" s="4"/>
-      <c r="F823" s="4"/>
+      <c r="F823" s="15"/>
       <c r="G823" s="4"/>
       <c r="H823" s="4"/>
       <c r="I823" s="4"/>
@@ -26243,7 +26331,7 @@
       <c r="C824" s="4"/>
       <c r="D824" s="4"/>
       <c r="E824" s="4"/>
-      <c r="F824" s="4"/>
+      <c r="F824" s="15"/>
       <c r="G824" s="4"/>
       <c r="H824" s="4"/>
       <c r="I824" s="4"/>
@@ -26274,7 +26362,7 @@
       <c r="C825" s="4"/>
       <c r="D825" s="4"/>
       <c r="E825" s="4"/>
-      <c r="F825" s="4"/>
+      <c r="F825" s="15"/>
       <c r="G825" s="4"/>
       <c r="H825" s="4"/>
       <c r="I825" s="4"/>
@@ -26305,7 +26393,7 @@
       <c r="C826" s="4"/>
       <c r="D826" s="4"/>
       <c r="E826" s="4"/>
-      <c r="F826" s="4"/>
+      <c r="F826" s="15"/>
       <c r="G826" s="4"/>
       <c r="H826" s="4"/>
       <c r="I826" s="4"/>
@@ -26336,7 +26424,7 @@
       <c r="C827" s="4"/>
       <c r="D827" s="4"/>
       <c r="E827" s="4"/>
-      <c r="F827" s="4"/>
+      <c r="F827" s="15"/>
       <c r="G827" s="4"/>
       <c r="H827" s="4"/>
       <c r="I827" s="4"/>
@@ -26367,7 +26455,7 @@
       <c r="C828" s="4"/>
       <c r="D828" s="4"/>
       <c r="E828" s="4"/>
-      <c r="F828" s="4"/>
+      <c r="F828" s="15"/>
       <c r="G828" s="4"/>
       <c r="H828" s="4"/>
       <c r="I828" s="4"/>
@@ -26398,7 +26486,7 @@
       <c r="C829" s="4"/>
       <c r="D829" s="4"/>
       <c r="E829" s="4"/>
-      <c r="F829" s="4"/>
+      <c r="F829" s="15"/>
       <c r="G829" s="4"/>
       <c r="H829" s="4"/>
       <c r="I829" s="4"/>
@@ -26429,7 +26517,7 @@
       <c r="C830" s="4"/>
       <c r="D830" s="4"/>
       <c r="E830" s="4"/>
-      <c r="F830" s="4"/>
+      <c r="F830" s="15"/>
       <c r="G830" s="4"/>
       <c r="H830" s="4"/>
       <c r="I830" s="4"/>
@@ -26460,7 +26548,7 @@
       <c r="C831" s="4"/>
       <c r="D831" s="4"/>
       <c r="E831" s="4"/>
-      <c r="F831" s="4"/>
+      <c r="F831" s="15"/>
       <c r="G831" s="4"/>
       <c r="H831" s="4"/>
       <c r="I831" s="4"/>
@@ -26491,7 +26579,7 @@
       <c r="C832" s="4"/>
       <c r="D832" s="4"/>
       <c r="E832" s="4"/>
-      <c r="F832" s="4"/>
+      <c r="F832" s="15"/>
       <c r="G832" s="4"/>
       <c r="H832" s="4"/>
       <c r="I832" s="4"/>
@@ -26522,7 +26610,7 @@
       <c r="C833" s="4"/>
       <c r="D833" s="4"/>
       <c r="E833" s="4"/>
-      <c r="F833" s="4"/>
+      <c r="F833" s="15"/>
       <c r="G833" s="4"/>
       <c r="H833" s="4"/>
       <c r="I833" s="4"/>
@@ -26553,7 +26641,7 @@
       <c r="C834" s="4"/>
       <c r="D834" s="4"/>
       <c r="E834" s="4"/>
-      <c r="F834" s="4"/>
+      <c r="F834" s="15"/>
       <c r="G834" s="4"/>
       <c r="H834" s="4"/>
       <c r="I834" s="4"/>
@@ -26584,7 +26672,7 @@
       <c r="C835" s="4"/>
       <c r="D835" s="4"/>
       <c r="E835" s="4"/>
-      <c r="F835" s="4"/>
+      <c r="F835" s="15"/>
       <c r="G835" s="4"/>
       <c r="H835" s="4"/>
       <c r="I835" s="4"/>
@@ -26615,7 +26703,7 @@
       <c r="C836" s="4"/>
       <c r="D836" s="4"/>
       <c r="E836" s="4"/>
-      <c r="F836" s="4"/>
+      <c r="F836" s="15"/>
       <c r="G836" s="4"/>
       <c r="H836" s="4"/>
       <c r="I836" s="4"/>
@@ -26646,7 +26734,7 @@
       <c r="C837" s="4"/>
       <c r="D837" s="4"/>
       <c r="E837" s="4"/>
-      <c r="F837" s="4"/>
+      <c r="F837" s="15"/>
       <c r="G837" s="4"/>
       <c r="H837" s="4"/>
       <c r="I837" s="4"/>
@@ -26677,7 +26765,7 @@
       <c r="C838" s="4"/>
       <c r="D838" s="4"/>
       <c r="E838" s="4"/>
-      <c r="F838" s="4"/>
+      <c r="F838" s="15"/>
       <c r="G838" s="4"/>
       <c r="H838" s="4"/>
       <c r="I838" s="4"/>
@@ -26708,7 +26796,7 @@
       <c r="C839" s="4"/>
       <c r="D839" s="4"/>
       <c r="E839" s="4"/>
-      <c r="F839" s="4"/>
+      <c r="F839" s="15"/>
       <c r="G839" s="4"/>
       <c r="H839" s="4"/>
       <c r="I839" s="4"/>
@@ -26739,7 +26827,7 @@
       <c r="C840" s="4"/>
       <c r="D840" s="4"/>
       <c r="E840" s="4"/>
-      <c r="F840" s="4"/>
+      <c r="F840" s="15"/>
       <c r="G840" s="4"/>
       <c r="H840" s="4"/>
       <c r="I840" s="4"/>
@@ -26770,7 +26858,7 @@
       <c r="C841" s="4"/>
       <c r="D841" s="4"/>
       <c r="E841" s="4"/>
-      <c r="F841" s="4"/>
+      <c r="F841" s="15"/>
       <c r="G841" s="4"/>
       <c r="H841" s="4"/>
       <c r="I841" s="4"/>
@@ -26801,7 +26889,7 @@
       <c r="C842" s="4"/>
       <c r="D842" s="4"/>
       <c r="E842" s="4"/>
-      <c r="F842" s="4"/>
+      <c r="F842" s="15"/>
       <c r="G842" s="4"/>
       <c r="H842" s="4"/>
       <c r="I842" s="4"/>
@@ -26832,7 +26920,7 @@
       <c r="C843" s="4"/>
       <c r="D843" s="4"/>
       <c r="E843" s="4"/>
-      <c r="F843" s="4"/>
+      <c r="F843" s="15"/>
       <c r="G843" s="4"/>
       <c r="H843" s="4"/>
       <c r="I843" s="4"/>
@@ -26863,7 +26951,7 @@
       <c r="C844" s="4"/>
       <c r="D844" s="4"/>
       <c r="E844" s="4"/>
-      <c r="F844" s="4"/>
+      <c r="F844" s="15"/>
       <c r="G844" s="4"/>
       <c r="H844" s="4"/>
       <c r="I844" s="4"/>
@@ -26894,7 +26982,7 @@
       <c r="C845" s="4"/>
       <c r="D845" s="4"/>
       <c r="E845" s="4"/>
-      <c r="F845" s="4"/>
+      <c r="F845" s="15"/>
       <c r="G845" s="4"/>
       <c r="H845" s="4"/>
       <c r="I845" s="4"/>
@@ -26925,7 +27013,7 @@
       <c r="C846" s="4"/>
       <c r="D846" s="4"/>
       <c r="E846" s="4"/>
-      <c r="F846" s="4"/>
+      <c r="F846" s="15"/>
       <c r="G846" s="4"/>
       <c r="H846" s="4"/>
       <c r="I846" s="4"/>
@@ -26956,7 +27044,7 @@
       <c r="C847" s="4"/>
       <c r="D847" s="4"/>
       <c r="E847" s="4"/>
-      <c r="F847" s="4"/>
+      <c r="F847" s="15"/>
       <c r="G847" s="4"/>
       <c r="H847" s="4"/>
       <c r="I847" s="4"/>
@@ -26987,7 +27075,7 @@
       <c r="C848" s="4"/>
       <c r="D848" s="4"/>
       <c r="E848" s="4"/>
-      <c r="F848" s="4"/>
+      <c r="F848" s="15"/>
       <c r="G848" s="4"/>
       <c r="H848" s="4"/>
       <c r="I848" s="4"/>
@@ -27018,7 +27106,7 @@
       <c r="C849" s="4"/>
       <c r="D849" s="4"/>
       <c r="E849" s="4"/>
-      <c r="F849" s="4"/>
+      <c r="F849" s="15"/>
       <c r="G849" s="4"/>
       <c r="H849" s="4"/>
       <c r="I849" s="4"/>
@@ -27049,7 +27137,7 @@
       <c r="C850" s="4"/>
       <c r="D850" s="4"/>
       <c r="E850" s="4"/>
-      <c r="F850" s="4"/>
+      <c r="F850" s="15"/>
       <c r="G850" s="4"/>
       <c r="H850" s="4"/>
       <c r="I850" s="4"/>
@@ -27080,7 +27168,7 @@
       <c r="C851" s="4"/>
       <c r="D851" s="4"/>
       <c r="E851" s="4"/>
-      <c r="F851" s="4"/>
+      <c r="F851" s="15"/>
       <c r="G851" s="4"/>
       <c r="H851" s="4"/>
       <c r="I851" s="4"/>
@@ -27111,7 +27199,7 @@
       <c r="C852" s="4"/>
       <c r="D852" s="4"/>
       <c r="E852" s="4"/>
-      <c r="F852" s="4"/>
+      <c r="F852" s="15"/>
       <c r="G852" s="4"/>
       <c r="H852" s="4"/>
       <c r="I852" s="4"/>
@@ -27142,7 +27230,7 @@
       <c r="C853" s="4"/>
       <c r="D853" s="4"/>
       <c r="E853" s="4"/>
-      <c r="F853" s="4"/>
+      <c r="F853" s="15"/>
       <c r="G853" s="4"/>
       <c r="H853" s="4"/>
       <c r="I853" s="4"/>
@@ -27173,7 +27261,7 @@
       <c r="C854" s="4"/>
       <c r="D854" s="4"/>
       <c r="E854" s="4"/>
-      <c r="F854" s="4"/>
+      <c r="F854" s="15"/>
       <c r="G854" s="4"/>
       <c r="H854" s="4"/>
       <c r="I854" s="4"/>
@@ -27204,7 +27292,7 @@
       <c r="C855" s="4"/>
       <c r="D855" s="4"/>
       <c r="E855" s="4"/>
-      <c r="F855" s="4"/>
+      <c r="F855" s="15"/>
       <c r="G855" s="4"/>
       <c r="H855" s="4"/>
       <c r="I855" s="4"/>
@@ -27235,7 +27323,7 @@
       <c r="C856" s="4"/>
       <c r="D856" s="4"/>
       <c r="E856" s="4"/>
-      <c r="F856" s="4"/>
+      <c r="F856" s="15"/>
       <c r="G856" s="4"/>
       <c r="H856" s="4"/>
       <c r="I856" s="4"/>
@@ -27266,7 +27354,7 @@
       <c r="C857" s="4"/>
       <c r="D857" s="4"/>
       <c r="E857" s="4"/>
-      <c r="F857" s="4"/>
+      <c r="F857" s="15"/>
       <c r="G857" s="4"/>
       <c r="H857" s="4"/>
       <c r="I857" s="4"/>
@@ -27297,7 +27385,7 @@
       <c r="C858" s="4"/>
       <c r="D858" s="4"/>
       <c r="E858" s="4"/>
-      <c r="F858" s="4"/>
+      <c r="F858" s="15"/>
       <c r="G858" s="4"/>
       <c r="H858" s="4"/>
       <c r="I858" s="4"/>
@@ -27328,7 +27416,7 @@
       <c r="C859" s="4"/>
       <c r="D859" s="4"/>
       <c r="E859" s="4"/>
-      <c r="F859" s="4"/>
+      <c r="F859" s="15"/>
       <c r="G859" s="4"/>
       <c r="H859" s="4"/>
       <c r="I859" s="4"/>
@@ -27359,7 +27447,7 @@
       <c r="C860" s="4"/>
       <c r="D860" s="4"/>
       <c r="E860" s="4"/>
-      <c r="F860" s="4"/>
+      <c r="F860" s="15"/>
       <c r="G860" s="4"/>
       <c r="H860" s="4"/>
       <c r="I860" s="4"/>
@@ -27390,7 +27478,7 @@
       <c r="C861" s="4"/>
       <c r="D861" s="4"/>
       <c r="E861" s="4"/>
-      <c r="F861" s="4"/>
+      <c r="F861" s="15"/>
       <c r="G861" s="4"/>
       <c r="H861" s="4"/>
       <c r="I861" s="4"/>
@@ -27421,7 +27509,7 @@
       <c r="C862" s="4"/>
       <c r="D862" s="4"/>
       <c r="E862" s="4"/>
-      <c r="F862" s="4"/>
+      <c r="F862" s="15"/>
       <c r="G862" s="4"/>
       <c r="H862" s="4"/>
       <c r="I862" s="4"/>
@@ -27452,7 +27540,7 @@
       <c r="C863" s="4"/>
       <c r="D863" s="4"/>
       <c r="E863" s="4"/>
-      <c r="F863" s="4"/>
+      <c r="F863" s="15"/>
       <c r="G863" s="4"/>
       <c r="H863" s="4"/>
       <c r="I863" s="4"/>
@@ -27483,7 +27571,7 @@
       <c r="C864" s="4"/>
       <c r="D864" s="4"/>
       <c r="E864" s="4"/>
-      <c r="F864" s="4"/>
+      <c r="F864" s="15"/>
       <c r="G864" s="4"/>
       <c r="H864" s="4"/>
       <c r="I864" s="4"/>
@@ -27514,7 +27602,7 @@
       <c r="C865" s="4"/>
       <c r="D865" s="4"/>
       <c r="E865" s="4"/>
-      <c r="F865" s="4"/>
+      <c r="F865" s="15"/>
       <c r="G865" s="4"/>
       <c r="H865" s="4"/>
       <c r="I865" s="4"/>
@@ -27545,7 +27633,7 @@
       <c r="C866" s="4"/>
       <c r="D866" s="4"/>
       <c r="E866" s="4"/>
-      <c r="F866" s="4"/>
+      <c r="F866" s="15"/>
       <c r="G866" s="4"/>
       <c r="H866" s="4"/>
       <c r="I866" s="4"/>
@@ -27576,7 +27664,7 @@
       <c r="C867" s="4"/>
       <c r="D867" s="4"/>
       <c r="E867" s="4"/>
-      <c r="F867" s="4"/>
+      <c r="F867" s="15"/>
       <c r="G867" s="4"/>
       <c r="H867" s="4"/>
       <c r="I867" s="4"/>
@@ -27607,7 +27695,7 @@
       <c r="C868" s="4"/>
       <c r="D868" s="4"/>
       <c r="E868" s="4"/>
-      <c r="F868" s="4"/>
+      <c r="F868" s="15"/>
       <c r="G868" s="4"/>
       <c r="H868" s="4"/>
       <c r="I868" s="4"/>
@@ -27638,7 +27726,7 @@
       <c r="C869" s="4"/>
       <c r="D869" s="4"/>
       <c r="E869" s="4"/>
-      <c r="F869" s="4"/>
+      <c r="F869" s="15"/>
       <c r="G869" s="4"/>
       <c r="H869" s="4"/>
       <c r="I869" s="4"/>
@@ -27669,7 +27757,7 @@
       <c r="C870" s="4"/>
       <c r="D870" s="4"/>
       <c r="E870" s="4"/>
-      <c r="F870" s="4"/>
+      <c r="F870" s="15"/>
       <c r="G870" s="4"/>
       <c r="H870" s="4"/>
       <c r="I870" s="4"/>
@@ -27700,7 +27788,7 @@
       <c r="C871" s="4"/>
       <c r="D871" s="4"/>
       <c r="E871" s="4"/>
-      <c r="F871" s="4"/>
+      <c r="F871" s="15"/>
       <c r="G871" s="4"/>
       <c r="H871" s="4"/>
       <c r="I871" s="4"/>
@@ -27731,7 +27819,7 @@
       <c r="C872" s="4"/>
       <c r="D872" s="4"/>
       <c r="E872" s="4"/>
-      <c r="F872" s="4"/>
+      <c r="F872" s="15"/>
       <c r="G872" s="4"/>
       <c r="H872" s="4"/>
       <c r="I872" s="4"/>
@@ -27762,7 +27850,7 @@
       <c r="C873" s="4"/>
       <c r="D873" s="4"/>
       <c r="E873" s="4"/>
-      <c r="F873" s="4"/>
+      <c r="F873" s="15"/>
       <c r="G873" s="4"/>
       <c r="H873" s="4"/>
       <c r="I873" s="4"/>
@@ -27793,7 +27881,7 @@
       <c r="C874" s="4"/>
       <c r="D874" s="4"/>
       <c r="E874" s="4"/>
-      <c r="F874" s="4"/>
+      <c r="F874" s="15"/>
       <c r="G874" s="4"/>
       <c r="H874" s="4"/>
       <c r="I874" s="4"/>
@@ -27824,7 +27912,7 @@
       <c r="C875" s="4"/>
       <c r="D875" s="4"/>
       <c r="E875" s="4"/>
-      <c r="F875" s="4"/>
+      <c r="F875" s="15"/>
       <c r="G875" s="4"/>
       <c r="H875" s="4"/>
       <c r="I875" s="4"/>
@@ -27855,7 +27943,7 @@
       <c r="C876" s="4"/>
       <c r="D876" s="4"/>
       <c r="E876" s="4"/>
-      <c r="F876" s="4"/>
+      <c r="F876" s="15"/>
       <c r="G876" s="4"/>
       <c r="H876" s="4"/>
       <c r="I876" s="4"/>
@@ -27886,7 +27974,7 @@
       <c r="C877" s="4"/>
       <c r="D877" s="4"/>
       <c r="E877" s="4"/>
-      <c r="F877" s="4"/>
+      <c r="F877" s="15"/>
       <c r="G877" s="4"/>
       <c r="H877" s="4"/>
       <c r="I877" s="4"/>
@@ -27917,7 +28005,7 @@
       <c r="C878" s="4"/>
       <c r="D878" s="4"/>
       <c r="E878" s="4"/>
-      <c r="F878" s="4"/>
+      <c r="F878" s="15"/>
       <c r="G878" s="4"/>
       <c r="H878" s="4"/>
       <c r="I878" s="4"/>
@@ -27948,7 +28036,7 @@
       <c r="C879" s="4"/>
       <c r="D879" s="4"/>
       <c r="E879" s="4"/>
-      <c r="F879" s="4"/>
+      <c r="F879" s="15"/>
       <c r="G879" s="4"/>
       <c r="H879" s="4"/>
       <c r="I879" s="4"/>
@@ -27979,7 +28067,7 @@
       <c r="C880" s="4"/>
       <c r="D880" s="4"/>
       <c r="E880" s="4"/>
-      <c r="F880" s="4"/>
+      <c r="F880" s="15"/>
       <c r="G880" s="4"/>
       <c r="H880" s="4"/>
       <c r="I880" s="4"/>
@@ -28010,7 +28098,7 @@
       <c r="C881" s="4"/>
       <c r="D881" s="4"/>
       <c r="E881" s="4"/>
-      <c r="F881" s="4"/>
+      <c r="F881" s="15"/>
       <c r="G881" s="4"/>
       <c r="H881" s="4"/>
       <c r="I881" s="4"/>
@@ -28041,7 +28129,7 @@
       <c r="C882" s="4"/>
       <c r="D882" s="4"/>
       <c r="E882" s="4"/>
-      <c r="F882" s="4"/>
+      <c r="F882" s="15"/>
       <c r="G882" s="4"/>
       <c r="H882" s="4"/>
       <c r="I882" s="4"/>
@@ -28072,7 +28160,7 @@
       <c r="C883" s="4"/>
       <c r="D883" s="4"/>
       <c r="E883" s="4"/>
-      <c r="F883" s="4"/>
+      <c r="F883" s="15"/>
       <c r="G883" s="4"/>
       <c r="H883" s="4"/>
       <c r="I883" s="4"/>
@@ -28103,7 +28191,7 @@
       <c r="C884" s="4"/>
       <c r="D884" s="4"/>
       <c r="E884" s="4"/>
-      <c r="F884" s="4"/>
+      <c r="F884" s="15"/>
       <c r="G884" s="4"/>
       <c r="H884" s="4"/>
       <c r="I884" s="4"/>
@@ -28134,7 +28222,7 @@
       <c r="C885" s="4"/>
       <c r="D885" s="4"/>
       <c r="E885" s="4"/>
-      <c r="F885" s="4"/>
+      <c r="F885" s="15"/>
       <c r="G885" s="4"/>
       <c r="H885" s="4"/>
       <c r="I885" s="4"/>
@@ -28165,7 +28253,7 @@
       <c r="C886" s="4"/>
       <c r="D886" s="4"/>
       <c r="E886" s="4"/>
-      <c r="F886" s="4"/>
+      <c r="F886" s="15"/>
       <c r="G886" s="4"/>
       <c r="H886" s="4"/>
       <c r="I886" s="4"/>
@@ -28196,7 +28284,7 @@
       <c r="C887" s="4"/>
       <c r="D887" s="4"/>
       <c r="E887" s="4"/>
-      <c r="F887" s="4"/>
+      <c r="F887" s="15"/>
       <c r="G887" s="4"/>
       <c r="H887" s="4"/>
       <c r="I887" s="4"/>
@@ -28227,7 +28315,7 @@
       <c r="C888" s="4"/>
       <c r="D888" s="4"/>
       <c r="E888" s="4"/>
-      <c r="F888" s="4"/>
+      <c r="F888" s="15"/>
       <c r="G888" s="4"/>
       <c r="H888" s="4"/>
       <c r="I888" s="4"/>
@@ -28258,7 +28346,7 @@
       <c r="C889" s="4"/>
       <c r="D889" s="4"/>
       <c r="E889" s="4"/>
-      <c r="F889" s="4"/>
+      <c r="F889" s="15"/>
       <c r="G889" s="4"/>
       <c r="H889" s="4"/>
       <c r="I889" s="4"/>
@@ -28289,7 +28377,7 @@
       <c r="C890" s="4"/>
       <c r="D890" s="4"/>
       <c r="E890" s="4"/>
-      <c r="F890" s="4"/>
+      <c r="F890" s="15"/>
       <c r="G890" s="4"/>
       <c r="H890" s="4"/>
       <c r="I890" s="4"/>
@@ -28320,7 +28408,7 @@
       <c r="C891" s="4"/>
       <c r="D891" s="4"/>
       <c r="E891" s="4"/>
-      <c r="F891" s="4"/>
+      <c r="F891" s="15"/>
       <c r="G891" s="4"/>
       <c r="H891" s="4"/>
       <c r="I891" s="4"/>
@@ -28351,7 +28439,7 @@
       <c r="C892" s="4"/>
       <c r="D892" s="4"/>
       <c r="E892" s="4"/>
-      <c r="F892" s="4"/>
+      <c r="F892" s="15"/>
       <c r="G892" s="4"/>
       <c r="H892" s="4"/>
       <c r="I892" s="4"/>
@@ -28382,7 +28470,7 @@
       <c r="C893" s="4"/>
       <c r="D893" s="4"/>
       <c r="E893" s="4"/>
-      <c r="F893" s="4"/>
+      <c r="F893" s="15"/>
       <c r="G893" s="4"/>
       <c r="H893" s="4"/>
       <c r="I893" s="4"/>
@@ -28413,7 +28501,7 @@
       <c r="C894" s="4"/>
       <c r="D894" s="4"/>
       <c r="E894" s="4"/>
-      <c r="F894" s="4"/>
+      <c r="F894" s="15"/>
       <c r="G894" s="4"/>
       <c r="H894" s="4"/>
       <c r="I894" s="4"/>
@@ -28444,7 +28532,7 @@
       <c r="C895" s="4"/>
       <c r="D895" s="4"/>
       <c r="E895" s="4"/>
-      <c r="F895" s="4"/>
+      <c r="F895" s="15"/>
       <c r="G895" s="4"/>
       <c r="H895" s="4"/>
       <c r="I895" s="4"/>
@@ -28475,7 +28563,7 @@
       <c r="C896" s="4"/>
       <c r="D896" s="4"/>
       <c r="E896" s="4"/>
-      <c r="F896" s="4"/>
+      <c r="F896" s="15"/>
       <c r="G896" s="4"/>
       <c r="H896" s="4"/>
       <c r="I896" s="4"/>
@@ -28506,7 +28594,7 @@
       <c r="C897" s="4"/>
       <c r="D897" s="4"/>
       <c r="E897" s="4"/>
-      <c r="F897" s="4"/>
+      <c r="F897" s="15"/>
       <c r="G897" s="4"/>
       <c r="H897" s="4"/>
       <c r="I897" s="4"/>
@@ -28537,7 +28625,7 @@
       <c r="C898" s="4"/>
       <c r="D898" s="4"/>
       <c r="E898" s="4"/>
-      <c r="F898" s="4"/>
+      <c r="F898" s="15"/>
       <c r="G898" s="4"/>
       <c r="H898" s="4"/>
       <c r="I898" s="4"/>
@@ -28568,7 +28656,7 @@
       <c r="C899" s="4"/>
       <c r="D899" s="4"/>
       <c r="E899" s="4"/>
-      <c r="F899" s="4"/>
+      <c r="F899" s="15"/>
       <c r="G899" s="4"/>
       <c r="H899" s="4"/>
       <c r="I899" s="4"/>
@@ -28599,7 +28687,7 @@
       <c r="C900" s="4"/>
       <c r="D900" s="4"/>
       <c r="E900" s="4"/>
-      <c r="F900" s="4"/>
+      <c r="F900" s="15"/>
       <c r="G900" s="4"/>
       <c r="H900" s="4"/>
       <c r="I900" s="4"/>
@@ -28630,7 +28718,7 @@
       <c r="C901" s="4"/>
       <c r="D901" s="4"/>
       <c r="E901" s="4"/>
-      <c r="F901" s="4"/>
+      <c r="F901" s="15"/>
       <c r="G901" s="4"/>
       <c r="H901" s="4"/>
       <c r="I901" s="4"/>
@@ -28661,7 +28749,7 @@
       <c r="C902" s="4"/>
       <c r="D902" s="4"/>
       <c r="E902" s="4"/>
-      <c r="F902" s="4"/>
+      <c r="F902" s="15"/>
       <c r="G902" s="4"/>
       <c r="H902" s="4"/>
       <c r="I902" s="4"/>
@@ -28692,7 +28780,7 @@
       <c r="C903" s="4"/>
       <c r="D903" s="4"/>
       <c r="E903" s="4"/>
-      <c r="F903" s="4"/>
+      <c r="F903" s="15"/>
       <c r="G903" s="4"/>
       <c r="H903" s="4"/>
       <c r="I903" s="4"/>
@@ -28723,7 +28811,7 @@
       <c r="C904" s="4"/>
       <c r="D904" s="4"/>
       <c r="E904" s="4"/>
-      <c r="F904" s="4"/>
+      <c r="F904" s="15"/>
       <c r="G904" s="4"/>
       <c r="H904" s="4"/>
       <c r="I904" s="4"/>
@@ -28754,7 +28842,7 @@
       <c r="C905" s="4"/>
       <c r="D905" s="4"/>
       <c r="E905" s="4"/>
-      <c r="F905" s="4"/>
+      <c r="F905" s="15"/>
       <c r="G905" s="4"/>
       <c r="H905" s="4"/>
       <c r="I905" s="4"/>
@@ -28785,7 +28873,7 @@
       <c r="C906" s="4"/>
       <c r="D906" s="4"/>
       <c r="E906" s="4"/>
-      <c r="F906" s="4"/>
+      <c r="F906" s="15"/>
       <c r="G906" s="4"/>
       <c r="H906" s="4"/>
       <c r="I906" s="4"/>
@@ -28816,7 +28904,7 @@
       <c r="C907" s="4"/>
       <c r="D907" s="4"/>
       <c r="E907" s="4"/>
-      <c r="F907" s="4"/>
+      <c r="F907" s="15"/>
       <c r="G907" s="4"/>
       <c r="H907" s="4"/>
       <c r="I907" s="4"/>
@@ -28847,7 +28935,7 @@
       <c r="C908" s="4"/>
       <c r="D908" s="4"/>
       <c r="E908" s="4"/>
-      <c r="F908" s="4"/>
+      <c r="F908" s="15"/>
       <c r="G908" s="4"/>
       <c r="H908" s="4"/>
       <c r="I908" s="4"/>
@@ -28878,7 +28966,7 @@
       <c r="C909" s="4"/>
       <c r="D909" s="4"/>
       <c r="E909" s="4"/>
-      <c r="F909" s="4"/>
+      <c r="F909" s="15"/>
       <c r="G909" s="4"/>
       <c r="H909" s="4"/>
       <c r="I909" s="4"/>
@@ -28909,7 +28997,7 @@
       <c r="C910" s="4"/>
       <c r="D910" s="4"/>
       <c r="E910" s="4"/>
-      <c r="F910" s="4"/>
+      <c r="F910" s="15"/>
       <c r="G910" s="4"/>
       <c r="H910" s="4"/>
       <c r="I910" s="4"/>
@@ -28940,7 +29028,7 @@
       <c r="C911" s="4"/>
       <c r="D911" s="4"/>
       <c r="E911" s="4"/>
-      <c r="F911" s="4"/>
+      <c r="F911" s="15"/>
       <c r="G911" s="4"/>
       <c r="H911" s="4"/>
       <c r="I911" s="4"/>
@@ -28971,7 +29059,7 @@
       <c r="C912" s="4"/>
       <c r="D912" s="4"/>
       <c r="E912" s="4"/>
-      <c r="F912" s="4"/>
+      <c r="F912" s="15"/>
       <c r="G912" s="4"/>
       <c r="H912" s="4"/>
       <c r="I912" s="4"/>
@@ -29002,7 +29090,7 @@
       <c r="C913" s="4"/>
       <c r="D913" s="4"/>
       <c r="E913" s="4"/>
-      <c r="F913" s="4"/>
+      <c r="F913" s="15"/>
       <c r="G913" s="4"/>
       <c r="H913" s="4"/>
       <c r="I913" s="4"/>
@@ -29033,7 +29121,7 @@
       <c r="C914" s="4"/>
       <c r="D914" s="4"/>
       <c r="E914" s="4"/>
-      <c r="F914" s="4"/>
+      <c r="F914" s="15"/>
       <c r="G914" s="4"/>
       <c r="H914" s="4"/>
       <c r="I914" s="4"/>
@@ -29064,7 +29152,7 @@
       <c r="C915" s="4"/>
       <c r="D915" s="4"/>
       <c r="E915" s="4"/>
-      <c r="F915" s="4"/>
+      <c r="F915" s="15"/>
       <c r="G915" s="4"/>
       <c r="H915" s="4"/>
       <c r="I915" s="4"/>
@@ -29095,7 +29183,7 @@
       <c r="C916" s="4"/>
       <c r="D916" s="4"/>
       <c r="E916" s="4"/>
-      <c r="F916" s="4"/>
+      <c r="F916" s="15"/>
       <c r="G916" s="4"/>
       <c r="H916" s="4"/>
       <c r="I916" s="4"/>
@@ -29126,7 +29214,7 @@
       <c r="C917" s="4"/>
       <c r="D917" s="4"/>
       <c r="E917" s="4"/>
-      <c r="F917" s="4"/>
+      <c r="F917" s="15"/>
       <c r="G917" s="4"/>
       <c r="H917" s="4"/>
       <c r="I917" s="4"/>
@@ -29157,7 +29245,7 @@
       <c r="C918" s="4"/>
       <c r="D918" s="4"/>
       <c r="E918" s="4"/>
-      <c r="F918" s="4"/>
+      <c r="F918" s="15"/>
       <c r="G918" s="4"/>
       <c r="H918" s="4"/>
       <c r="I918" s="4"/>
@@ -29188,7 +29276,7 @@
       <c r="C919" s="4"/>
       <c r="D919" s="4"/>
       <c r="E919" s="4"/>
-      <c r="F919" s="4"/>
+      <c r="F919" s="15"/>
       <c r="G919" s="4"/>
       <c r="H919" s="4"/>
       <c r="I919" s="4"/>
@@ -29219,7 +29307,7 @@
       <c r="C920" s="4"/>
       <c r="D920" s="4"/>
       <c r="E920" s="4"/>
-      <c r="F920" s="4"/>
+      <c r="F920" s="15"/>
       <c r="G920" s="4"/>
       <c r="H920" s="4"/>
       <c r="I920" s="4"/>
@@ -29250,7 +29338,7 @@
       <c r="C921" s="4"/>
       <c r="D921" s="4"/>
       <c r="E921" s="4"/>
-      <c r="F921" s="4"/>
+      <c r="F921" s="15"/>
       <c r="G921" s="4"/>
       <c r="H921" s="4"/>
       <c r="I921" s="4"/>
@@ -29281,7 +29369,7 @@
       <c r="C922" s="4"/>
       <c r="D922" s="4"/>
       <c r="E922" s="4"/>
-      <c r="F922" s="4"/>
+      <c r="F922" s="15"/>
       <c r="G922" s="4"/>
       <c r="H922" s="4"/>
       <c r="I922" s="4"/>
@@ -29312,7 +29400,7 @@
       <c r="C923" s="4"/>
       <c r="D923" s="4"/>
       <c r="E923" s="4"/>
-      <c r="F923" s="4"/>
+      <c r="F923" s="15"/>
       <c r="G923" s="4"/>
       <c r="H923" s="4"/>
       <c r="I923" s="4"/>
@@ -29343,7 +29431,7 @@
       <c r="C924" s="4"/>
       <c r="D924" s="4"/>
       <c r="E924" s="4"/>
-      <c r="F924" s="4"/>
+      <c r="F924" s="15"/>
       <c r="G924" s="4"/>
       <c r="H924" s="4"/>
       <c r="I924" s="4"/>
@@ -29374,7 +29462,7 @@
       <c r="C925" s="4"/>
       <c r="D925" s="4"/>
       <c r="E925" s="4"/>
-      <c r="F925" s="4"/>
+      <c r="F925" s="15"/>
       <c r="G925" s="4"/>
       <c r="H925" s="4"/>
       <c r="I925" s="4"/>
@@ -29405,7 +29493,7 @@
       <c r="C926" s="4"/>
       <c r="D926" s="4"/>
       <c r="E926" s="4"/>
-      <c r="F926" s="4"/>
+      <c r="F926" s="15"/>
       <c r="G926" s="4"/>
       <c r="H926" s="4"/>
       <c r="I926" s="4"/>
@@ -29436,7 +29524,7 @@
       <c r="C927" s="4"/>
       <c r="D927" s="4"/>
       <c r="E927" s="4"/>
-      <c r="F927" s="4"/>
+      <c r="F927" s="15"/>
       <c r="G927" s="4"/>
       <c r="H927" s="4"/>
       <c r="I927" s="4"/>
@@ -29467,7 +29555,7 @@
       <c r="C928" s="4"/>
       <c r="D928" s="4"/>
       <c r="E928" s="4"/>
-      <c r="F928" s="4"/>
+      <c r="F928" s="15"/>
       <c r="G928" s="4"/>
       <c r="H928" s="4"/>
       <c r="I928" s="4"/>
@@ -29498,7 +29586,7 @@
       <c r="C929" s="4"/>
       <c r="D929" s="4"/>
       <c r="E929" s="4"/>
-      <c r="F929" s="4"/>
+      <c r="F929" s="15"/>
       <c r="G929" s="4"/>
       <c r="H929" s="4"/>
       <c r="I929" s="4"/>
@@ -29529,7 +29617,7 @@
       <c r="C930" s="4"/>
       <c r="D930" s="4"/>
       <c r="E930" s="4"/>
-      <c r="F930" s="4"/>
+      <c r="F930" s="15"/>
       <c r="G930" s="4"/>
       <c r="H930" s="4"/>
       <c r="I930" s="4"/>
@@ -29560,7 +29648,7 @@
       <c r="C931" s="4"/>
       <c r="D931" s="4"/>
       <c r="E931" s="4"/>
-      <c r="F931" s="4"/>
+      <c r="F931" s="15"/>
       <c r="G931" s="4"/>
       <c r="H931" s="4"/>
       <c r="I931" s="4"/>
@@ -29591,7 +29679,7 @@
       <c r="C932" s="4"/>
       <c r="D932" s="4"/>
       <c r="E932" s="4"/>
-      <c r="F932" s="4"/>
+      <c r="F932" s="15"/>
       <c r="G932" s="4"/>
       <c r="H932" s="4"/>
       <c r="I932" s="4"/>
@@ -29622,7 +29710,7 @@
       <c r="C933" s="4"/>
       <c r="D933" s="4"/>
       <c r="E933" s="4"/>
-      <c r="F933" s="4"/>
+      <c r="F933" s="15"/>
       <c r="G933" s="4"/>
       <c r="H933" s="4"/>
       <c r="I933" s="4"/>
@@ -29653,7 +29741,7 @@
       <c r="C934" s="4"/>
       <c r="D934" s="4"/>
       <c r="E934" s="4"/>
-      <c r="F934" s="4"/>
+      <c r="F934" s="15"/>
       <c r="G934" s="4"/>
       <c r="H934" s="4"/>
       <c r="I934" s="4"/>
@@ -29684,7 +29772,7 @@
       <c r="C935" s="4"/>
       <c r="D935" s="4"/>
       <c r="E935" s="4"/>
-      <c r="F935" s="4"/>
+      <c r="F935" s="15"/>
       <c r="G935" s="4"/>
       <c r="H935" s="4"/>
       <c r="I935" s="4"/>
@@ -29715,7 +29803,7 @@
       <c r="C936" s="4"/>
       <c r="D936" s="4"/>
       <c r="E936" s="4"/>
-      <c r="F936" s="4"/>
+      <c r="F936" s="15"/>
       <c r="G936" s="4"/>
       <c r="H936" s="4"/>
       <c r="I936" s="4"/>
@@ -29746,7 +29834,7 @@
       <c r="C937" s="4"/>
       <c r="D937" s="4"/>
       <c r="E937" s="4"/>
-      <c r="F937" s="4"/>
+      <c r="F937" s="15"/>
       <c r="G937" s="4"/>
       <c r="H937" s="4"/>
       <c r="I937" s="4"/>
@@ -29777,7 +29865,7 @@
       <c r="C938" s="4"/>
       <c r="D938" s="4"/>
       <c r="E938" s="4"/>
-      <c r="F938" s="4"/>
+      <c r="F938" s="15"/>
       <c r="G938" s="4"/>
       <c r="H938" s="4"/>
       <c r="I938" s="4"/>
@@ -29808,7 +29896,7 @@
       <c r="C939" s="4"/>
       <c r="D939" s="4"/>
       <c r="E939" s="4"/>
-      <c r="F939" s="4"/>
+      <c r="F939" s="15"/>
       <c r="G939" s="4"/>
       <c r="H939" s="4"/>
       <c r="I939" s="4"/>
@@ -29839,7 +29927,7 @@
       <c r="C940" s="4"/>
       <c r="D940" s="4"/>
       <c r="E940" s="4"/>
-      <c r="F940" s="4"/>
+      <c r="F940" s="15"/>
       <c r="G940" s="4"/>
       <c r="H940" s="4"/>
       <c r="I940" s="4"/>
@@ -29870,7 +29958,7 @@
       <c r="C941" s="4"/>
       <c r="D941" s="4"/>
       <c r="E941" s="4"/>
-      <c r="F941" s="4"/>
+      <c r="F941" s="15"/>
       <c r="G941" s="4"/>
       <c r="H941" s="4"/>
       <c r="I941" s="4"/>
@@ -29901,7 +29989,7 @@
       <c r="C942" s="4"/>
       <c r="D942" s="4"/>
       <c r="E942" s="4"/>
-      <c r="F942" s="4"/>
+      <c r="F942" s="15"/>
       <c r="G942" s="4"/>
       <c r="H942" s="4"/>
       <c r="I942" s="4"/>
@@ -29932,7 +30020,7 @@
       <c r="C943" s="4"/>
       <c r="D943" s="4"/>
       <c r="E943" s="4"/>
-      <c r="F943" s="4"/>
+      <c r="F943" s="15"/>
       <c r="G943" s="4"/>
       <c r="H943" s="4"/>
       <c r="I943" s="4"/>
@@ -29963,7 +30051,7 @@
       <c r="C944" s="4"/>
       <c r="D944" s="4"/>
       <c r="E944" s="4"/>
-      <c r="F944" s="4"/>
+      <c r="F944" s="15"/>
       <c r="G944" s="4"/>
       <c r="H944" s="4"/>
       <c r="I944" s="4"/>
@@ -29994,7 +30082,7 @@
       <c r="C945" s="4"/>
       <c r="D945" s="4"/>
       <c r="E945" s="4"/>
-      <c r="F945" s="4"/>
+      <c r="F945" s="15"/>
       <c r="G945" s="4"/>
       <c r="H945" s="4"/>
       <c r="I945" s="4"/>
@@ -30025,7 +30113,7 @@
       <c r="C946" s="4"/>
       <c r="D946" s="4"/>
       <c r="E946" s="4"/>
-      <c r="F946" s="4"/>
+      <c r="F946" s="15"/>
       <c r="G946" s="4"/>
       <c r="H946" s="4"/>
       <c r="I946" s="4"/>
@@ -30056,7 +30144,7 @@
       <c r="C947" s="4"/>
       <c r="D947" s="4"/>
       <c r="E947" s="4"/>
-      <c r="F947" s="4"/>
+      <c r="F947" s="15"/>
       <c r="G947" s="4"/>
       <c r="H947" s="4"/>
       <c r="I947" s="4"/>
@@ -30087,7 +30175,7 @@
       <c r="C948" s="4"/>
       <c r="D948" s="4"/>
       <c r="E948" s="4"/>
-      <c r="F948" s="4"/>
+      <c r="F948" s="15"/>
       <c r="G948" s="4"/>
       <c r="H948" s="4"/>
       <c r="I948" s="4"/>
@@ -30118,7 +30206,7 @@
       <c r="C949" s="4"/>
       <c r="D949" s="4"/>
       <c r="E949" s="4"/>
-      <c r="F949" s="4"/>
+      <c r="F949" s="15"/>
       <c r="G949" s="4"/>
       <c r="H949" s="4"/>
       <c r="I949" s="4"/>
@@ -30149,7 +30237,7 @@
       <c r="C950" s="4"/>
       <c r="D950" s="4"/>
       <c r="E950" s="4"/>
-      <c r="F950" s="4"/>
+      <c r="F950" s="15"/>
       <c r="G950" s="4"/>
       <c r="H950" s="4"/>
       <c r="I950" s="4"/>
@@ -30180,7 +30268,7 @@
       <c r="C951" s="4"/>
       <c r="D951" s="4"/>
       <c r="E951" s="4"/>
-      <c r="F951" s="4"/>
+      <c r="F951" s="15"/>
       <c r="G951" s="4"/>
       <c r="H951" s="4"/>
       <c r="I951" s="4"/>
@@ -30211,7 +30299,7 @@
       <c r="C952" s="4"/>
       <c r="D952" s="4"/>
       <c r="E952" s="4"/>
-      <c r="F952" s="4"/>
+      <c r="F952" s="15"/>
       <c r="G952" s="4"/>
       <c r="H952" s="4"/>
       <c r="I952" s="4"/>
@@ -30242,7 +30330,7 @@
       <c r="C953" s="4"/>
       <c r="D953" s="4"/>
       <c r="E953" s="4"/>
-      <c r="F953" s="4"/>
+      <c r="F953" s="15"/>
       <c r="G953" s="4"/>
       <c r="H953" s="4"/>
       <c r="I953" s="4"/>
@@ -30273,7 +30361,7 @@
       <c r="C954" s="4"/>
       <c r="D954" s="4"/>
       <c r="E954" s="4"/>
-      <c r="F954" s="4"/>
+      <c r="F954" s="15"/>
       <c r="G954" s="4"/>
       <c r="H954" s="4"/>
       <c r="I954" s="4"/>
@@ -30304,7 +30392,7 @@
       <c r="C955" s="4"/>
       <c r="D955" s="4"/>
       <c r="E955" s="4"/>
-      <c r="F955" s="4"/>
+      <c r="F955" s="15"/>
       <c r="G955" s="4"/>
       <c r="H955" s="4"/>
       <c r="I955" s="4"/>
@@ -30335,7 +30423,7 @@
       <c r="C956" s="4"/>
       <c r="D956" s="4"/>
       <c r="E956" s="4"/>
-      <c r="F956" s="4"/>
+      <c r="F956" s="15"/>
       <c r="G956" s="4"/>
       <c r="H956" s="4"/>
       <c r="I956" s="4"/>
@@ -30366,7 +30454,7 @@
       <c r="C957" s="4"/>
       <c r="D957" s="4"/>
       <c r="E957" s="4"/>
-      <c r="F957" s="4"/>
+      <c r="F957" s="15"/>
       <c r="G957" s="4"/>
       <c r="H957" s="4"/>
       <c r="I957" s="4"/>
@@ -30397,7 +30485,7 @@
       <c r="C958" s="4"/>
       <c r="D958" s="4"/>
       <c r="E958" s="4"/>
-      <c r="F958" s="4"/>
+      <c r="F958" s="15"/>
       <c r="G958" s="4"/>
       <c r="H958" s="4"/>
       <c r="I958" s="4"/>
@@ -30428,7 +30516,7 @@
       <c r="C959" s="4"/>
       <c r="D959" s="4"/>
       <c r="E959" s="4"/>
-      <c r="F959" s="4"/>
+      <c r="F959" s="15"/>
       <c r="G959" s="4"/>
       <c r="H959" s="4"/>
       <c r="I959" s="4"/>
@@ -30459,7 +30547,7 @@
       <c r="C960" s="4"/>
       <c r="D960" s="4"/>
       <c r="E960" s="4"/>
-      <c r="F960" s="4"/>
+      <c r="F960" s="15"/>
       <c r="G960" s="4"/>
       <c r="H960" s="4"/>
       <c r="I960" s="4"/>
@@ -30490,7 +30578,7 @@
       <c r="C961" s="4"/>
       <c r="D961" s="4"/>
       <c r="E961" s="4"/>
-      <c r="F961" s="4"/>
+      <c r="F961" s="15"/>
       <c r="G961" s="4"/>
       <c r="H961" s="4"/>
       <c r="I961" s="4"/>
@@ -30521,7 +30609,7 @@
       <c r="C962" s="4"/>
       <c r="D962" s="4"/>
       <c r="E962" s="4"/>
-      <c r="F962" s="4"/>
+      <c r="F962" s="15"/>
       <c r="G962" s="4"/>
       <c r="H962" s="4"/>
       <c r="I962" s="4"/>
@@ -30552,7 +30640,7 @@
       <c r="C963" s="4"/>
       <c r="D963" s="4"/>
       <c r="E963" s="4"/>
-      <c r="F963" s="4"/>
+      <c r="F963" s="15"/>
       <c r="G963" s="4"/>
       <c r="H963" s="4"/>
       <c r="I963" s="4"/>
@@ -30583,7 +30671,7 @@
       <c r="C964" s="4"/>
       <c r="D964" s="4"/>
       <c r="E964" s="4"/>
-      <c r="F964" s="4"/>
+      <c r="F964" s="15"/>
       <c r="G964" s="4"/>
       <c r="H964" s="4"/>
       <c r="I964" s="4"/>
@@ -30614,7 +30702,7 @@
       <c r="C965" s="4"/>
       <c r="D965" s="4"/>
       <c r="E965" s="4"/>
-      <c r="F965" s="4"/>
+      <c r="F965" s="15"/>
       <c r="G965" s="4"/>
       <c r="H965" s="4"/>
       <c r="I965" s="4"/>
@@ -30645,7 +30733,7 @@
       <c r="C966" s="4"/>
       <c r="D966" s="4"/>
       <c r="E966" s="4"/>
-      <c r="F966" s="4"/>
+      <c r="F966" s="15"/>
       <c r="G966" s="4"/>
       <c r="H966" s="4"/>
       <c r="I966" s="4"/>
@@ -30676,7 +30764,7 @@
       <c r="C967" s="4"/>
       <c r="D967" s="4"/>
       <c r="E967" s="4"/>
-      <c r="F967" s="4"/>
+      <c r="F967" s="15"/>
       <c r="G967" s="4"/>
       <c r="H967" s="4"/>
       <c r="I967" s="4"/>
@@ -30707,7 +30795,7 @@
       <c r="C968" s="4"/>
       <c r="D968" s="4"/>
       <c r="E968" s="4"/>
-      <c r="F968" s="4"/>
+      <c r="F968" s="15"/>
       <c r="G968" s="4"/>
       <c r="H968" s="4"/>
       <c r="I968" s="4"/>
@@ -30738,7 +30826,7 @@
       <c r="C969" s="4"/>
       <c r="D969" s="4"/>
       <c r="E969" s="4"/>
-      <c r="F969" s="4"/>
+      <c r="F969" s="15"/>
       <c r="G969" s="4"/>
       <c r="H969" s="4"/>
       <c r="I969" s="4"/>
@@ -30769,7 +30857,7 @@
       <c r="C970" s="4"/>
       <c r="D970" s="4"/>
       <c r="E970" s="4"/>
-      <c r="F970" s="4"/>
+      <c r="F970" s="15"/>
       <c r="G970" s="4"/>
       <c r="H970" s="4"/>
       <c r="I970" s="4"/>
@@ -30800,7 +30888,7 @@
       <c r="C971" s="4"/>
       <c r="D971" s="4"/>
       <c r="E971" s="4"/>
-      <c r="F971" s="4"/>
+      <c r="F971" s="15"/>
       <c r="G971" s="4"/>
       <c r="H971" s="4"/>
       <c r="I971" s="4"/>
@@ -30831,7 +30919,7 @@
       <c r="C972" s="4"/>
       <c r="D972" s="4"/>
       <c r="E972" s="4"/>
-      <c r="F972" s="4"/>
+      <c r="F972" s="15"/>
       <c r="G972" s="4"/>
       <c r="H972" s="4"/>
       <c r="I972" s="4"/>
@@ -30862,7 +30950,7 @@
       <c r="C973" s="4"/>
       <c r="D973" s="4"/>
       <c r="E973" s="4"/>
-      <c r="F973" s="4"/>
+      <c r="F973" s="15"/>
       <c r="G973" s="4"/>
       <c r="H973" s="4"/>
       <c r="I973" s="4"/>
@@ -30893,7 +30981,7 @@
       <c r="C974" s="4"/>
       <c r="D974" s="4"/>
       <c r="E974" s="4"/>
-      <c r="F974" s="4"/>
+      <c r="F974" s="15"/>
       <c r="G974" s="4"/>
       <c r="H974" s="4"/>
       <c r="I974" s="4"/>
@@ -30924,7 +31012,7 @@
       <c r="C975" s="4"/>
       <c r="D975" s="4"/>
       <c r="E975" s="4"/>
-      <c r="F975" s="4"/>
+      <c r="F975" s="15"/>
       <c r="G975" s="4"/>
       <c r="H975" s="4"/>
       <c r="I975" s="4"/>
@@ -30955,7 +31043,7 @@
       <c r="C976" s="4"/>
       <c r="D976" s="4"/>
       <c r="E976" s="4"/>
-      <c r="F976" s="4"/>
+      <c r="F976" s="15"/>
       <c r="G976" s="4"/>
       <c r="H976" s="4"/>
       <c r="I976" s="4"/>
@@ -30986,7 +31074,7 @@
       <c r="C977" s="4"/>
       <c r="D977" s="4"/>
       <c r="E977" s="4"/>
-      <c r="F977" s="4"/>
+      <c r="F977" s="15"/>
       <c r="G977" s="4"/>
       <c r="H977" s="4"/>
       <c r="I977" s="4"/>
@@ -31017,7 +31105,7 @@
       <c r="C978" s="4"/>
       <c r="D978" s="4"/>
       <c r="E978" s="4"/>
-      <c r="F978" s="4"/>
+      <c r="F978" s="15"/>
       <c r="G978" s="4"/>
       <c r="H978" s="4"/>
       <c r="I978" s="4"/>
@@ -31048,7 +31136,7 @@
       <c r="C979" s="4"/>
       <c r="D979" s="4"/>
       <c r="E979" s="4"/>
-      <c r="F979" s="4"/>
+      <c r="F979" s="15"/>
       <c r="G979" s="4"/>
       <c r="H979" s="4"/>
       <c r="I979" s="4"/>
@@ -31079,7 +31167,7 @@
       <c r="C980" s="4"/>
       <c r="D980" s="4"/>
       <c r="E980" s="4"/>
-      <c r="F980" s="4"/>
+      <c r="F980" s="15"/>
       <c r="G980" s="4"/>
       <c r="H980" s="4"/>
       <c r="I980" s="4"/>
@@ -31110,7 +31198,7 @@
       <c r="C981" s="4"/>
       <c r="D981" s="4"/>
       <c r="E981" s="4"/>
-      <c r="F981" s="4"/>
+      <c r="F981" s="15"/>
       <c r="G981" s="4"/>
       <c r="H981" s="4"/>
       <c r="I981" s="4"/>
@@ -31141,7 +31229,7 @@
       <c r="C982" s="4"/>
       <c r="D982" s="4"/>
       <c r="E982" s="4"/>
-      <c r="F982" s="4"/>
+      <c r="F982" s="15"/>
       <c r="G982" s="4"/>
       <c r="H982" s="4"/>
       <c r="I982" s="4"/>
@@ -31172,7 +31260,7 @@
       <c r="C983" s="4"/>
       <c r="D983" s="4"/>
       <c r="E983" s="4"/>
-      <c r="F983" s="4"/>
+      <c r="F983" s="15"/>
       <c r="G983" s="4"/>
       <c r="H983" s="4"/>
       <c r="I983" s="4"/>
@@ -31203,7 +31291,7 @@
       <c r="C984" s="4"/>
       <c r="D984" s="4"/>
       <c r="E984" s="4"/>
-      <c r="F984" s="4"/>
+      <c r="F984" s="15"/>
       <c r="G984" s="4"/>
       <c r="H984" s="4"/>
       <c r="I984" s="4"/>
@@ -31234,7 +31322,7 @@
       <c r="C985" s="4"/>
       <c r="D985" s="4"/>
       <c r="E985" s="4"/>
-      <c r="F985" s="4"/>
+      <c r="F985" s="15"/>
       <c r="G985" s="4"/>
       <c r="H985" s="4"/>
       <c r="I985" s="4"/>
@@ -31265,7 +31353,7 @@
       <c r="C986" s="4"/>
       <c r="D986" s="4"/>
       <c r="E986" s="4"/>
-      <c r="F986" s="4"/>
+      <c r="F986" s="15"/>
       <c r="G986" s="4"/>
       <c r="H986" s="4"/>
       <c r="I986" s="4"/>
@@ -31296,7 +31384,7 @@
       <c r="C987" s="4"/>
       <c r="D987" s="4"/>
       <c r="E987" s="4"/>
-      <c r="F987" s="4"/>
+      <c r="F987" s="15"/>
       <c r="G987" s="4"/>
       <c r="H987" s="4"/>
       <c r="I987" s="4"/>
@@ -31327,7 +31415,7 @@
       <c r="C988" s="4"/>
       <c r="D988" s="4"/>
       <c r="E988" s="4"/>
-      <c r="F988" s="4"/>
+      <c r="F988" s="15"/>
       <c r="G988" s="4"/>
       <c r="H988" s="4"/>
       <c r="I988" s="4"/>
@@ -31358,7 +31446,7 @@
       <c r="C989" s="4"/>
       <c r="D989" s="4"/>
       <c r="E989" s="4"/>
-      <c r="F989" s="4"/>
+      <c r="F989" s="15"/>
       <c r="G989" s="4"/>
       <c r="H989" s="4"/>
       <c r="I989" s="4"/>
@@ -31389,7 +31477,7 @@
       <c r="C990" s="4"/>
       <c r="D990" s="4"/>
       <c r="E990" s="4"/>
-      <c r="F990" s="4"/>
+      <c r="F990" s="15"/>
       <c r="G990" s="4"/>
       <c r="H990" s="4"/>
       <c r="I990" s="4"/>
@@ -31420,7 +31508,7 @@
       <c r="C991" s="4"/>
       <c r="D991" s="4"/>
       <c r="E991" s="4"/>
-      <c r="F991" s="4"/>
+      <c r="F991" s="15"/>
       <c r="G991" s="4"/>
       <c r="H991" s="4"/>
       <c r="I991" s="4"/>
@@ -31451,7 +31539,7 @@
       <c r="C992" s="4"/>
       <c r="D992" s="4"/>
       <c r="E992" s="4"/>
-      <c r="F992" s="4"/>
+      <c r="F992" s="15"/>
       <c r="G992" s="4"/>
       <c r="H992" s="4"/>
       <c r="I992" s="4"/>
@@ -31482,7 +31570,7 @@
       <c r="C993" s="4"/>
       <c r="D993" s="4"/>
       <c r="E993" s="4"/>
-      <c r="F993" s="4"/>
+      <c r="F993" s="15"/>
       <c r="G993" s="4"/>
       <c r="H993" s="4"/>
       <c r="I993" s="4"/>
@@ -31513,7 +31601,7 @@
       <c r="C994" s="4"/>
       <c r="D994" s="4"/>
       <c r="E994" s="4"/>
-      <c r="F994" s="4"/>
+      <c r="F994" s="15"/>
       <c r="G994" s="4"/>
       <c r="H994" s="4"/>
       <c r="I994" s="4"/>
@@ -31544,7 +31632,7 @@
       <c r="C995" s="4"/>
       <c r="D995" s="4"/>
       <c r="E995" s="4"/>
-      <c r="F995" s="4"/>
+      <c r="F995" s="15"/>
       <c r="G995" s="4"/>
       <c r="H995" s="4"/>
       <c r="I995" s="4"/>
@@ -31575,7 +31663,7 @@
       <c r="C996" s="4"/>
       <c r="D996" s="4"/>
       <c r="E996" s="4"/>
-      <c r="F996" s="4"/>
+      <c r="F996" s="15"/>
       <c r="G996" s="4"/>
       <c r="H996" s="4"/>
       <c r="I996" s="4"/>
@@ -31606,7 +31694,7 @@
       <c r="C997" s="4"/>
       <c r="D997" s="4"/>
       <c r="E997" s="4"/>
-      <c r="F997" s="4"/>
+      <c r="F997" s="15"/>
       <c r="G997" s="4"/>
       <c r="H997" s="4"/>
       <c r="I997" s="4"/>
@@ -31637,7 +31725,7 @@
       <c r="C998" s="4"/>
       <c r="D998" s="4"/>
       <c r="E998" s="4"/>
-      <c r="F998" s="4"/>
+      <c r="F998" s="15"/>
       <c r="G998" s="4"/>
       <c r="H998" s="4"/>
       <c r="I998" s="4"/>
@@ -31668,7 +31756,7 @@
       <c r="C999" s="4"/>
       <c r="D999" s="4"/>
       <c r="E999" s="4"/>
-      <c r="F999" s="4"/>
+      <c r="F999" s="15"/>
       <c r="G999" s="4"/>
       <c r="H999" s="4"/>
       <c r="I999" s="4"/>
@@ -31699,7 +31787,7 @@
       <c r="C1000" s="4"/>
       <c r="D1000" s="4"/>
       <c r="E1000" s="4"/>
-      <c r="F1000" s="4"/>
+      <c r="F1000" s="15"/>
       <c r="G1000" s="4"/>
       <c r="H1000" s="4"/>
       <c r="I1000" s="4"/>
@@ -31730,7 +31818,7 @@
       <c r="C1001" s="4"/>
       <c r="D1001" s="4"/>
       <c r="E1001" s="4"/>
-      <c r="F1001" s="4"/>
+      <c r="F1001" s="15"/>
       <c r="G1001" s="4"/>
       <c r="H1001" s="4"/>
       <c r="I1001" s="4"/>
@@ -31761,7 +31849,7 @@
       <c r="C1002" s="4"/>
       <c r="D1002" s="4"/>
       <c r="E1002" s="4"/>
-      <c r="F1002" s="4"/>
+      <c r="F1002" s="15"/>
       <c r="G1002" s="4"/>
       <c r="H1002" s="4"/>
       <c r="I1002" s="4"/>
@@ -31792,7 +31880,7 @@
       <c r="C1003" s="4"/>
       <c r="D1003" s="4"/>
       <c r="E1003" s="4"/>
-      <c r="F1003" s="4"/>
+      <c r="F1003" s="15"/>
       <c r="G1003" s="4"/>
       <c r="H1003" s="4"/>
       <c r="I1003" s="4"/>
@@ -31823,7 +31911,7 @@
       <c r="C1004" s="4"/>
       <c r="D1004" s="4"/>
       <c r="E1004" s="4"/>
-      <c r="F1004" s="4"/>
+      <c r="F1004" s="15"/>
       <c r="G1004" s="4"/>
       <c r="H1004" s="4"/>
       <c r="I1004" s="4"/>
@@ -31854,7 +31942,7 @@
       <c r="C1005" s="4"/>
       <c r="D1005" s="4"/>
       <c r="E1005" s="4"/>
-      <c r="F1005" s="4"/>
+      <c r="F1005" s="15"/>
       <c r="G1005" s="4"/>
       <c r="H1005" s="4"/>
       <c r="I1005" s="4"/>
@@ -31885,7 +31973,7 @@
       <c r="C1006" s="4"/>
       <c r="D1006" s="4"/>
       <c r="E1006" s="4"/>
-      <c r="F1006" s="4"/>
+      <c r="F1006" s="15"/>
       <c r="G1006" s="4"/>
       <c r="H1006" s="4"/>
       <c r="I1006" s="4"/>
@@ -31916,7 +32004,7 @@
       <c r="C1007" s="4"/>
       <c r="D1007" s="4"/>
       <c r="E1007" s="4"/>
-      <c r="F1007" s="4"/>
+      <c r="F1007" s="15"/>
       <c r="G1007" s="4"/>
       <c r="H1007" s="4"/>
       <c r="I1007" s="4"/>
@@ -31947,7 +32035,7 @@
       <c r="C1008" s="4"/>
       <c r="D1008" s="4"/>
       <c r="E1008" s="4"/>
-      <c r="F1008" s="4"/>
+      <c r="F1008" s="15"/>
       <c r="G1008" s="4"/>
       <c r="H1008" s="4"/>
       <c r="I1008" s="4"/>
@@ -31978,7 +32066,7 @@
       <c r="C1009" s="4"/>
       <c r="D1009" s="4"/>
       <c r="E1009" s="4"/>
-      <c r="F1009" s="4"/>
+      <c r="F1009" s="15"/>
       <c r="G1009" s="4"/>
       <c r="H1009" s="4"/>
       <c r="I1009" s="4"/>
@@ -32009,7 +32097,7 @@
       <c r="C1010" s="4"/>
       <c r="D1010" s="4"/>
       <c r="E1010" s="4"/>
-      <c r="F1010" s="4"/>
+      <c r="F1010" s="15"/>
       <c r="G1010" s="4"/>
       <c r="H1010" s="4"/>
       <c r="I1010" s="4"/>

--- a/Data/CombatInputPanel.xlsx
+++ b/Data/CombatInputPanel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\CombatCalculatorTest\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52DC344D-2BE9-4094-9DE8-2C5AB2C79D28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58E7B0D4-52FC-44A5-BCE8-A09D3DBFBC04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1205,7 +1205,7 @@
         <v>1</v>
       </c>
       <c r="E14" s="5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F14" s="14" t="b">
         <v>1</v>

--- a/Data/CombatInputPanel.xlsx
+++ b/Data/CombatInputPanel.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="7" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\CombatCalculatorTest\Data\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58E7B0D4-52FC-44A5-BCE8-A09D3DBFBC04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520"/>
   </bookViews>
   <sheets>
     <sheet name="CombatInputPanel" sheetId="1" r:id="rId1"/>
@@ -25,12 +19,12 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author/>
   </authors>
   <commentList>
-    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+    <comment ref="E1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -45,7 +39,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
+    <comment ref="F1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -106,7 +100,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
+    <comment ref="G1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -121,7 +115,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
+    <comment ref="H1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -137,7 +131,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
+    <comment ref="I1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -152,7 +146,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000006000000}">
+    <comment ref="L1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -266,7 +260,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
@@ -619,7 +613,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -718,7 +712,7 @@
         <v>17</v>
       </c>
       <c r="D2" s="5">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="E2" s="5">
         <v>4</v>
@@ -1147,7 +1141,7 @@
         <v>27</v>
       </c>
       <c r="D13" s="5">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="E13" s="5">
         <v>2</v>
@@ -1202,7 +1196,7 @@
         <v>17</v>
       </c>
       <c r="D14" s="5">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="E14" s="5">
         <v>3</v>
